--- a/docs/TAPP_EPMA_filled.xlsx
+++ b/docs/TAPP_EPMA_filled.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/944a82e2ddcde9eb/Documents/GithubC/USGIN/geochemBuildingBlocks/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="278" documentId="11_3C209AD99577444EEF615C96566D1EBF266D99FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{587812C6-6FFF-49C7-9FA9-EF533DB21C2F}"/>
+  <xr:revisionPtr revIDLastSave="279" documentId="11_3C209AD99577444EEF615C96566D1EBF266D99FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88AEFEA8-2993-49E2-8699-4CC11906C290}"/>
   <bookViews>
-    <workbookView xWindow="555" yWindow="690" windowWidth="27930" windowHeight="14610" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1065" windowWidth="27930" windowHeight="14610" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TAPP" sheetId="1" r:id="rId1"/>
@@ -2109,7 +2109,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="182">
+  <cellXfs count="181">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2619,9 +2619,6 @@
     <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2706,6 +2703,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2894,9 +2895,9 @@
     <col min="5" max="5" width="32" style="32" customWidth="1"/>
     <col min="6" max="6" width="7.85546875" style="4" customWidth="1"/>
     <col min="7" max="7" width="17.140625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="38" style="167" customWidth="1"/>
-    <col min="9" max="12" width="38" style="58" customWidth="1"/>
-    <col min="13" max="17" width="30" style="58" customWidth="1"/>
+    <col min="8" max="8" width="38" style="167" hidden="1" customWidth="1"/>
+    <col min="9" max="12" width="38" style="58" hidden="1" customWidth="1"/>
+    <col min="13" max="17" width="30" style="58" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="8.42578125" style="168" customWidth="1"/>
     <col min="19" max="19" width="37.140625" style="4" customWidth="1"/>
     <col min="20" max="20" width="49.140625" style="4" customWidth="1"/>
@@ -5234,7 +5235,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S51" s="181" t="s">
+      <c r="S51" s="3" t="s">
         <v>213</v>
       </c>
       <c r="T51" s="3" t="s">
@@ -5278,7 +5279,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S52" s="181" t="s">
+      <c r="S52" s="3" t="s">
         <v>213</v>
       </c>
       <c r="T52" s="3" t="s">
@@ -5322,7 +5323,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S53" s="181" t="s">
+      <c r="S53" s="3" t="s">
         <v>213</v>
       </c>
       <c r="T53" s="3" t="s">
@@ -5412,7 +5413,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S55" s="181" t="s">
+      <c r="S55" s="3" t="s">
         <v>213</v>
       </c>
       <c r="T55" s="3" t="s">
@@ -5456,7 +5457,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S56" s="181" t="s">
+      <c r="S56" s="3" t="s">
         <v>213</v>
       </c>
       <c r="T56" s="3" t="s">
@@ -5566,7 +5567,7 @@
         <f t="shared" ref="R59:R68" si="4">COUNTA(H59:Q59)/10</f>
         <v>0.9</v>
       </c>
-      <c r="S59" s="181" t="s">
+      <c r="S59" s="3" t="s">
         <v>213</v>
       </c>
       <c r="T59" s="3" t="s">
@@ -5616,7 +5617,7 @@
         <f t="shared" si="4"/>
         <v>0.3</v>
       </c>
-      <c r="S60" s="181" t="s">
+      <c r="S60" s="3" t="s">
         <v>213</v>
       </c>
       <c r="T60" s="3" t="s">
@@ -5660,7 +5661,7 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S61" s="181" t="s">
+      <c r="S61" s="3" t="s">
         <v>213</v>
       </c>
       <c r="T61" s="3" t="s">
@@ -5748,7 +5749,7 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S63" s="181" t="s">
+      <c r="S63" s="3" t="s">
         <v>213</v>
       </c>
       <c r="T63" s="3" t="s">
@@ -5802,7 +5803,7 @@
         <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
-      <c r="S64" s="181" t="s">
+      <c r="S64" s="3" t="s">
         <v>213</v>
       </c>
       <c r="T64" s="3" t="s">
@@ -5846,7 +5847,7 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S65" s="181" t="s">
+      <c r="S65" s="3" t="s">
         <v>213</v>
       </c>
       <c r="T65" s="3"/>
@@ -5888,7 +5889,7 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S66" s="181" t="s">
+      <c r="S66" s="3" t="s">
         <v>213</v>
       </c>
       <c r="T66" s="3" t="s">
@@ -5932,7 +5933,7 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S67" s="181" t="s">
+      <c r="S67" s="3" t="s">
         <v>213</v>
       </c>
       <c r="T67" s="9" t="s">
@@ -5976,7 +5977,7 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S68" s="181" t="s">
+      <c r="S68" s="3" t="s">
         <v>213</v>
       </c>
       <c r="T68" s="9" t="s">

--- a/docs/TAPP_EPMA_filled.xlsx
+++ b/docs/TAPP_EPMA_filled.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/944a82e2ddcde9eb/Documents/GithubC/USGIN/geochemBuildingBlocks/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="279" documentId="11_3C209AD99577444EEF615C96566D1EBF266D99FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88AEFEA8-2993-49E2-8699-4CC11906C290}"/>
+  <xr:revisionPtr revIDLastSave="299" documentId="11_3C209AD99577444EEF615C96566D1EBF266D99FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1E778BF-00DE-4010-B5A4-4CECD611067F}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1065" windowWidth="27930" windowHeight="14610" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8520" yWindow="990" windowWidth="27930" windowHeight="14610" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TAPP" sheetId="1" r:id="rId1"/>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="463">
   <si>
     <t>Metadata Item</t>
   </si>
@@ -340,9 +340,6 @@
     <t>Silicate minerals (tissintite, maskelynite, pigeonite, fayalite)</t>
   </si>
   <si>
-    <t>Maskelynite, melt inclusion glasses, silica glass, coesite aggregates, mesostasis</t>
-  </si>
-  <si>
     <t>Olivine, pyroxene, Fe-Ti-Cr oxides, maskelynite, phosphate, sulfide, glass</t>
   </si>
   <si>
@@ -706,28 +703,16 @@
     <t>e.g., 10 | 50 | 100</t>
   </si>
   <si>
-    <t>Element specific</t>
-  </si>
-  <si>
     <t>5</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>20 nA (silicates/oxides); 10 nA (glass/maskelynite/phosphate)</t>
-  </si>
-  <si>
     <t>25 nA</t>
   </si>
   <si>
     <t>20 nA</t>
-  </si>
-  <si>
-    <t>20 nA (X-ray maps/BSE); 20 nA silicates/sulfides/oxides; 8 nA phosphates; 4 nA carbonates</t>
-  </si>
-  <si>
-    <t>10 nA (carbonate/Mg,Na phosphate); 10 nA (oxides/olivine, 1 µm)</t>
   </si>
   <si>
     <t>EPMA Technique per Element</t>
@@ -1207,15 +1192,6 @@
   </si>
   <si>
     <t>parameter: DriftCorrection</t>
-  </si>
-  <si>
-    <t>Items marked 'Element Specific' in column F of this table become entries in the ada:analyteColumns Array.  a row in the analyte column array with name=BeamCurrentDefault</t>
-  </si>
-  <si>
-    <t>have to construct analyte template for properties associated with each analyte, defined in the analyteColumns Array, which is an array of schema:PropertyValueSpecification objects.The schema:valueName in the schema:PropertyValueSpecification becomes the (no namespace) keys in the elements in the default analytes array.  The base template only defines one analyteColumn: : ("schema:name": "Analysed Oxide-Element",
-        "schema:valueName": "element | oxide | isotope | isotopeRatio...etc",), and the default analytes array is simply an array like e.g. ("ada:defaultAnalytes": [
-      { "element": "Si"}, { "element": "Fe"},{ "element": "Mn"},... ]
-other columnss defined in the analyteColumn array are selected from the following 'Element specific' properties.</t>
   </si>
   <si>
     <t>analyteColumn : spectrometerNumber 
@@ -1414,14 +1390,6 @@
     <t>Match. analyte-level parameter with ada:enumeration of background correction methods (linear, exponential, mean of two points, etc.).</t>
   </si>
   <si>
-    <t>property:analyteTemplate
-  readOnly:true
-Dataset level parameter: reportedAnalyte
-  dataType: need 'analyte'  that is array of propertyValue? Or investigate DDI-CDI data point…These must be consistent with the method-level analyteTEmplate; they provide specific analyte-level reporting analtyteTemplate. In current model these would be the variableMeasured/Instance variables in the dataset metadata. The metod-level element-specific properties become additional properties on the measureVariable/PropertyValue.  
-For the element-specific properties, if a property is read only, it only need be specified in the tapp definition, not in the instance data, under the assumption that it always holds if this tapp is followed.
-User can add or delete an element when filling out the webform. Also, user should be allowed to copy and paste the filled content for different elements</t>
-  </si>
-  <si>
     <t>implementation notes</t>
   </si>
   <si>
@@ -1527,21 +1495,63 @@
   readOnly:True</t>
   </si>
   <si>
-    <t>property: : acceleratingVoltageDefault
+    <t>match. Same container as row 20 with ada:toolRole='reduction' for matrix-correction/data-reduction software.</t>
+  </si>
+  <si>
+    <t>MethodParameter (ada:fieldScope='method') , ada:dataType='number', schema:unitText='kV'</t>
+  </si>
+  <si>
+    <t>MethodParameter (ada:fieldScope='method') , ada:dataType='number', schema:unitText='um'.</t>
+  </si>
+  <si>
+    <t>parameter: BeamRasterDimenstion. 
+  dataType: schema:PropertyValue
+  readOnly: False</t>
+  </si>
+  <si>
+    <t>parameter:  BeamDamageMinimization. 
+  dataType:  text
+  readOnly: True</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> property: matrixCorrectionMethod
+  datatype: enum {PAP (Pouchou &amp; Pichoir Full) | XPP (Simplified PAP) | PhiRhoZ Bastin (EPQ-91) | Love-Scott I | Love-Scott II | Armstrong/Love-Scott | Heinrich/Duncumb-Reed | Conventional Philibert/Duncumb-Reed | Other | Unknown}
+   readOnly: true</t>
+  </si>
+  <si>
+    <t>$.ada:matrixCorrectionMethod</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.ada:beamMode</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.ada:acceleratingVoltageDefault</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.ada:beamDiameterDefault</t>
+  </si>
+  <si>
+    <t>Method property (ada:fieldScope='method') with ada:enumeration of allowed values (focused|defocused|rastered) and ada:dataType='string'.</t>
+  </si>
+  <si>
+    <t>have to construct analyte template for properties associated with each analyte, defined in the analyteColumns Array, which is an array of schema:PropertyValueSpecification objects.The schema:valueName in the schema:PropertyValueSpecification becomes the (no namespace) keys in the elements in the default analytes array.  The base template only defines one analyteColumn: : ("schema:name": "Analysed Oxide-Element",
+        "schema:analyte",), and the default analytes array is simply an array like e.g. ("ada:defaultAnalytes": [
+      { "analyte": "Si"}, { "analyte": "Fe"},{ "analyte": "Mn"},... ]
+other columns defined in the analyteColumn array are selected from the following 'Analyte specific' properties.</t>
+  </si>
+  <si>
+    <t>Analyte specific</t>
+  </si>
+  <si>
+    <t>Items marked 'Analyte Specific' in column F of this table become entries in the ada:analyteColumns Array.  a row in the analyte column array with name=BeamCurrentDefault</t>
+  </si>
+  <si>
+    <t>property:  acceleratingVoltageDefault
   datatype: schema:PropertyValue
-  readonly True 
+  readonly: True 
 parameter: acceleratingVoltage
   dataType: schema:PropertyValue
-  parameter: readOnly: False</t>
-  </si>
-  <si>
-    <t>match. Same container as row 20 with ada:toolRole='reduction' for matrix-correction/data-reduction software.</t>
-  </si>
-  <si>
-    <t>MethodParameter (ada:fieldScope='method') , ada:dataType='number', schema:unitText='kV'</t>
-  </si>
-  <si>
-    <t>MethodParameter (ada:fieldScope='method') , ada:dataType='number', schema:unitText='um'.</t>
+  readOnly: False</t>
   </si>
   <si>
     <t>property: beamDiameterDefault
@@ -1549,37 +1559,56 @@
   dataType: schema:PropertyValue
 parameter: beamDiameter
   dataType: schema:PropertyValue
-  dataType: readOnly: False</t>
-  </si>
-  <si>
-    <t>parameter: BeamRasterDimenstion. 
-  dataType: schema:PropertyValue
   readOnly: False</t>
   </si>
   <si>
-    <t>parameter:  BeamDamageMinimization. 
-  dataType:  text
-  readOnly: True</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> property: matrixCorrectionMethod
-  datatype: enum {PAP (Pouchou &amp; Pichoir Full) | XPP (Simplified PAP) | PhiRhoZ Bastin (EPQ-91) | Love-Scott I | Love-Scott II | Armstrong/Love-Scott | Heinrich/Duncumb-Reed | Conventional Philibert/Duncumb-Reed | Other | Unknown}
-   readOnly: true</t>
-  </si>
-  <si>
-    <t>$.ada:matrixCorrectionMethod</t>
-  </si>
-  <si>
-    <t>$MethodDefinition.ada:beamMode</t>
-  </si>
-  <si>
-    <t>$MethodDefinition.ada:acceleratingVoltageDefault</t>
-  </si>
-  <si>
-    <t>$MethodDefinition.ada:beamDiameterDefault</t>
-  </si>
-  <si>
-    <t>Method property (ada:fieldScope='method') with ada:enumeration of allowed values (focused|defocused|rastered) and ada:dataType='string'.</t>
+    <t>property:analyteTemplate
+  readOnly: true
+Dataset level parameter: reportedAnalyte
+  dataType: need 'analyte'  that is array of propertyValue? Or investigate DDI-CDI data point…These must be consistent with the method-level analyteTEmplate; they provide specific analyte-level reporting analtyteTemplate. In current model these would be the variableMeasured/Instance variables in the dataset metadata. The metod-level element-specific properties become additional properties on the measureVariable/PropertyValue.  
+For the element-specific properties, if a property is read only, it only need be specified in the tapp definition, not in the instance data, under the assumption that it always holds if this tapp is followed.
+User can add or delete an element when filling out the webform. Also, user should be allowed to copy and paste the filled content for different elements</t>
+  </si>
+  <si>
+    <t>Asbestos microcline (Si Kα, Al Kα, K Kα);
+ Synthetic anorthite (Ca Kα); 
+Amelia albite (Na Kα); 
+Synthetic fayalite (Fe Kα); 
+Synthetic forsterite (Mg Kα); 
+Synthetic TiO2 (Ti Kα); 
+Synthetic Cr2O3 (Cr Kα); 
+Synthetic Mn-olivine (Mn Kα)</t>
+  </si>
+  <si>
+    <t>Anorthite (Si Kα, Al Kα, Ca Kα); 
+Albite (Na Kα); 
+Fayalite (Fe Kα); 
+Forsterite (Mg Kα); 
+Mn2SiO4 (Mn Kα); 
+TiO2 (Ti Kα); 
+Cr2O3 (Cr Kα); 
+Microcline (K Kα)</t>
+  </si>
+  <si>
+    <t>20 nA (X-ray maps/BSE); 
+20 nA silicates/sulfides/oxides;
+8 nA phosphates; 
+4 nA carbonates</t>
+  </si>
+  <si>
+    <t>20 nA (silicates/oxides); 
+10 nA (glass/maskelynite/phosphate)</t>
+  </si>
+  <si>
+    <t>10 nA (carbonate/Mg,Na phosphate); 
+10 nA (oxides/olivine, 1 µm)</t>
+  </si>
+  <si>
+    <t>Maskelynite, 
+melt inclusion glasses, 
+silica glass, 
+coesite aggregates, 
+mesostasis</t>
   </si>
 </sst>
 </file>
@@ -2892,16 +2921,19 @@
     <col min="2" max="2" width="33" style="58" customWidth="1"/>
     <col min="3" max="3" width="14.7109375" style="58" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.85546875" style="58" customWidth="1"/>
-    <col min="5" max="5" width="32" style="32" customWidth="1"/>
+    <col min="5" max="5" width="26.140625" style="32" customWidth="1"/>
     <col min="6" max="6" width="7.85546875" style="4" customWidth="1"/>
-    <col min="7" max="7" width="17.140625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="38" style="167" hidden="1" customWidth="1"/>
-    <col min="9" max="12" width="38" style="58" hidden="1" customWidth="1"/>
-    <col min="13" max="17" width="30" style="58" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="8.42578125" style="168" customWidth="1"/>
+    <col min="7" max="7" width="28.28515625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="28.28515625" style="167" customWidth="1"/>
+    <col min="9" max="9" width="28.28515625" style="58" customWidth="1"/>
+    <col min="10" max="10" width="36.85546875" style="58" customWidth="1"/>
+    <col min="11" max="14" width="28.28515625" style="58" customWidth="1"/>
+    <col min="15" max="15" width="33.42578125" style="58" customWidth="1"/>
+    <col min="16" max="17" width="28.28515625" style="58" customWidth="1"/>
+    <col min="18" max="18" width="28.28515625" style="168" customWidth="1"/>
     <col min="19" max="19" width="37.140625" style="4" customWidth="1"/>
     <col min="20" max="20" width="49.140625" style="4" customWidth="1"/>
-    <col min="21" max="21" width="49.5703125" style="4" customWidth="1"/>
+    <col min="21" max="21" width="56.5703125" style="4" customWidth="1"/>
     <col min="22" max="16384" width="12.7109375" style="4"/>
   </cols>
   <sheetData>
@@ -2922,7 +2954,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="G1" s="2"/>
       <c r="H1" s="112" t="s">
@@ -2965,7 +2997,7 @@
         <v>17</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.2">
@@ -3046,10 +3078,10 @@
         <v>1</v>
       </c>
       <c r="S3" s="63" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="T3" s="169" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="U3" s="63"/>
     </row>
@@ -3106,13 +3138,13 @@
         <v>1</v>
       </c>
       <c r="S4" s="69" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="T4" s="170" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="U4" s="69" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
     </row>
     <row r="5" spans="1:21" s="70" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
@@ -3168,10 +3200,10 @@
         <v>1</v>
       </c>
       <c r="S5" s="69" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="T5" s="170" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="U5" s="69"/>
     </row>
@@ -3228,10 +3260,10 @@
         <v>1</v>
       </c>
       <c r="S6" s="69" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="T6" s="170" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="U6" s="69"/>
     </row>
@@ -3268,10 +3300,10 @@
         <v>0</v>
       </c>
       <c r="S7" s="69" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="T7" s="170" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="U7" s="69"/>
     </row>
@@ -3308,10 +3340,10 @@
         <v>0</v>
       </c>
       <c r="S8" s="69" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="T8" s="170" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="U8" s="69"/>
     </row>
@@ -3348,13 +3380,13 @@
         <v>0</v>
       </c>
       <c r="S9" s="69" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="T9" s="170" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="U9" s="69" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
     </row>
     <row r="10" spans="1:21" s="70" customFormat="1" ht="42.75" x14ac:dyDescent="0.2">
@@ -3390,10 +3422,10 @@
         <v>0</v>
       </c>
       <c r="S10" s="69" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="T10" s="170" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="U10" s="69"/>
     </row>
@@ -3445,7 +3477,7 @@
       <c r="T12" s="69"/>
       <c r="U12" s="69"/>
     </row>
-    <row r="13" spans="1:21" s="70" customFormat="1" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" s="70" customFormat="1" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A13" s="80" t="s">
         <v>74</v>
       </c>
@@ -3467,50 +3499,50 @@
         <v>78</v>
       </c>
       <c r="I13" s="81" t="s">
+        <v>462</v>
+      </c>
+      <c r="J13" s="81" t="s">
         <v>79</v>
       </c>
-      <c r="J13" s="81" t="s">
+      <c r="K13" s="81" t="s">
         <v>80</v>
       </c>
-      <c r="K13" s="81" t="s">
+      <c r="L13" s="81" t="s">
         <v>81</v>
       </c>
-      <c r="L13" s="81" t="s">
+      <c r="M13" s="81" t="s">
         <v>82</v>
       </c>
-      <c r="M13" s="81" t="s">
+      <c r="N13" s="81" t="s">
         <v>83</v>
       </c>
-      <c r="N13" s="81" t="s">
+      <c r="O13" s="81" t="s">
         <v>84</v>
       </c>
-      <c r="O13" s="81" t="s">
+      <c r="P13" s="81" t="s">
         <v>85</v>
       </c>
-      <c r="P13" s="81" t="s">
+      <c r="Q13" s="81" t="s">
         <v>86</v>
-      </c>
-      <c r="Q13" s="81" t="s">
-        <v>87</v>
       </c>
       <c r="R13" s="130">
         <f>COUNTA(H13:Q13)/10</f>
         <v>1</v>
       </c>
       <c r="S13" s="69" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="T13" s="69" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="U13" s="69"/>
     </row>
     <row r="14" spans="1:21" s="70" customFormat="1" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A14" s="84" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" s="85" t="s">
         <v>88</v>
-      </c>
-      <c r="B14" s="85" t="s">
-        <v>89</v>
       </c>
       <c r="C14" s="86" t="s">
         <v>60</v>
@@ -3519,52 +3551,52 @@
         <v>22</v>
       </c>
       <c r="E14" s="87" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F14" s="69"/>
       <c r="G14" s="69"/>
       <c r="H14" s="131" t="s">
+        <v>90</v>
+      </c>
+      <c r="I14" s="85" t="s">
         <v>91</v>
       </c>
-      <c r="I14" s="85" t="s">
+      <c r="J14" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="J14" s="85" t="s">
+      <c r="K14" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="K14" s="85" t="s">
+      <c r="L14" s="85" t="s">
         <v>94</v>
       </c>
-      <c r="L14" s="85" t="s">
+      <c r="M14" s="85" t="s">
         <v>95</v>
       </c>
-      <c r="M14" s="85" t="s">
+      <c r="N14" s="85" t="s">
         <v>96</v>
       </c>
-      <c r="N14" s="85" t="s">
+      <c r="O14" s="85" t="s">
         <v>97</v>
       </c>
-      <c r="O14" s="85" t="s">
+      <c r="P14" s="85" t="s">
         <v>98</v>
       </c>
-      <c r="P14" s="85" t="s">
+      <c r="Q14" s="85" t="s">
         <v>99</v>
-      </c>
-      <c r="Q14" s="85" t="s">
-        <v>100</v>
       </c>
       <c r="R14" s="132">
         <f>COUNTA(H14:Q14)/10</f>
         <v>1</v>
       </c>
       <c r="S14" s="69" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="T14" s="69" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="U14" s="69" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
     </row>
     <row r="15" spans="1:21" s="70" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -3592,7 +3624,7 @@
     </row>
     <row r="16" spans="1:21" s="70" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="178" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B16" s="176"/>
       <c r="C16" s="176"/>
@@ -3617,10 +3649,10 @@
     </row>
     <row r="17" spans="1:21" s="70" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A17" s="88" t="s">
+        <v>101</v>
+      </c>
+      <c r="B17" s="89" t="s">
         <v>102</v>
-      </c>
-      <c r="B17" s="89" t="s">
-        <v>103</v>
       </c>
       <c r="C17" s="90" t="s">
         <v>21</v>
@@ -3629,58 +3661,58 @@
         <v>31</v>
       </c>
       <c r="E17" s="91" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F17" s="69"/>
       <c r="G17" s="69"/>
       <c r="H17" s="133" t="s">
+        <v>104</v>
+      </c>
+      <c r="I17" s="89" t="s">
+        <v>104</v>
+      </c>
+      <c r="J17" s="89" t="s">
         <v>105</v>
       </c>
-      <c r="I17" s="89" t="s">
+      <c r="K17" s="89" t="s">
+        <v>104</v>
+      </c>
+      <c r="L17" s="89" t="s">
+        <v>106</v>
+      </c>
+      <c r="M17" s="89" t="s">
+        <v>104</v>
+      </c>
+      <c r="N17" s="89" t="s">
+        <v>104</v>
+      </c>
+      <c r="O17" s="89" t="s">
         <v>105</v>
       </c>
-      <c r="J17" s="89" t="s">
-        <v>106</v>
-      </c>
-      <c r="K17" s="89" t="s">
-        <v>105</v>
-      </c>
-      <c r="L17" s="89" t="s">
+      <c r="P17" s="89" t="s">
         <v>107</v>
       </c>
-      <c r="M17" s="89" t="s">
-        <v>105</v>
-      </c>
-      <c r="N17" s="89" t="s">
-        <v>105</v>
-      </c>
-      <c r="O17" s="89" t="s">
-        <v>106</v>
-      </c>
-      <c r="P17" s="89" t="s">
-        <v>108</v>
-      </c>
       <c r="Q17" s="89" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R17" s="134">
         <f t="shared" ref="R17:R23" si="1">COUNTA(H17:Q17)/10</f>
         <v>1</v>
       </c>
       <c r="S17" s="69" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="T17" s="170" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="U17" s="69"/>
     </row>
     <row r="18" spans="1:21" s="70" customFormat="1" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A18" s="88" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" s="89" t="s">
         <v>109</v>
-      </c>
-      <c r="B18" s="89" t="s">
-        <v>110</v>
       </c>
       <c r="C18" s="90" t="s">
         <v>21</v>
@@ -3689,58 +3721,58 @@
         <v>31</v>
       </c>
       <c r="E18" s="91" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F18" s="69"/>
       <c r="G18" s="69"/>
       <c r="H18" s="133" t="s">
+        <v>111</v>
+      </c>
+      <c r="I18" s="89" t="s">
         <v>112</v>
       </c>
-      <c r="I18" s="89" t="s">
+      <c r="J18" s="89" t="s">
         <v>113</v>
       </c>
-      <c r="J18" s="89" t="s">
+      <c r="K18" s="89" t="s">
+        <v>111</v>
+      </c>
+      <c r="L18" s="89" t="s">
         <v>114</v>
       </c>
-      <c r="K18" s="89" t="s">
-        <v>112</v>
-      </c>
-      <c r="L18" s="89" t="s">
+      <c r="M18" s="89" t="s">
+        <v>111</v>
+      </c>
+      <c r="N18" s="89" t="s">
         <v>115</v>
       </c>
-      <c r="M18" s="89" t="s">
-        <v>112</v>
-      </c>
-      <c r="N18" s="89" t="s">
+      <c r="O18" s="89" t="s">
         <v>116</v>
       </c>
-      <c r="O18" s="89" t="s">
+      <c r="P18" s="89" t="s">
         <v>117</v>
       </c>
-      <c r="P18" s="89" t="s">
+      <c r="Q18" s="89" t="s">
         <v>118</v>
-      </c>
-      <c r="Q18" s="89" t="s">
-        <v>119</v>
       </c>
       <c r="R18" s="134">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S18" s="69" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="T18" s="170" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="U18" s="69"/>
     </row>
     <row r="19" spans="1:21" s="70" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A19" s="88" t="s">
+        <v>119</v>
+      </c>
+      <c r="B19" s="89" t="s">
         <v>120</v>
-      </c>
-      <c r="B19" s="89" t="s">
-        <v>121</v>
       </c>
       <c r="C19" s="90" t="s">
         <v>21</v>
@@ -3749,7 +3781,7 @@
         <v>31</v>
       </c>
       <c r="E19" s="91" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F19" s="69"/>
       <c r="G19" s="69"/>
@@ -3760,11 +3792,11 @@
       <c r="L19" s="89"/>
       <c r="M19" s="89"/>
       <c r="N19" s="89" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O19" s="89"/>
       <c r="P19" s="89" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q19" s="89"/>
       <c r="R19" s="134">
@@ -3772,19 +3804,19 @@
         <v>0.2</v>
       </c>
       <c r="S19" s="69" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="T19" s="69" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="U19" s="69"/>
     </row>
     <row r="20" spans="1:21" s="70" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A20" s="88" t="s">
+        <v>123</v>
+      </c>
+      <c r="B20" s="89" t="s">
         <v>124</v>
-      </c>
-      <c r="B20" s="89" t="s">
-        <v>125</v>
       </c>
       <c r="C20" s="90" t="s">
         <v>21</v>
@@ -3793,25 +3825,25 @@
         <v>22</v>
       </c>
       <c r="E20" s="91" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F20" s="69"/>
       <c r="G20" s="69"/>
       <c r="H20" s="133" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I20" s="89"/>
       <c r="J20" s="89"/>
       <c r="K20" s="89" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L20" s="89"/>
       <c r="M20" s="89" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N20" s="89"/>
       <c r="O20" s="89" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P20" s="89"/>
       <c r="Q20" s="89"/>
@@ -3820,75 +3852,75 @@
         <v>0.4</v>
       </c>
       <c r="S20" s="69" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="T20" s="170" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="U20" s="69" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
     </row>
     <row r="21" spans="1:21" s="70" customFormat="1" ht="57" x14ac:dyDescent="0.2">
       <c r="A21" s="88" t="s">
+        <v>128</v>
+      </c>
+      <c r="B21" s="89" t="s">
         <v>129</v>
-      </c>
-      <c r="B21" s="89" t="s">
-        <v>130</v>
       </c>
       <c r="C21" s="90" t="s">
         <v>21</v>
       </c>
       <c r="D21" s="89" t="s">
+        <v>130</v>
+      </c>
+      <c r="E21" s="91" t="s">
         <v>131</v>
-      </c>
-      <c r="E21" s="91" t="s">
-        <v>132</v>
       </c>
       <c r="F21" s="69"/>
       <c r="G21" s="69"/>
       <c r="H21" s="133" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I21" s="89"/>
       <c r="J21" s="89"/>
       <c r="K21" s="89" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L21" s="89"/>
       <c r="M21" s="89" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="N21" s="89"/>
       <c r="O21" s="89" t="s">
+        <v>134</v>
+      </c>
+      <c r="P21" s="89" t="s">
         <v>135</v>
       </c>
-      <c r="P21" s="89" t="s">
-        <v>136</v>
-      </c>
       <c r="Q21" s="89" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="R21" s="134">
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
       <c r="S21" s="69" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="T21" s="170" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="U21" s="69" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
     </row>
     <row r="22" spans="1:21" s="70" customFormat="1" ht="57" x14ac:dyDescent="0.2">
       <c r="A22" s="92" t="s">
+        <v>136</v>
+      </c>
+      <c r="B22" s="93" t="s">
         <v>137</v>
-      </c>
-      <c r="B22" s="93" t="s">
-        <v>138</v>
       </c>
       <c r="C22" s="94" t="s">
         <v>60</v>
@@ -3897,7 +3929,7 @@
         <v>22</v>
       </c>
       <c r="E22" s="95" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F22" s="69"/>
       <c r="G22" s="69"/>
@@ -3907,7 +3939,7 @@
       <c r="K22" s="93"/>
       <c r="L22" s="93"/>
       <c r="M22" s="93" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N22" s="93"/>
       <c r="O22" s="93"/>
@@ -3918,21 +3950,21 @@
         <v>0.1</v>
       </c>
       <c r="S22" s="69" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="T22" s="69" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="U22" s="69" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
     </row>
     <row r="23" spans="1:21" s="70" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A23" s="92" t="s">
+        <v>141</v>
+      </c>
+      <c r="B23" s="93" t="s">
         <v>142</v>
-      </c>
-      <c r="B23" s="93" t="s">
-        <v>143</v>
       </c>
       <c r="C23" s="94" t="s">
         <v>60</v>
@@ -3941,7 +3973,7 @@
         <v>22</v>
       </c>
       <c r="E23" s="95" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F23" s="69"/>
       <c r="G23" s="69"/>
@@ -3951,7 +3983,7 @@
       <c r="K23" s="93"/>
       <c r="L23" s="93"/>
       <c r="M23" s="93" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N23" s="93"/>
       <c r="O23" s="93"/>
@@ -3962,13 +3994,13 @@
         <v>0.1</v>
       </c>
       <c r="S23" s="69" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="T23" s="69" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="U23" s="69" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
     </row>
     <row r="24" spans="1:21" s="70" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -3996,7 +4028,7 @@
     </row>
     <row r="25" spans="1:21" s="70" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="179" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B25" s="176"/>
       <c r="C25" s="176"/>
@@ -4021,10 +4053,10 @@
     </row>
     <row r="26" spans="1:21" s="70" customFormat="1" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A26" s="96" t="s">
+        <v>147</v>
+      </c>
+      <c r="B26" s="97" t="s">
         <v>148</v>
-      </c>
-      <c r="B26" s="97" t="s">
-        <v>149</v>
       </c>
       <c r="C26" s="98" t="s">
         <v>21</v>
@@ -4033,191 +4065,191 @@
         <v>31</v>
       </c>
       <c r="E26" s="99" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F26" s="69"/>
       <c r="G26" s="69"/>
       <c r="H26" s="137" t="s">
+        <v>150</v>
+      </c>
+      <c r="I26" s="97" t="s">
+        <v>150</v>
+      </c>
+      <c r="J26" s="97" t="s">
         <v>151</v>
       </c>
-      <c r="I26" s="97" t="s">
-        <v>151</v>
-      </c>
-      <c r="J26" s="97" t="s">
+      <c r="K26" s="97" t="s">
+        <v>150</v>
+      </c>
+      <c r="L26" s="97" t="s">
+        <v>150</v>
+      </c>
+      <c r="M26" s="97" t="s">
+        <v>150</v>
+      </c>
+      <c r="N26" s="97" t="s">
         <v>152</v>
       </c>
-      <c r="K26" s="97" t="s">
-        <v>151</v>
-      </c>
-      <c r="L26" s="97" t="s">
-        <v>151</v>
-      </c>
-      <c r="M26" s="97" t="s">
-        <v>151</v>
-      </c>
-      <c r="N26" s="97" t="s">
+      <c r="O26" s="97" t="s">
         <v>153</v>
       </c>
-      <c r="O26" s="97" t="s">
+      <c r="P26" s="97" t="s">
         <v>154</v>
       </c>
-      <c r="P26" s="97" t="s">
+      <c r="Q26" s="97" t="s">
         <v>155</v>
-      </c>
-      <c r="Q26" s="97" t="s">
-        <v>156</v>
       </c>
       <c r="R26" s="138">
         <f t="shared" ref="R26:R43" si="2">COUNTA(H26:Q26)/10</f>
         <v>1</v>
       </c>
       <c r="S26" s="69" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="T26" s="170" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="U26" s="171" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
     </row>
     <row r="27" spans="1:21" s="70" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A27" s="96" t="s">
+        <v>157</v>
+      </c>
+      <c r="B27" s="97" t="s">
         <v>158</v>
-      </c>
-      <c r="B27" s="97" t="s">
-        <v>159</v>
       </c>
       <c r="C27" s="100" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="97" t="s">
+        <v>159</v>
+      </c>
+      <c r="E27" s="99" t="s">
         <v>160</v>
-      </c>
-      <c r="E27" s="99" t="s">
-        <v>161</v>
       </c>
       <c r="F27" s="69"/>
       <c r="G27" s="69"/>
       <c r="H27" s="137" t="s">
+        <v>161</v>
+      </c>
+      <c r="I27" s="97" t="s">
+        <v>161</v>
+      </c>
+      <c r="J27" s="97" t="s">
+        <v>161</v>
+      </c>
+      <c r="K27" s="97" t="s">
+        <v>161</v>
+      </c>
+      <c r="L27" s="97" t="s">
         <v>162</v>
       </c>
-      <c r="I27" s="97" t="s">
-        <v>162</v>
-      </c>
-      <c r="J27" s="97" t="s">
-        <v>162</v>
-      </c>
-      <c r="K27" s="97" t="s">
-        <v>162</v>
-      </c>
-      <c r="L27" s="97" t="s">
-        <v>163</v>
-      </c>
       <c r="M27" s="97" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N27" s="97" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O27" s="97" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P27" s="97" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q27" s="97" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="R27" s="138">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S27" s="101" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="T27" s="170" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="U27" s="171" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
     </row>
     <row r="28" spans="1:21" s="70" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A28" s="96" t="s">
+        <v>164</v>
+      </c>
+      <c r="B28" s="97" t="s">
         <v>165</v>
-      </c>
-      <c r="B28" s="97" t="s">
-        <v>166</v>
       </c>
       <c r="C28" s="100" t="s">
         <v>21</v>
       </c>
       <c r="D28" s="97" t="s">
+        <v>166</v>
+      </c>
+      <c r="E28" s="99" t="s">
         <v>167</v>
-      </c>
-      <c r="E28" s="99" t="s">
-        <v>168</v>
       </c>
       <c r="F28" s="69"/>
       <c r="G28" s="69"/>
       <c r="H28" s="137" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I28" s="97"/>
       <c r="J28" s="97" t="s">
+        <v>169</v>
+      </c>
+      <c r="K28" s="97" t="s">
+        <v>168</v>
+      </c>
+      <c r="L28" s="97" t="s">
         <v>170</v>
       </c>
-      <c r="K28" s="97" t="s">
-        <v>169</v>
-      </c>
-      <c r="L28" s="97" t="s">
+      <c r="M28" s="97" t="s">
+        <v>168</v>
+      </c>
+      <c r="N28" s="97" t="s">
         <v>171</v>
       </c>
-      <c r="M28" s="97" t="s">
-        <v>169</v>
-      </c>
-      <c r="N28" s="97" t="s">
+      <c r="O28" s="97" t="s">
         <v>172</v>
       </c>
-      <c r="O28" s="97" t="s">
+      <c r="P28" s="97" t="s">
         <v>173</v>
       </c>
-      <c r="P28" s="97" t="s">
+      <c r="Q28" s="97" t="s">
         <v>174</v>
-      </c>
-      <c r="Q28" s="97" t="s">
-        <v>175</v>
       </c>
       <c r="R28" s="138">
         <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
       <c r="S28" s="101" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="T28" s="170" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="U28" s="171" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="29" spans="1:21" s="70" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A29" s="102" t="s">
+        <v>175</v>
+      </c>
+      <c r="B29" s="103" t="s">
         <v>176</v>
-      </c>
-      <c r="B29" s="103" t="s">
-        <v>177</v>
       </c>
       <c r="C29" s="104" t="s">
         <v>60</v>
       </c>
       <c r="D29" s="103" t="s">
+        <v>177</v>
+      </c>
+      <c r="E29" s="105" t="s">
         <v>178</v>
-      </c>
-      <c r="E29" s="105" t="s">
-        <v>179</v>
       </c>
       <c r="F29" s="69"/>
       <c r="G29" s="69"/>
@@ -4236,21 +4268,21 @@
         <v>0</v>
       </c>
       <c r="S29" s="69" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T29" s="69" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="U29" s="69" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
     </row>
     <row r="30" spans="1:21" s="70" customFormat="1" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A30" s="102" t="s">
+        <v>180</v>
+      </c>
+      <c r="B30" s="103" t="s">
         <v>181</v>
-      </c>
-      <c r="B30" s="103" t="s">
-        <v>182</v>
       </c>
       <c r="C30" s="104" t="s">
         <v>60</v>
@@ -4259,7 +4291,7 @@
         <v>22</v>
       </c>
       <c r="E30" s="105" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F30" s="69"/>
       <c r="G30" s="69"/>
@@ -4269,10 +4301,10 @@
       <c r="K30" s="103"/>
       <c r="L30" s="103"/>
       <c r="M30" s="103" t="s">
+        <v>183</v>
+      </c>
+      <c r="N30" s="103" t="s">
         <v>184</v>
-      </c>
-      <c r="N30" s="103" t="s">
-        <v>185</v>
       </c>
       <c r="O30" s="103"/>
       <c r="P30" s="103"/>
@@ -4282,21 +4314,21 @@
         <v>0.2</v>
       </c>
       <c r="S30" s="69" t="s">
+        <v>185</v>
+      </c>
+      <c r="T30" s="69" t="s">
         <v>186</v>
       </c>
-      <c r="T30" s="69" t="s">
-        <v>187</v>
-      </c>
       <c r="U30" s="69" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
     </row>
     <row r="31" spans="1:21" s="111" customFormat="1" ht="72" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="106" t="s">
+        <v>187</v>
+      </c>
+      <c r="B31" s="107" t="s">
         <v>188</v>
-      </c>
-      <c r="B31" s="107" t="s">
-        <v>189</v>
       </c>
       <c r="C31" s="108" t="s">
         <v>60</v>
@@ -4305,7 +4337,7 @@
         <v>22</v>
       </c>
       <c r="E31" s="109" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F31" s="110"/>
       <c r="G31" s="110"/>
@@ -4324,21 +4356,21 @@
         <v>0</v>
       </c>
       <c r="S31" s="110" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="T31" s="110" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U31" s="110" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
     </row>
     <row r="32" spans="1:21" ht="234" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="B32" s="36" t="s">
         <v>192</v>
-      </c>
-      <c r="B32" s="36" t="s">
-        <v>193</v>
       </c>
       <c r="C32" s="37" t="s">
         <v>21</v>
@@ -4347,11 +4379,11 @@
         <v>31</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H32" s="143"/>
       <c r="I32" s="36"/>
@@ -4368,85 +4400,85 @@
         <v>0</v>
       </c>
       <c r="S32" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="T32" s="3" t="s">
-        <v>369</v>
+        <v>451</v>
       </c>
       <c r="U32" s="3" t="s">
-        <v>413</v>
+        <v>456</v>
       </c>
     </row>
     <row r="33" spans="1:21" ht="77.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="B33" s="36" t="s">
         <v>197</v>
-      </c>
-      <c r="B33" s="36" t="s">
-        <v>198</v>
       </c>
       <c r="C33" s="38" t="s">
         <v>21</v>
       </c>
       <c r="D33" s="36" t="s">
+        <v>198</v>
+      </c>
+      <c r="E33" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="E33" s="21" t="s">
-        <v>200</v>
-      </c>
       <c r="F33" s="3" t="s">
-        <v>201</v>
+        <v>452</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="143" t="s">
+        <v>200</v>
+      </c>
+      <c r="I33" s="36" t="s">
+        <v>201</v>
+      </c>
+      <c r="J33" s="36" t="s">
+        <v>460</v>
+      </c>
+      <c r="K33" s="36" t="s">
+        <v>200</v>
+      </c>
+      <c r="L33" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="M33" s="36" t="s">
         <v>202</v>
       </c>
-      <c r="I33" s="36" t="s">
+      <c r="N33" s="36" t="s">
         <v>203</v>
       </c>
-      <c r="J33" s="36" t="s">
-        <v>204</v>
-      </c>
-      <c r="K33" s="36" t="s">
-        <v>202</v>
-      </c>
-      <c r="L33" s="36" t="s">
-        <v>163</v>
-      </c>
-      <c r="M33" s="36" t="s">
-        <v>205</v>
-      </c>
-      <c r="N33" s="36" t="s">
-        <v>206</v>
-      </c>
       <c r="O33" s="36" t="s">
-        <v>207</v>
+        <v>459</v>
       </c>
       <c r="P33" s="36" t="s">
-        <v>208</v>
+        <v>461</v>
       </c>
       <c r="Q33" s="36" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="R33" s="144">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S33" s="11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="T33" s="3" t="s">
-        <v>368</v>
+        <v>453</v>
       </c>
       <c r="U33" s="3" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C34" s="38" t="s">
         <v>21</v>
@@ -4455,74 +4487,74 @@
         <v>31</v>
       </c>
       <c r="E34" s="21" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>201</v>
+        <v>452</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="143" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="I34" s="36" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="J34" s="36" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="K34" s="36" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="L34" s="36" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="M34" s="36" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="N34" s="36" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="O34" s="36" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="P34" s="36" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="Q34" s="36" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="R34" s="144">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S34" s="11" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="T34" s="3" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="U34" s="3" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
     </row>
     <row r="35" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B35" s="39" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C35" s="40" t="s">
         <v>60</v>
       </c>
       <c r="D35" s="39" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>201</v>
+        <v>452</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="145"/>
@@ -4540,33 +4572,33 @@
         <v>0</v>
       </c>
       <c r="S35" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="T35" s="3" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="U35" s="3" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
     </row>
     <row r="36" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B36" s="39" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C36" s="40" t="s">
         <v>60</v>
       </c>
       <c r="D36" s="39" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E36" s="22" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>201</v>
+        <v>452</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="145"/>
@@ -4584,21 +4616,21 @@
         <v>0</v>
       </c>
       <c r="S36" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="T36" s="3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="U36" s="3" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
     </row>
     <row r="37" spans="1:21" ht="72" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C37" s="37" t="s">
         <v>21</v>
@@ -4607,10 +4639,10 @@
         <v>31</v>
       </c>
       <c r="E37" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>201</v>
+        <v>452</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="143"/>
@@ -4619,7 +4651,7 @@
       <c r="K37" s="36"/>
       <c r="L37" s="36"/>
       <c r="M37" s="36" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="N37" s="36"/>
       <c r="O37" s="36"/>
@@ -4630,21 +4662,21 @@
         <v>0.1</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="T37" s="3" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="U37" s="3" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
     </row>
     <row r="38" spans="1:21" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B38" s="39" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C38" s="40" t="s">
         <v>60</v>
@@ -4653,10 +4685,10 @@
         <v>31</v>
       </c>
       <c r="E38" s="22" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>201</v>
+        <v>452</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="145"/>
@@ -4674,21 +4706,21 @@
         <v>0</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="T38" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C39" s="40" t="s">
         <v>60</v>
@@ -4697,10 +4729,10 @@
         <v>31</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>201</v>
+        <v>452</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="145"/>
@@ -4718,21 +4750,21 @@
         <v>0</v>
       </c>
       <c r="S39" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="T39" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="U39" s="3" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="40" spans="1:21" ht="100.5" thickBot="1" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" ht="129" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C40" s="38" t="s">
         <v>21</v>
@@ -4741,19 +4773,19 @@
         <v>31</v>
       </c>
       <c r="E40" s="21" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>201</v>
+        <v>452</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="143" t="s">
-        <v>239</v>
+        <v>458</v>
       </c>
       <c r="I40" s="36"/>
       <c r="J40" s="36"/>
       <c r="K40" s="36" t="s">
-        <v>240</v>
+        <v>457</v>
       </c>
       <c r="L40" s="36"/>
       <c r="M40" s="36"/>
@@ -4766,52 +4798,52 @@
         <v>0.2</v>
       </c>
       <c r="S40" s="11" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="U40" s="3" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
     </row>
     <row r="41" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C41" s="38" t="s">
         <v>21</v>
       </c>
       <c r="D41" s="36" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="E41" s="21" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>201</v>
+        <v>452</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="143" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I41" s="36"/>
       <c r="J41" s="36"/>
       <c r="K41" s="36" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L41" s="36" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="M41" s="36"/>
       <c r="N41" s="36" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="O41" s="36" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="P41" s="36"/>
       <c r="Q41" s="36"/>
@@ -4820,50 +4852,50 @@
         <v>0.5</v>
       </c>
       <c r="S41" s="11" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="T41" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="U41" s="3" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C42" s="38" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="36" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="E42" s="21" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>201</v>
+        <v>452</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="143" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I42" s="36"/>
       <c r="J42" s="36"/>
       <c r="K42" s="36" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="L42" s="36"/>
       <c r="M42" s="36"/>
       <c r="N42" s="36" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="O42" s="36" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="P42" s="36"/>
       <c r="Q42" s="36"/>
@@ -4872,33 +4904,33 @@
         <v>0.4</v>
       </c>
       <c r="S42" s="11" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="T42" s="3" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="U42" s="3" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="72" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C43" s="40" t="s">
         <v>60</v>
       </c>
       <c r="D43" s="39" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>201</v>
+        <v>452</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="145"/>
@@ -4916,13 +4948,13 @@
         <v>0</v>
       </c>
       <c r="S43" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="T43" s="3" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="U43" s="3" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
     </row>
     <row r="44" spans="1:21" ht="14.25" x14ac:dyDescent="0.2">
@@ -4950,7 +4982,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A45" s="180" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B45" s="173"/>
       <c r="C45" s="173"/>
@@ -4975,10 +5007,10 @@
     </row>
     <row r="46" spans="1:21" ht="114" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B46" s="41" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C46" s="35" t="s">
         <v>21</v>
@@ -4987,54 +5019,54 @@
         <v>31</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
       <c r="H46" s="147" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="I46" s="41" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="J46" s="41"/>
       <c r="K46" s="41" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="L46" s="41"/>
       <c r="M46" s="41" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="N46" s="41"/>
       <c r="O46" s="41" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="P46" s="41" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="Q46" s="41" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="R46" s="148">
         <f t="shared" ref="R46:R56" si="3">COUNTA(H46:Q46)/10</f>
         <v>0.7</v>
       </c>
       <c r="S46" s="11" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="T46" s="3" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
     </row>
     <row r="47" spans="1:21" ht="51" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B47" s="41" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C47" s="42" t="s">
         <v>21</v>
@@ -5043,7 +5075,7 @@
         <v>31</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
@@ -5062,30 +5094,30 @@
         <v>0</v>
       </c>
       <c r="S47" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T47" s="3" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="U47" s="3" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
     </row>
     <row r="48" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A48" s="7" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B48" s="43" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C48" s="44" t="s">
         <v>60</v>
       </c>
       <c r="D48" s="43" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E48" s="24" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
@@ -5095,10 +5127,10 @@
       <c r="K48" s="43"/>
       <c r="L48" s="43"/>
       <c r="M48" s="43" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="N48" s="43" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="O48" s="43"/>
       <c r="P48" s="43"/>
@@ -5108,21 +5140,21 @@
         <v>0.2</v>
       </c>
       <c r="S48" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T48" s="3" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="U48" s="3" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
     </row>
     <row r="49" spans="1:21" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="B49" s="41" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C49" s="42" t="s">
         <v>21</v>
@@ -5131,7 +5163,7 @@
         <v>31</v>
       </c>
       <c r="E49" s="23" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
@@ -5150,21 +5182,21 @@
         <v>0</v>
       </c>
       <c r="S49" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T49" s="3" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="U49" s="3" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
     </row>
     <row r="50" spans="1:21" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B50" s="43" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C50" s="44" t="s">
         <v>60</v>
@@ -5173,7 +5205,7 @@
         <v>31</v>
       </c>
       <c r="E50" s="24" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
@@ -5192,21 +5224,21 @@
         <v>0</v>
       </c>
       <c r="S50" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T50" s="3" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="U50" s="3" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
     </row>
     <row r="51" spans="1:21" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="14" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B51" s="45" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C51" s="46" t="s">
         <v>60</v>
@@ -5215,10 +5247,10 @@
         <v>22</v>
       </c>
       <c r="E51" s="25" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>201</v>
+        <v>452</v>
       </c>
       <c r="G51" s="3"/>
       <c r="H51" s="151"/>
@@ -5236,21 +5268,21 @@
         <v>0</v>
       </c>
       <c r="S51" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="T51" s="3" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="U51" s="3" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B52" s="45" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C52" s="46" t="s">
         <v>60</v>
@@ -5259,10 +5291,10 @@
         <v>22</v>
       </c>
       <c r="E52" s="25" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>201</v>
+        <v>452</v>
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="151"/>
@@ -5280,21 +5312,21 @@
         <v>0</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
     </row>
     <row r="53" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="15" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B53" s="47" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C53" s="48" t="s">
         <v>60</v>
@@ -5303,10 +5335,10 @@
         <v>22</v>
       </c>
       <c r="E53" s="26" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>201</v>
+        <v>452</v>
       </c>
       <c r="G53" s="3"/>
       <c r="H53" s="153"/>
@@ -5324,21 +5356,21 @@
         <v>0</v>
       </c>
       <c r="S53" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
     </row>
     <row r="54" spans="1:21" ht="114.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A54" s="16" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B54" s="49" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C54" s="38" t="s">
         <v>21</v>
@@ -5347,10 +5379,10 @@
         <v>31</v>
       </c>
       <c r="E54" s="27" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>201</v>
+        <v>452</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="155"/>
@@ -5359,7 +5391,7 @@
       <c r="K54" s="49"/>
       <c r="L54" s="49"/>
       <c r="M54" s="49" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="N54" s="49"/>
       <c r="O54" s="49"/>
@@ -5370,21 +5402,21 @@
         <v>0.1</v>
       </c>
       <c r="S54" s="11" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="T54" s="3" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="U54" s="3" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
     </row>
     <row r="55" spans="1:21" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A55" s="14" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B55" s="45" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C55" s="50" t="s">
         <v>60</v>
@@ -5393,10 +5425,10 @@
         <v>31</v>
       </c>
       <c r="E55" s="25" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>201</v>
+        <v>452</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="151"/>
@@ -5414,21 +5446,21 @@
         <v>0</v>
       </c>
       <c r="S55" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="T55" s="3" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="U55" s="3" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
     </row>
     <row r="56" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A56" s="14" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B56" s="45" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C56" s="50" t="s">
         <v>60</v>
@@ -5437,10 +5469,10 @@
         <v>31</v>
       </c>
       <c r="E56" s="25" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>201</v>
+        <v>452</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="151"/>
@@ -5458,13 +5490,13 @@
         <v>0</v>
       </c>
       <c r="S56" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="T56" s="3" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="U56" s="3" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
     <row r="57" spans="1:21" ht="14.25" x14ac:dyDescent="0.2">
@@ -5492,7 +5524,7 @@
     </row>
     <row r="58" spans="1:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A58" s="172" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B58" s="173"/>
       <c r="C58" s="173"/>
@@ -5517,10 +5549,10 @@
     </row>
     <row r="59" spans="1:21" ht="91.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A59" s="17" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B59" s="51" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C59" s="38" t="s">
         <v>21</v>
@@ -5529,60 +5561,60 @@
         <v>22</v>
       </c>
       <c r="E59" s="28" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>201</v>
+        <v>452</v>
       </c>
       <c r="G59" s="3"/>
       <c r="H59" s="160" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="I59" s="51" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="J59" s="51"/>
       <c r="K59" s="51" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="L59" s="51" t="s">
+        <v>311</v>
+      </c>
+      <c r="M59" s="51" t="s">
+        <v>312</v>
+      </c>
+      <c r="N59" s="51" t="s">
+        <v>313</v>
+      </c>
+      <c r="O59" s="51" t="s">
+        <v>314</v>
+      </c>
+      <c r="P59" s="51" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q59" s="51" t="s">
         <v>316</v>
-      </c>
-      <c r="M59" s="51" t="s">
-        <v>317</v>
-      </c>
-      <c r="N59" s="51" t="s">
-        <v>318</v>
-      </c>
-      <c r="O59" s="51" t="s">
-        <v>319</v>
-      </c>
-      <c r="P59" s="51" t="s">
-        <v>320</v>
-      </c>
-      <c r="Q59" s="51" t="s">
-        <v>321</v>
       </c>
       <c r="R59" s="161">
         <f t="shared" ref="R59:R68" si="4">COUNTA(H59:Q59)/10</f>
         <v>0.9</v>
       </c>
       <c r="S59" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="T59" s="3" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="U59" s="3" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
     </row>
     <row r="60" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A60" s="17" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B60" s="51" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C60" s="52" t="s">
         <v>21</v>
@@ -5591,10 +5623,10 @@
         <v>22</v>
       </c>
       <c r="E60" s="28" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>201</v>
+        <v>452</v>
       </c>
       <c r="G60" s="3"/>
       <c r="H60" s="160"/>
@@ -5603,14 +5635,14 @@
       <c r="K60" s="51"/>
       <c r="L60" s="51"/>
       <c r="M60" s="51" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="N60" s="51" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="O60" s="51"/>
       <c r="P60" s="51" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="Q60" s="51"/>
       <c r="R60" s="161">
@@ -5618,33 +5650,33 @@
         <v>0.3</v>
       </c>
       <c r="S60" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="T60" s="3" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="U60" s="3" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
     </row>
     <row r="61" spans="1:21" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A61" s="17" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="B61" s="51" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C61" s="38" t="s">
         <v>21</v>
       </c>
       <c r="D61" s="51" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E61" s="28" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>201</v>
+        <v>452</v>
       </c>
       <c r="G61" s="3"/>
       <c r="H61" s="160"/>
@@ -5662,21 +5694,21 @@
         <v>0</v>
       </c>
       <c r="S61" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="T61" s="3" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="U61" s="3" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
     </row>
     <row r="62" spans="1:21" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A62" s="18" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="B62" s="53" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="C62" s="54" t="s">
         <v>60</v>
@@ -5685,10 +5717,10 @@
         <v>22</v>
       </c>
       <c r="E62" s="29" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>201</v>
+        <v>452</v>
       </c>
       <c r="G62" s="3"/>
       <c r="H62" s="162"/>
@@ -5706,21 +5738,21 @@
         <v>0</v>
       </c>
       <c r="S62" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="T62" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="U62" s="3" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
     </row>
     <row r="63" spans="1:21" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A63" s="18" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="B63" s="53" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="C63" s="54" t="s">
         <v>60</v>
@@ -5729,10 +5761,10 @@
         <v>22</v>
       </c>
       <c r="E63" s="29" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>201</v>
+        <v>452</v>
       </c>
       <c r="G63" s="3"/>
       <c r="H63" s="162"/>
@@ -5750,87 +5782,87 @@
         <v>0</v>
       </c>
       <c r="S63" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="T63" s="3" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="U63" s="3" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
     </row>
     <row r="64" spans="1:21" ht="114.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A64" s="18" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="B64" s="53" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="C64" s="54" t="s">
         <v>60</v>
       </c>
       <c r="D64" s="53" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="E64" s="29" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>201</v>
+        <v>452</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="162"/>
       <c r="I64" s="53" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="J64" s="53" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="K64" s="53" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="L64" s="53" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="M64" s="53"/>
       <c r="N64" s="53"/>
       <c r="O64" s="53"/>
       <c r="P64" s="53"/>
       <c r="Q64" s="53" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="R64" s="163">
         <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="S64" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="T64" s="3" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="U64" s="3" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
     </row>
     <row r="65" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A65" s="18" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="B65" s="53" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C65" s="54" t="s">
         <v>60</v>
       </c>
       <c r="D65" s="53" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E65" s="29" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>201</v>
+        <v>452</v>
       </c>
       <c r="G65" s="3"/>
       <c r="H65" s="162"/>
@@ -5848,19 +5880,19 @@
         <v>0</v>
       </c>
       <c r="S65" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="T65" s="3"/>
       <c r="U65" s="3" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
     </row>
     <row r="66" spans="1:21" ht="72" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A66" s="18" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="B66" s="53" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="C66" s="54" t="s">
         <v>60</v>
@@ -5869,10 +5901,10 @@
         <v>22</v>
       </c>
       <c r="E66" s="29" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>201</v>
+        <v>452</v>
       </c>
       <c r="G66" s="8"/>
       <c r="H66" s="162"/>
@@ -5890,21 +5922,21 @@
         <v>0</v>
       </c>
       <c r="S66" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="T66" s="3" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="U66" s="3" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
     </row>
     <row r="67" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A67" s="18" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="B67" s="53" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C67" s="54" t="s">
         <v>60</v>
@@ -5913,10 +5945,10 @@
         <v>22</v>
       </c>
       <c r="E67" s="29" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>201</v>
+        <v>452</v>
       </c>
       <c r="G67" s="8"/>
       <c r="H67" s="162"/>
@@ -5934,21 +5966,21 @@
         <v>0</v>
       </c>
       <c r="S67" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="T67" s="9" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="U67" s="3" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
     </row>
     <row r="68" spans="1:21" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A68" s="18" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B68" s="53" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="C68" s="54" t="s">
         <v>60</v>
@@ -5957,10 +5989,10 @@
         <v>22</v>
       </c>
       <c r="E68" s="29" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>201</v>
+        <v>452</v>
       </c>
       <c r="G68" s="8"/>
       <c r="H68" s="162"/>
@@ -5978,13 +6010,13 @@
         <v>0</v>
       </c>
       <c r="S68" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="T68" s="9" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="U68" s="3" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.2">
@@ -6012,10 +6044,10 @@
     </row>
     <row r="70" spans="1:21" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A70" s="10" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B70" s="56" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="C70" s="57" t="s">
         <v>60</v>
@@ -6038,13 +6070,13 @@
       <c r="Q70" s="166"/>
       <c r="R70" s="114"/>
       <c r="S70" s="3" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="T70" s="3" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="U70" s="3" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.2">

--- a/docs/TAPP_EPMA_filled.xlsx
+++ b/docs/TAPP_EPMA_filled.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/944a82e2ddcde9eb/Documents/GithubC/USGIN/geochemBuildingBlocks/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="299" documentId="11_3C209AD99577444EEF615C96566D1EBF266D99FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1E778BF-00DE-4010-B5A4-4CECD611067F}"/>
+  <xr:revisionPtr revIDLastSave="301" documentId="11_3C209AD99577444EEF615C96566D1EBF266D99FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E128C9A9-D278-4B17-86BE-75B69BB4BEA7}"/>
   <bookViews>
-    <workbookView xWindow="8520" yWindow="990" windowWidth="27930" windowHeight="14610" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1245" yWindow="8535" windowWidth="27930" windowHeight="14610" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TAPP" sheetId="1" r:id="rId1"/>
@@ -964,9 +964,6 @@
     <t>Method (e.g., single-sample mean) + blank material name</t>
   </si>
   <si>
-    <t>Match. Method-level parameter with free-text schema:description; alternatively a Data Processing step's description.</t>
-  </si>
-  <si>
     <t>Normalization / Standards-Based Correction</t>
   </si>
   <si>
@@ -986,9 +983,6 @@
   </si>
   <si>
     <t>e.g., 10-12 %</t>
-  </si>
-  <si>
-    <t>Match. Method-level parameter with ada:dataType='number', schema:unitText='%'.</t>
   </si>
   <si>
     <t>Background Correction Method</t>
@@ -1609,6 +1603,12 @@
 silica glass, 
 coesite aggregates, 
 mesostasis</t>
+  </si>
+  <si>
+    <t>Match. Method-level parameter</t>
+  </si>
+  <si>
+    <t>Match. Method-level parameter with free-text schema:description</t>
   </si>
 </sst>
 </file>
@@ -2954,7 +2954,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="G1" s="2"/>
       <c r="H1" s="112" t="s">
@@ -2997,7 +2997,7 @@
         <v>17</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.2">
@@ -3078,10 +3078,10 @@
         <v>1</v>
       </c>
       <c r="S3" s="63" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="T3" s="169" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="U3" s="63"/>
     </row>
@@ -3138,13 +3138,13 @@
         <v>1</v>
       </c>
       <c r="S4" s="69" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="T4" s="170" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="U4" s="69" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="5" spans="1:21" s="70" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
@@ -3200,14 +3200,14 @@
         <v>1</v>
       </c>
       <c r="S5" s="69" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="T5" s="170" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="U5" s="69"/>
     </row>
-    <row r="6" spans="1:21" s="70" customFormat="1" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" s="70" customFormat="1" ht="57" x14ac:dyDescent="0.2">
       <c r="A6" s="65" t="s">
         <v>46</v>
       </c>
@@ -3260,10 +3260,10 @@
         <v>1</v>
       </c>
       <c r="S6" s="69" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="T6" s="170" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="U6" s="69"/>
     </row>
@@ -3300,10 +3300,10 @@
         <v>0</v>
       </c>
       <c r="S7" s="69" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="T7" s="170" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="U7" s="69"/>
     </row>
@@ -3340,10 +3340,10 @@
         <v>0</v>
       </c>
       <c r="S8" s="69" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="T8" s="170" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="U8" s="69"/>
     </row>
@@ -3380,13 +3380,13 @@
         <v>0</v>
       </c>
       <c r="S9" s="69" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="T9" s="170" t="s">
+        <v>410</v>
+      </c>
+      <c r="U9" s="69" t="s">
         <v>412</v>
-      </c>
-      <c r="U9" s="69" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="10" spans="1:21" s="70" customFormat="1" ht="42.75" x14ac:dyDescent="0.2">
@@ -3422,10 +3422,10 @@
         <v>0</v>
       </c>
       <c r="S10" s="69" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="T10" s="170" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="U10" s="69"/>
     </row>
@@ -3499,7 +3499,7 @@
         <v>78</v>
       </c>
       <c r="I13" s="81" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="J13" s="81" t="s">
         <v>79</v>
@@ -3530,10 +3530,10 @@
         <v>1</v>
       </c>
       <c r="S13" s="69" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="T13" s="69" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="U13" s="69"/>
     </row>
@@ -3590,13 +3590,13 @@
         <v>1</v>
       </c>
       <c r="S14" s="69" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="T14" s="69" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="U14" s="69" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="15" spans="1:21" s="70" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -3700,14 +3700,14 @@
         <v>1</v>
       </c>
       <c r="S17" s="69" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="T17" s="170" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="U17" s="69"/>
     </row>
-    <row r="18" spans="1:21" s="70" customFormat="1" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:21" s="70" customFormat="1" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A18" s="88" t="s">
         <v>108</v>
       </c>
@@ -3760,10 +3760,10 @@
         <v>1</v>
       </c>
       <c r="S18" s="69" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="T18" s="170" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="U18" s="69"/>
     </row>
@@ -3804,14 +3804,14 @@
         <v>0.2</v>
       </c>
       <c r="S19" s="69" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="T19" s="69" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="U19" s="69"/>
     </row>
-    <row r="20" spans="1:21" s="70" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:21" s="70" customFormat="1" ht="57" x14ac:dyDescent="0.2">
       <c r="A20" s="88" t="s">
         <v>123</v>
       </c>
@@ -3852,13 +3852,13 @@
         <v>0.4</v>
       </c>
       <c r="S20" s="69" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="T20" s="170" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="U20" s="69" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="21" spans="1:21" s="70" customFormat="1" ht="57" x14ac:dyDescent="0.2">
@@ -3906,13 +3906,13 @@
         <v>0.6</v>
       </c>
       <c r="S21" s="69" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="T21" s="170" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="U21" s="69" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="22" spans="1:21" s="70" customFormat="1" ht="57" x14ac:dyDescent="0.2">
@@ -3950,16 +3950,16 @@
         <v>0.1</v>
       </c>
       <c r="S22" s="69" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="T22" s="69" t="s">
         <v>140</v>
       </c>
       <c r="U22" s="69" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" s="70" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" s="70" customFormat="1" ht="57" x14ac:dyDescent="0.2">
       <c r="A23" s="92" t="s">
         <v>141</v>
       </c>
@@ -3994,13 +3994,13 @@
         <v>0.1</v>
       </c>
       <c r="S23" s="69" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="T23" s="69" t="s">
         <v>145</v>
       </c>
       <c r="U23" s="69" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="24" spans="1:21" s="70" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -4104,13 +4104,13 @@
         <v>1</v>
       </c>
       <c r="S26" s="69" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="T26" s="170" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="U26" s="171" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="27" spans="1:21" s="70" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
@@ -4166,13 +4166,13 @@
         <v>1</v>
       </c>
       <c r="S27" s="101" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="T27" s="170" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="U27" s="171" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="28" spans="1:21" s="70" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
@@ -4226,13 +4226,13 @@
         <v>0.9</v>
       </c>
       <c r="S28" s="101" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="T28" s="170" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="U28" s="171" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="29" spans="1:21" s="70" customFormat="1" ht="51" x14ac:dyDescent="0.2">
@@ -4274,10 +4274,10 @@
         <v>179</v>
       </c>
       <c r="U29" s="69" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" s="70" customFormat="1" ht="71.25" x14ac:dyDescent="0.2">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" s="70" customFormat="1" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A30" s="102" t="s">
         <v>180</v>
       </c>
@@ -4320,10 +4320,10 @@
         <v>186</v>
       </c>
       <c r="U30" s="69" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" s="111" customFormat="1" ht="72" thickBot="1" x14ac:dyDescent="0.25">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" s="111" customFormat="1" ht="100.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="106" t="s">
         <v>187</v>
       </c>
@@ -4362,7 +4362,7 @@
         <v>190</v>
       </c>
       <c r="U31" s="110" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="32" spans="1:21" ht="234" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -4403,10 +4403,10 @@
         <v>195</v>
       </c>
       <c r="T32" s="3" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="U32" s="3" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="33" spans="1:21" ht="77.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -4426,7 +4426,7 @@
         <v>199</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="143" t="s">
@@ -4436,7 +4436,7 @@
         <v>201</v>
       </c>
       <c r="J33" s="36" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K33" s="36" t="s">
         <v>200</v>
@@ -4451,10 +4451,10 @@
         <v>203</v>
       </c>
       <c r="O33" s="36" t="s">
+        <v>457</v>
+      </c>
+      <c r="P33" s="36" t="s">
         <v>459</v>
-      </c>
-      <c r="P33" s="36" t="s">
-        <v>461</v>
       </c>
       <c r="Q33" s="36" t="s">
         <v>203</v>
@@ -4467,10 +4467,10 @@
         <v>163</v>
       </c>
       <c r="T33" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="U33" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
@@ -4490,7 +4490,7 @@
         <v>206</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="143" t="s">
@@ -4534,7 +4534,7 @@
         <v>209</v>
       </c>
       <c r="U34" s="3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="35" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
@@ -4554,7 +4554,7 @@
         <v>213</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="145"/>
@@ -4578,7 +4578,7 @@
         <v>214</v>
       </c>
       <c r="U35" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="36" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
@@ -4598,7 +4598,7 @@
         <v>213</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="145"/>
@@ -4622,10 +4622,10 @@
         <v>217</v>
       </c>
       <c r="U36" s="3" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" ht="72" thickBot="1" x14ac:dyDescent="0.25">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" ht="86.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
         <v>218</v>
       </c>
@@ -4642,7 +4642,7 @@
         <v>220</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="143"/>
@@ -4668,10 +4668,10 @@
         <v>222</v>
       </c>
       <c r="U37" s="3" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
         <v>223</v>
       </c>
@@ -4688,7 +4688,7 @@
         <v>225</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="145"/>
@@ -4712,7 +4712,7 @@
         <v>226</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
@@ -4732,7 +4732,7 @@
         <v>229</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="145"/>
@@ -4756,7 +4756,7 @@
         <v>230</v>
       </c>
       <c r="U39" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="129" thickBot="1" x14ac:dyDescent="0.25">
@@ -4776,16 +4776,16 @@
         <v>233</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="143" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="I40" s="36"/>
       <c r="J40" s="36"/>
       <c r="K40" s="36" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="L40" s="36"/>
       <c r="M40" s="36"/>
@@ -4804,7 +4804,7 @@
         <v>236</v>
       </c>
       <c r="U40" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="41" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -4824,7 +4824,7 @@
         <v>240</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="143" t="s">
@@ -4858,7 +4858,7 @@
         <v>245</v>
       </c>
       <c r="U41" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -4878,7 +4878,7 @@
         <v>248</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="143" t="s">
@@ -4910,7 +4910,7 @@
         <v>251</v>
       </c>
       <c r="U42" s="3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="72" thickBot="1" x14ac:dyDescent="0.25">
@@ -4930,7 +4930,7 @@
         <v>255</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="145"/>
@@ -4954,7 +4954,7 @@
         <v>256</v>
       </c>
       <c r="U43" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="44" spans="1:21" ht="14.25" x14ac:dyDescent="0.2">
@@ -5005,7 +5005,7 @@
       <c r="T45" s="3"/>
       <c r="U45" s="3"/>
     </row>
-    <row r="46" spans="1:21" ht="114" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:21" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>258</v>
       </c>
@@ -5052,16 +5052,16 @@
         <v>0.7</v>
       </c>
       <c r="S46" s="11" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="T46" s="3" t="s">
         <v>264</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="47" spans="1:21" ht="51" x14ac:dyDescent="0.2">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>265</v>
       </c>
@@ -5100,7 +5100,7 @@
         <v>268</v>
       </c>
       <c r="U47" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="48" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -5146,10 +5146,10 @@
         <v>275</v>
       </c>
       <c r="U48" s="3" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="49" spans="1:21" ht="99.75" x14ac:dyDescent="0.2">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>276</v>
       </c>
@@ -5188,10 +5188,10 @@
         <v>279</v>
       </c>
       <c r="U49" s="3" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="50" spans="1:21" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>280</v>
       </c>
@@ -5230,7 +5230,7 @@
         <v>283</v>
       </c>
       <c r="U50" s="3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="51" spans="1:21" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -5250,7 +5250,7 @@
         <v>286</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G51" s="3"/>
       <c r="H51" s="151"/>
@@ -5271,18 +5271,18 @@
         <v>208</v>
       </c>
       <c r="T51" s="3" t="s">
-        <v>287</v>
+        <v>462</v>
       </c>
       <c r="U51" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="B52" s="45" t="s">
         <v>288</v>
-      </c>
-      <c r="B52" s="45" t="s">
-        <v>289</v>
       </c>
       <c r="C52" s="46" t="s">
         <v>60</v>
@@ -5291,10 +5291,10 @@
         <v>22</v>
       </c>
       <c r="E52" s="25" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="151"/>
@@ -5315,18 +5315,18 @@
         <v>208</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="53" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="B53" s="47" t="s">
         <v>292</v>
-      </c>
-      <c r="B53" s="47" t="s">
-        <v>293</v>
       </c>
       <c r="C53" s="48" t="s">
         <v>60</v>
@@ -5335,10 +5335,10 @@
         <v>22</v>
       </c>
       <c r="E53" s="26" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G53" s="3"/>
       <c r="H53" s="153"/>
@@ -5359,18 +5359,18 @@
         <v>208</v>
       </c>
       <c r="T53" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="U53" s="3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" ht="143.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="B54" s="49" t="s">
         <v>295</v>
-      </c>
-      <c r="U53" s="3" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="54" spans="1:21" ht="114.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="16" t="s">
-        <v>296</v>
-      </c>
-      <c r="B54" s="49" t="s">
-        <v>297</v>
       </c>
       <c r="C54" s="38" t="s">
         <v>21</v>
@@ -5379,10 +5379,10 @@
         <v>31</v>
       </c>
       <c r="E54" s="27" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="155"/>
@@ -5391,7 +5391,7 @@
       <c r="K54" s="49"/>
       <c r="L54" s="49"/>
       <c r="M54" s="49" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="N54" s="49"/>
       <c r="O54" s="49"/>
@@ -5405,18 +5405,18 @@
         <v>208</v>
       </c>
       <c r="T54" s="3" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="U54" s="3" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="55" spans="1:21" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A55" s="14" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B55" s="45" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C55" s="50" t="s">
         <v>60</v>
@@ -5425,10 +5425,10 @@
         <v>31</v>
       </c>
       <c r="E55" s="25" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="151"/>
@@ -5449,18 +5449,18 @@
         <v>208</v>
       </c>
       <c r="T55" s="3" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="U55" s="3" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="56" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A56" s="14" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B56" s="45" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C56" s="50" t="s">
         <v>60</v>
@@ -5469,10 +5469,10 @@
         <v>31</v>
       </c>
       <c r="E56" s="25" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="151"/>
@@ -5493,10 +5493,10 @@
         <v>208</v>
       </c>
       <c r="T56" s="3" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="U56" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="57" spans="1:21" ht="14.25" x14ac:dyDescent="0.2">
@@ -5524,7 +5524,7 @@
     </row>
     <row r="58" spans="1:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A58" s="172" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B58" s="173"/>
       <c r="C58" s="173"/>
@@ -5549,10 +5549,10 @@
     </row>
     <row r="59" spans="1:21" ht="91.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A59" s="17" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B59" s="51" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C59" s="38" t="s">
         <v>21</v>
@@ -5561,39 +5561,39 @@
         <v>22</v>
       </c>
       <c r="E59" s="28" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G59" s="3"/>
       <c r="H59" s="160" t="s">
         <v>234</v>
       </c>
       <c r="I59" s="51" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J59" s="51"/>
       <c r="K59" s="51" t="s">
         <v>235</v>
       </c>
       <c r="L59" s="51" t="s">
+        <v>309</v>
+      </c>
+      <c r="M59" s="51" t="s">
+        <v>310</v>
+      </c>
+      <c r="N59" s="51" t="s">
         <v>311</v>
       </c>
-      <c r="M59" s="51" t="s">
+      <c r="O59" s="51" t="s">
         <v>312</v>
       </c>
-      <c r="N59" s="51" t="s">
+      <c r="P59" s="51" t="s">
         <v>313</v>
       </c>
-      <c r="O59" s="51" t="s">
+      <c r="Q59" s="51" t="s">
         <v>314</v>
-      </c>
-      <c r="P59" s="51" t="s">
-        <v>315</v>
-      </c>
-      <c r="Q59" s="51" t="s">
-        <v>316</v>
       </c>
       <c r="R59" s="161">
         <f t="shared" ref="R59:R68" si="4">COUNTA(H59:Q59)/10</f>
@@ -5603,18 +5603,18 @@
         <v>208</v>
       </c>
       <c r="T59" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="U59" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="60" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A60" s="17" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B60" s="51" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C60" s="52" t="s">
         <v>21</v>
@@ -5623,10 +5623,10 @@
         <v>22</v>
       </c>
       <c r="E60" s="28" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G60" s="3"/>
       <c r="H60" s="160"/>
@@ -5635,14 +5635,14 @@
       <c r="K60" s="51"/>
       <c r="L60" s="51"/>
       <c r="M60" s="51" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="N60" s="51" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="O60" s="51"/>
       <c r="P60" s="51" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="Q60" s="51"/>
       <c r="R60" s="161">
@@ -5653,18 +5653,18 @@
         <v>208</v>
       </c>
       <c r="T60" s="3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="U60" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="61" spans="1:21" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A61" s="17" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B61" s="51" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C61" s="38" t="s">
         <v>21</v>
@@ -5673,10 +5673,10 @@
         <v>271</v>
       </c>
       <c r="E61" s="28" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G61" s="3"/>
       <c r="H61" s="160"/>
@@ -5697,18 +5697,18 @@
         <v>208</v>
       </c>
       <c r="T61" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="U61" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="62" spans="1:21" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A62" s="18" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B62" s="53" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C62" s="54" t="s">
         <v>60</v>
@@ -5717,10 +5717,10 @@
         <v>22</v>
       </c>
       <c r="E62" s="29" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G62" s="3"/>
       <c r="H62" s="162"/>
@@ -5741,18 +5741,18 @@
         <v>208</v>
       </c>
       <c r="T62" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="U62" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="63" spans="1:21" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A63" s="18" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B63" s="53" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C63" s="54" t="s">
         <v>60</v>
@@ -5761,10 +5761,10 @@
         <v>22</v>
       </c>
       <c r="E63" s="29" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G63" s="3"/>
       <c r="H63" s="162"/>
@@ -5785,51 +5785,51 @@
         <v>208</v>
       </c>
       <c r="T63" s="3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="U63" s="3" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="64" spans="1:21" ht="114.75" thickBot="1" x14ac:dyDescent="0.25">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" ht="171.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A64" s="18" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B64" s="53" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C64" s="54" t="s">
         <v>60</v>
       </c>
       <c r="D64" s="53" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E64" s="29" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="162"/>
       <c r="I64" s="53" t="s">
+        <v>336</v>
+      </c>
+      <c r="J64" s="53" t="s">
+        <v>337</v>
+      </c>
+      <c r="K64" s="53" t="s">
         <v>338</v>
       </c>
-      <c r="J64" s="53" t="s">
+      <c r="L64" s="53" t="s">
         <v>339</v>
-      </c>
-      <c r="K64" s="53" t="s">
-        <v>340</v>
-      </c>
-      <c r="L64" s="53" t="s">
-        <v>341</v>
       </c>
       <c r="M64" s="53"/>
       <c r="N64" s="53"/>
       <c r="O64" s="53"/>
       <c r="P64" s="53"/>
       <c r="Q64" s="53" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="R64" s="163">
         <f t="shared" si="4"/>
@@ -5839,18 +5839,18 @@
         <v>208</v>
       </c>
       <c r="T64" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="U64" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="65" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A65" s="18" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B65" s="53" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C65" s="54" t="s">
         <v>60</v>
@@ -5859,10 +5859,10 @@
         <v>130</v>
       </c>
       <c r="E65" s="29" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G65" s="3"/>
       <c r="H65" s="162"/>
@@ -5884,15 +5884,15 @@
       </c>
       <c r="T65" s="3"/>
       <c r="U65" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="66" spans="1:21" ht="72" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A66" s="18" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B66" s="53" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C66" s="54" t="s">
         <v>60</v>
@@ -5901,10 +5901,10 @@
         <v>22</v>
       </c>
       <c r="E66" s="29" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G66" s="8"/>
       <c r="H66" s="162"/>
@@ -5925,18 +5925,18 @@
         <v>208</v>
       </c>
       <c r="T66" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="U66" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="67" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A67" s="18" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B67" s="53" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C67" s="54" t="s">
         <v>60</v>
@@ -5945,10 +5945,10 @@
         <v>22</v>
       </c>
       <c r="E67" s="29" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G67" s="8"/>
       <c r="H67" s="162"/>
@@ -5969,18 +5969,18 @@
         <v>208</v>
       </c>
       <c r="T67" s="9" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="U67" s="3" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="68" spans="1:21" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A68" s="18" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B68" s="53" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C68" s="54" t="s">
         <v>60</v>
@@ -5989,10 +5989,10 @@
         <v>22</v>
       </c>
       <c r="E68" s="29" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G68" s="8"/>
       <c r="H68" s="162"/>
@@ -6013,10 +6013,10 @@
         <v>208</v>
       </c>
       <c r="T68" s="9" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="U68" s="3" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.2">
@@ -6044,10 +6044,10 @@
     </row>
     <row r="70" spans="1:21" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A70" s="10" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B70" s="56" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C70" s="57" t="s">
         <v>60</v>
@@ -6070,13 +6070,13 @@
       <c r="Q70" s="166"/>
       <c r="R70" s="114"/>
       <c r="S70" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="T70" s="3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="U70" s="3" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.2">

--- a/docs/TAPP_EPMA_filled.xlsx
+++ b/docs/TAPP_EPMA_filled.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/944a82e2ddcde9eb/Documents/GithubC/USGIN/geochemBuildingBlocks/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="301" documentId="11_3C209AD99577444EEF615C96566D1EBF266D99FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E128C9A9-D278-4B17-86BE-75B69BB4BEA7}"/>
+  <xr:revisionPtr revIDLastSave="324" documentId="11_3C209AD99577444EEF615C96566D1EBF266D99FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41ED8E6A-55F5-4C5A-8FFF-A2266BC2973F}"/>
   <bookViews>
-    <workbookView xWindow="1245" yWindow="8535" windowWidth="27930" windowHeight="14610" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1365" windowWidth="27330" windowHeight="14610" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TAPP" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TAPP!$S$1:$S$1001</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -91,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="466">
   <si>
     <t>Metadata Item</t>
   </si>
@@ -1256,11 +1259,6 @@
    readOnly: true</t>
   </si>
   <si>
-    <t>parameter: wdsDeadTimeCorrectioni
-   datatype: enum {Default constant 3µs (Cameca) | Adjusted constant (Cameca) | Default constant (JEOL) | Adjusted constant (JEOL) | High-precision (Probe for EPMA) | Logarithmic | Super-precision | Simple | Other | Unknown}
-   readOnly: true</t>
-  </si>
-  <si>
     <t>parameter: edsSpectralProcessingType
    datatype: enum {Background fitting | Peak deconvolution | Top hat | Gaussian | Filter fit | Other | Unknown}
    readOnly: true</t>
@@ -1393,9 +1391,6 @@
     <t>match. methodDefinition.schema:measurementTechnique is a DefinedTerm; use .schema:termCode for the controlled-list code (EPMA-WDS etc.).</t>
   </si>
   <si>
-    <t>match. schema:agent is a Person or Organization; schema:name carries the author name (plus schema:identifier for ORCID).</t>
-  </si>
-  <si>
     <t>match. ada:laboratory extends spatialExtent (schema:Place); schema:name is the lab/facility name.</t>
   </si>
   <si>
@@ -1427,9 +1422,6 @@
     <t>$MethodDefinition.schema:measurementTechnique.schema:DefinedTerm.schema:name</t>
   </si>
   <si>
-    <t>$MethodDefinition.schema:agent.schema:Person | schema.Organization.schema:name</t>
-  </si>
-  <si>
     <t>$MethodDefinition.schema:location.scheme:Place.schema:name</t>
   </si>
   <si>
@@ -1470,9 +1462,6 @@
   </si>
   <si>
     <t>$MethodDefinition.schema:instrument.schema:model.schema:name</t>
-  </si>
-  <si>
-    <t>$MethodDefinition.schema:instrument.schema:hasPart[]</t>
   </si>
   <si>
     <t>$MethodDefinition.bios:computationalTool[]</t>
@@ -1609,6 +1598,29 @@
   </si>
   <si>
     <t>Match. Method-level parameter with free-text schema:description</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:creator.schema:Person | schema.Organization.schema:name</t>
+  </si>
+  <si>
+    <t>match. schema:creator is a Person or Organization; schema:name carries the author name (plus schema:identifier for ORCID).</t>
+  </si>
+  <si>
+    <t>schema:instrument.schema.hasPart.</t>
+  </si>
+  <si>
+    <t>parameter: wdsDeadTimeCorrection
+   datatype: enum {Default constant 3µs (Cameca) | Adjusted constant (Cameca) | Default constant (JEOL) | Adjusted constant (JEOL) | High-precision (Probe for EPMA) | Logarithmic | Super-precision | Simple | Other | Unknown}
+   readOnly: true</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType = 'ElectronSource'</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType = 'wdsSpectrometer'</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType = 'edsDetector'</t>
   </si>
 </sst>
 </file>
@@ -2914,6 +2926,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:U1001"/>
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2923,13 +2936,13 @@
     <col min="4" max="4" width="16.85546875" style="58" customWidth="1"/>
     <col min="5" max="5" width="26.140625" style="32" customWidth="1"/>
     <col min="6" max="6" width="7.85546875" style="4" customWidth="1"/>
-    <col min="7" max="7" width="28.28515625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="28.28515625" style="167" customWidth="1"/>
-    <col min="9" max="9" width="28.28515625" style="58" customWidth="1"/>
-    <col min="10" max="10" width="36.85546875" style="58" customWidth="1"/>
-    <col min="11" max="14" width="28.28515625" style="58" customWidth="1"/>
-    <col min="15" max="15" width="33.42578125" style="58" customWidth="1"/>
-    <col min="16" max="17" width="28.28515625" style="58" customWidth="1"/>
+    <col min="7" max="7" width="28.28515625" style="4" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="28.28515625" style="167" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="28.28515625" style="58" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="36.85546875" style="58" hidden="1" customWidth="1"/>
+    <col min="11" max="14" width="28.28515625" style="58" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="33.42578125" style="58" hidden="1" customWidth="1"/>
+    <col min="16" max="17" width="28.28515625" style="58" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="28.28515625" style="168" customWidth="1"/>
     <col min="19" max="19" width="37.140625" style="4" customWidth="1"/>
     <col min="20" max="20" width="49.140625" style="4" customWidth="1"/>
@@ -2954,7 +2967,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="G1" s="2"/>
       <c r="H1" s="112" t="s">
@@ -2997,10 +3010,10 @@
         <v>17</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="177" t="s">
         <v>18</v>
       </c>
@@ -3025,7 +3038,7 @@
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
     </row>
-    <row r="3" spans="1:21" s="64" customFormat="1" ht="57" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" s="64" customFormat="1" ht="57" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="59" t="s">
         <v>19</v>
       </c>
@@ -3078,14 +3091,14 @@
         <v>1</v>
       </c>
       <c r="S3" s="63" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="T3" s="169" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="U3" s="63"/>
     </row>
-    <row r="4" spans="1:21" s="70" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" s="70" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="65" t="s">
         <v>29</v>
       </c>
@@ -3138,16 +3151,16 @@
         <v>1</v>
       </c>
       <c r="S4" s="69" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="T4" s="170" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="U4" s="69" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" s="70" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" s="70" customFormat="1" ht="38.25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="65" t="s">
         <v>34</v>
       </c>
@@ -3200,14 +3213,14 @@
         <v>1</v>
       </c>
       <c r="S5" s="69" t="s">
-        <v>418</v>
+        <v>459</v>
       </c>
       <c r="T5" s="170" t="s">
-        <v>407</v>
+        <v>460</v>
       </c>
       <c r="U5" s="69"/>
     </row>
-    <row r="6" spans="1:21" s="70" customFormat="1" ht="57" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" s="70" customFormat="1" ht="57" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="65" t="s">
         <v>46</v>
       </c>
@@ -3260,14 +3273,14 @@
         <v>1</v>
       </c>
       <c r="S6" s="69" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="T6" s="170" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="U6" s="69"/>
     </row>
-    <row r="7" spans="1:21" s="70" customFormat="1" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" s="70" customFormat="1" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="71" t="s">
         <v>58</v>
       </c>
@@ -3300,14 +3313,14 @@
         <v>0</v>
       </c>
       <c r="S7" s="69" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="T7" s="170" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="U7" s="69"/>
     </row>
-    <row r="8" spans="1:21" s="70" customFormat="1" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" s="70" customFormat="1" ht="42.75" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="65" t="s">
         <v>63</v>
       </c>
@@ -3340,14 +3353,14 @@
         <v>0</v>
       </c>
       <c r="S8" s="69" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="T8" s="170" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="U8" s="69"/>
     </row>
-    <row r="9" spans="1:21" s="70" customFormat="1" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" s="70" customFormat="1" ht="42.75" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="71" t="s">
         <v>66</v>
       </c>
@@ -3380,16 +3393,16 @@
         <v>0</v>
       </c>
       <c r="S9" s="69" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="T9" s="170" t="s">
+        <v>408</v>
+      </c>
+      <c r="U9" s="69" t="s">
         <v>410</v>
       </c>
-      <c r="U9" s="69" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" s="70" customFormat="1" ht="42.75" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:21" s="70" customFormat="1" ht="42.75" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="71" t="s">
         <v>69</v>
       </c>
@@ -3422,14 +3435,14 @@
         <v>0</v>
       </c>
       <c r="S10" s="69" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="T10" s="170" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="U10" s="69"/>
     </row>
-    <row r="11" spans="1:21" s="70" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" s="70" customFormat="1" ht="14.25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="77"/>
       <c r="B11" s="78"/>
       <c r="C11" s="78"/>
@@ -3452,7 +3465,7 @@
       <c r="T11" s="69"/>
       <c r="U11" s="69"/>
     </row>
-    <row r="12" spans="1:21" s="70" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" s="70" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="175" t="s">
         <v>73</v>
       </c>
@@ -3477,7 +3490,7 @@
       <c r="T12" s="69"/>
       <c r="U12" s="69"/>
     </row>
-    <row r="13" spans="1:21" s="70" customFormat="1" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" s="70" customFormat="1" ht="85.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="80" t="s">
         <v>74</v>
       </c>
@@ -3499,7 +3512,7 @@
         <v>78</v>
       </c>
       <c r="I13" s="81" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="J13" s="81" t="s">
         <v>79</v>
@@ -3530,14 +3543,14 @@
         <v>1</v>
       </c>
       <c r="S13" s="69" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="T13" s="69" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="U13" s="69"/>
     </row>
-    <row r="14" spans="1:21" s="70" customFormat="1" ht="89.25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" s="70" customFormat="1" ht="89.25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="84" t="s">
         <v>87</v>
       </c>
@@ -3590,7 +3603,7 @@
         <v>1</v>
       </c>
       <c r="S14" s="69" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="T14" s="69" t="s">
         <v>356</v>
@@ -3599,7 +3612,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="15" spans="1:21" s="70" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" s="70" customFormat="1" ht="14.25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="77"/>
       <c r="B15" s="78"/>
       <c r="C15" s="78"/>
@@ -3622,7 +3635,7 @@
       <c r="T15" s="69"/>
       <c r="U15" s="69"/>
     </row>
-    <row r="16" spans="1:21" s="70" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" s="70" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="178" t="s">
         <v>100</v>
       </c>
@@ -3700,10 +3713,10 @@
         <v>1</v>
       </c>
       <c r="S17" s="69" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="T17" s="170" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="U17" s="69"/>
     </row>
@@ -3760,10 +3773,10 @@
         <v>1</v>
       </c>
       <c r="S18" s="69" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="T18" s="170" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="U18" s="69"/>
     </row>
@@ -3804,14 +3817,16 @@
         <v>0.2</v>
       </c>
       <c r="S19" s="69" t="s">
-        <v>433</v>
+        <v>463</v>
       </c>
       <c r="T19" s="69" t="s">
-        <v>430</v>
-      </c>
-      <c r="U19" s="69"/>
-    </row>
-    <row r="20" spans="1:21" s="70" customFormat="1" ht="57" x14ac:dyDescent="0.2">
+        <v>427</v>
+      </c>
+      <c r="U19" s="69" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" s="70" customFormat="1" ht="57" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="88" t="s">
         <v>123</v>
       </c>
@@ -3852,16 +3867,16 @@
         <v>0.4</v>
       </c>
       <c r="S20" s="69" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="T20" s="170" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="U20" s="69" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="21" spans="1:21" s="70" customFormat="1" ht="57" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:21" s="70" customFormat="1" ht="57" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="88" t="s">
         <v>128</v>
       </c>
@@ -3906,10 +3921,10 @@
         <v>0.6</v>
       </c>
       <c r="S21" s="69" t="s">
+        <v>430</v>
+      </c>
+      <c r="T21" s="170" t="s">
         <v>434</v>
-      </c>
-      <c r="T21" s="170" t="s">
-        <v>438</v>
       </c>
       <c r="U21" s="69" t="s">
         <v>359</v>
@@ -3950,13 +3965,13 @@
         <v>0.1</v>
       </c>
       <c r="S22" s="69" t="s">
-        <v>433</v>
+        <v>464</v>
       </c>
       <c r="T22" s="69" t="s">
         <v>140</v>
       </c>
       <c r="U22" s="69" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="23" spans="1:21" s="70" customFormat="1" ht="57" x14ac:dyDescent="0.2">
@@ -3994,16 +4009,16 @@
         <v>0.1</v>
       </c>
       <c r="S23" s="69" t="s">
-        <v>433</v>
+        <v>465</v>
       </c>
       <c r="T23" s="69" t="s">
         <v>145</v>
       </c>
       <c r="U23" s="69" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" s="70" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" s="70" customFormat="1" ht="14.25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="77"/>
       <c r="B24" s="78"/>
       <c r="C24" s="78"/>
@@ -4026,7 +4041,7 @@
       <c r="T24" s="69"/>
       <c r="U24" s="69"/>
     </row>
-    <row r="25" spans="1:21" s="70" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:21" s="70" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="179" t="s">
         <v>146</v>
       </c>
@@ -4051,7 +4066,7 @@
       <c r="T25" s="69"/>
       <c r="U25" s="69"/>
     </row>
-    <row r="26" spans="1:21" s="70" customFormat="1" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:21" s="70" customFormat="1" ht="71.25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="96" t="s">
         <v>147</v>
       </c>
@@ -4104,16 +4119,16 @@
         <v>1</v>
       </c>
       <c r="S26" s="69" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="T26" s="170" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="U26" s="171" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" s="70" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" s="70" customFormat="1" ht="76.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="96" t="s">
         <v>157</v>
       </c>
@@ -4166,16 +4181,16 @@
         <v>1</v>
       </c>
       <c r="S27" s="101" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="T27" s="170" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="U27" s="171" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" s="70" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" s="70" customFormat="1" ht="76.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="96" t="s">
         <v>164</v>
       </c>
@@ -4226,16 +4241,16 @@
         <v>0.9</v>
       </c>
       <c r="S28" s="101" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="T28" s="170" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="U28" s="171" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" s="70" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" s="70" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="102" t="s">
         <v>175</v>
       </c>
@@ -4274,10 +4289,10 @@
         <v>179</v>
       </c>
       <c r="U29" s="69" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" s="70" customFormat="1" ht="85.5" x14ac:dyDescent="0.2">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" s="70" customFormat="1" ht="85.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="102" t="s">
         <v>180</v>
       </c>
@@ -4320,10 +4335,10 @@
         <v>186</v>
       </c>
       <c r="U30" s="69" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" s="111" customFormat="1" ht="100.5" thickBot="1" x14ac:dyDescent="0.25">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" s="111" customFormat="1" ht="99.75" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="106" t="s">
         <v>187</v>
       </c>
@@ -4365,7 +4380,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="234" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" ht="234" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
         <v>191</v>
       </c>
@@ -4403,13 +4418,13 @@
         <v>195</v>
       </c>
       <c r="T32" s="3" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="U32" s="3" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="33" spans="1:21" ht="77.25" thickBot="1" x14ac:dyDescent="0.25">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" ht="77.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
         <v>196</v>
       </c>
@@ -4426,7 +4441,7 @@
         <v>199</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="143" t="s">
@@ -4436,7 +4451,7 @@
         <v>201</v>
       </c>
       <c r="J33" s="36" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="K33" s="36" t="s">
         <v>200</v>
@@ -4451,10 +4466,10 @@
         <v>203</v>
       </c>
       <c r="O33" s="36" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="P33" s="36" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="Q33" s="36" t="s">
         <v>203</v>
@@ -4467,13 +4482,13 @@
         <v>163</v>
       </c>
       <c r="T33" s="3" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="34" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
         <v>204</v>
       </c>
@@ -4490,7 +4505,7 @@
         <v>206</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="143" t="s">
@@ -4537,7 +4552,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="35" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
         <v>210</v>
       </c>
@@ -4554,7 +4569,7 @@
         <v>213</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="145"/>
@@ -4581,7 +4596,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="36" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
         <v>215</v>
       </c>
@@ -4598,7 +4613,7 @@
         <v>213</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="145"/>
@@ -4625,7 +4640,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="37" spans="1:21" ht="86.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" ht="86.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
         <v>218</v>
       </c>
@@ -4642,7 +4657,7 @@
         <v>220</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="143"/>
@@ -4671,7 +4686,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="38" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" ht="57.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
         <v>223</v>
       </c>
@@ -4688,7 +4703,7 @@
         <v>225</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="145"/>
@@ -4715,7 +4730,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="39" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
         <v>227</v>
       </c>
@@ -4732,7 +4747,7 @@
         <v>229</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="145"/>
@@ -4759,7 +4774,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="40" spans="1:21" ht="129" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" ht="129" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
         <v>231</v>
       </c>
@@ -4776,16 +4791,16 @@
         <v>233</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="143" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="I40" s="36"/>
       <c r="J40" s="36"/>
       <c r="K40" s="36" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="L40" s="36"/>
       <c r="M40" s="36"/>
@@ -4807,7 +4822,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="41" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21" ht="57.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
         <v>237</v>
       </c>
@@ -4824,7 +4839,7 @@
         <v>240</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="143" t="s">
@@ -4861,7 +4876,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="42" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" ht="57.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
         <v>246</v>
       </c>
@@ -4878,7 +4893,7 @@
         <v>248</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="143" t="s">
@@ -4913,7 +4928,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="43" spans="1:21" ht="72" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21" ht="72" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
         <v>252</v>
       </c>
@@ -4930,7 +4945,7 @@
         <v>255</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="145"/>
@@ -4957,7 +4972,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="44" spans="1:21" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:21" ht="14.25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="5"/>
       <c r="B44" s="34"/>
       <c r="C44" s="34"/>
@@ -4980,7 +4995,7 @@
       <c r="T44" s="3"/>
       <c r="U44" s="3"/>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="180" t="s">
         <v>257</v>
       </c>
@@ -5005,7 +5020,7 @@
       <c r="T45" s="3"/>
       <c r="U45" s="3"/>
     </row>
-    <row r="46" spans="1:21" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:21" ht="142.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>258</v>
       </c>
@@ -5052,16 +5067,16 @@
         <v>0.7</v>
       </c>
       <c r="S46" s="11" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="T46" s="3" t="s">
         <v>264</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="47" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" ht="57" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>265</v>
       </c>
@@ -5103,7 +5118,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="48" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:21" ht="57" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="7" t="s">
         <v>269</v>
       </c>
@@ -5149,7 +5164,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="49" spans="1:21" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:21" ht="128.25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>276</v>
       </c>
@@ -5188,10 +5203,10 @@
         <v>279</v>
       </c>
       <c r="U49" s="3" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="50" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" ht="57" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="7" t="s">
         <v>280</v>
       </c>
@@ -5230,10 +5245,10 @@
         <v>283</v>
       </c>
       <c r="U50" s="3" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="51" spans="1:21" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" ht="43.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="14" t="s">
         <v>284</v>
       </c>
@@ -5250,7 +5265,7 @@
         <v>286</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G51" s="3"/>
       <c r="H51" s="151"/>
@@ -5271,13 +5286,13 @@
         <v>208</v>
       </c>
       <c r="T51" s="3" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="U51" s="3" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="52" spans="1:21" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" ht="43.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
         <v>287</v>
       </c>
@@ -5294,7 +5309,7 @@
         <v>289</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="151"/>
@@ -5318,10 +5333,10 @@
         <v>290</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="53" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="15" t="s">
         <v>291</v>
       </c>
@@ -5338,7 +5353,7 @@
         <v>293</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G53" s="3"/>
       <c r="H53" s="153"/>
@@ -5359,13 +5374,13 @@
         <v>208</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="54" spans="1:21" ht="143.25" thickBot="1" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" ht="143.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A54" s="16" t="s">
         <v>294</v>
       </c>
@@ -5382,7 +5397,7 @@
         <v>296</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="155"/>
@@ -5405,13 +5420,13 @@
         <v>208</v>
       </c>
       <c r="T54" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="U54" s="3" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="55" spans="1:21" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" ht="51.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A55" s="14" t="s">
         <v>298</v>
       </c>
@@ -5428,7 +5443,7 @@
         <v>300</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="151"/>
@@ -5449,13 +5464,13 @@
         <v>208</v>
       </c>
       <c r="T55" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="U55" s="3" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="56" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" ht="57.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A56" s="14" t="s">
         <v>301</v>
       </c>
@@ -5472,7 +5487,7 @@
         <v>303</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="151"/>
@@ -5493,13 +5508,13 @@
         <v>208</v>
       </c>
       <c r="T56" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="U56" s="3" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="57" spans="1:21" ht="14.25" x14ac:dyDescent="0.2">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" ht="14.25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="5"/>
       <c r="B57" s="34"/>
       <c r="C57" s="34"/>
@@ -5522,7 +5537,7 @@
       <c r="T57" s="3"/>
       <c r="U57" s="3"/>
     </row>
-    <row r="58" spans="1:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="172" t="s">
         <v>304</v>
       </c>
@@ -5547,7 +5562,7 @@
       <c r="T58" s="3"/>
       <c r="U58" s="3"/>
     </row>
-    <row r="59" spans="1:21" ht="91.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:21" ht="91.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A59" s="17" t="s">
         <v>305</v>
       </c>
@@ -5564,7 +5579,7 @@
         <v>307</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G59" s="3"/>
       <c r="H59" s="160" t="s">
@@ -5603,13 +5618,13 @@
         <v>208</v>
       </c>
       <c r="T59" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="U59" s="3" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="60" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" ht="57.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A60" s="17" t="s">
         <v>315</v>
       </c>
@@ -5626,7 +5641,7 @@
         <v>317</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G60" s="3"/>
       <c r="H60" s="160"/>
@@ -5653,13 +5668,13 @@
         <v>208</v>
       </c>
       <c r="T60" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="U60" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="61" spans="1:21" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" ht="43.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A61" s="17" t="s">
         <v>321</v>
       </c>
@@ -5676,7 +5691,7 @@
         <v>323</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G61" s="3"/>
       <c r="H61" s="160"/>
@@ -5700,10 +5715,10 @@
         <v>324</v>
       </c>
       <c r="U61" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="62" spans="1:21" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" ht="43.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A62" s="18" t="s">
         <v>325</v>
       </c>
@@ -5720,7 +5735,7 @@
         <v>327</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G62" s="3"/>
       <c r="H62" s="162"/>
@@ -5744,10 +5759,10 @@
         <v>328</v>
       </c>
       <c r="U62" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="63" spans="1:21" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" ht="43.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A63" s="18" t="s">
         <v>329</v>
       </c>
@@ -5764,7 +5779,7 @@
         <v>331</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G63" s="3"/>
       <c r="H63" s="162"/>
@@ -5785,13 +5800,13 @@
         <v>208</v>
       </c>
       <c r="T63" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="U63" s="3" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="64" spans="1:21" ht="171.75" thickBot="1" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" ht="171.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A64" s="18" t="s">
         <v>332</v>
       </c>
@@ -5808,7 +5823,7 @@
         <v>335</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="162"/>
@@ -5839,13 +5854,13 @@
         <v>208</v>
       </c>
       <c r="T64" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="U64" s="3" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="65" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A65" s="18" t="s">
         <v>341</v>
       </c>
@@ -5862,7 +5877,7 @@
         <v>343</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G65" s="3"/>
       <c r="H65" s="162"/>
@@ -5884,10 +5899,10 @@
       </c>
       <c r="T65" s="3"/>
       <c r="U65" s="3" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="66" spans="1:21" ht="72" thickBot="1" x14ac:dyDescent="0.25">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" ht="72" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A66" s="18" t="s">
         <v>344</v>
       </c>
@@ -5904,7 +5919,7 @@
         <v>346</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G66" s="8"/>
       <c r="H66" s="162"/>
@@ -5925,13 +5940,13 @@
         <v>208</v>
       </c>
       <c r="T66" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="U66" s="3" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="67" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" ht="57.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A67" s="18" t="s">
         <v>347</v>
       </c>
@@ -5948,7 +5963,7 @@
         <v>349</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G67" s="8"/>
       <c r="H67" s="162"/>
@@ -5969,13 +5984,13 @@
         <v>208</v>
       </c>
       <c r="T67" s="9" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="U67" s="3" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="68" spans="1:21" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" ht="43.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A68" s="18" t="s">
         <v>350</v>
       </c>
@@ -5992,7 +6007,7 @@
         <v>352</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G68" s="8"/>
       <c r="H68" s="162"/>
@@ -6013,13 +6028,13 @@
         <v>208</v>
       </c>
       <c r="T68" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="U68" s="3" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.2">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="9"/>
       <c r="B69" s="55"/>
       <c r="C69" s="55"/>
@@ -6042,7 +6057,7 @@
       <c r="T69" s="9"/>
       <c r="U69" s="9"/>
     </row>
-    <row r="70" spans="1:21" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:21" ht="42.75" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" s="10" t="s">
         <v>353</v>
       </c>
@@ -6073,13 +6088,13 @@
         <v>355</v>
       </c>
       <c r="T70" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="U70" s="3" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.2">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="9"/>
       <c r="B71" s="55"/>
       <c r="C71" s="55"/>
@@ -6102,7 +6117,7 @@
       <c r="T71" s="9"/>
       <c r="U71" s="9"/>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="9"/>
       <c r="B72" s="55"/>
       <c r="C72" s="55"/>
@@ -6125,7 +6140,7 @@
       <c r="T72" s="9"/>
       <c r="U72" s="9"/>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" s="9"/>
       <c r="B73" s="55"/>
       <c r="C73" s="55"/>
@@ -6148,7 +6163,7 @@
       <c r="T73" s="9"/>
       <c r="U73" s="9"/>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" s="9"/>
       <c r="B74" s="55"/>
       <c r="C74" s="55"/>
@@ -6171,7 +6186,7 @@
       <c r="T74" s="9"/>
       <c r="U74" s="9"/>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" s="9"/>
       <c r="B75" s="55"/>
       <c r="C75" s="55"/>
@@ -6194,7 +6209,7 @@
       <c r="T75" s="9"/>
       <c r="U75" s="9"/>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" s="9"/>
       <c r="B76" s="55"/>
       <c r="C76" s="55"/>
@@ -6217,7 +6232,7 @@
       <c r="T76" s="9"/>
       <c r="U76" s="9"/>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" s="9"/>
       <c r="B77" s="55"/>
       <c r="C77" s="55"/>
@@ -6240,7 +6255,7 @@
       <c r="T77" s="9"/>
       <c r="U77" s="9"/>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" s="9"/>
       <c r="B78" s="55"/>
       <c r="C78" s="55"/>
@@ -6263,7 +6278,7 @@
       <c r="T78" s="9"/>
       <c r="U78" s="9"/>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" s="9"/>
       <c r="B79" s="55"/>
       <c r="C79" s="55"/>
@@ -6286,7 +6301,7 @@
       <c r="T79" s="9"/>
       <c r="U79" s="9"/>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" s="9"/>
       <c r="B80" s="55"/>
       <c r="C80" s="55"/>
@@ -6309,7 +6324,7 @@
       <c r="T80" s="9"/>
       <c r="U80" s="9"/>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" s="9"/>
       <c r="B81" s="55"/>
       <c r="C81" s="55"/>
@@ -6332,7 +6347,7 @@
       <c r="T81" s="9"/>
       <c r="U81" s="9"/>
     </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" s="9"/>
       <c r="B82" s="55"/>
       <c r="C82" s="55"/>
@@ -6355,7 +6370,7 @@
       <c r="T82" s="9"/>
       <c r="U82" s="9"/>
     </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" s="9"/>
       <c r="B83" s="55"/>
       <c r="C83" s="55"/>
@@ -6378,7 +6393,7 @@
       <c r="T83" s="9"/>
       <c r="U83" s="9"/>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" s="9"/>
       <c r="B84" s="55"/>
       <c r="C84" s="55"/>
@@ -6401,7 +6416,7 @@
       <c r="T84" s="9"/>
       <c r="U84" s="9"/>
     </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" s="9"/>
       <c r="B85" s="55"/>
       <c r="C85" s="55"/>
@@ -6424,7 +6439,7 @@
       <c r="T85" s="9"/>
       <c r="U85" s="9"/>
     </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" s="9"/>
       <c r="B86" s="55"/>
       <c r="C86" s="55"/>
@@ -6447,7 +6462,7 @@
       <c r="T86" s="9"/>
       <c r="U86" s="9"/>
     </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" s="9"/>
       <c r="B87" s="55"/>
       <c r="C87" s="55"/>
@@ -6470,7 +6485,7 @@
       <c r="T87" s="9"/>
       <c r="U87" s="9"/>
     </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" s="9"/>
       <c r="B88" s="55"/>
       <c r="C88" s="55"/>
@@ -6493,7 +6508,7 @@
       <c r="T88" s="9"/>
       <c r="U88" s="9"/>
     </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" s="9"/>
       <c r="B89" s="55"/>
       <c r="C89" s="55"/>
@@ -6516,7 +6531,7 @@
       <c r="T89" s="9"/>
       <c r="U89" s="9"/>
     </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" s="9"/>
       <c r="B90" s="55"/>
       <c r="C90" s="55"/>
@@ -6539,7 +6554,7 @@
       <c r="T90" s="9"/>
       <c r="U90" s="9"/>
     </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" s="9"/>
       <c r="B91" s="55"/>
       <c r="C91" s="55"/>
@@ -6562,7 +6577,7 @@
       <c r="T91" s="9"/>
       <c r="U91" s="9"/>
     </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" s="9"/>
       <c r="B92" s="55"/>
       <c r="C92" s="55"/>
@@ -6585,7 +6600,7 @@
       <c r="T92" s="9"/>
       <c r="U92" s="9"/>
     </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" s="9"/>
       <c r="B93" s="55"/>
       <c r="C93" s="55"/>
@@ -6608,7 +6623,7 @@
       <c r="T93" s="9"/>
       <c r="U93" s="9"/>
     </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" s="9"/>
       <c r="B94" s="55"/>
       <c r="C94" s="55"/>
@@ -6631,7 +6646,7 @@
       <c r="T94" s="9"/>
       <c r="U94" s="9"/>
     </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" s="9"/>
       <c r="B95" s="55"/>
       <c r="C95" s="55"/>
@@ -6654,7 +6669,7 @@
       <c r="T95" s="9"/>
       <c r="U95" s="9"/>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" s="9"/>
       <c r="B96" s="55"/>
       <c r="C96" s="55"/>
@@ -6677,7 +6692,7 @@
       <c r="T96" s="9"/>
       <c r="U96" s="9"/>
     </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" s="9"/>
       <c r="B97" s="55"/>
       <c r="C97" s="55"/>
@@ -6700,7 +6715,7 @@
       <c r="T97" s="9"/>
       <c r="U97" s="9"/>
     </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" s="9"/>
       <c r="B98" s="55"/>
       <c r="C98" s="55"/>
@@ -6723,7 +6738,7 @@
       <c r="T98" s="9"/>
       <c r="U98" s="9"/>
     </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" s="9"/>
       <c r="B99" s="55"/>
       <c r="C99" s="55"/>
@@ -6746,7 +6761,7 @@
       <c r="T99" s="9"/>
       <c r="U99" s="9"/>
     </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" s="9"/>
       <c r="B100" s="55"/>
       <c r="C100" s="55"/>
@@ -6769,7 +6784,7 @@
       <c r="T100" s="9"/>
       <c r="U100" s="9"/>
     </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" s="9"/>
       <c r="B101" s="55"/>
       <c r="C101" s="55"/>
@@ -6792,7 +6807,7 @@
       <c r="T101" s="9"/>
       <c r="U101" s="9"/>
     </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" s="9"/>
       <c r="B102" s="55"/>
       <c r="C102" s="55"/>
@@ -6815,7 +6830,7 @@
       <c r="T102" s="9"/>
       <c r="U102" s="9"/>
     </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" s="9"/>
       <c r="B103" s="55"/>
       <c r="C103" s="55"/>
@@ -6838,7 +6853,7 @@
       <c r="T103" s="9"/>
       <c r="U103" s="9"/>
     </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" s="9"/>
       <c r="B104" s="55"/>
       <c r="C104" s="55"/>
@@ -6861,7 +6876,7 @@
       <c r="T104" s="9"/>
       <c r="U104" s="9"/>
     </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" s="9"/>
       <c r="B105" s="55"/>
       <c r="C105" s="55"/>
@@ -6884,7 +6899,7 @@
       <c r="T105" s="9"/>
       <c r="U105" s="9"/>
     </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" s="9"/>
       <c r="B106" s="55"/>
       <c r="C106" s="55"/>
@@ -6907,7 +6922,7 @@
       <c r="T106" s="9"/>
       <c r="U106" s="9"/>
     </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" s="9"/>
       <c r="B107" s="55"/>
       <c r="C107" s="55"/>
@@ -6930,7 +6945,7 @@
       <c r="T107" s="9"/>
       <c r="U107" s="9"/>
     </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" s="9"/>
       <c r="B108" s="55"/>
       <c r="C108" s="55"/>
@@ -6953,7 +6968,7 @@
       <c r="T108" s="9"/>
       <c r="U108" s="9"/>
     </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" s="9"/>
       <c r="B109" s="55"/>
       <c r="C109" s="55"/>
@@ -6976,7 +6991,7 @@
       <c r="T109" s="9"/>
       <c r="U109" s="9"/>
     </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" s="9"/>
       <c r="B110" s="55"/>
       <c r="C110" s="55"/>
@@ -6999,7 +7014,7 @@
       <c r="T110" s="9"/>
       <c r="U110" s="9"/>
     </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" s="9"/>
       <c r="B111" s="55"/>
       <c r="C111" s="55"/>
@@ -7022,7 +7037,7 @@
       <c r="T111" s="9"/>
       <c r="U111" s="9"/>
     </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" s="9"/>
       <c r="B112" s="55"/>
       <c r="C112" s="55"/>
@@ -7045,7 +7060,7 @@
       <c r="T112" s="9"/>
       <c r="U112" s="9"/>
     </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" s="9"/>
       <c r="B113" s="55"/>
       <c r="C113" s="55"/>
@@ -7068,7 +7083,7 @@
       <c r="T113" s="9"/>
       <c r="U113" s="9"/>
     </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" s="9"/>
       <c r="B114" s="55"/>
       <c r="C114" s="55"/>
@@ -7091,7 +7106,7 @@
       <c r="T114" s="9"/>
       <c r="U114" s="9"/>
     </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" s="9"/>
       <c r="B115" s="55"/>
       <c r="C115" s="55"/>
@@ -7114,7 +7129,7 @@
       <c r="T115" s="9"/>
       <c r="U115" s="9"/>
     </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" s="9"/>
       <c r="B116" s="55"/>
       <c r="C116" s="55"/>
@@ -7137,7 +7152,7 @@
       <c r="T116" s="9"/>
       <c r="U116" s="9"/>
     </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" s="9"/>
       <c r="B117" s="55"/>
       <c r="C117" s="55"/>
@@ -7160,7 +7175,7 @@
       <c r="T117" s="9"/>
       <c r="U117" s="9"/>
     </row>
-    <row r="118" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" s="9"/>
       <c r="B118" s="55"/>
       <c r="C118" s="55"/>
@@ -7183,7 +7198,7 @@
       <c r="T118" s="9"/>
       <c r="U118" s="9"/>
     </row>
-    <row r="119" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" s="9"/>
       <c r="B119" s="55"/>
       <c r="C119" s="55"/>
@@ -7206,7 +7221,7 @@
       <c r="T119" s="9"/>
       <c r="U119" s="9"/>
     </row>
-    <row r="120" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" s="9"/>
       <c r="B120" s="55"/>
       <c r="C120" s="55"/>
@@ -7229,7 +7244,7 @@
       <c r="T120" s="9"/>
       <c r="U120" s="9"/>
     </row>
-    <row r="121" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" s="9"/>
       <c r="B121" s="55"/>
       <c r="C121" s="55"/>
@@ -7252,7 +7267,7 @@
       <c r="T121" s="9"/>
       <c r="U121" s="9"/>
     </row>
-    <row r="122" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" s="9"/>
       <c r="B122" s="55"/>
       <c r="C122" s="55"/>
@@ -7275,7 +7290,7 @@
       <c r="T122" s="9"/>
       <c r="U122" s="9"/>
     </row>
-    <row r="123" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" s="9"/>
       <c r="B123" s="55"/>
       <c r="C123" s="55"/>
@@ -7298,7 +7313,7 @@
       <c r="T123" s="9"/>
       <c r="U123" s="9"/>
     </row>
-    <row r="124" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" s="9"/>
       <c r="B124" s="55"/>
       <c r="C124" s="55"/>
@@ -7321,7 +7336,7 @@
       <c r="T124" s="9"/>
       <c r="U124" s="9"/>
     </row>
-    <row r="125" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" s="9"/>
       <c r="B125" s="55"/>
       <c r="C125" s="55"/>
@@ -7344,7 +7359,7 @@
       <c r="T125" s="9"/>
       <c r="U125" s="9"/>
     </row>
-    <row r="126" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" s="9"/>
       <c r="B126" s="55"/>
       <c r="C126" s="55"/>
@@ -7367,7 +7382,7 @@
       <c r="T126" s="9"/>
       <c r="U126" s="9"/>
     </row>
-    <row r="127" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" s="9"/>
       <c r="B127" s="55"/>
       <c r="C127" s="55"/>
@@ -7390,7 +7405,7 @@
       <c r="T127" s="9"/>
       <c r="U127" s="9"/>
     </row>
-    <row r="128" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" s="9"/>
       <c r="B128" s="55"/>
       <c r="C128" s="55"/>
@@ -7413,7 +7428,7 @@
       <c r="T128" s="9"/>
       <c r="U128" s="9"/>
     </row>
-    <row r="129" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" s="9"/>
       <c r="B129" s="55"/>
       <c r="C129" s="55"/>
@@ -7436,7 +7451,7 @@
       <c r="T129" s="9"/>
       <c r="U129" s="9"/>
     </row>
-    <row r="130" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" s="9"/>
       <c r="B130" s="55"/>
       <c r="C130" s="55"/>
@@ -7459,7 +7474,7 @@
       <c r="T130" s="9"/>
       <c r="U130" s="9"/>
     </row>
-    <row r="131" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" s="9"/>
       <c r="B131" s="55"/>
       <c r="C131" s="55"/>
@@ -7482,7 +7497,7 @@
       <c r="T131" s="9"/>
       <c r="U131" s="9"/>
     </row>
-    <row r="132" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" s="9"/>
       <c r="B132" s="55"/>
       <c r="C132" s="55"/>
@@ -7505,7 +7520,7 @@
       <c r="T132" s="9"/>
       <c r="U132" s="9"/>
     </row>
-    <row r="133" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" s="9"/>
       <c r="B133" s="55"/>
       <c r="C133" s="55"/>
@@ -7528,7 +7543,7 @@
       <c r="T133" s="9"/>
       <c r="U133" s="9"/>
     </row>
-    <row r="134" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" s="9"/>
       <c r="B134" s="55"/>
       <c r="C134" s="55"/>
@@ -7551,7 +7566,7 @@
       <c r="T134" s="9"/>
       <c r="U134" s="9"/>
     </row>
-    <row r="135" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" s="9"/>
       <c r="B135" s="55"/>
       <c r="C135" s="55"/>
@@ -7574,7 +7589,7 @@
       <c r="T135" s="9"/>
       <c r="U135" s="9"/>
     </row>
-    <row r="136" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" s="9"/>
       <c r="B136" s="55"/>
       <c r="C136" s="55"/>
@@ -7597,7 +7612,7 @@
       <c r="T136" s="9"/>
       <c r="U136" s="9"/>
     </row>
-    <row r="137" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" s="9"/>
       <c r="B137" s="55"/>
       <c r="C137" s="55"/>
@@ -7620,7 +7635,7 @@
       <c r="T137" s="9"/>
       <c r="U137" s="9"/>
     </row>
-    <row r="138" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" s="9"/>
       <c r="B138" s="55"/>
       <c r="C138" s="55"/>
@@ -7643,7 +7658,7 @@
       <c r="T138" s="9"/>
       <c r="U138" s="9"/>
     </row>
-    <row r="139" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" s="9"/>
       <c r="B139" s="55"/>
       <c r="C139" s="55"/>
@@ -7666,7 +7681,7 @@
       <c r="T139" s="9"/>
       <c r="U139" s="9"/>
     </row>
-    <row r="140" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" s="9"/>
       <c r="B140" s="55"/>
       <c r="C140" s="55"/>
@@ -7689,7 +7704,7 @@
       <c r="T140" s="9"/>
       <c r="U140" s="9"/>
     </row>
-    <row r="141" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" s="9"/>
       <c r="B141" s="55"/>
       <c r="C141" s="55"/>
@@ -7712,7 +7727,7 @@
       <c r="T141" s="9"/>
       <c r="U141" s="9"/>
     </row>
-    <row r="142" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" s="9"/>
       <c r="B142" s="55"/>
       <c r="C142" s="55"/>
@@ -7735,7 +7750,7 @@
       <c r="T142" s="9"/>
       <c r="U142" s="9"/>
     </row>
-    <row r="143" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" s="9"/>
       <c r="B143" s="55"/>
       <c r="C143" s="55"/>
@@ -7758,7 +7773,7 @@
       <c r="T143" s="9"/>
       <c r="U143" s="9"/>
     </row>
-    <row r="144" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" s="9"/>
       <c r="B144" s="55"/>
       <c r="C144" s="55"/>
@@ -7781,7 +7796,7 @@
       <c r="T144" s="9"/>
       <c r="U144" s="9"/>
     </row>
-    <row r="145" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" s="9"/>
       <c r="B145" s="55"/>
       <c r="C145" s="55"/>
@@ -7804,7 +7819,7 @@
       <c r="T145" s="9"/>
       <c r="U145" s="9"/>
     </row>
-    <row r="146" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" s="9"/>
       <c r="B146" s="55"/>
       <c r="C146" s="55"/>
@@ -7827,7 +7842,7 @@
       <c r="T146" s="9"/>
       <c r="U146" s="9"/>
     </row>
-    <row r="147" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" s="9"/>
       <c r="B147" s="55"/>
       <c r="C147" s="55"/>
@@ -7850,7 +7865,7 @@
       <c r="T147" s="9"/>
       <c r="U147" s="9"/>
     </row>
-    <row r="148" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" s="9"/>
       <c r="B148" s="55"/>
       <c r="C148" s="55"/>
@@ -7873,7 +7888,7 @@
       <c r="T148" s="9"/>
       <c r="U148" s="9"/>
     </row>
-    <row r="149" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" s="9"/>
       <c r="B149" s="55"/>
       <c r="C149" s="55"/>
@@ -7896,7 +7911,7 @@
       <c r="T149" s="9"/>
       <c r="U149" s="9"/>
     </row>
-    <row r="150" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" s="9"/>
       <c r="B150" s="55"/>
       <c r="C150" s="55"/>
@@ -7919,7 +7934,7 @@
       <c r="T150" s="9"/>
       <c r="U150" s="9"/>
     </row>
-    <row r="151" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" s="9"/>
       <c r="B151" s="55"/>
       <c r="C151" s="55"/>
@@ -7942,7 +7957,7 @@
       <c r="T151" s="9"/>
       <c r="U151" s="9"/>
     </row>
-    <row r="152" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" s="9"/>
       <c r="B152" s="55"/>
       <c r="C152" s="55"/>
@@ -7965,7 +7980,7 @@
       <c r="T152" s="9"/>
       <c r="U152" s="9"/>
     </row>
-    <row r="153" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" s="9"/>
       <c r="B153" s="55"/>
       <c r="C153" s="55"/>
@@ -7988,7 +8003,7 @@
       <c r="T153" s="9"/>
       <c r="U153" s="9"/>
     </row>
-    <row r="154" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" s="9"/>
       <c r="B154" s="55"/>
       <c r="C154" s="55"/>
@@ -8011,7 +8026,7 @@
       <c r="T154" s="9"/>
       <c r="U154" s="9"/>
     </row>
-    <row r="155" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" s="9"/>
       <c r="B155" s="55"/>
       <c r="C155" s="55"/>
@@ -8034,7 +8049,7 @@
       <c r="T155" s="9"/>
       <c r="U155" s="9"/>
     </row>
-    <row r="156" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" s="9"/>
       <c r="B156" s="55"/>
       <c r="C156" s="55"/>
@@ -8057,7 +8072,7 @@
       <c r="T156" s="9"/>
       <c r="U156" s="9"/>
     </row>
-    <row r="157" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" s="9"/>
       <c r="B157" s="55"/>
       <c r="C157" s="55"/>
@@ -8080,7 +8095,7 @@
       <c r="T157" s="9"/>
       <c r="U157" s="9"/>
     </row>
-    <row r="158" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" s="9"/>
       <c r="B158" s="55"/>
       <c r="C158" s="55"/>
@@ -8103,7 +8118,7 @@
       <c r="T158" s="9"/>
       <c r="U158" s="9"/>
     </row>
-    <row r="159" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" s="9"/>
       <c r="B159" s="55"/>
       <c r="C159" s="55"/>
@@ -8126,7 +8141,7 @@
       <c r="T159" s="9"/>
       <c r="U159" s="9"/>
     </row>
-    <row r="160" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" s="9"/>
       <c r="B160" s="55"/>
       <c r="C160" s="55"/>
@@ -8149,7 +8164,7 @@
       <c r="T160" s="9"/>
       <c r="U160" s="9"/>
     </row>
-    <row r="161" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161" s="9"/>
       <c r="B161" s="55"/>
       <c r="C161" s="55"/>
@@ -8172,7 +8187,7 @@
       <c r="T161" s="9"/>
       <c r="U161" s="9"/>
     </row>
-    <row r="162" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" s="9"/>
       <c r="B162" s="55"/>
       <c r="C162" s="55"/>
@@ -8195,7 +8210,7 @@
       <c r="T162" s="9"/>
       <c r="U162" s="9"/>
     </row>
-    <row r="163" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" s="9"/>
       <c r="B163" s="55"/>
       <c r="C163" s="55"/>
@@ -8218,7 +8233,7 @@
       <c r="T163" s="9"/>
       <c r="U163" s="9"/>
     </row>
-    <row r="164" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" s="9"/>
       <c r="B164" s="55"/>
       <c r="C164" s="55"/>
@@ -8241,7 +8256,7 @@
       <c r="T164" s="9"/>
       <c r="U164" s="9"/>
     </row>
-    <row r="165" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" s="9"/>
       <c r="B165" s="55"/>
       <c r="C165" s="55"/>
@@ -8264,7 +8279,7 @@
       <c r="T165" s="9"/>
       <c r="U165" s="9"/>
     </row>
-    <row r="166" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" s="9"/>
       <c r="B166" s="55"/>
       <c r="C166" s="55"/>
@@ -8287,7 +8302,7 @@
       <c r="T166" s="9"/>
       <c r="U166" s="9"/>
     </row>
-    <row r="167" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" s="9"/>
       <c r="B167" s="55"/>
       <c r="C167" s="55"/>
@@ -8310,7 +8325,7 @@
       <c r="T167" s="9"/>
       <c r="U167" s="9"/>
     </row>
-    <row r="168" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" s="9"/>
       <c r="B168" s="55"/>
       <c r="C168" s="55"/>
@@ -8333,7 +8348,7 @@
       <c r="T168" s="9"/>
       <c r="U168" s="9"/>
     </row>
-    <row r="169" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" s="9"/>
       <c r="B169" s="55"/>
       <c r="C169" s="55"/>
@@ -8356,7 +8371,7 @@
       <c r="T169" s="9"/>
       <c r="U169" s="9"/>
     </row>
-    <row r="170" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" s="9"/>
       <c r="B170" s="55"/>
       <c r="C170" s="55"/>
@@ -8379,7 +8394,7 @@
       <c r="T170" s="9"/>
       <c r="U170" s="9"/>
     </row>
-    <row r="171" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" s="9"/>
       <c r="B171" s="55"/>
       <c r="C171" s="55"/>
@@ -8402,7 +8417,7 @@
       <c r="T171" s="9"/>
       <c r="U171" s="9"/>
     </row>
-    <row r="172" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" s="9"/>
       <c r="B172" s="55"/>
       <c r="C172" s="55"/>
@@ -8425,7 +8440,7 @@
       <c r="T172" s="9"/>
       <c r="U172" s="9"/>
     </row>
-    <row r="173" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" s="9"/>
       <c r="B173" s="55"/>
       <c r="C173" s="55"/>
@@ -8448,7 +8463,7 @@
       <c r="T173" s="9"/>
       <c r="U173" s="9"/>
     </row>
-    <row r="174" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" s="9"/>
       <c r="B174" s="55"/>
       <c r="C174" s="55"/>
@@ -8471,7 +8486,7 @@
       <c r="T174" s="9"/>
       <c r="U174" s="9"/>
     </row>
-    <row r="175" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" s="9"/>
       <c r="B175" s="55"/>
       <c r="C175" s="55"/>
@@ -8494,7 +8509,7 @@
       <c r="T175" s="9"/>
       <c r="U175" s="9"/>
     </row>
-    <row r="176" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" s="9"/>
       <c r="B176" s="55"/>
       <c r="C176" s="55"/>
@@ -8517,7 +8532,7 @@
       <c r="T176" s="9"/>
       <c r="U176" s="9"/>
     </row>
-    <row r="177" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" s="9"/>
       <c r="B177" s="55"/>
       <c r="C177" s="55"/>
@@ -8540,7 +8555,7 @@
       <c r="T177" s="9"/>
       <c r="U177" s="9"/>
     </row>
-    <row r="178" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" s="9"/>
       <c r="B178" s="55"/>
       <c r="C178" s="55"/>
@@ -8563,7 +8578,7 @@
       <c r="T178" s="9"/>
       <c r="U178" s="9"/>
     </row>
-    <row r="179" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" s="9"/>
       <c r="B179" s="55"/>
       <c r="C179" s="55"/>
@@ -8586,7 +8601,7 @@
       <c r="T179" s="9"/>
       <c r="U179" s="9"/>
     </row>
-    <row r="180" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" s="9"/>
       <c r="B180" s="55"/>
       <c r="C180" s="55"/>
@@ -8609,7 +8624,7 @@
       <c r="T180" s="9"/>
       <c r="U180" s="9"/>
     </row>
-    <row r="181" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" s="9"/>
       <c r="B181" s="55"/>
       <c r="C181" s="55"/>
@@ -8632,7 +8647,7 @@
       <c r="T181" s="9"/>
       <c r="U181" s="9"/>
     </row>
-    <row r="182" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" s="9"/>
       <c r="B182" s="55"/>
       <c r="C182" s="55"/>
@@ -8655,7 +8670,7 @@
       <c r="T182" s="9"/>
       <c r="U182" s="9"/>
     </row>
-    <row r="183" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" s="9"/>
       <c r="B183" s="55"/>
       <c r="C183" s="55"/>
@@ -8678,7 +8693,7 @@
       <c r="T183" s="9"/>
       <c r="U183" s="9"/>
     </row>
-    <row r="184" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" s="9"/>
       <c r="B184" s="55"/>
       <c r="C184" s="55"/>
@@ -8701,7 +8716,7 @@
       <c r="T184" s="9"/>
       <c r="U184" s="9"/>
     </row>
-    <row r="185" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" s="9"/>
       <c r="B185" s="55"/>
       <c r="C185" s="55"/>
@@ -8724,7 +8739,7 @@
       <c r="T185" s="9"/>
       <c r="U185" s="9"/>
     </row>
-    <row r="186" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" s="9"/>
       <c r="B186" s="55"/>
       <c r="C186" s="55"/>
@@ -8747,7 +8762,7 @@
       <c r="T186" s="9"/>
       <c r="U186" s="9"/>
     </row>
-    <row r="187" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" s="9"/>
       <c r="B187" s="55"/>
       <c r="C187" s="55"/>
@@ -8770,7 +8785,7 @@
       <c r="T187" s="9"/>
       <c r="U187" s="9"/>
     </row>
-    <row r="188" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" s="9"/>
       <c r="B188" s="55"/>
       <c r="C188" s="55"/>
@@ -8793,7 +8808,7 @@
       <c r="T188" s="9"/>
       <c r="U188" s="9"/>
     </row>
-    <row r="189" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" s="9"/>
       <c r="B189" s="55"/>
       <c r="C189" s="55"/>
@@ -8816,7 +8831,7 @@
       <c r="T189" s="9"/>
       <c r="U189" s="9"/>
     </row>
-    <row r="190" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" s="9"/>
       <c r="B190" s="55"/>
       <c r="C190" s="55"/>
@@ -8839,7 +8854,7 @@
       <c r="T190" s="9"/>
       <c r="U190" s="9"/>
     </row>
-    <row r="191" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" s="9"/>
       <c r="B191" s="55"/>
       <c r="C191" s="55"/>
@@ -8862,7 +8877,7 @@
       <c r="T191" s="9"/>
       <c r="U191" s="9"/>
     </row>
-    <row r="192" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" s="9"/>
       <c r="B192" s="55"/>
       <c r="C192" s="55"/>
@@ -8885,7 +8900,7 @@
       <c r="T192" s="9"/>
       <c r="U192" s="9"/>
     </row>
-    <row r="193" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" s="9"/>
       <c r="B193" s="55"/>
       <c r="C193" s="55"/>
@@ -8908,7 +8923,7 @@
       <c r="T193" s="9"/>
       <c r="U193" s="9"/>
     </row>
-    <row r="194" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" s="9"/>
       <c r="B194" s="55"/>
       <c r="C194" s="55"/>
@@ -8931,7 +8946,7 @@
       <c r="T194" s="9"/>
       <c r="U194" s="9"/>
     </row>
-    <row r="195" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" s="9"/>
       <c r="B195" s="55"/>
       <c r="C195" s="55"/>
@@ -8954,7 +8969,7 @@
       <c r="T195" s="9"/>
       <c r="U195" s="9"/>
     </row>
-    <row r="196" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" s="9"/>
       <c r="B196" s="55"/>
       <c r="C196" s="55"/>
@@ -8977,7 +8992,7 @@
       <c r="T196" s="9"/>
       <c r="U196" s="9"/>
     </row>
-    <row r="197" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" s="9"/>
       <c r="B197" s="55"/>
       <c r="C197" s="55"/>
@@ -9000,7 +9015,7 @@
       <c r="T197" s="9"/>
       <c r="U197" s="9"/>
     </row>
-    <row r="198" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" s="9"/>
       <c r="B198" s="55"/>
       <c r="C198" s="55"/>
@@ -9023,7 +9038,7 @@
       <c r="T198" s="9"/>
       <c r="U198" s="9"/>
     </row>
-    <row r="199" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" s="9"/>
       <c r="B199" s="55"/>
       <c r="C199" s="55"/>
@@ -9046,7 +9061,7 @@
       <c r="T199" s="9"/>
       <c r="U199" s="9"/>
     </row>
-    <row r="200" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" s="9"/>
       <c r="B200" s="55"/>
       <c r="C200" s="55"/>
@@ -9069,7 +9084,7 @@
       <c r="T200" s="9"/>
       <c r="U200" s="9"/>
     </row>
-    <row r="201" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" s="9"/>
       <c r="B201" s="55"/>
       <c r="C201" s="55"/>
@@ -9092,7 +9107,7 @@
       <c r="T201" s="9"/>
       <c r="U201" s="9"/>
     </row>
-    <row r="202" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" s="9"/>
       <c r="B202" s="55"/>
       <c r="C202" s="55"/>
@@ -9115,7 +9130,7 @@
       <c r="T202" s="9"/>
       <c r="U202" s="9"/>
     </row>
-    <row r="203" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" s="9"/>
       <c r="B203" s="55"/>
       <c r="C203" s="55"/>
@@ -9138,7 +9153,7 @@
       <c r="T203" s="9"/>
       <c r="U203" s="9"/>
     </row>
-    <row r="204" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" s="9"/>
       <c r="B204" s="55"/>
       <c r="C204" s="55"/>
@@ -9161,7 +9176,7 @@
       <c r="T204" s="9"/>
       <c r="U204" s="9"/>
     </row>
-    <row r="205" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" s="9"/>
       <c r="B205" s="55"/>
       <c r="C205" s="55"/>
@@ -9184,7 +9199,7 @@
       <c r="T205" s="9"/>
       <c r="U205" s="9"/>
     </row>
-    <row r="206" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" s="9"/>
       <c r="B206" s="55"/>
       <c r="C206" s="55"/>
@@ -9207,7 +9222,7 @@
       <c r="T206" s="9"/>
       <c r="U206" s="9"/>
     </row>
-    <row r="207" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" s="9"/>
       <c r="B207" s="55"/>
       <c r="C207" s="55"/>
@@ -9230,7 +9245,7 @@
       <c r="T207" s="9"/>
       <c r="U207" s="9"/>
     </row>
-    <row r="208" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" s="9"/>
       <c r="B208" s="55"/>
       <c r="C208" s="55"/>
@@ -9253,7 +9268,7 @@
       <c r="T208" s="9"/>
       <c r="U208" s="9"/>
     </row>
-    <row r="209" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" s="9"/>
       <c r="B209" s="55"/>
       <c r="C209" s="55"/>
@@ -9276,7 +9291,7 @@
       <c r="T209" s="9"/>
       <c r="U209" s="9"/>
     </row>
-    <row r="210" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" s="9"/>
       <c r="B210" s="55"/>
       <c r="C210" s="55"/>
@@ -9299,7 +9314,7 @@
       <c r="T210" s="9"/>
       <c r="U210" s="9"/>
     </row>
-    <row r="211" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211" s="9"/>
       <c r="B211" s="55"/>
       <c r="C211" s="55"/>
@@ -9322,7 +9337,7 @@
       <c r="T211" s="9"/>
       <c r="U211" s="9"/>
     </row>
-    <row r="212" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212" s="9"/>
       <c r="B212" s="55"/>
       <c r="C212" s="55"/>
@@ -9345,7 +9360,7 @@
       <c r="T212" s="9"/>
       <c r="U212" s="9"/>
     </row>
-    <row r="213" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213" s="9"/>
       <c r="B213" s="55"/>
       <c r="C213" s="55"/>
@@ -9368,7 +9383,7 @@
       <c r="T213" s="9"/>
       <c r="U213" s="9"/>
     </row>
-    <row r="214" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" s="9"/>
       <c r="B214" s="55"/>
       <c r="C214" s="55"/>
@@ -9391,7 +9406,7 @@
       <c r="T214" s="9"/>
       <c r="U214" s="9"/>
     </row>
-    <row r="215" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215" s="9"/>
       <c r="B215" s="55"/>
       <c r="C215" s="55"/>
@@ -9414,7 +9429,7 @@
       <c r="T215" s="9"/>
       <c r="U215" s="9"/>
     </row>
-    <row r="216" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216" s="9"/>
       <c r="B216" s="55"/>
       <c r="C216" s="55"/>
@@ -9437,7 +9452,7 @@
       <c r="T216" s="9"/>
       <c r="U216" s="9"/>
     </row>
-    <row r="217" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217" s="9"/>
       <c r="B217" s="55"/>
       <c r="C217" s="55"/>
@@ -9460,7 +9475,7 @@
       <c r="T217" s="9"/>
       <c r="U217" s="9"/>
     </row>
-    <row r="218" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218" s="9"/>
       <c r="B218" s="55"/>
       <c r="C218" s="55"/>
@@ -9483,7 +9498,7 @@
       <c r="T218" s="9"/>
       <c r="U218" s="9"/>
     </row>
-    <row r="219" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A219" s="9"/>
       <c r="B219" s="55"/>
       <c r="C219" s="55"/>
@@ -9506,7 +9521,7 @@
       <c r="T219" s="9"/>
       <c r="U219" s="9"/>
     </row>
-    <row r="220" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220" s="9"/>
       <c r="B220" s="55"/>
       <c r="C220" s="55"/>
@@ -9529,7 +9544,7 @@
       <c r="T220" s="9"/>
       <c r="U220" s="9"/>
     </row>
-    <row r="221" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221" s="9"/>
       <c r="B221" s="55"/>
       <c r="C221" s="55"/>
@@ -9552,7 +9567,7 @@
       <c r="T221" s="9"/>
       <c r="U221" s="9"/>
     </row>
-    <row r="222" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222" s="9"/>
       <c r="B222" s="55"/>
       <c r="C222" s="55"/>
@@ -9575,7 +9590,7 @@
       <c r="T222" s="9"/>
       <c r="U222" s="9"/>
     </row>
-    <row r="223" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223" s="9"/>
       <c r="B223" s="55"/>
       <c r="C223" s="55"/>
@@ -9598,7 +9613,7 @@
       <c r="T223" s="9"/>
       <c r="U223" s="9"/>
     </row>
-    <row r="224" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224" s="9"/>
       <c r="B224" s="55"/>
       <c r="C224" s="55"/>
@@ -9621,7 +9636,7 @@
       <c r="T224" s="9"/>
       <c r="U224" s="9"/>
     </row>
-    <row r="225" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A225" s="9"/>
       <c r="B225" s="55"/>
       <c r="C225" s="55"/>
@@ -9644,7 +9659,7 @@
       <c r="T225" s="9"/>
       <c r="U225" s="9"/>
     </row>
-    <row r="226" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A226" s="9"/>
       <c r="B226" s="55"/>
       <c r="C226" s="55"/>
@@ -9667,7 +9682,7 @@
       <c r="T226" s="9"/>
       <c r="U226" s="9"/>
     </row>
-    <row r="227" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227" s="9"/>
       <c r="B227" s="55"/>
       <c r="C227" s="55"/>
@@ -9690,7 +9705,7 @@
       <c r="T227" s="9"/>
       <c r="U227" s="9"/>
     </row>
-    <row r="228" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A228" s="9"/>
       <c r="B228" s="55"/>
       <c r="C228" s="55"/>
@@ -9713,7 +9728,7 @@
       <c r="T228" s="9"/>
       <c r="U228" s="9"/>
     </row>
-    <row r="229" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A229" s="9"/>
       <c r="B229" s="55"/>
       <c r="C229" s="55"/>
@@ -9736,7 +9751,7 @@
       <c r="T229" s="9"/>
       <c r="U229" s="9"/>
     </row>
-    <row r="230" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230" s="9"/>
       <c r="B230" s="55"/>
       <c r="C230" s="55"/>
@@ -9759,7 +9774,7 @@
       <c r="T230" s="9"/>
       <c r="U230" s="9"/>
     </row>
-    <row r="231" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A231" s="9"/>
       <c r="B231" s="55"/>
       <c r="C231" s="55"/>
@@ -9782,7 +9797,7 @@
       <c r="T231" s="9"/>
       <c r="U231" s="9"/>
     </row>
-    <row r="232" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A232" s="9"/>
       <c r="B232" s="55"/>
       <c r="C232" s="55"/>
@@ -9805,7 +9820,7 @@
       <c r="T232" s="9"/>
       <c r="U232" s="9"/>
     </row>
-    <row r="233" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A233" s="9"/>
       <c r="B233" s="55"/>
       <c r="C233" s="55"/>
@@ -9828,7 +9843,7 @@
       <c r="T233" s="9"/>
       <c r="U233" s="9"/>
     </row>
-    <row r="234" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A234" s="9"/>
       <c r="B234" s="55"/>
       <c r="C234" s="55"/>
@@ -9851,7 +9866,7 @@
       <c r="T234" s="9"/>
       <c r="U234" s="9"/>
     </row>
-    <row r="235" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A235" s="9"/>
       <c r="B235" s="55"/>
       <c r="C235" s="55"/>
@@ -9874,7 +9889,7 @@
       <c r="T235" s="9"/>
       <c r="U235" s="9"/>
     </row>
-    <row r="236" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A236" s="9"/>
       <c r="B236" s="55"/>
       <c r="C236" s="55"/>
@@ -9897,7 +9912,7 @@
       <c r="T236" s="9"/>
       <c r="U236" s="9"/>
     </row>
-    <row r="237" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A237" s="9"/>
       <c r="B237" s="55"/>
       <c r="C237" s="55"/>
@@ -9920,7 +9935,7 @@
       <c r="T237" s="9"/>
       <c r="U237" s="9"/>
     </row>
-    <row r="238" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A238" s="9"/>
       <c r="B238" s="55"/>
       <c r="C238" s="55"/>
@@ -9943,7 +9958,7 @@
       <c r="T238" s="9"/>
       <c r="U238" s="9"/>
     </row>
-    <row r="239" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A239" s="9"/>
       <c r="B239" s="55"/>
       <c r="C239" s="55"/>
@@ -9966,7 +9981,7 @@
       <c r="T239" s="9"/>
       <c r="U239" s="9"/>
     </row>
-    <row r="240" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240" s="9"/>
       <c r="B240" s="55"/>
       <c r="C240" s="55"/>
@@ -9989,7 +10004,7 @@
       <c r="T240" s="9"/>
       <c r="U240" s="9"/>
     </row>
-    <row r="241" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A241" s="9"/>
       <c r="B241" s="55"/>
       <c r="C241" s="55"/>
@@ -10012,7 +10027,7 @@
       <c r="T241" s="9"/>
       <c r="U241" s="9"/>
     </row>
-    <row r="242" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A242" s="9"/>
       <c r="B242" s="55"/>
       <c r="C242" s="55"/>
@@ -10035,7 +10050,7 @@
       <c r="T242" s="9"/>
       <c r="U242" s="9"/>
     </row>
-    <row r="243" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A243" s="9"/>
       <c r="B243" s="55"/>
       <c r="C243" s="55"/>
@@ -10058,7 +10073,7 @@
       <c r="T243" s="9"/>
       <c r="U243" s="9"/>
     </row>
-    <row r="244" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244" s="9"/>
       <c r="B244" s="55"/>
       <c r="C244" s="55"/>
@@ -10081,7 +10096,7 @@
       <c r="T244" s="9"/>
       <c r="U244" s="9"/>
     </row>
-    <row r="245" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A245" s="9"/>
       <c r="B245" s="55"/>
       <c r="C245" s="55"/>
@@ -10104,7 +10119,7 @@
       <c r="T245" s="9"/>
       <c r="U245" s="9"/>
     </row>
-    <row r="246" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A246" s="9"/>
       <c r="B246" s="55"/>
       <c r="C246" s="55"/>
@@ -10127,7 +10142,7 @@
       <c r="T246" s="9"/>
       <c r="U246" s="9"/>
     </row>
-    <row r="247" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247" s="9"/>
       <c r="B247" s="55"/>
       <c r="C247" s="55"/>
@@ -10150,7 +10165,7 @@
       <c r="T247" s="9"/>
       <c r="U247" s="9"/>
     </row>
-    <row r="248" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A248" s="9"/>
       <c r="B248" s="55"/>
       <c r="C248" s="55"/>
@@ -10173,7 +10188,7 @@
       <c r="T248" s="9"/>
       <c r="U248" s="9"/>
     </row>
-    <row r="249" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A249" s="9"/>
       <c r="B249" s="55"/>
       <c r="C249" s="55"/>
@@ -10196,7 +10211,7 @@
       <c r="T249" s="9"/>
       <c r="U249" s="9"/>
     </row>
-    <row r="250" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A250" s="9"/>
       <c r="B250" s="55"/>
       <c r="C250" s="55"/>
@@ -10219,7 +10234,7 @@
       <c r="T250" s="9"/>
       <c r="U250" s="9"/>
     </row>
-    <row r="251" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A251" s="9"/>
       <c r="B251" s="55"/>
       <c r="C251" s="55"/>
@@ -10242,7 +10257,7 @@
       <c r="T251" s="9"/>
       <c r="U251" s="9"/>
     </row>
-    <row r="252" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A252" s="9"/>
       <c r="B252" s="55"/>
       <c r="C252" s="55"/>
@@ -10265,7 +10280,7 @@
       <c r="T252" s="9"/>
       <c r="U252" s="9"/>
     </row>
-    <row r="253" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A253" s="9"/>
       <c r="B253" s="55"/>
       <c r="C253" s="55"/>
@@ -10288,7 +10303,7 @@
       <c r="T253" s="9"/>
       <c r="U253" s="9"/>
     </row>
-    <row r="254" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A254" s="9"/>
       <c r="B254" s="55"/>
       <c r="C254" s="55"/>
@@ -10311,7 +10326,7 @@
       <c r="T254" s="9"/>
       <c r="U254" s="9"/>
     </row>
-    <row r="255" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A255" s="9"/>
       <c r="B255" s="55"/>
       <c r="C255" s="55"/>
@@ -10334,7 +10349,7 @@
       <c r="T255" s="9"/>
       <c r="U255" s="9"/>
     </row>
-    <row r="256" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A256" s="9"/>
       <c r="B256" s="55"/>
       <c r="C256" s="55"/>
@@ -10357,7 +10372,7 @@
       <c r="T256" s="9"/>
       <c r="U256" s="9"/>
     </row>
-    <row r="257" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A257" s="9"/>
       <c r="B257" s="55"/>
       <c r="C257" s="55"/>
@@ -10380,7 +10395,7 @@
       <c r="T257" s="9"/>
       <c r="U257" s="9"/>
     </row>
-    <row r="258" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A258" s="9"/>
       <c r="B258" s="55"/>
       <c r="C258" s="55"/>
@@ -10403,7 +10418,7 @@
       <c r="T258" s="9"/>
       <c r="U258" s="9"/>
     </row>
-    <row r="259" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A259" s="9"/>
       <c r="B259" s="55"/>
       <c r="C259" s="55"/>
@@ -10426,7 +10441,7 @@
       <c r="T259" s="9"/>
       <c r="U259" s="9"/>
     </row>
-    <row r="260" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A260" s="9"/>
       <c r="B260" s="55"/>
       <c r="C260" s="55"/>
@@ -10449,7 +10464,7 @@
       <c r="T260" s="9"/>
       <c r="U260" s="9"/>
     </row>
-    <row r="261" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A261" s="9"/>
       <c r="B261" s="55"/>
       <c r="C261" s="55"/>
@@ -10472,7 +10487,7 @@
       <c r="T261" s="9"/>
       <c r="U261" s="9"/>
     </row>
-    <row r="262" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A262" s="9"/>
       <c r="B262" s="55"/>
       <c r="C262" s="55"/>
@@ -10495,7 +10510,7 @@
       <c r="T262" s="9"/>
       <c r="U262" s="9"/>
     </row>
-    <row r="263" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A263" s="9"/>
       <c r="B263" s="55"/>
       <c r="C263" s="55"/>
@@ -10518,7 +10533,7 @@
       <c r="T263" s="9"/>
       <c r="U263" s="9"/>
     </row>
-    <row r="264" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A264" s="9"/>
       <c r="B264" s="55"/>
       <c r="C264" s="55"/>
@@ -10541,7 +10556,7 @@
       <c r="T264" s="9"/>
       <c r="U264" s="9"/>
     </row>
-    <row r="265" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A265" s="9"/>
       <c r="B265" s="55"/>
       <c r="C265" s="55"/>
@@ -10564,7 +10579,7 @@
       <c r="T265" s="9"/>
       <c r="U265" s="9"/>
     </row>
-    <row r="266" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A266" s="9"/>
       <c r="B266" s="55"/>
       <c r="C266" s="55"/>
@@ -10587,7 +10602,7 @@
       <c r="T266" s="9"/>
       <c r="U266" s="9"/>
     </row>
-    <row r="267" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A267" s="9"/>
       <c r="B267" s="55"/>
       <c r="C267" s="55"/>
@@ -10610,7 +10625,7 @@
       <c r="T267" s="9"/>
       <c r="U267" s="9"/>
     </row>
-    <row r="268" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A268" s="9"/>
       <c r="B268" s="55"/>
       <c r="C268" s="55"/>
@@ -10633,7 +10648,7 @@
       <c r="T268" s="9"/>
       <c r="U268" s="9"/>
     </row>
-    <row r="269" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A269" s="9"/>
       <c r="B269" s="55"/>
       <c r="C269" s="55"/>
@@ -10656,7 +10671,7 @@
       <c r="T269" s="9"/>
       <c r="U269" s="9"/>
     </row>
-    <row r="270" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A270" s="9"/>
       <c r="B270" s="55"/>
       <c r="C270" s="55"/>
@@ -10679,7 +10694,7 @@
       <c r="T270" s="9"/>
       <c r="U270" s="9"/>
     </row>
-    <row r="271" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A271" s="9"/>
       <c r="B271" s="55"/>
       <c r="C271" s="55"/>
@@ -10702,7 +10717,7 @@
       <c r="T271" s="9"/>
       <c r="U271" s="9"/>
     </row>
-    <row r="272" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A272" s="9"/>
       <c r="B272" s="55"/>
       <c r="C272" s="55"/>
@@ -10725,7 +10740,7 @@
       <c r="T272" s="9"/>
       <c r="U272" s="9"/>
     </row>
-    <row r="273" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A273" s="9"/>
       <c r="B273" s="55"/>
       <c r="C273" s="55"/>
@@ -10748,7 +10763,7 @@
       <c r="T273" s="9"/>
       <c r="U273" s="9"/>
     </row>
-    <row r="274" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A274" s="9"/>
       <c r="B274" s="55"/>
       <c r="C274" s="55"/>
@@ -10771,7 +10786,7 @@
       <c r="T274" s="9"/>
       <c r="U274" s="9"/>
     </row>
-    <row r="275" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A275" s="9"/>
       <c r="B275" s="55"/>
       <c r="C275" s="55"/>
@@ -10794,7 +10809,7 @@
       <c r="T275" s="9"/>
       <c r="U275" s="9"/>
     </row>
-    <row r="276" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A276" s="9"/>
       <c r="B276" s="55"/>
       <c r="C276" s="55"/>
@@ -10817,7 +10832,7 @@
       <c r="T276" s="9"/>
       <c r="U276" s="9"/>
     </row>
-    <row r="277" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A277" s="9"/>
       <c r="B277" s="55"/>
       <c r="C277" s="55"/>
@@ -10840,7 +10855,7 @@
       <c r="T277" s="9"/>
       <c r="U277" s="9"/>
     </row>
-    <row r="278" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A278" s="9"/>
       <c r="B278" s="55"/>
       <c r="C278" s="55"/>
@@ -10863,7 +10878,7 @@
       <c r="T278" s="9"/>
       <c r="U278" s="9"/>
     </row>
-    <row r="279" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A279" s="9"/>
       <c r="B279" s="55"/>
       <c r="C279" s="55"/>
@@ -10886,7 +10901,7 @@
       <c r="T279" s="9"/>
       <c r="U279" s="9"/>
     </row>
-    <row r="280" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A280" s="9"/>
       <c r="B280" s="55"/>
       <c r="C280" s="55"/>
@@ -10909,7 +10924,7 @@
       <c r="T280" s="9"/>
       <c r="U280" s="9"/>
     </row>
-    <row r="281" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A281" s="9"/>
       <c r="B281" s="55"/>
       <c r="C281" s="55"/>
@@ -10932,7 +10947,7 @@
       <c r="T281" s="9"/>
       <c r="U281" s="9"/>
     </row>
-    <row r="282" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A282" s="9"/>
       <c r="B282" s="55"/>
       <c r="C282" s="55"/>
@@ -10955,7 +10970,7 @@
       <c r="T282" s="9"/>
       <c r="U282" s="9"/>
     </row>
-    <row r="283" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A283" s="9"/>
       <c r="B283" s="55"/>
       <c r="C283" s="55"/>
@@ -10978,7 +10993,7 @@
       <c r="T283" s="9"/>
       <c r="U283" s="9"/>
     </row>
-    <row r="284" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A284" s="9"/>
       <c r="B284" s="55"/>
       <c r="C284" s="55"/>
@@ -11001,7 +11016,7 @@
       <c r="T284" s="9"/>
       <c r="U284" s="9"/>
     </row>
-    <row r="285" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A285" s="9"/>
       <c r="B285" s="55"/>
       <c r="C285" s="55"/>
@@ -11024,7 +11039,7 @@
       <c r="T285" s="9"/>
       <c r="U285" s="9"/>
     </row>
-    <row r="286" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A286" s="9"/>
       <c r="B286" s="55"/>
       <c r="C286" s="55"/>
@@ -11047,7 +11062,7 @@
       <c r="T286" s="9"/>
       <c r="U286" s="9"/>
     </row>
-    <row r="287" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A287" s="9"/>
       <c r="B287" s="55"/>
       <c r="C287" s="55"/>
@@ -11070,7 +11085,7 @@
       <c r="T287" s="9"/>
       <c r="U287" s="9"/>
     </row>
-    <row r="288" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A288" s="9"/>
       <c r="B288" s="55"/>
       <c r="C288" s="55"/>
@@ -11093,7 +11108,7 @@
       <c r="T288" s="9"/>
       <c r="U288" s="9"/>
     </row>
-    <row r="289" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A289" s="9"/>
       <c r="B289" s="55"/>
       <c r="C289" s="55"/>
@@ -11116,7 +11131,7 @@
       <c r="T289" s="9"/>
       <c r="U289" s="9"/>
     </row>
-    <row r="290" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A290" s="9"/>
       <c r="B290" s="55"/>
       <c r="C290" s="55"/>
@@ -11139,7 +11154,7 @@
       <c r="T290" s="9"/>
       <c r="U290" s="9"/>
     </row>
-    <row r="291" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A291" s="9"/>
       <c r="B291" s="55"/>
       <c r="C291" s="55"/>
@@ -11162,7 +11177,7 @@
       <c r="T291" s="9"/>
       <c r="U291" s="9"/>
     </row>
-    <row r="292" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A292" s="9"/>
       <c r="B292" s="55"/>
       <c r="C292" s="55"/>
@@ -11185,7 +11200,7 @@
       <c r="T292" s="9"/>
       <c r="U292" s="9"/>
     </row>
-    <row r="293" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A293" s="9"/>
       <c r="B293" s="55"/>
       <c r="C293" s="55"/>
@@ -11208,7 +11223,7 @@
       <c r="T293" s="9"/>
       <c r="U293" s="9"/>
     </row>
-    <row r="294" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A294" s="9"/>
       <c r="B294" s="55"/>
       <c r="C294" s="55"/>
@@ -11231,7 +11246,7 @@
       <c r="T294" s="9"/>
       <c r="U294" s="9"/>
     </row>
-    <row r="295" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A295" s="9"/>
       <c r="B295" s="55"/>
       <c r="C295" s="55"/>
@@ -11254,7 +11269,7 @@
       <c r="T295" s="9"/>
       <c r="U295" s="9"/>
     </row>
-    <row r="296" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A296" s="9"/>
       <c r="B296" s="55"/>
       <c r="C296" s="55"/>
@@ -11277,7 +11292,7 @@
       <c r="T296" s="9"/>
       <c r="U296" s="9"/>
     </row>
-    <row r="297" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A297" s="9"/>
       <c r="B297" s="55"/>
       <c r="C297" s="55"/>
@@ -11300,7 +11315,7 @@
       <c r="T297" s="9"/>
       <c r="U297" s="9"/>
     </row>
-    <row r="298" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A298" s="9"/>
       <c r="B298" s="55"/>
       <c r="C298" s="55"/>
@@ -11323,7 +11338,7 @@
       <c r="T298" s="9"/>
       <c r="U298" s="9"/>
     </row>
-    <row r="299" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A299" s="9"/>
       <c r="B299" s="55"/>
       <c r="C299" s="55"/>
@@ -11346,7 +11361,7 @@
       <c r="T299" s="9"/>
       <c r="U299" s="9"/>
     </row>
-    <row r="300" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A300" s="9"/>
       <c r="B300" s="55"/>
       <c r="C300" s="55"/>
@@ -11369,7 +11384,7 @@
       <c r="T300" s="9"/>
       <c r="U300" s="9"/>
     </row>
-    <row r="301" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A301" s="9"/>
       <c r="B301" s="55"/>
       <c r="C301" s="55"/>
@@ -11392,7 +11407,7 @@
       <c r="T301" s="9"/>
       <c r="U301" s="9"/>
     </row>
-    <row r="302" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A302" s="9"/>
       <c r="B302" s="55"/>
       <c r="C302" s="55"/>
@@ -11415,7 +11430,7 @@
       <c r="T302" s="9"/>
       <c r="U302" s="9"/>
     </row>
-    <row r="303" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A303" s="9"/>
       <c r="B303" s="55"/>
       <c r="C303" s="55"/>
@@ -11438,7 +11453,7 @@
       <c r="T303" s="9"/>
       <c r="U303" s="9"/>
     </row>
-    <row r="304" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A304" s="9"/>
       <c r="B304" s="55"/>
       <c r="C304" s="55"/>
@@ -11461,7 +11476,7 @@
       <c r="T304" s="9"/>
       <c r="U304" s="9"/>
     </row>
-    <row r="305" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A305" s="9"/>
       <c r="B305" s="55"/>
       <c r="C305" s="55"/>
@@ -11484,7 +11499,7 @@
       <c r="T305" s="9"/>
       <c r="U305" s="9"/>
     </row>
-    <row r="306" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A306" s="9"/>
       <c r="B306" s="55"/>
       <c r="C306" s="55"/>
@@ -11507,7 +11522,7 @@
       <c r="T306" s="9"/>
       <c r="U306" s="9"/>
     </row>
-    <row r="307" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A307" s="9"/>
       <c r="B307" s="55"/>
       <c r="C307" s="55"/>
@@ -11530,7 +11545,7 @@
       <c r="T307" s="9"/>
       <c r="U307" s="9"/>
     </row>
-    <row r="308" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A308" s="9"/>
       <c r="B308" s="55"/>
       <c r="C308" s="55"/>
@@ -11553,7 +11568,7 @@
       <c r="T308" s="9"/>
       <c r="U308" s="9"/>
     </row>
-    <row r="309" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A309" s="9"/>
       <c r="B309" s="55"/>
       <c r="C309" s="55"/>
@@ -11576,7 +11591,7 @@
       <c r="T309" s="9"/>
       <c r="U309" s="9"/>
     </row>
-    <row r="310" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A310" s="9"/>
       <c r="B310" s="55"/>
       <c r="C310" s="55"/>
@@ -11599,7 +11614,7 @@
       <c r="T310" s="9"/>
       <c r="U310" s="9"/>
     </row>
-    <row r="311" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A311" s="9"/>
       <c r="B311" s="55"/>
       <c r="C311" s="55"/>
@@ -11622,7 +11637,7 @@
       <c r="T311" s="9"/>
       <c r="U311" s="9"/>
     </row>
-    <row r="312" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A312" s="9"/>
       <c r="B312" s="55"/>
       <c r="C312" s="55"/>
@@ -11645,7 +11660,7 @@
       <c r="T312" s="9"/>
       <c r="U312" s="9"/>
     </row>
-    <row r="313" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A313" s="9"/>
       <c r="B313" s="55"/>
       <c r="C313" s="55"/>
@@ -11668,7 +11683,7 @@
       <c r="T313" s="9"/>
       <c r="U313" s="9"/>
     </row>
-    <row r="314" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A314" s="9"/>
       <c r="B314" s="55"/>
       <c r="C314" s="55"/>
@@ -11691,7 +11706,7 @@
       <c r="T314" s="9"/>
       <c r="U314" s="9"/>
     </row>
-    <row r="315" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A315" s="9"/>
       <c r="B315" s="55"/>
       <c r="C315" s="55"/>
@@ -11714,7 +11729,7 @@
       <c r="T315" s="9"/>
       <c r="U315" s="9"/>
     </row>
-    <row r="316" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A316" s="9"/>
       <c r="B316" s="55"/>
       <c r="C316" s="55"/>
@@ -11737,7 +11752,7 @@
       <c r="T316" s="9"/>
       <c r="U316" s="9"/>
     </row>
-    <row r="317" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A317" s="9"/>
       <c r="B317" s="55"/>
       <c r="C317" s="55"/>
@@ -11760,7 +11775,7 @@
       <c r="T317" s="9"/>
       <c r="U317" s="9"/>
     </row>
-    <row r="318" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A318" s="9"/>
       <c r="B318" s="55"/>
       <c r="C318" s="55"/>
@@ -11783,7 +11798,7 @@
       <c r="T318" s="9"/>
       <c r="U318" s="9"/>
     </row>
-    <row r="319" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A319" s="9"/>
       <c r="B319" s="55"/>
       <c r="C319" s="55"/>
@@ -11806,7 +11821,7 @@
       <c r="T319" s="9"/>
       <c r="U319" s="9"/>
     </row>
-    <row r="320" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A320" s="9"/>
       <c r="B320" s="55"/>
       <c r="C320" s="55"/>
@@ -11829,7 +11844,7 @@
       <c r="T320" s="9"/>
       <c r="U320" s="9"/>
     </row>
-    <row r="321" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A321" s="9"/>
       <c r="B321" s="55"/>
       <c r="C321" s="55"/>
@@ -11852,7 +11867,7 @@
       <c r="T321" s="9"/>
       <c r="U321" s="9"/>
     </row>
-    <row r="322" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A322" s="9"/>
       <c r="B322" s="55"/>
       <c r="C322" s="55"/>
@@ -11875,7 +11890,7 @@
       <c r="T322" s="9"/>
       <c r="U322" s="9"/>
     </row>
-    <row r="323" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A323" s="9"/>
       <c r="B323" s="55"/>
       <c r="C323" s="55"/>
@@ -11898,7 +11913,7 @@
       <c r="T323" s="9"/>
       <c r="U323" s="9"/>
     </row>
-    <row r="324" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A324" s="9"/>
       <c r="B324" s="55"/>
       <c r="C324" s="55"/>
@@ -11921,7 +11936,7 @@
       <c r="T324" s="9"/>
       <c r="U324" s="9"/>
     </row>
-    <row r="325" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A325" s="9"/>
       <c r="B325" s="55"/>
       <c r="C325" s="55"/>
@@ -11944,7 +11959,7 @@
       <c r="T325" s="9"/>
       <c r="U325" s="9"/>
     </row>
-    <row r="326" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A326" s="9"/>
       <c r="B326" s="55"/>
       <c r="C326" s="55"/>
@@ -11967,7 +11982,7 @@
       <c r="T326" s="9"/>
       <c r="U326" s="9"/>
     </row>
-    <row r="327" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A327" s="9"/>
       <c r="B327" s="55"/>
       <c r="C327" s="55"/>
@@ -11990,7 +12005,7 @@
       <c r="T327" s="9"/>
       <c r="U327" s="9"/>
     </row>
-    <row r="328" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A328" s="9"/>
       <c r="B328" s="55"/>
       <c r="C328" s="55"/>
@@ -12013,7 +12028,7 @@
       <c r="T328" s="9"/>
       <c r="U328" s="9"/>
     </row>
-    <row r="329" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A329" s="9"/>
       <c r="B329" s="55"/>
       <c r="C329" s="55"/>
@@ -12036,7 +12051,7 @@
       <c r="T329" s="9"/>
       <c r="U329" s="9"/>
     </row>
-    <row r="330" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A330" s="9"/>
       <c r="B330" s="55"/>
       <c r="C330" s="55"/>
@@ -12059,7 +12074,7 @@
       <c r="T330" s="9"/>
       <c r="U330" s="9"/>
     </row>
-    <row r="331" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A331" s="9"/>
       <c r="B331" s="55"/>
       <c r="C331" s="55"/>
@@ -12082,7 +12097,7 @@
       <c r="T331" s="9"/>
       <c r="U331" s="9"/>
     </row>
-    <row r="332" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A332" s="9"/>
       <c r="B332" s="55"/>
       <c r="C332" s="55"/>
@@ -12105,7 +12120,7 @@
       <c r="T332" s="9"/>
       <c r="U332" s="9"/>
     </row>
-    <row r="333" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A333" s="9"/>
       <c r="B333" s="55"/>
       <c r="C333" s="55"/>
@@ -12128,7 +12143,7 @@
       <c r="T333" s="9"/>
       <c r="U333" s="9"/>
     </row>
-    <row r="334" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A334" s="9"/>
       <c r="B334" s="55"/>
       <c r="C334" s="55"/>
@@ -12151,7 +12166,7 @@
       <c r="T334" s="9"/>
       <c r="U334" s="9"/>
     </row>
-    <row r="335" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A335" s="9"/>
       <c r="B335" s="55"/>
       <c r="C335" s="55"/>
@@ -12174,7 +12189,7 @@
       <c r="T335" s="9"/>
       <c r="U335" s="9"/>
     </row>
-    <row r="336" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A336" s="9"/>
       <c r="B336" s="55"/>
       <c r="C336" s="55"/>
@@ -12197,7 +12212,7 @@
       <c r="T336" s="9"/>
       <c r="U336" s="9"/>
     </row>
-    <row r="337" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A337" s="9"/>
       <c r="B337" s="55"/>
       <c r="C337" s="55"/>
@@ -12220,7 +12235,7 @@
       <c r="T337" s="9"/>
       <c r="U337" s="9"/>
     </row>
-    <row r="338" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A338" s="9"/>
       <c r="B338" s="55"/>
       <c r="C338" s="55"/>
@@ -12243,7 +12258,7 @@
       <c r="T338" s="9"/>
       <c r="U338" s="9"/>
     </row>
-    <row r="339" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A339" s="9"/>
       <c r="B339" s="55"/>
       <c r="C339" s="55"/>
@@ -12266,7 +12281,7 @@
       <c r="T339" s="9"/>
       <c r="U339" s="9"/>
     </row>
-    <row r="340" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A340" s="9"/>
       <c r="B340" s="55"/>
       <c r="C340" s="55"/>
@@ -12289,7 +12304,7 @@
       <c r="T340" s="9"/>
       <c r="U340" s="9"/>
     </row>
-    <row r="341" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A341" s="9"/>
       <c r="B341" s="55"/>
       <c r="C341" s="55"/>
@@ -12312,7 +12327,7 @@
       <c r="T341" s="9"/>
       <c r="U341" s="9"/>
     </row>
-    <row r="342" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A342" s="9"/>
       <c r="B342" s="55"/>
       <c r="C342" s="55"/>
@@ -12335,7 +12350,7 @@
       <c r="T342" s="9"/>
       <c r="U342" s="9"/>
     </row>
-    <row r="343" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A343" s="9"/>
       <c r="B343" s="55"/>
       <c r="C343" s="55"/>
@@ -12358,7 +12373,7 @@
       <c r="T343" s="9"/>
       <c r="U343" s="9"/>
     </row>
-    <row r="344" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A344" s="9"/>
       <c r="B344" s="55"/>
       <c r="C344" s="55"/>
@@ -12381,7 +12396,7 @@
       <c r="T344" s="9"/>
       <c r="U344" s="9"/>
     </row>
-    <row r="345" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A345" s="9"/>
       <c r="B345" s="55"/>
       <c r="C345" s="55"/>
@@ -12404,7 +12419,7 @@
       <c r="T345" s="9"/>
       <c r="U345" s="9"/>
     </row>
-    <row r="346" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A346" s="9"/>
       <c r="B346" s="55"/>
       <c r="C346" s="55"/>
@@ -12427,7 +12442,7 @@
       <c r="T346" s="9"/>
       <c r="U346" s="9"/>
     </row>
-    <row r="347" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A347" s="9"/>
       <c r="B347" s="55"/>
       <c r="C347" s="55"/>
@@ -12450,7 +12465,7 @@
       <c r="T347" s="9"/>
       <c r="U347" s="9"/>
     </row>
-    <row r="348" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A348" s="9"/>
       <c r="B348" s="55"/>
       <c r="C348" s="55"/>
@@ -12473,7 +12488,7 @@
       <c r="T348" s="9"/>
       <c r="U348" s="9"/>
     </row>
-    <row r="349" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A349" s="9"/>
       <c r="B349" s="55"/>
       <c r="C349" s="55"/>
@@ -12496,7 +12511,7 @@
       <c r="T349" s="9"/>
       <c r="U349" s="9"/>
     </row>
-    <row r="350" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A350" s="9"/>
       <c r="B350" s="55"/>
       <c r="C350" s="55"/>
@@ -12519,7 +12534,7 @@
       <c r="T350" s="9"/>
       <c r="U350" s="9"/>
     </row>
-    <row r="351" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A351" s="9"/>
       <c r="B351" s="55"/>
       <c r="C351" s="55"/>
@@ -12542,7 +12557,7 @@
       <c r="T351" s="9"/>
       <c r="U351" s="9"/>
     </row>
-    <row r="352" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A352" s="9"/>
       <c r="B352" s="55"/>
       <c r="C352" s="55"/>
@@ -12565,7 +12580,7 @@
       <c r="T352" s="9"/>
       <c r="U352" s="9"/>
     </row>
-    <row r="353" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A353" s="9"/>
       <c r="B353" s="55"/>
       <c r="C353" s="55"/>
@@ -12588,7 +12603,7 @@
       <c r="T353" s="9"/>
       <c r="U353" s="9"/>
     </row>
-    <row r="354" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A354" s="9"/>
       <c r="B354" s="55"/>
       <c r="C354" s="55"/>
@@ -12611,7 +12626,7 @@
       <c r="T354" s="9"/>
       <c r="U354" s="9"/>
     </row>
-    <row r="355" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A355" s="9"/>
       <c r="B355" s="55"/>
       <c r="C355" s="55"/>
@@ -12634,7 +12649,7 @@
       <c r="T355" s="9"/>
       <c r="U355" s="9"/>
     </row>
-    <row r="356" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A356" s="9"/>
       <c r="B356" s="55"/>
       <c r="C356" s="55"/>
@@ -12657,7 +12672,7 @@
       <c r="T356" s="9"/>
       <c r="U356" s="9"/>
     </row>
-    <row r="357" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A357" s="9"/>
       <c r="B357" s="55"/>
       <c r="C357" s="55"/>
@@ -12680,7 +12695,7 @@
       <c r="T357" s="9"/>
       <c r="U357" s="9"/>
     </row>
-    <row r="358" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A358" s="9"/>
       <c r="B358" s="55"/>
       <c r="C358" s="55"/>
@@ -12703,7 +12718,7 @@
       <c r="T358" s="9"/>
       <c r="U358" s="9"/>
     </row>
-    <row r="359" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A359" s="9"/>
       <c r="B359" s="55"/>
       <c r="C359" s="55"/>
@@ -12726,7 +12741,7 @@
       <c r="T359" s="9"/>
       <c r="U359" s="9"/>
     </row>
-    <row r="360" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A360" s="9"/>
       <c r="B360" s="55"/>
       <c r="C360" s="55"/>
@@ -12749,7 +12764,7 @@
       <c r="T360" s="9"/>
       <c r="U360" s="9"/>
     </row>
-    <row r="361" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A361" s="9"/>
       <c r="B361" s="55"/>
       <c r="C361" s="55"/>
@@ -12772,7 +12787,7 @@
       <c r="T361" s="9"/>
       <c r="U361" s="9"/>
     </row>
-    <row r="362" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A362" s="9"/>
       <c r="B362" s="55"/>
       <c r="C362" s="55"/>
@@ -12795,7 +12810,7 @@
       <c r="T362" s="9"/>
       <c r="U362" s="9"/>
     </row>
-    <row r="363" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A363" s="9"/>
       <c r="B363" s="55"/>
       <c r="C363" s="55"/>
@@ -12818,7 +12833,7 @@
       <c r="T363" s="9"/>
       <c r="U363" s="9"/>
     </row>
-    <row r="364" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A364" s="9"/>
       <c r="B364" s="55"/>
       <c r="C364" s="55"/>
@@ -12841,7 +12856,7 @@
       <c r="T364" s="9"/>
       <c r="U364" s="9"/>
     </row>
-    <row r="365" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A365" s="9"/>
       <c r="B365" s="55"/>
       <c r="C365" s="55"/>
@@ -12864,7 +12879,7 @@
       <c r="T365" s="9"/>
       <c r="U365" s="9"/>
     </row>
-    <row r="366" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A366" s="9"/>
       <c r="B366" s="55"/>
       <c r="C366" s="55"/>
@@ -12887,7 +12902,7 @@
       <c r="T366" s="9"/>
       <c r="U366" s="9"/>
     </row>
-    <row r="367" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A367" s="9"/>
       <c r="B367" s="55"/>
       <c r="C367" s="55"/>
@@ -12910,7 +12925,7 @@
       <c r="T367" s="9"/>
       <c r="U367" s="9"/>
     </row>
-    <row r="368" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A368" s="9"/>
       <c r="B368" s="55"/>
       <c r="C368" s="55"/>
@@ -12933,7 +12948,7 @@
       <c r="T368" s="9"/>
       <c r="U368" s="9"/>
     </row>
-    <row r="369" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A369" s="9"/>
       <c r="B369" s="55"/>
       <c r="C369" s="55"/>
@@ -12956,7 +12971,7 @@
       <c r="T369" s="9"/>
       <c r="U369" s="9"/>
     </row>
-    <row r="370" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A370" s="9"/>
       <c r="B370" s="55"/>
       <c r="C370" s="55"/>
@@ -12979,7 +12994,7 @@
       <c r="T370" s="9"/>
       <c r="U370" s="9"/>
     </row>
-    <row r="371" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A371" s="9"/>
       <c r="B371" s="55"/>
       <c r="C371" s="55"/>
@@ -13002,7 +13017,7 @@
       <c r="T371" s="9"/>
       <c r="U371" s="9"/>
     </row>
-    <row r="372" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A372" s="9"/>
       <c r="B372" s="55"/>
       <c r="C372" s="55"/>
@@ -13025,7 +13040,7 @@
       <c r="T372" s="9"/>
       <c r="U372" s="9"/>
     </row>
-    <row r="373" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A373" s="9"/>
       <c r="B373" s="55"/>
       <c r="C373" s="55"/>
@@ -13048,7 +13063,7 @@
       <c r="T373" s="9"/>
       <c r="U373" s="9"/>
     </row>
-    <row r="374" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A374" s="9"/>
       <c r="B374" s="55"/>
       <c r="C374" s="55"/>
@@ -13071,7 +13086,7 @@
       <c r="T374" s="9"/>
       <c r="U374" s="9"/>
     </row>
-    <row r="375" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A375" s="9"/>
       <c r="B375" s="55"/>
       <c r="C375" s="55"/>
@@ -13094,7 +13109,7 @@
       <c r="T375" s="9"/>
       <c r="U375" s="9"/>
     </row>
-    <row r="376" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A376" s="9"/>
       <c r="B376" s="55"/>
       <c r="C376" s="55"/>
@@ -13117,7 +13132,7 @@
       <c r="T376" s="9"/>
       <c r="U376" s="9"/>
     </row>
-    <row r="377" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A377" s="9"/>
       <c r="B377" s="55"/>
       <c r="C377" s="55"/>
@@ -13140,7 +13155,7 @@
       <c r="T377" s="9"/>
       <c r="U377" s="9"/>
     </row>
-    <row r="378" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A378" s="9"/>
       <c r="B378" s="55"/>
       <c r="C378" s="55"/>
@@ -13163,7 +13178,7 @@
       <c r="T378" s="9"/>
       <c r="U378" s="9"/>
     </row>
-    <row r="379" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A379" s="9"/>
       <c r="B379" s="55"/>
       <c r="C379" s="55"/>
@@ -13186,7 +13201,7 @@
       <c r="T379" s="9"/>
       <c r="U379" s="9"/>
     </row>
-    <row r="380" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A380" s="9"/>
       <c r="B380" s="55"/>
       <c r="C380" s="55"/>
@@ -13209,7 +13224,7 @@
       <c r="T380" s="9"/>
       <c r="U380" s="9"/>
     </row>
-    <row r="381" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A381" s="9"/>
       <c r="B381" s="55"/>
       <c r="C381" s="55"/>
@@ -13232,7 +13247,7 @@
       <c r="T381" s="9"/>
       <c r="U381" s="9"/>
     </row>
-    <row r="382" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A382" s="9"/>
       <c r="B382" s="55"/>
       <c r="C382" s="55"/>
@@ -13255,7 +13270,7 @@
       <c r="T382" s="9"/>
       <c r="U382" s="9"/>
     </row>
-    <row r="383" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A383" s="9"/>
       <c r="B383" s="55"/>
       <c r="C383" s="55"/>
@@ -13278,7 +13293,7 @@
       <c r="T383" s="9"/>
       <c r="U383" s="9"/>
     </row>
-    <row r="384" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A384" s="9"/>
       <c r="B384" s="55"/>
       <c r="C384" s="55"/>
@@ -13301,7 +13316,7 @@
       <c r="T384" s="9"/>
       <c r="U384" s="9"/>
     </row>
-    <row r="385" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A385" s="9"/>
       <c r="B385" s="55"/>
       <c r="C385" s="55"/>
@@ -13324,7 +13339,7 @@
       <c r="T385" s="9"/>
       <c r="U385" s="9"/>
     </row>
-    <row r="386" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A386" s="9"/>
       <c r="B386" s="55"/>
       <c r="C386" s="55"/>
@@ -13347,7 +13362,7 @@
       <c r="T386" s="9"/>
       <c r="U386" s="9"/>
     </row>
-    <row r="387" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A387" s="9"/>
       <c r="B387" s="55"/>
       <c r="C387" s="55"/>
@@ -13370,7 +13385,7 @@
       <c r="T387" s="9"/>
       <c r="U387" s="9"/>
     </row>
-    <row r="388" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A388" s="9"/>
       <c r="B388" s="55"/>
       <c r="C388" s="55"/>
@@ -13393,7 +13408,7 @@
       <c r="T388" s="9"/>
       <c r="U388" s="9"/>
     </row>
-    <row r="389" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A389" s="9"/>
       <c r="B389" s="55"/>
       <c r="C389" s="55"/>
@@ -13416,7 +13431,7 @@
       <c r="T389" s="9"/>
       <c r="U389" s="9"/>
     </row>
-    <row r="390" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A390" s="9"/>
       <c r="B390" s="55"/>
       <c r="C390" s="55"/>
@@ -13439,7 +13454,7 @@
       <c r="T390" s="9"/>
       <c r="U390" s="9"/>
     </row>
-    <row r="391" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A391" s="9"/>
       <c r="B391" s="55"/>
       <c r="C391" s="55"/>
@@ -13462,7 +13477,7 @@
       <c r="T391" s="9"/>
       <c r="U391" s="9"/>
     </row>
-    <row r="392" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A392" s="9"/>
       <c r="B392" s="55"/>
       <c r="C392" s="55"/>
@@ -13485,7 +13500,7 @@
       <c r="T392" s="9"/>
       <c r="U392" s="9"/>
     </row>
-    <row r="393" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A393" s="9"/>
       <c r="B393" s="55"/>
       <c r="C393" s="55"/>
@@ -13508,7 +13523,7 @@
       <c r="T393" s="9"/>
       <c r="U393" s="9"/>
     </row>
-    <row r="394" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A394" s="9"/>
       <c r="B394" s="55"/>
       <c r="C394" s="55"/>
@@ -13531,7 +13546,7 @@
       <c r="T394" s="9"/>
       <c r="U394" s="9"/>
     </row>
-    <row r="395" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A395" s="9"/>
       <c r="B395" s="55"/>
       <c r="C395" s="55"/>
@@ -13554,7 +13569,7 @@
       <c r="T395" s="9"/>
       <c r="U395" s="9"/>
     </row>
-    <row r="396" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A396" s="9"/>
       <c r="B396" s="55"/>
       <c r="C396" s="55"/>
@@ -13577,7 +13592,7 @@
       <c r="T396" s="9"/>
       <c r="U396" s="9"/>
     </row>
-    <row r="397" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A397" s="9"/>
       <c r="B397" s="55"/>
       <c r="C397" s="55"/>
@@ -13600,7 +13615,7 @@
       <c r="T397" s="9"/>
       <c r="U397" s="9"/>
     </row>
-    <row r="398" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A398" s="9"/>
       <c r="B398" s="55"/>
       <c r="C398" s="55"/>
@@ -13623,7 +13638,7 @@
       <c r="T398" s="9"/>
       <c r="U398" s="9"/>
     </row>
-    <row r="399" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A399" s="9"/>
       <c r="B399" s="55"/>
       <c r="C399" s="55"/>
@@ -13646,7 +13661,7 @@
       <c r="T399" s="9"/>
       <c r="U399" s="9"/>
     </row>
-    <row r="400" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A400" s="9"/>
       <c r="B400" s="55"/>
       <c r="C400" s="55"/>
@@ -13669,7 +13684,7 @@
       <c r="T400" s="9"/>
       <c r="U400" s="9"/>
     </row>
-    <row r="401" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A401" s="9"/>
       <c r="B401" s="55"/>
       <c r="C401" s="55"/>
@@ -13692,7 +13707,7 @@
       <c r="T401" s="9"/>
       <c r="U401" s="9"/>
     </row>
-    <row r="402" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A402" s="9"/>
       <c r="B402" s="55"/>
       <c r="C402" s="55"/>
@@ -13715,7 +13730,7 @@
       <c r="T402" s="9"/>
       <c r="U402" s="9"/>
     </row>
-    <row r="403" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A403" s="9"/>
       <c r="B403" s="55"/>
       <c r="C403" s="55"/>
@@ -13738,7 +13753,7 @@
       <c r="T403" s="9"/>
       <c r="U403" s="9"/>
     </row>
-    <row r="404" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A404" s="9"/>
       <c r="B404" s="55"/>
       <c r="C404" s="55"/>
@@ -13761,7 +13776,7 @@
       <c r="T404" s="9"/>
       <c r="U404" s="9"/>
     </row>
-    <row r="405" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A405" s="9"/>
       <c r="B405" s="55"/>
       <c r="C405" s="55"/>
@@ -13784,7 +13799,7 @@
       <c r="T405" s="9"/>
       <c r="U405" s="9"/>
     </row>
-    <row r="406" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A406" s="9"/>
       <c r="B406" s="55"/>
       <c r="C406" s="55"/>
@@ -13807,7 +13822,7 @@
       <c r="T406" s="9"/>
       <c r="U406" s="9"/>
     </row>
-    <row r="407" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A407" s="9"/>
       <c r="B407" s="55"/>
       <c r="C407" s="55"/>
@@ -13830,7 +13845,7 @@
       <c r="T407" s="9"/>
       <c r="U407" s="9"/>
     </row>
-    <row r="408" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A408" s="9"/>
       <c r="B408" s="55"/>
       <c r="C408" s="55"/>
@@ -13853,7 +13868,7 @@
       <c r="T408" s="9"/>
       <c r="U408" s="9"/>
     </row>
-    <row r="409" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A409" s="9"/>
       <c r="B409" s="55"/>
       <c r="C409" s="55"/>
@@ -13876,7 +13891,7 @@
       <c r="T409" s="9"/>
       <c r="U409" s="9"/>
     </row>
-    <row r="410" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A410" s="9"/>
       <c r="B410" s="55"/>
       <c r="C410" s="55"/>
@@ -13899,7 +13914,7 @@
       <c r="T410" s="9"/>
       <c r="U410" s="9"/>
     </row>
-    <row r="411" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A411" s="9"/>
       <c r="B411" s="55"/>
       <c r="C411" s="55"/>
@@ -13922,7 +13937,7 @@
       <c r="T411" s="9"/>
       <c r="U411" s="9"/>
     </row>
-    <row r="412" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A412" s="9"/>
       <c r="B412" s="55"/>
       <c r="C412" s="55"/>
@@ -13945,7 +13960,7 @@
       <c r="T412" s="9"/>
       <c r="U412" s="9"/>
     </row>
-    <row r="413" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A413" s="9"/>
       <c r="B413" s="55"/>
       <c r="C413" s="55"/>
@@ -13968,7 +13983,7 @@
       <c r="T413" s="9"/>
       <c r="U413" s="9"/>
     </row>
-    <row r="414" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A414" s="9"/>
       <c r="B414" s="55"/>
       <c r="C414" s="55"/>
@@ -13991,7 +14006,7 @@
       <c r="T414" s="9"/>
       <c r="U414" s="9"/>
     </row>
-    <row r="415" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A415" s="9"/>
       <c r="B415" s="55"/>
       <c r="C415" s="55"/>
@@ -14014,7 +14029,7 @@
       <c r="T415" s="9"/>
       <c r="U415" s="9"/>
     </row>
-    <row r="416" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A416" s="9"/>
       <c r="B416" s="55"/>
       <c r="C416" s="55"/>
@@ -14037,7 +14052,7 @@
       <c r="T416" s="9"/>
       <c r="U416" s="9"/>
     </row>
-    <row r="417" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A417" s="9"/>
       <c r="B417" s="55"/>
       <c r="C417" s="55"/>
@@ -14060,7 +14075,7 @@
       <c r="T417" s="9"/>
       <c r="U417" s="9"/>
     </row>
-    <row r="418" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A418" s="9"/>
       <c r="B418" s="55"/>
       <c r="C418" s="55"/>
@@ -14083,7 +14098,7 @@
       <c r="T418" s="9"/>
       <c r="U418" s="9"/>
     </row>
-    <row r="419" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A419" s="9"/>
       <c r="B419" s="55"/>
       <c r="C419" s="55"/>
@@ -14106,7 +14121,7 @@
       <c r="T419" s="9"/>
       <c r="U419" s="9"/>
     </row>
-    <row r="420" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A420" s="9"/>
       <c r="B420" s="55"/>
       <c r="C420" s="55"/>
@@ -14129,7 +14144,7 @@
       <c r="T420" s="9"/>
       <c r="U420" s="9"/>
     </row>
-    <row r="421" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A421" s="9"/>
       <c r="B421" s="55"/>
       <c r="C421" s="55"/>
@@ -14152,7 +14167,7 @@
       <c r="T421" s="9"/>
       <c r="U421" s="9"/>
     </row>
-    <row r="422" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A422" s="9"/>
       <c r="B422" s="55"/>
       <c r="C422" s="55"/>
@@ -14175,7 +14190,7 @@
       <c r="T422" s="9"/>
       <c r="U422" s="9"/>
     </row>
-    <row r="423" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A423" s="9"/>
       <c r="B423" s="55"/>
       <c r="C423" s="55"/>
@@ -14198,7 +14213,7 @@
       <c r="T423" s="9"/>
       <c r="U423" s="9"/>
     </row>
-    <row r="424" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A424" s="9"/>
       <c r="B424" s="55"/>
       <c r="C424" s="55"/>
@@ -14221,7 +14236,7 @@
       <c r="T424" s="9"/>
       <c r="U424" s="9"/>
     </row>
-    <row r="425" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A425" s="9"/>
       <c r="B425" s="55"/>
       <c r="C425" s="55"/>
@@ -14244,7 +14259,7 @@
       <c r="T425" s="9"/>
       <c r="U425" s="9"/>
     </row>
-    <row r="426" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A426" s="9"/>
       <c r="B426" s="55"/>
       <c r="C426" s="55"/>
@@ -14267,7 +14282,7 @@
       <c r="T426" s="9"/>
       <c r="U426" s="9"/>
     </row>
-    <row r="427" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A427" s="9"/>
       <c r="B427" s="55"/>
       <c r="C427" s="55"/>
@@ -14290,7 +14305,7 @@
       <c r="T427" s="9"/>
       <c r="U427" s="9"/>
     </row>
-    <row r="428" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A428" s="9"/>
       <c r="B428" s="55"/>
       <c r="C428" s="55"/>
@@ -14313,7 +14328,7 @@
       <c r="T428" s="9"/>
       <c r="U428" s="9"/>
     </row>
-    <row r="429" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A429" s="9"/>
       <c r="B429" s="55"/>
       <c r="C429" s="55"/>
@@ -14336,7 +14351,7 @@
       <c r="T429" s="9"/>
       <c r="U429" s="9"/>
     </row>
-    <row r="430" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A430" s="9"/>
       <c r="B430" s="55"/>
       <c r="C430" s="55"/>
@@ -14359,7 +14374,7 @@
       <c r="T430" s="9"/>
       <c r="U430" s="9"/>
     </row>
-    <row r="431" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A431" s="9"/>
       <c r="B431" s="55"/>
       <c r="C431" s="55"/>
@@ -14382,7 +14397,7 @@
       <c r="T431" s="9"/>
       <c r="U431" s="9"/>
     </row>
-    <row r="432" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A432" s="9"/>
       <c r="B432" s="55"/>
       <c r="C432" s="55"/>
@@ -14405,7 +14420,7 @@
       <c r="T432" s="9"/>
       <c r="U432" s="9"/>
     </row>
-    <row r="433" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A433" s="9"/>
       <c r="B433" s="55"/>
       <c r="C433" s="55"/>
@@ -14428,7 +14443,7 @@
       <c r="T433" s="9"/>
       <c r="U433" s="9"/>
     </row>
-    <row r="434" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A434" s="9"/>
       <c r="B434" s="55"/>
       <c r="C434" s="55"/>
@@ -14451,7 +14466,7 @@
       <c r="T434" s="9"/>
       <c r="U434" s="9"/>
     </row>
-    <row r="435" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A435" s="9"/>
       <c r="B435" s="55"/>
       <c r="C435" s="55"/>
@@ -14474,7 +14489,7 @@
       <c r="T435" s="9"/>
       <c r="U435" s="9"/>
     </row>
-    <row r="436" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A436" s="9"/>
       <c r="B436" s="55"/>
       <c r="C436" s="55"/>
@@ -14497,7 +14512,7 @@
       <c r="T436" s="9"/>
       <c r="U436" s="9"/>
     </row>
-    <row r="437" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A437" s="9"/>
       <c r="B437" s="55"/>
       <c r="C437" s="55"/>
@@ -14520,7 +14535,7 @@
       <c r="T437" s="9"/>
       <c r="U437" s="9"/>
     </row>
-    <row r="438" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A438" s="9"/>
       <c r="B438" s="55"/>
       <c r="C438" s="55"/>
@@ -14543,7 +14558,7 @@
       <c r="T438" s="9"/>
       <c r="U438" s="9"/>
     </row>
-    <row r="439" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A439" s="9"/>
       <c r="B439" s="55"/>
       <c r="C439" s="55"/>
@@ -14566,7 +14581,7 @@
       <c r="T439" s="9"/>
       <c r="U439" s="9"/>
     </row>
-    <row r="440" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A440" s="9"/>
       <c r="B440" s="55"/>
       <c r="C440" s="55"/>
@@ -14589,7 +14604,7 @@
       <c r="T440" s="9"/>
       <c r="U440" s="9"/>
     </row>
-    <row r="441" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A441" s="9"/>
       <c r="B441" s="55"/>
       <c r="C441" s="55"/>
@@ -14612,7 +14627,7 @@
       <c r="T441" s="9"/>
       <c r="U441" s="9"/>
     </row>
-    <row r="442" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A442" s="9"/>
       <c r="B442" s="55"/>
       <c r="C442" s="55"/>
@@ -14635,7 +14650,7 @@
       <c r="T442" s="9"/>
       <c r="U442" s="9"/>
     </row>
-    <row r="443" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A443" s="9"/>
       <c r="B443" s="55"/>
       <c r="C443" s="55"/>
@@ -14658,7 +14673,7 @@
       <c r="T443" s="9"/>
       <c r="U443" s="9"/>
     </row>
-    <row r="444" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A444" s="9"/>
       <c r="B444" s="55"/>
       <c r="C444" s="55"/>
@@ -14681,7 +14696,7 @@
       <c r="T444" s="9"/>
       <c r="U444" s="9"/>
     </row>
-    <row r="445" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A445" s="9"/>
       <c r="B445" s="55"/>
       <c r="C445" s="55"/>
@@ -14704,7 +14719,7 @@
       <c r="T445" s="9"/>
       <c r="U445" s="9"/>
     </row>
-    <row r="446" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A446" s="9"/>
       <c r="B446" s="55"/>
       <c r="C446" s="55"/>
@@ -14727,7 +14742,7 @@
       <c r="T446" s="9"/>
       <c r="U446" s="9"/>
     </row>
-    <row r="447" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A447" s="9"/>
       <c r="B447" s="55"/>
       <c r="C447" s="55"/>
@@ -14750,7 +14765,7 @@
       <c r="T447" s="9"/>
       <c r="U447" s="9"/>
     </row>
-    <row r="448" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A448" s="9"/>
       <c r="B448" s="55"/>
       <c r="C448" s="55"/>
@@ -14773,7 +14788,7 @@
       <c r="T448" s="9"/>
       <c r="U448" s="9"/>
     </row>
-    <row r="449" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A449" s="9"/>
       <c r="B449" s="55"/>
       <c r="C449" s="55"/>
@@ -14796,7 +14811,7 @@
       <c r="T449" s="9"/>
       <c r="U449" s="9"/>
     </row>
-    <row r="450" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A450" s="9"/>
       <c r="B450" s="55"/>
       <c r="C450" s="55"/>
@@ -14819,7 +14834,7 @@
       <c r="T450" s="9"/>
       <c r="U450" s="9"/>
     </row>
-    <row r="451" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A451" s="9"/>
       <c r="B451" s="55"/>
       <c r="C451" s="55"/>
@@ -14842,7 +14857,7 @@
       <c r="T451" s="9"/>
       <c r="U451" s="9"/>
     </row>
-    <row r="452" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A452" s="9"/>
       <c r="B452" s="55"/>
       <c r="C452" s="55"/>
@@ -14865,7 +14880,7 @@
       <c r="T452" s="9"/>
       <c r="U452" s="9"/>
     </row>
-    <row r="453" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A453" s="9"/>
       <c r="B453" s="55"/>
       <c r="C453" s="55"/>
@@ -14888,7 +14903,7 @@
       <c r="T453" s="9"/>
       <c r="U453" s="9"/>
     </row>
-    <row r="454" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A454" s="9"/>
       <c r="B454" s="55"/>
       <c r="C454" s="55"/>
@@ -14911,7 +14926,7 @@
       <c r="T454" s="9"/>
       <c r="U454" s="9"/>
     </row>
-    <row r="455" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A455" s="9"/>
       <c r="B455" s="55"/>
       <c r="C455" s="55"/>
@@ -14934,7 +14949,7 @@
       <c r="T455" s="9"/>
       <c r="U455" s="9"/>
     </row>
-    <row r="456" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A456" s="9"/>
       <c r="B456" s="55"/>
       <c r="C456" s="55"/>
@@ -14957,7 +14972,7 @@
       <c r="T456" s="9"/>
       <c r="U456" s="9"/>
     </row>
-    <row r="457" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A457" s="9"/>
       <c r="B457" s="55"/>
       <c r="C457" s="55"/>
@@ -14980,7 +14995,7 @@
       <c r="T457" s="9"/>
       <c r="U457" s="9"/>
     </row>
-    <row r="458" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A458" s="9"/>
       <c r="B458" s="55"/>
       <c r="C458" s="55"/>
@@ -15003,7 +15018,7 @@
       <c r="T458" s="9"/>
       <c r="U458" s="9"/>
     </row>
-    <row r="459" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A459" s="9"/>
       <c r="B459" s="55"/>
       <c r="C459" s="55"/>
@@ -15026,7 +15041,7 @@
       <c r="T459" s="9"/>
       <c r="U459" s="9"/>
     </row>
-    <row r="460" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A460" s="9"/>
       <c r="B460" s="55"/>
       <c r="C460" s="55"/>
@@ -15049,7 +15064,7 @@
       <c r="T460" s="9"/>
       <c r="U460" s="9"/>
     </row>
-    <row r="461" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A461" s="9"/>
       <c r="B461" s="55"/>
       <c r="C461" s="55"/>
@@ -15072,7 +15087,7 @@
       <c r="T461" s="9"/>
       <c r="U461" s="9"/>
     </row>
-    <row r="462" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A462" s="9"/>
       <c r="B462" s="55"/>
       <c r="C462" s="55"/>
@@ -15095,7 +15110,7 @@
       <c r="T462" s="9"/>
       <c r="U462" s="9"/>
     </row>
-    <row r="463" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A463" s="9"/>
       <c r="B463" s="55"/>
       <c r="C463" s="55"/>
@@ -15118,7 +15133,7 @@
       <c r="T463" s="9"/>
       <c r="U463" s="9"/>
     </row>
-    <row r="464" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A464" s="9"/>
       <c r="B464" s="55"/>
       <c r="C464" s="55"/>
@@ -15141,7 +15156,7 @@
       <c r="T464" s="9"/>
       <c r="U464" s="9"/>
     </row>
-    <row r="465" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A465" s="9"/>
       <c r="B465" s="55"/>
       <c r="C465" s="55"/>
@@ -15164,7 +15179,7 @@
       <c r="T465" s="9"/>
       <c r="U465" s="9"/>
     </row>
-    <row r="466" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A466" s="9"/>
       <c r="B466" s="55"/>
       <c r="C466" s="55"/>
@@ -15187,7 +15202,7 @@
       <c r="T466" s="9"/>
       <c r="U466" s="9"/>
     </row>
-    <row r="467" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A467" s="9"/>
       <c r="B467" s="55"/>
       <c r="C467" s="55"/>
@@ -15210,7 +15225,7 @@
       <c r="T467" s="9"/>
       <c r="U467" s="9"/>
     </row>
-    <row r="468" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A468" s="9"/>
       <c r="B468" s="55"/>
       <c r="C468" s="55"/>
@@ -15233,7 +15248,7 @@
       <c r="T468" s="9"/>
       <c r="U468" s="9"/>
     </row>
-    <row r="469" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A469" s="9"/>
       <c r="B469" s="55"/>
       <c r="C469" s="55"/>
@@ -15256,7 +15271,7 @@
       <c r="T469" s="9"/>
       <c r="U469" s="9"/>
     </row>
-    <row r="470" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A470" s="9"/>
       <c r="B470" s="55"/>
       <c r="C470" s="55"/>
@@ -15279,7 +15294,7 @@
       <c r="T470" s="9"/>
       <c r="U470" s="9"/>
     </row>
-    <row r="471" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A471" s="9"/>
       <c r="B471" s="55"/>
       <c r="C471" s="55"/>
@@ -15302,7 +15317,7 @@
       <c r="T471" s="9"/>
       <c r="U471" s="9"/>
     </row>
-    <row r="472" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A472" s="9"/>
       <c r="B472" s="55"/>
       <c r="C472" s="55"/>
@@ -15325,7 +15340,7 @@
       <c r="T472" s="9"/>
       <c r="U472" s="9"/>
     </row>
-    <row r="473" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A473" s="9"/>
       <c r="B473" s="55"/>
       <c r="C473" s="55"/>
@@ -15348,7 +15363,7 @@
       <c r="T473" s="9"/>
       <c r="U473" s="9"/>
     </row>
-    <row r="474" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A474" s="9"/>
       <c r="B474" s="55"/>
       <c r="C474" s="55"/>
@@ -15371,7 +15386,7 @@
       <c r="T474" s="9"/>
       <c r="U474" s="9"/>
     </row>
-    <row r="475" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A475" s="9"/>
       <c r="B475" s="55"/>
       <c r="C475" s="55"/>
@@ -15394,7 +15409,7 @@
       <c r="T475" s="9"/>
       <c r="U475" s="9"/>
     </row>
-    <row r="476" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A476" s="9"/>
       <c r="B476" s="55"/>
       <c r="C476" s="55"/>
@@ -15417,7 +15432,7 @@
       <c r="T476" s="9"/>
       <c r="U476" s="9"/>
     </row>
-    <row r="477" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A477" s="9"/>
       <c r="B477" s="55"/>
       <c r="C477" s="55"/>
@@ -15440,7 +15455,7 @@
       <c r="T477" s="9"/>
       <c r="U477" s="9"/>
     </row>
-    <row r="478" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A478" s="9"/>
       <c r="B478" s="55"/>
       <c r="C478" s="55"/>
@@ -15463,7 +15478,7 @@
       <c r="T478" s="9"/>
       <c r="U478" s="9"/>
     </row>
-    <row r="479" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A479" s="9"/>
       <c r="B479" s="55"/>
       <c r="C479" s="55"/>
@@ -15486,7 +15501,7 @@
       <c r="T479" s="9"/>
       <c r="U479" s="9"/>
     </row>
-    <row r="480" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A480" s="9"/>
       <c r="B480" s="55"/>
       <c r="C480" s="55"/>
@@ -15509,7 +15524,7 @@
       <c r="T480" s="9"/>
       <c r="U480" s="9"/>
     </row>
-    <row r="481" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A481" s="9"/>
       <c r="B481" s="55"/>
       <c r="C481" s="55"/>
@@ -15532,7 +15547,7 @@
       <c r="T481" s="9"/>
       <c r="U481" s="9"/>
     </row>
-    <row r="482" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A482" s="9"/>
       <c r="B482" s="55"/>
       <c r="C482" s="55"/>
@@ -15555,7 +15570,7 @@
       <c r="T482" s="9"/>
       <c r="U482" s="9"/>
     </row>
-    <row r="483" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A483" s="9"/>
       <c r="B483" s="55"/>
       <c r="C483" s="55"/>
@@ -15578,7 +15593,7 @@
       <c r="T483" s="9"/>
       <c r="U483" s="9"/>
     </row>
-    <row r="484" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A484" s="9"/>
       <c r="B484" s="55"/>
       <c r="C484" s="55"/>
@@ -15601,7 +15616,7 @@
       <c r="T484" s="9"/>
       <c r="U484" s="9"/>
     </row>
-    <row r="485" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A485" s="9"/>
       <c r="B485" s="55"/>
       <c r="C485" s="55"/>
@@ -15624,7 +15639,7 @@
       <c r="T485" s="9"/>
       <c r="U485" s="9"/>
     </row>
-    <row r="486" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A486" s="9"/>
       <c r="B486" s="55"/>
       <c r="C486" s="55"/>
@@ -15647,7 +15662,7 @@
       <c r="T486" s="9"/>
       <c r="U486" s="9"/>
     </row>
-    <row r="487" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A487" s="9"/>
       <c r="B487" s="55"/>
       <c r="C487" s="55"/>
@@ -15670,7 +15685,7 @@
       <c r="T487" s="9"/>
       <c r="U487" s="9"/>
     </row>
-    <row r="488" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A488" s="9"/>
       <c r="B488" s="55"/>
       <c r="C488" s="55"/>
@@ -15693,7 +15708,7 @@
       <c r="T488" s="9"/>
       <c r="U488" s="9"/>
     </row>
-    <row r="489" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A489" s="9"/>
       <c r="B489" s="55"/>
       <c r="C489" s="55"/>
@@ -15716,7 +15731,7 @@
       <c r="T489" s="9"/>
       <c r="U489" s="9"/>
     </row>
-    <row r="490" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A490" s="9"/>
       <c r="B490" s="55"/>
       <c r="C490" s="55"/>
@@ -15739,7 +15754,7 @@
       <c r="T490" s="9"/>
       <c r="U490" s="9"/>
     </row>
-    <row r="491" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A491" s="9"/>
       <c r="B491" s="55"/>
       <c r="C491" s="55"/>
@@ -15762,7 +15777,7 @@
       <c r="T491" s="9"/>
       <c r="U491" s="9"/>
     </row>
-    <row r="492" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A492" s="9"/>
       <c r="B492" s="55"/>
       <c r="C492" s="55"/>
@@ -15785,7 +15800,7 @@
       <c r="T492" s="9"/>
       <c r="U492" s="9"/>
     </row>
-    <row r="493" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A493" s="9"/>
       <c r="B493" s="55"/>
       <c r="C493" s="55"/>
@@ -15808,7 +15823,7 @@
       <c r="T493" s="9"/>
       <c r="U493" s="9"/>
     </row>
-    <row r="494" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A494" s="9"/>
       <c r="B494" s="55"/>
       <c r="C494" s="55"/>
@@ -15831,7 +15846,7 @@
       <c r="T494" s="9"/>
       <c r="U494" s="9"/>
     </row>
-    <row r="495" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A495" s="9"/>
       <c r="B495" s="55"/>
       <c r="C495" s="55"/>
@@ -15854,7 +15869,7 @@
       <c r="T495" s="9"/>
       <c r="U495" s="9"/>
     </row>
-    <row r="496" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A496" s="9"/>
       <c r="B496" s="55"/>
       <c r="C496" s="55"/>
@@ -15877,7 +15892,7 @@
       <c r="T496" s="9"/>
       <c r="U496" s="9"/>
     </row>
-    <row r="497" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A497" s="9"/>
       <c r="B497" s="55"/>
       <c r="C497" s="55"/>
@@ -15900,7 +15915,7 @@
       <c r="T497" s="9"/>
       <c r="U497" s="9"/>
     </row>
-    <row r="498" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A498" s="9"/>
       <c r="B498" s="55"/>
       <c r="C498" s="55"/>
@@ -15923,7 +15938,7 @@
       <c r="T498" s="9"/>
       <c r="U498" s="9"/>
     </row>
-    <row r="499" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A499" s="9"/>
       <c r="B499" s="55"/>
       <c r="C499" s="55"/>
@@ -15946,7 +15961,7 @@
       <c r="T499" s="9"/>
       <c r="U499" s="9"/>
     </row>
-    <row r="500" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A500" s="9"/>
       <c r="B500" s="55"/>
       <c r="C500" s="55"/>
@@ -15969,7 +15984,7 @@
       <c r="T500" s="9"/>
       <c r="U500" s="9"/>
     </row>
-    <row r="501" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A501" s="9"/>
       <c r="B501" s="55"/>
       <c r="C501" s="55"/>
@@ -15992,7 +16007,7 @@
       <c r="T501" s="9"/>
       <c r="U501" s="9"/>
     </row>
-    <row r="502" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A502" s="9"/>
       <c r="B502" s="55"/>
       <c r="C502" s="55"/>
@@ -16015,7 +16030,7 @@
       <c r="T502" s="9"/>
       <c r="U502" s="9"/>
     </row>
-    <row r="503" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A503" s="9"/>
       <c r="B503" s="55"/>
       <c r="C503" s="55"/>
@@ -16038,7 +16053,7 @@
       <c r="T503" s="9"/>
       <c r="U503" s="9"/>
     </row>
-    <row r="504" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A504" s="9"/>
       <c r="B504" s="55"/>
       <c r="C504" s="55"/>
@@ -16061,7 +16076,7 @@
       <c r="T504" s="9"/>
       <c r="U504" s="9"/>
     </row>
-    <row r="505" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A505" s="9"/>
       <c r="B505" s="55"/>
       <c r="C505" s="55"/>
@@ -16084,7 +16099,7 @@
       <c r="T505" s="9"/>
       <c r="U505" s="9"/>
     </row>
-    <row r="506" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A506" s="9"/>
       <c r="B506" s="55"/>
       <c r="C506" s="55"/>
@@ -16107,7 +16122,7 @@
       <c r="T506" s="9"/>
       <c r="U506" s="9"/>
     </row>
-    <row r="507" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A507" s="9"/>
       <c r="B507" s="55"/>
       <c r="C507" s="55"/>
@@ -16130,7 +16145,7 @@
       <c r="T507" s="9"/>
       <c r="U507" s="9"/>
     </row>
-    <row r="508" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A508" s="9"/>
       <c r="B508" s="55"/>
       <c r="C508" s="55"/>
@@ -16153,7 +16168,7 @@
       <c r="T508" s="9"/>
       <c r="U508" s="9"/>
     </row>
-    <row r="509" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A509" s="9"/>
       <c r="B509" s="55"/>
       <c r="C509" s="55"/>
@@ -16176,7 +16191,7 @@
       <c r="T509" s="9"/>
       <c r="U509" s="9"/>
     </row>
-    <row r="510" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A510" s="9"/>
       <c r="B510" s="55"/>
       <c r="C510" s="55"/>
@@ -16199,7 +16214,7 @@
       <c r="T510" s="9"/>
       <c r="U510" s="9"/>
     </row>
-    <row r="511" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A511" s="9"/>
       <c r="B511" s="55"/>
       <c r="C511" s="55"/>
@@ -16222,7 +16237,7 @@
       <c r="T511" s="9"/>
       <c r="U511" s="9"/>
     </row>
-    <row r="512" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A512" s="9"/>
       <c r="B512" s="55"/>
       <c r="C512" s="55"/>
@@ -16245,7 +16260,7 @@
       <c r="T512" s="9"/>
       <c r="U512" s="9"/>
     </row>
-    <row r="513" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A513" s="9"/>
       <c r="B513" s="55"/>
       <c r="C513" s="55"/>
@@ -16268,7 +16283,7 @@
       <c r="T513" s="9"/>
       <c r="U513" s="9"/>
     </row>
-    <row r="514" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A514" s="9"/>
       <c r="B514" s="55"/>
       <c r="C514" s="55"/>
@@ -16291,7 +16306,7 @@
       <c r="T514" s="9"/>
       <c r="U514" s="9"/>
     </row>
-    <row r="515" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A515" s="9"/>
       <c r="B515" s="55"/>
       <c r="C515" s="55"/>
@@ -16314,7 +16329,7 @@
       <c r="T515" s="9"/>
       <c r="U515" s="9"/>
     </row>
-    <row r="516" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A516" s="9"/>
       <c r="B516" s="55"/>
       <c r="C516" s="55"/>
@@ -16337,7 +16352,7 @@
       <c r="T516" s="9"/>
       <c r="U516" s="9"/>
     </row>
-    <row r="517" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A517" s="9"/>
       <c r="B517" s="55"/>
       <c r="C517" s="55"/>
@@ -16360,7 +16375,7 @@
       <c r="T517" s="9"/>
       <c r="U517" s="9"/>
     </row>
-    <row r="518" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A518" s="9"/>
       <c r="B518" s="55"/>
       <c r="C518" s="55"/>
@@ -16383,7 +16398,7 @@
       <c r="T518" s="9"/>
       <c r="U518" s="9"/>
     </row>
-    <row r="519" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A519" s="9"/>
       <c r="B519" s="55"/>
       <c r="C519" s="55"/>
@@ -16406,7 +16421,7 @@
       <c r="T519" s="9"/>
       <c r="U519" s="9"/>
     </row>
-    <row r="520" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A520" s="9"/>
       <c r="B520" s="55"/>
       <c r="C520" s="55"/>
@@ -16429,7 +16444,7 @@
       <c r="T520" s="9"/>
       <c r="U520" s="9"/>
     </row>
-    <row r="521" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A521" s="9"/>
       <c r="B521" s="55"/>
       <c r="C521" s="55"/>
@@ -16452,7 +16467,7 @@
       <c r="T521" s="9"/>
       <c r="U521" s="9"/>
     </row>
-    <row r="522" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A522" s="9"/>
       <c r="B522" s="55"/>
       <c r="C522" s="55"/>
@@ -16475,7 +16490,7 @@
       <c r="T522" s="9"/>
       <c r="U522" s="9"/>
     </row>
-    <row r="523" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A523" s="9"/>
       <c r="B523" s="55"/>
       <c r="C523" s="55"/>
@@ -16498,7 +16513,7 @@
       <c r="T523" s="9"/>
       <c r="U523" s="9"/>
     </row>
-    <row r="524" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A524" s="9"/>
       <c r="B524" s="55"/>
       <c r="C524" s="55"/>
@@ -16521,7 +16536,7 @@
       <c r="T524" s="9"/>
       <c r="U524" s="9"/>
     </row>
-    <row r="525" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A525" s="9"/>
       <c r="B525" s="55"/>
       <c r="C525" s="55"/>
@@ -16544,7 +16559,7 @@
       <c r="T525" s="9"/>
       <c r="U525" s="9"/>
     </row>
-    <row r="526" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A526" s="9"/>
       <c r="B526" s="55"/>
       <c r="C526" s="55"/>
@@ -16567,7 +16582,7 @@
       <c r="T526" s="9"/>
       <c r="U526" s="9"/>
     </row>
-    <row r="527" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A527" s="9"/>
       <c r="B527" s="55"/>
       <c r="C527" s="55"/>
@@ -16590,7 +16605,7 @@
       <c r="T527" s="9"/>
       <c r="U527" s="9"/>
     </row>
-    <row r="528" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A528" s="9"/>
       <c r="B528" s="55"/>
       <c r="C528" s="55"/>
@@ -16613,7 +16628,7 @@
       <c r="T528" s="9"/>
       <c r="U528" s="9"/>
     </row>
-    <row r="529" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A529" s="9"/>
       <c r="B529" s="55"/>
       <c r="C529" s="55"/>
@@ -16636,7 +16651,7 @@
       <c r="T529" s="9"/>
       <c r="U529" s="9"/>
     </row>
-    <row r="530" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A530" s="9"/>
       <c r="B530" s="55"/>
       <c r="C530" s="55"/>
@@ -16659,7 +16674,7 @@
       <c r="T530" s="9"/>
       <c r="U530" s="9"/>
     </row>
-    <row r="531" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A531" s="9"/>
       <c r="B531" s="55"/>
       <c r="C531" s="55"/>
@@ -16682,7 +16697,7 @@
       <c r="T531" s="9"/>
       <c r="U531" s="9"/>
     </row>
-    <row r="532" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A532" s="9"/>
       <c r="B532" s="55"/>
       <c r="C532" s="55"/>
@@ -16705,7 +16720,7 @@
       <c r="T532" s="9"/>
       <c r="U532" s="9"/>
     </row>
-    <row r="533" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A533" s="9"/>
       <c r="B533" s="55"/>
       <c r="C533" s="55"/>
@@ -16728,7 +16743,7 @@
       <c r="T533" s="9"/>
       <c r="U533" s="9"/>
     </row>
-    <row r="534" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A534" s="9"/>
       <c r="B534" s="55"/>
       <c r="C534" s="55"/>
@@ -16751,7 +16766,7 @@
       <c r="T534" s="9"/>
       <c r="U534" s="9"/>
     </row>
-    <row r="535" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A535" s="9"/>
       <c r="B535" s="55"/>
       <c r="C535" s="55"/>
@@ -16774,7 +16789,7 @@
       <c r="T535" s="9"/>
       <c r="U535" s="9"/>
     </row>
-    <row r="536" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A536" s="9"/>
       <c r="B536" s="55"/>
       <c r="C536" s="55"/>
@@ -16797,7 +16812,7 @@
       <c r="T536" s="9"/>
       <c r="U536" s="9"/>
     </row>
-    <row r="537" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A537" s="9"/>
       <c r="B537" s="55"/>
       <c r="C537" s="55"/>
@@ -16820,7 +16835,7 @@
       <c r="T537" s="9"/>
       <c r="U537" s="9"/>
     </row>
-    <row r="538" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A538" s="9"/>
       <c r="B538" s="55"/>
       <c r="C538" s="55"/>
@@ -16843,7 +16858,7 @@
       <c r="T538" s="9"/>
       <c r="U538" s="9"/>
     </row>
-    <row r="539" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A539" s="9"/>
       <c r="B539" s="55"/>
       <c r="C539" s="55"/>
@@ -16866,7 +16881,7 @@
       <c r="T539" s="9"/>
       <c r="U539" s="9"/>
     </row>
-    <row r="540" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A540" s="9"/>
       <c r="B540" s="55"/>
       <c r="C540" s="55"/>
@@ -16889,7 +16904,7 @@
       <c r="T540" s="9"/>
       <c r="U540" s="9"/>
     </row>
-    <row r="541" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A541" s="9"/>
       <c r="B541" s="55"/>
       <c r="C541" s="55"/>
@@ -16912,7 +16927,7 @@
       <c r="T541" s="9"/>
       <c r="U541" s="9"/>
     </row>
-    <row r="542" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A542" s="9"/>
       <c r="B542" s="55"/>
       <c r="C542" s="55"/>
@@ -16935,7 +16950,7 @@
       <c r="T542" s="9"/>
       <c r="U542" s="9"/>
     </row>
-    <row r="543" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A543" s="9"/>
       <c r="B543" s="55"/>
       <c r="C543" s="55"/>
@@ -16958,7 +16973,7 @@
       <c r="T543" s="9"/>
       <c r="U543" s="9"/>
     </row>
-    <row r="544" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A544" s="9"/>
       <c r="B544" s="55"/>
       <c r="C544" s="55"/>
@@ -16981,7 +16996,7 @@
       <c r="T544" s="9"/>
       <c r="U544" s="9"/>
     </row>
-    <row r="545" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A545" s="9"/>
       <c r="B545" s="55"/>
       <c r="C545" s="55"/>
@@ -17004,7 +17019,7 @@
       <c r="T545" s="9"/>
       <c r="U545" s="9"/>
     </row>
-    <row r="546" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A546" s="9"/>
       <c r="B546" s="55"/>
       <c r="C546" s="55"/>
@@ -17027,7 +17042,7 @@
       <c r="T546" s="9"/>
       <c r="U546" s="9"/>
     </row>
-    <row r="547" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A547" s="9"/>
       <c r="B547" s="55"/>
       <c r="C547" s="55"/>
@@ -17050,7 +17065,7 @@
       <c r="T547" s="9"/>
       <c r="U547" s="9"/>
     </row>
-    <row r="548" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A548" s="9"/>
       <c r="B548" s="55"/>
       <c r="C548" s="55"/>
@@ -17073,7 +17088,7 @@
       <c r="T548" s="9"/>
       <c r="U548" s="9"/>
     </row>
-    <row r="549" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A549" s="9"/>
       <c r="B549" s="55"/>
       <c r="C549" s="55"/>
@@ -17096,7 +17111,7 @@
       <c r="T549" s="9"/>
       <c r="U549" s="9"/>
     </row>
-    <row r="550" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A550" s="9"/>
       <c r="B550" s="55"/>
       <c r="C550" s="55"/>
@@ -17119,7 +17134,7 @@
       <c r="T550" s="9"/>
       <c r="U550" s="9"/>
     </row>
-    <row r="551" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A551" s="9"/>
       <c r="B551" s="55"/>
       <c r="C551" s="55"/>
@@ -17142,7 +17157,7 @@
       <c r="T551" s="9"/>
       <c r="U551" s="9"/>
     </row>
-    <row r="552" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A552" s="9"/>
       <c r="B552" s="55"/>
       <c r="C552" s="55"/>
@@ -17165,7 +17180,7 @@
       <c r="T552" s="9"/>
       <c r="U552" s="9"/>
     </row>
-    <row r="553" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A553" s="9"/>
       <c r="B553" s="55"/>
       <c r="C553" s="55"/>
@@ -17188,7 +17203,7 @@
       <c r="T553" s="9"/>
       <c r="U553" s="9"/>
     </row>
-    <row r="554" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A554" s="9"/>
       <c r="B554" s="55"/>
       <c r="C554" s="55"/>
@@ -17211,7 +17226,7 @@
       <c r="T554" s="9"/>
       <c r="U554" s="9"/>
     </row>
-    <row r="555" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A555" s="9"/>
       <c r="B555" s="55"/>
       <c r="C555" s="55"/>
@@ -17234,7 +17249,7 @@
       <c r="T555" s="9"/>
       <c r="U555" s="9"/>
     </row>
-    <row r="556" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A556" s="9"/>
       <c r="B556" s="55"/>
       <c r="C556" s="55"/>
@@ -17257,7 +17272,7 @@
       <c r="T556" s="9"/>
       <c r="U556" s="9"/>
     </row>
-    <row r="557" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A557" s="9"/>
       <c r="B557" s="55"/>
       <c r="C557" s="55"/>
@@ -17280,7 +17295,7 @@
       <c r="T557" s="9"/>
       <c r="U557" s="9"/>
     </row>
-    <row r="558" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A558" s="9"/>
       <c r="B558" s="55"/>
       <c r="C558" s="55"/>
@@ -17303,7 +17318,7 @@
       <c r="T558" s="9"/>
       <c r="U558" s="9"/>
     </row>
-    <row r="559" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A559" s="9"/>
       <c r="B559" s="55"/>
       <c r="C559" s="55"/>
@@ -17326,7 +17341,7 @@
       <c r="T559" s="9"/>
       <c r="U559" s="9"/>
     </row>
-    <row r="560" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A560" s="9"/>
       <c r="B560" s="55"/>
       <c r="C560" s="55"/>
@@ -17349,7 +17364,7 @@
       <c r="T560" s="9"/>
       <c r="U560" s="9"/>
     </row>
-    <row r="561" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A561" s="9"/>
       <c r="B561" s="55"/>
       <c r="C561" s="55"/>
@@ -17372,7 +17387,7 @@
       <c r="T561" s="9"/>
       <c r="U561" s="9"/>
     </row>
-    <row r="562" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A562" s="9"/>
       <c r="B562" s="55"/>
       <c r="C562" s="55"/>
@@ -17395,7 +17410,7 @@
       <c r="T562" s="9"/>
       <c r="U562" s="9"/>
     </row>
-    <row r="563" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A563" s="9"/>
       <c r="B563" s="55"/>
       <c r="C563" s="55"/>
@@ -17418,7 +17433,7 @@
       <c r="T563" s="9"/>
       <c r="U563" s="9"/>
     </row>
-    <row r="564" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A564" s="9"/>
       <c r="B564" s="55"/>
       <c r="C564" s="55"/>
@@ -17441,7 +17456,7 @@
       <c r="T564" s="9"/>
       <c r="U564" s="9"/>
     </row>
-    <row r="565" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A565" s="9"/>
       <c r="B565" s="55"/>
       <c r="C565" s="55"/>
@@ -17464,7 +17479,7 @@
       <c r="T565" s="9"/>
       <c r="U565" s="9"/>
     </row>
-    <row r="566" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A566" s="9"/>
       <c r="B566" s="55"/>
       <c r="C566" s="55"/>
@@ -17487,7 +17502,7 @@
       <c r="T566" s="9"/>
       <c r="U566" s="9"/>
     </row>
-    <row r="567" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A567" s="9"/>
       <c r="B567" s="55"/>
       <c r="C567" s="55"/>
@@ -17510,7 +17525,7 @@
       <c r="T567" s="9"/>
       <c r="U567" s="9"/>
     </row>
-    <row r="568" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A568" s="9"/>
       <c r="B568" s="55"/>
       <c r="C568" s="55"/>
@@ -17533,7 +17548,7 @@
       <c r="T568" s="9"/>
       <c r="U568" s="9"/>
     </row>
-    <row r="569" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A569" s="9"/>
       <c r="B569" s="55"/>
       <c r="C569" s="55"/>
@@ -17556,7 +17571,7 @@
       <c r="T569" s="9"/>
       <c r="U569" s="9"/>
     </row>
-    <row r="570" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A570" s="9"/>
       <c r="B570" s="55"/>
       <c r="C570" s="55"/>
@@ -17579,7 +17594,7 @@
       <c r="T570" s="9"/>
       <c r="U570" s="9"/>
     </row>
-    <row r="571" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A571" s="9"/>
       <c r="B571" s="55"/>
       <c r="C571" s="55"/>
@@ -17602,7 +17617,7 @@
       <c r="T571" s="9"/>
       <c r="U571" s="9"/>
     </row>
-    <row r="572" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A572" s="9"/>
       <c r="B572" s="55"/>
       <c r="C572" s="55"/>
@@ -17625,7 +17640,7 @@
       <c r="T572" s="9"/>
       <c r="U572" s="9"/>
     </row>
-    <row r="573" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A573" s="9"/>
       <c r="B573" s="55"/>
       <c r="C573" s="55"/>
@@ -17648,7 +17663,7 @@
       <c r="T573" s="9"/>
       <c r="U573" s="9"/>
     </row>
-    <row r="574" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A574" s="9"/>
       <c r="B574" s="55"/>
       <c r="C574" s="55"/>
@@ -17671,7 +17686,7 @@
       <c r="T574" s="9"/>
       <c r="U574" s="9"/>
     </row>
-    <row r="575" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A575" s="9"/>
       <c r="B575" s="55"/>
       <c r="C575" s="55"/>
@@ -17694,7 +17709,7 @@
       <c r="T575" s="9"/>
       <c r="U575" s="9"/>
     </row>
-    <row r="576" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A576" s="9"/>
       <c r="B576" s="55"/>
       <c r="C576" s="55"/>
@@ -17717,7 +17732,7 @@
       <c r="T576" s="9"/>
       <c r="U576" s="9"/>
     </row>
-    <row r="577" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A577" s="9"/>
       <c r="B577" s="55"/>
       <c r="C577" s="55"/>
@@ -17740,7 +17755,7 @@
       <c r="T577" s="9"/>
       <c r="U577" s="9"/>
     </row>
-    <row r="578" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A578" s="9"/>
       <c r="B578" s="55"/>
       <c r="C578" s="55"/>
@@ -17763,7 +17778,7 @@
       <c r="T578" s="9"/>
       <c r="U578" s="9"/>
     </row>
-    <row r="579" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A579" s="9"/>
       <c r="B579" s="55"/>
       <c r="C579" s="55"/>
@@ -17786,7 +17801,7 @@
       <c r="T579" s="9"/>
       <c r="U579" s="9"/>
     </row>
-    <row r="580" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A580" s="9"/>
       <c r="B580" s="55"/>
       <c r="C580" s="55"/>
@@ -17809,7 +17824,7 @@
       <c r="T580" s="9"/>
       <c r="U580" s="9"/>
     </row>
-    <row r="581" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A581" s="9"/>
       <c r="B581" s="55"/>
       <c r="C581" s="55"/>
@@ -17832,7 +17847,7 @@
       <c r="T581" s="9"/>
       <c r="U581" s="9"/>
     </row>
-    <row r="582" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A582" s="9"/>
       <c r="B582" s="55"/>
       <c r="C582" s="55"/>
@@ -17855,7 +17870,7 @@
       <c r="T582" s="9"/>
       <c r="U582" s="9"/>
     </row>
-    <row r="583" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A583" s="9"/>
       <c r="B583" s="55"/>
       <c r="C583" s="55"/>
@@ -17878,7 +17893,7 @@
       <c r="T583" s="9"/>
       <c r="U583" s="9"/>
     </row>
-    <row r="584" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A584" s="9"/>
       <c r="B584" s="55"/>
       <c r="C584" s="55"/>
@@ -17901,7 +17916,7 @@
       <c r="T584" s="9"/>
       <c r="U584" s="9"/>
     </row>
-    <row r="585" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A585" s="9"/>
       <c r="B585" s="55"/>
       <c r="C585" s="55"/>
@@ -17924,7 +17939,7 @@
       <c r="T585" s="9"/>
       <c r="U585" s="9"/>
     </row>
-    <row r="586" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A586" s="9"/>
       <c r="B586" s="55"/>
       <c r="C586" s="55"/>
@@ -17947,7 +17962,7 @@
       <c r="T586" s="9"/>
       <c r="U586" s="9"/>
     </row>
-    <row r="587" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A587" s="9"/>
       <c r="B587" s="55"/>
       <c r="C587" s="55"/>
@@ -17970,7 +17985,7 @@
       <c r="T587" s="9"/>
       <c r="U587" s="9"/>
     </row>
-    <row r="588" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A588" s="9"/>
       <c r="B588" s="55"/>
       <c r="C588" s="55"/>
@@ -17993,7 +18008,7 @@
       <c r="T588" s="9"/>
       <c r="U588" s="9"/>
     </row>
-    <row r="589" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A589" s="9"/>
       <c r="B589" s="55"/>
       <c r="C589" s="55"/>
@@ -18016,7 +18031,7 @@
       <c r="T589" s="9"/>
       <c r="U589" s="9"/>
     </row>
-    <row r="590" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A590" s="9"/>
       <c r="B590" s="55"/>
       <c r="C590" s="55"/>
@@ -18039,7 +18054,7 @@
       <c r="T590" s="9"/>
       <c r="U590" s="9"/>
     </row>
-    <row r="591" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A591" s="9"/>
       <c r="B591" s="55"/>
       <c r="C591" s="55"/>
@@ -18062,7 +18077,7 @@
       <c r="T591" s="9"/>
       <c r="U591" s="9"/>
     </row>
-    <row r="592" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A592" s="9"/>
       <c r="B592" s="55"/>
       <c r="C592" s="55"/>
@@ -18085,7 +18100,7 @@
       <c r="T592" s="9"/>
       <c r="U592" s="9"/>
     </row>
-    <row r="593" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A593" s="9"/>
       <c r="B593" s="55"/>
       <c r="C593" s="55"/>
@@ -18108,7 +18123,7 @@
       <c r="T593" s="9"/>
       <c r="U593" s="9"/>
     </row>
-    <row r="594" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A594" s="9"/>
       <c r="B594" s="55"/>
       <c r="C594" s="55"/>
@@ -18131,7 +18146,7 @@
       <c r="T594" s="9"/>
       <c r="U594" s="9"/>
     </row>
-    <row r="595" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A595" s="9"/>
       <c r="B595" s="55"/>
       <c r="C595" s="55"/>
@@ -18154,7 +18169,7 @@
       <c r="T595" s="9"/>
       <c r="U595" s="9"/>
     </row>
-    <row r="596" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A596" s="9"/>
       <c r="B596" s="55"/>
       <c r="C596" s="55"/>
@@ -18177,7 +18192,7 @@
       <c r="T596" s="9"/>
       <c r="U596" s="9"/>
     </row>
-    <row r="597" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A597" s="9"/>
       <c r="B597" s="55"/>
       <c r="C597" s="55"/>
@@ -18200,7 +18215,7 @@
       <c r="T597" s="9"/>
       <c r="U597" s="9"/>
     </row>
-    <row r="598" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A598" s="9"/>
       <c r="B598" s="55"/>
       <c r="C598" s="55"/>
@@ -18223,7 +18238,7 @@
       <c r="T598" s="9"/>
       <c r="U598" s="9"/>
     </row>
-    <row r="599" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A599" s="9"/>
       <c r="B599" s="55"/>
       <c r="C599" s="55"/>
@@ -18246,7 +18261,7 @@
       <c r="T599" s="9"/>
       <c r="U599" s="9"/>
     </row>
-    <row r="600" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A600" s="9"/>
       <c r="B600" s="55"/>
       <c r="C600" s="55"/>
@@ -18269,7 +18284,7 @@
       <c r="T600" s="9"/>
       <c r="U600" s="9"/>
     </row>
-    <row r="601" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A601" s="9"/>
       <c r="B601" s="55"/>
       <c r="C601" s="55"/>
@@ -18292,7 +18307,7 @@
       <c r="T601" s="9"/>
       <c r="U601" s="9"/>
     </row>
-    <row r="602" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A602" s="9"/>
       <c r="B602" s="55"/>
       <c r="C602" s="55"/>
@@ -18315,7 +18330,7 @@
       <c r="T602" s="9"/>
       <c r="U602" s="9"/>
     </row>
-    <row r="603" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A603" s="9"/>
       <c r="B603" s="55"/>
       <c r="C603" s="55"/>
@@ -18338,7 +18353,7 @@
       <c r="T603" s="9"/>
       <c r="U603" s="9"/>
     </row>
-    <row r="604" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A604" s="9"/>
       <c r="B604" s="55"/>
       <c r="C604" s="55"/>
@@ -18361,7 +18376,7 @@
       <c r="T604" s="9"/>
       <c r="U604" s="9"/>
     </row>
-    <row r="605" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A605" s="9"/>
       <c r="B605" s="55"/>
       <c r="C605" s="55"/>
@@ -18384,7 +18399,7 @@
       <c r="T605" s="9"/>
       <c r="U605" s="9"/>
     </row>
-    <row r="606" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A606" s="9"/>
       <c r="B606" s="55"/>
       <c r="C606" s="55"/>
@@ -18407,7 +18422,7 @@
       <c r="T606" s="9"/>
       <c r="U606" s="9"/>
     </row>
-    <row r="607" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A607" s="9"/>
       <c r="B607" s="55"/>
       <c r="C607" s="55"/>
@@ -18430,7 +18445,7 @@
       <c r="T607" s="9"/>
       <c r="U607" s="9"/>
     </row>
-    <row r="608" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A608" s="9"/>
       <c r="B608" s="55"/>
       <c r="C608" s="55"/>
@@ -18453,7 +18468,7 @@
       <c r="T608" s="9"/>
       <c r="U608" s="9"/>
     </row>
-    <row r="609" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A609" s="9"/>
       <c r="B609" s="55"/>
       <c r="C609" s="55"/>
@@ -18476,7 +18491,7 @@
       <c r="T609" s="9"/>
       <c r="U609" s="9"/>
     </row>
-    <row r="610" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A610" s="9"/>
       <c r="B610" s="55"/>
       <c r="C610" s="55"/>
@@ -18499,7 +18514,7 @@
       <c r="T610" s="9"/>
       <c r="U610" s="9"/>
     </row>
-    <row r="611" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A611" s="9"/>
       <c r="B611" s="55"/>
       <c r="C611" s="55"/>
@@ -18522,7 +18537,7 @@
       <c r="T611" s="9"/>
       <c r="U611" s="9"/>
     </row>
-    <row r="612" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A612" s="9"/>
       <c r="B612" s="55"/>
       <c r="C612" s="55"/>
@@ -18545,7 +18560,7 @@
       <c r="T612" s="9"/>
       <c r="U612" s="9"/>
     </row>
-    <row r="613" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A613" s="9"/>
       <c r="B613" s="55"/>
       <c r="C613" s="55"/>
@@ -18568,7 +18583,7 @@
       <c r="T613" s="9"/>
       <c r="U613" s="9"/>
     </row>
-    <row r="614" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A614" s="9"/>
       <c r="B614" s="55"/>
       <c r="C614" s="55"/>
@@ -18591,7 +18606,7 @@
       <c r="T614" s="9"/>
       <c r="U614" s="9"/>
     </row>
-    <row r="615" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A615" s="9"/>
       <c r="B615" s="55"/>
       <c r="C615" s="55"/>
@@ -18614,7 +18629,7 @@
       <c r="T615" s="9"/>
       <c r="U615" s="9"/>
     </row>
-    <row r="616" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A616" s="9"/>
       <c r="B616" s="55"/>
       <c r="C616" s="55"/>
@@ -18637,7 +18652,7 @@
       <c r="T616" s="9"/>
       <c r="U616" s="9"/>
     </row>
-    <row r="617" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A617" s="9"/>
       <c r="B617" s="55"/>
       <c r="C617" s="55"/>
@@ -18660,7 +18675,7 @@
       <c r="T617" s="9"/>
       <c r="U617" s="9"/>
     </row>
-    <row r="618" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A618" s="9"/>
       <c r="B618" s="55"/>
       <c r="C618" s="55"/>
@@ -18683,7 +18698,7 @@
       <c r="T618" s="9"/>
       <c r="U618" s="9"/>
     </row>
-    <row r="619" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A619" s="9"/>
       <c r="B619" s="55"/>
       <c r="C619" s="55"/>
@@ -18706,7 +18721,7 @@
       <c r="T619" s="9"/>
       <c r="U619" s="9"/>
     </row>
-    <row r="620" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A620" s="9"/>
       <c r="B620" s="55"/>
       <c r="C620" s="55"/>
@@ -18729,7 +18744,7 @@
       <c r="T620" s="9"/>
       <c r="U620" s="9"/>
     </row>
-    <row r="621" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A621" s="9"/>
       <c r="B621" s="55"/>
       <c r="C621" s="55"/>
@@ -18752,7 +18767,7 @@
       <c r="T621" s="9"/>
       <c r="U621" s="9"/>
     </row>
-    <row r="622" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A622" s="9"/>
       <c r="B622" s="55"/>
       <c r="C622" s="55"/>
@@ -18775,7 +18790,7 @@
       <c r="T622" s="9"/>
       <c r="U622" s="9"/>
     </row>
-    <row r="623" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A623" s="9"/>
       <c r="B623" s="55"/>
       <c r="C623" s="55"/>
@@ -18798,7 +18813,7 @@
       <c r="T623" s="9"/>
       <c r="U623" s="9"/>
     </row>
-    <row r="624" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A624" s="9"/>
       <c r="B624" s="55"/>
       <c r="C624" s="55"/>
@@ -18821,7 +18836,7 @@
       <c r="T624" s="9"/>
       <c r="U624" s="9"/>
     </row>
-    <row r="625" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A625" s="9"/>
       <c r="B625" s="55"/>
       <c r="C625" s="55"/>
@@ -18844,7 +18859,7 @@
       <c r="T625" s="9"/>
       <c r="U625" s="9"/>
     </row>
-    <row r="626" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A626" s="9"/>
       <c r="B626" s="55"/>
       <c r="C626" s="55"/>
@@ -18867,7 +18882,7 @@
       <c r="T626" s="9"/>
       <c r="U626" s="9"/>
     </row>
-    <row r="627" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A627" s="9"/>
       <c r="B627" s="55"/>
       <c r="C627" s="55"/>
@@ -18890,7 +18905,7 @@
       <c r="T627" s="9"/>
       <c r="U627" s="9"/>
     </row>
-    <row r="628" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A628" s="9"/>
       <c r="B628" s="55"/>
       <c r="C628" s="55"/>
@@ -18913,7 +18928,7 @@
       <c r="T628" s="9"/>
       <c r="U628" s="9"/>
     </row>
-    <row r="629" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A629" s="9"/>
       <c r="B629" s="55"/>
       <c r="C629" s="55"/>
@@ -18936,7 +18951,7 @@
       <c r="T629" s="9"/>
       <c r="U629" s="9"/>
     </row>
-    <row r="630" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A630" s="9"/>
       <c r="B630" s="55"/>
       <c r="C630" s="55"/>
@@ -18959,7 +18974,7 @@
       <c r="T630" s="9"/>
       <c r="U630" s="9"/>
     </row>
-    <row r="631" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A631" s="9"/>
       <c r="B631" s="55"/>
       <c r="C631" s="55"/>
@@ -18982,7 +18997,7 @@
       <c r="T631" s="9"/>
       <c r="U631" s="9"/>
     </row>
-    <row r="632" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A632" s="9"/>
       <c r="B632" s="55"/>
       <c r="C632" s="55"/>
@@ -19005,7 +19020,7 @@
       <c r="T632" s="9"/>
       <c r="U632" s="9"/>
     </row>
-    <row r="633" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A633" s="9"/>
       <c r="B633" s="55"/>
       <c r="C633" s="55"/>
@@ -19028,7 +19043,7 @@
       <c r="T633" s="9"/>
       <c r="U633" s="9"/>
     </row>
-    <row r="634" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A634" s="9"/>
       <c r="B634" s="55"/>
       <c r="C634" s="55"/>
@@ -19051,7 +19066,7 @@
       <c r="T634" s="9"/>
       <c r="U634" s="9"/>
     </row>
-    <row r="635" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A635" s="9"/>
       <c r="B635" s="55"/>
       <c r="C635" s="55"/>
@@ -19074,7 +19089,7 @@
       <c r="T635" s="9"/>
       <c r="U635" s="9"/>
     </row>
-    <row r="636" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A636" s="9"/>
       <c r="B636" s="55"/>
       <c r="C636" s="55"/>
@@ -19097,7 +19112,7 @@
       <c r="T636" s="9"/>
       <c r="U636" s="9"/>
     </row>
-    <row r="637" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A637" s="9"/>
       <c r="B637" s="55"/>
       <c r="C637" s="55"/>
@@ -19120,7 +19135,7 @@
       <c r="T637" s="9"/>
       <c r="U637" s="9"/>
     </row>
-    <row r="638" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A638" s="9"/>
       <c r="B638" s="55"/>
       <c r="C638" s="55"/>
@@ -19143,7 +19158,7 @@
       <c r="T638" s="9"/>
       <c r="U638" s="9"/>
     </row>
-    <row r="639" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A639" s="9"/>
       <c r="B639" s="55"/>
       <c r="C639" s="55"/>
@@ -19166,7 +19181,7 @@
       <c r="T639" s="9"/>
       <c r="U639" s="9"/>
     </row>
-    <row r="640" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A640" s="9"/>
       <c r="B640" s="55"/>
       <c r="C640" s="55"/>
@@ -19189,7 +19204,7 @@
       <c r="T640" s="9"/>
       <c r="U640" s="9"/>
     </row>
-    <row r="641" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A641" s="9"/>
       <c r="B641" s="55"/>
       <c r="C641" s="55"/>
@@ -19212,7 +19227,7 @@
       <c r="T641" s="9"/>
       <c r="U641" s="9"/>
     </row>
-    <row r="642" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A642" s="9"/>
       <c r="B642" s="55"/>
       <c r="C642" s="55"/>
@@ -19235,7 +19250,7 @@
       <c r="T642" s="9"/>
       <c r="U642" s="9"/>
     </row>
-    <row r="643" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A643" s="9"/>
       <c r="B643" s="55"/>
       <c r="C643" s="55"/>
@@ -19258,7 +19273,7 @@
       <c r="T643" s="9"/>
       <c r="U643" s="9"/>
     </row>
-    <row r="644" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A644" s="9"/>
       <c r="B644" s="55"/>
       <c r="C644" s="55"/>
@@ -19281,7 +19296,7 @@
       <c r="T644" s="9"/>
       <c r="U644" s="9"/>
     </row>
-    <row r="645" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A645" s="9"/>
       <c r="B645" s="55"/>
       <c r="C645" s="55"/>
@@ -19304,7 +19319,7 @@
       <c r="T645" s="9"/>
       <c r="U645" s="9"/>
     </row>
-    <row r="646" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A646" s="9"/>
       <c r="B646" s="55"/>
       <c r="C646" s="55"/>
@@ -19327,7 +19342,7 @@
       <c r="T646" s="9"/>
       <c r="U646" s="9"/>
     </row>
-    <row r="647" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A647" s="9"/>
       <c r="B647" s="55"/>
       <c r="C647" s="55"/>
@@ -19350,7 +19365,7 @@
       <c r="T647" s="9"/>
       <c r="U647" s="9"/>
     </row>
-    <row r="648" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A648" s="9"/>
       <c r="B648" s="55"/>
       <c r="C648" s="55"/>
@@ -19373,7 +19388,7 @@
       <c r="T648" s="9"/>
       <c r="U648" s="9"/>
     </row>
-    <row r="649" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A649" s="9"/>
       <c r="B649" s="55"/>
       <c r="C649" s="55"/>
@@ -19396,7 +19411,7 @@
       <c r="T649" s="9"/>
       <c r="U649" s="9"/>
     </row>
-    <row r="650" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A650" s="9"/>
       <c r="B650" s="55"/>
       <c r="C650" s="55"/>
@@ -19419,7 +19434,7 @@
       <c r="T650" s="9"/>
       <c r="U650" s="9"/>
     </row>
-    <row r="651" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A651" s="9"/>
       <c r="B651" s="55"/>
       <c r="C651" s="55"/>
@@ -19442,7 +19457,7 @@
       <c r="T651" s="9"/>
       <c r="U651" s="9"/>
     </row>
-    <row r="652" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A652" s="9"/>
       <c r="B652" s="55"/>
       <c r="C652" s="55"/>
@@ -19465,7 +19480,7 @@
       <c r="T652" s="9"/>
       <c r="U652" s="9"/>
     </row>
-    <row r="653" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A653" s="9"/>
       <c r="B653" s="55"/>
       <c r="C653" s="55"/>
@@ -19488,7 +19503,7 @@
       <c r="T653" s="9"/>
       <c r="U653" s="9"/>
     </row>
-    <row r="654" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A654" s="9"/>
       <c r="B654" s="55"/>
       <c r="C654" s="55"/>
@@ -19511,7 +19526,7 @@
       <c r="T654" s="9"/>
       <c r="U654" s="9"/>
     </row>
-    <row r="655" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A655" s="9"/>
       <c r="B655" s="55"/>
       <c r="C655" s="55"/>
@@ -19534,7 +19549,7 @@
       <c r="T655" s="9"/>
       <c r="U655" s="9"/>
     </row>
-    <row r="656" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A656" s="9"/>
       <c r="B656" s="55"/>
       <c r="C656" s="55"/>
@@ -19557,7 +19572,7 @@
       <c r="T656" s="9"/>
       <c r="U656" s="9"/>
     </row>
-    <row r="657" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A657" s="9"/>
       <c r="B657" s="55"/>
       <c r="C657" s="55"/>
@@ -19580,7 +19595,7 @@
       <c r="T657" s="9"/>
       <c r="U657" s="9"/>
     </row>
-    <row r="658" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A658" s="9"/>
       <c r="B658" s="55"/>
       <c r="C658" s="55"/>
@@ -19603,7 +19618,7 @@
       <c r="T658" s="9"/>
       <c r="U658" s="9"/>
     </row>
-    <row r="659" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A659" s="9"/>
       <c r="B659" s="55"/>
       <c r="C659" s="55"/>
@@ -19626,7 +19641,7 @@
       <c r="T659" s="9"/>
       <c r="U659" s="9"/>
     </row>
-    <row r="660" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A660" s="9"/>
       <c r="B660" s="55"/>
       <c r="C660" s="55"/>
@@ -19649,7 +19664,7 @@
       <c r="T660" s="9"/>
       <c r="U660" s="9"/>
     </row>
-    <row r="661" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A661" s="9"/>
       <c r="B661" s="55"/>
       <c r="C661" s="55"/>
@@ -19672,7 +19687,7 @@
       <c r="T661" s="9"/>
       <c r="U661" s="9"/>
     </row>
-    <row r="662" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A662" s="9"/>
       <c r="B662" s="55"/>
       <c r="C662" s="55"/>
@@ -19695,7 +19710,7 @@
       <c r="T662" s="9"/>
       <c r="U662" s="9"/>
     </row>
-    <row r="663" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A663" s="9"/>
       <c r="B663" s="55"/>
       <c r="C663" s="55"/>
@@ -19718,7 +19733,7 @@
       <c r="T663" s="9"/>
       <c r="U663" s="9"/>
     </row>
-    <row r="664" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A664" s="9"/>
       <c r="B664" s="55"/>
       <c r="C664" s="55"/>
@@ -19741,7 +19756,7 @@
       <c r="T664" s="9"/>
       <c r="U664" s="9"/>
     </row>
-    <row r="665" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A665" s="9"/>
       <c r="B665" s="55"/>
       <c r="C665" s="55"/>
@@ -19764,7 +19779,7 @@
       <c r="T665" s="9"/>
       <c r="U665" s="9"/>
     </row>
-    <row r="666" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A666" s="9"/>
       <c r="B666" s="55"/>
       <c r="C666" s="55"/>
@@ -19787,7 +19802,7 @@
       <c r="T666" s="9"/>
       <c r="U666" s="9"/>
     </row>
-    <row r="667" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A667" s="9"/>
       <c r="B667" s="55"/>
       <c r="C667" s="55"/>
@@ -19810,7 +19825,7 @@
       <c r="T667" s="9"/>
       <c r="U667" s="9"/>
     </row>
-    <row r="668" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A668" s="9"/>
       <c r="B668" s="55"/>
       <c r="C668" s="55"/>
@@ -19833,7 +19848,7 @@
       <c r="T668" s="9"/>
       <c r="U668" s="9"/>
     </row>
-    <row r="669" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A669" s="9"/>
       <c r="B669" s="55"/>
       <c r="C669" s="55"/>
@@ -19856,7 +19871,7 @@
       <c r="T669" s="9"/>
       <c r="U669" s="9"/>
     </row>
-    <row r="670" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A670" s="9"/>
       <c r="B670" s="55"/>
       <c r="C670" s="55"/>
@@ -19879,7 +19894,7 @@
       <c r="T670" s="9"/>
       <c r="U670" s="9"/>
     </row>
-    <row r="671" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A671" s="9"/>
       <c r="B671" s="55"/>
       <c r="C671" s="55"/>
@@ -19902,7 +19917,7 @@
       <c r="T671" s="9"/>
       <c r="U671" s="9"/>
     </row>
-    <row r="672" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A672" s="9"/>
       <c r="B672" s="55"/>
       <c r="C672" s="55"/>
@@ -19925,7 +19940,7 @@
       <c r="T672" s="9"/>
       <c r="U672" s="9"/>
     </row>
-    <row r="673" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A673" s="9"/>
       <c r="B673" s="55"/>
       <c r="C673" s="55"/>
@@ -19948,7 +19963,7 @@
       <c r="T673" s="9"/>
       <c r="U673" s="9"/>
     </row>
-    <row r="674" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A674" s="9"/>
       <c r="B674" s="55"/>
       <c r="C674" s="55"/>
@@ -19971,7 +19986,7 @@
       <c r="T674" s="9"/>
       <c r="U674" s="9"/>
     </row>
-    <row r="675" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A675" s="9"/>
       <c r="B675" s="55"/>
       <c r="C675" s="55"/>
@@ -19994,7 +20009,7 @@
       <c r="T675" s="9"/>
       <c r="U675" s="9"/>
     </row>
-    <row r="676" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A676" s="9"/>
       <c r="B676" s="55"/>
       <c r="C676" s="55"/>
@@ -20017,7 +20032,7 @@
       <c r="T676" s="9"/>
       <c r="U676" s="9"/>
     </row>
-    <row r="677" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A677" s="9"/>
       <c r="B677" s="55"/>
       <c r="C677" s="55"/>
@@ -20040,7 +20055,7 @@
       <c r="T677" s="9"/>
       <c r="U677" s="9"/>
     </row>
-    <row r="678" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A678" s="9"/>
       <c r="B678" s="55"/>
       <c r="C678" s="55"/>
@@ -20063,7 +20078,7 @@
       <c r="T678" s="9"/>
       <c r="U678" s="9"/>
     </row>
-    <row r="679" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A679" s="9"/>
       <c r="B679" s="55"/>
       <c r="C679" s="55"/>
@@ -20086,7 +20101,7 @@
       <c r="T679" s="9"/>
       <c r="U679" s="9"/>
     </row>
-    <row r="680" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A680" s="9"/>
       <c r="B680" s="55"/>
       <c r="C680" s="55"/>
@@ -20109,7 +20124,7 @@
       <c r="T680" s="9"/>
       <c r="U680" s="9"/>
     </row>
-    <row r="681" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A681" s="9"/>
       <c r="B681" s="55"/>
       <c r="C681" s="55"/>
@@ -20132,7 +20147,7 @@
       <c r="T681" s="9"/>
       <c r="U681" s="9"/>
     </row>
-    <row r="682" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A682" s="9"/>
       <c r="B682" s="55"/>
       <c r="C682" s="55"/>
@@ -20155,7 +20170,7 @@
       <c r="T682" s="9"/>
       <c r="U682" s="9"/>
     </row>
-    <row r="683" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A683" s="9"/>
       <c r="B683" s="55"/>
       <c r="C683" s="55"/>
@@ -20178,7 +20193,7 @@
       <c r="T683" s="9"/>
       <c r="U683" s="9"/>
     </row>
-    <row r="684" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A684" s="9"/>
       <c r="B684" s="55"/>
       <c r="C684" s="55"/>
@@ -20201,7 +20216,7 @@
       <c r="T684" s="9"/>
       <c r="U684" s="9"/>
     </row>
-    <row r="685" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A685" s="9"/>
       <c r="B685" s="55"/>
       <c r="C685" s="55"/>
@@ -20224,7 +20239,7 @@
       <c r="T685" s="9"/>
       <c r="U685" s="9"/>
     </row>
-    <row r="686" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A686" s="9"/>
       <c r="B686" s="55"/>
       <c r="C686" s="55"/>
@@ -20247,7 +20262,7 @@
       <c r="T686" s="9"/>
       <c r="U686" s="9"/>
     </row>
-    <row r="687" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A687" s="9"/>
       <c r="B687" s="55"/>
       <c r="C687" s="55"/>
@@ -20270,7 +20285,7 @@
       <c r="T687" s="9"/>
       <c r="U687" s="9"/>
     </row>
-    <row r="688" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A688" s="9"/>
       <c r="B688" s="55"/>
       <c r="C688" s="55"/>
@@ -20293,7 +20308,7 @@
       <c r="T688" s="9"/>
       <c r="U688" s="9"/>
     </row>
-    <row r="689" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A689" s="9"/>
       <c r="B689" s="55"/>
       <c r="C689" s="55"/>
@@ -20316,7 +20331,7 @@
       <c r="T689" s="9"/>
       <c r="U689" s="9"/>
     </row>
-    <row r="690" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A690" s="9"/>
       <c r="B690" s="55"/>
       <c r="C690" s="55"/>
@@ -20339,7 +20354,7 @@
       <c r="T690" s="9"/>
       <c r="U690" s="9"/>
     </row>
-    <row r="691" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A691" s="9"/>
       <c r="B691" s="55"/>
       <c r="C691" s="55"/>
@@ -20362,7 +20377,7 @@
       <c r="T691" s="9"/>
       <c r="U691" s="9"/>
     </row>
-    <row r="692" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A692" s="9"/>
       <c r="B692" s="55"/>
       <c r="C692" s="55"/>
@@ -20385,7 +20400,7 @@
       <c r="T692" s="9"/>
       <c r="U692" s="9"/>
     </row>
-    <row r="693" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A693" s="9"/>
       <c r="B693" s="55"/>
       <c r="C693" s="55"/>
@@ -20408,7 +20423,7 @@
       <c r="T693" s="9"/>
       <c r="U693" s="9"/>
     </row>
-    <row r="694" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A694" s="9"/>
       <c r="B694" s="55"/>
       <c r="C694" s="55"/>
@@ -20431,7 +20446,7 @@
       <c r="T694" s="9"/>
       <c r="U694" s="9"/>
     </row>
-    <row r="695" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A695" s="9"/>
       <c r="B695" s="55"/>
       <c r="C695" s="55"/>
@@ -20454,7 +20469,7 @@
       <c r="T695" s="9"/>
       <c r="U695" s="9"/>
     </row>
-    <row r="696" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A696" s="9"/>
       <c r="B696" s="55"/>
       <c r="C696" s="55"/>
@@ -20477,7 +20492,7 @@
       <c r="T696" s="9"/>
       <c r="U696" s="9"/>
     </row>
-    <row r="697" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A697" s="9"/>
       <c r="B697" s="55"/>
       <c r="C697" s="55"/>
@@ -20500,7 +20515,7 @@
       <c r="T697" s="9"/>
       <c r="U697" s="9"/>
     </row>
-    <row r="698" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A698" s="9"/>
       <c r="B698" s="55"/>
       <c r="C698" s="55"/>
@@ -20523,7 +20538,7 @@
       <c r="T698" s="9"/>
       <c r="U698" s="9"/>
     </row>
-    <row r="699" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A699" s="9"/>
       <c r="B699" s="55"/>
       <c r="C699" s="55"/>
@@ -20546,7 +20561,7 @@
       <c r="T699" s="9"/>
       <c r="U699" s="9"/>
     </row>
-    <row r="700" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A700" s="9"/>
       <c r="B700" s="55"/>
       <c r="C700" s="55"/>
@@ -20569,7 +20584,7 @@
       <c r="T700" s="9"/>
       <c r="U700" s="9"/>
     </row>
-    <row r="701" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A701" s="9"/>
       <c r="B701" s="55"/>
       <c r="C701" s="55"/>
@@ -20592,7 +20607,7 @@
       <c r="T701" s="9"/>
       <c r="U701" s="9"/>
     </row>
-    <row r="702" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A702" s="9"/>
       <c r="B702" s="55"/>
       <c r="C702" s="55"/>
@@ -20615,7 +20630,7 @@
       <c r="T702" s="9"/>
       <c r="U702" s="9"/>
     </row>
-    <row r="703" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A703" s="9"/>
       <c r="B703" s="55"/>
       <c r="C703" s="55"/>
@@ -20638,7 +20653,7 @@
       <c r="T703" s="9"/>
       <c r="U703" s="9"/>
     </row>
-    <row r="704" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A704" s="9"/>
       <c r="B704" s="55"/>
       <c r="C704" s="55"/>
@@ -20661,7 +20676,7 @@
       <c r="T704" s="9"/>
       <c r="U704" s="9"/>
     </row>
-    <row r="705" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A705" s="9"/>
       <c r="B705" s="55"/>
       <c r="C705" s="55"/>
@@ -20684,7 +20699,7 @@
       <c r="T705" s="9"/>
       <c r="U705" s="9"/>
     </row>
-    <row r="706" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A706" s="9"/>
       <c r="B706" s="55"/>
       <c r="C706" s="55"/>
@@ -20707,7 +20722,7 @@
       <c r="T706" s="9"/>
       <c r="U706" s="9"/>
     </row>
-    <row r="707" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A707" s="9"/>
       <c r="B707" s="55"/>
       <c r="C707" s="55"/>
@@ -20730,7 +20745,7 @@
       <c r="T707" s="9"/>
       <c r="U707" s="9"/>
     </row>
-    <row r="708" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A708" s="9"/>
       <c r="B708" s="55"/>
       <c r="C708" s="55"/>
@@ -20753,7 +20768,7 @@
       <c r="T708" s="9"/>
       <c r="U708" s="9"/>
     </row>
-    <row r="709" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A709" s="9"/>
       <c r="B709" s="55"/>
       <c r="C709" s="55"/>
@@ -20776,7 +20791,7 @@
       <c r="T709" s="9"/>
       <c r="U709" s="9"/>
     </row>
-    <row r="710" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A710" s="9"/>
       <c r="B710" s="55"/>
       <c r="C710" s="55"/>
@@ -20799,7 +20814,7 @@
       <c r="T710" s="9"/>
       <c r="U710" s="9"/>
     </row>
-    <row r="711" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A711" s="9"/>
       <c r="B711" s="55"/>
       <c r="C711" s="55"/>
@@ -20822,7 +20837,7 @@
       <c r="T711" s="9"/>
       <c r="U711" s="9"/>
     </row>
-    <row r="712" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A712" s="9"/>
       <c r="B712" s="55"/>
       <c r="C712" s="55"/>
@@ -20845,7 +20860,7 @@
       <c r="T712" s="9"/>
       <c r="U712" s="9"/>
     </row>
-    <row r="713" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A713" s="9"/>
       <c r="B713" s="55"/>
       <c r="C713" s="55"/>
@@ -20868,7 +20883,7 @@
       <c r="T713" s="9"/>
       <c r="U713" s="9"/>
     </row>
-    <row r="714" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A714" s="9"/>
       <c r="B714" s="55"/>
       <c r="C714" s="55"/>
@@ -20891,7 +20906,7 @@
       <c r="T714" s="9"/>
       <c r="U714" s="9"/>
     </row>
-    <row r="715" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A715" s="9"/>
       <c r="B715" s="55"/>
       <c r="C715" s="55"/>
@@ -20914,7 +20929,7 @@
       <c r="T715" s="9"/>
       <c r="U715" s="9"/>
     </row>
-    <row r="716" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A716" s="9"/>
       <c r="B716" s="55"/>
       <c r="C716" s="55"/>
@@ -20937,7 +20952,7 @@
       <c r="T716" s="9"/>
       <c r="U716" s="9"/>
     </row>
-    <row r="717" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A717" s="9"/>
       <c r="B717" s="55"/>
       <c r="C717" s="55"/>
@@ -20960,7 +20975,7 @@
       <c r="T717" s="9"/>
       <c r="U717" s="9"/>
     </row>
-    <row r="718" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A718" s="9"/>
       <c r="B718" s="55"/>
       <c r="C718" s="55"/>
@@ -20983,7 +20998,7 @@
       <c r="T718" s="9"/>
       <c r="U718" s="9"/>
     </row>
-    <row r="719" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A719" s="9"/>
       <c r="B719" s="55"/>
       <c r="C719" s="55"/>
@@ -21006,7 +21021,7 @@
       <c r="T719" s="9"/>
       <c r="U719" s="9"/>
     </row>
-    <row r="720" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A720" s="9"/>
       <c r="B720" s="55"/>
       <c r="C720" s="55"/>
@@ -21029,7 +21044,7 @@
       <c r="T720" s="9"/>
       <c r="U720" s="9"/>
     </row>
-    <row r="721" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A721" s="9"/>
       <c r="B721" s="55"/>
       <c r="C721" s="55"/>
@@ -21052,7 +21067,7 @@
       <c r="T721" s="9"/>
       <c r="U721" s="9"/>
     </row>
-    <row r="722" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A722" s="9"/>
       <c r="B722" s="55"/>
       <c r="C722" s="55"/>
@@ -21075,7 +21090,7 @@
       <c r="T722" s="9"/>
       <c r="U722" s="9"/>
     </row>
-    <row r="723" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A723" s="9"/>
       <c r="B723" s="55"/>
       <c r="C723" s="55"/>
@@ -21098,7 +21113,7 @@
       <c r="T723" s="9"/>
       <c r="U723" s="9"/>
     </row>
-    <row r="724" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A724" s="9"/>
       <c r="B724" s="55"/>
       <c r="C724" s="55"/>
@@ -21121,7 +21136,7 @@
       <c r="T724" s="9"/>
       <c r="U724" s="9"/>
     </row>
-    <row r="725" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A725" s="9"/>
       <c r="B725" s="55"/>
       <c r="C725" s="55"/>
@@ -21144,7 +21159,7 @@
       <c r="T725" s="9"/>
       <c r="U725" s="9"/>
     </row>
-    <row r="726" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A726" s="9"/>
       <c r="B726" s="55"/>
       <c r="C726" s="55"/>
@@ -21167,7 +21182,7 @@
       <c r="T726" s="9"/>
       <c r="U726" s="9"/>
     </row>
-    <row r="727" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A727" s="9"/>
       <c r="B727" s="55"/>
       <c r="C727" s="55"/>
@@ -21190,7 +21205,7 @@
       <c r="T727" s="9"/>
       <c r="U727" s="9"/>
     </row>
-    <row r="728" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A728" s="9"/>
       <c r="B728" s="55"/>
       <c r="C728" s="55"/>
@@ -21213,7 +21228,7 @@
       <c r="T728" s="9"/>
       <c r="U728" s="9"/>
     </row>
-    <row r="729" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A729" s="9"/>
       <c r="B729" s="55"/>
       <c r="C729" s="55"/>
@@ -21236,7 +21251,7 @@
       <c r="T729" s="9"/>
       <c r="U729" s="9"/>
     </row>
-    <row r="730" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A730" s="9"/>
       <c r="B730" s="55"/>
       <c r="C730" s="55"/>
@@ -21259,7 +21274,7 @@
       <c r="T730" s="9"/>
       <c r="U730" s="9"/>
     </row>
-    <row r="731" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A731" s="9"/>
       <c r="B731" s="55"/>
       <c r="C731" s="55"/>
@@ -21282,7 +21297,7 @@
       <c r="T731" s="9"/>
       <c r="U731" s="9"/>
     </row>
-    <row r="732" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A732" s="9"/>
       <c r="B732" s="55"/>
       <c r="C732" s="55"/>
@@ -21305,7 +21320,7 @@
       <c r="T732" s="9"/>
       <c r="U732" s="9"/>
     </row>
-    <row r="733" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A733" s="9"/>
       <c r="B733" s="55"/>
       <c r="C733" s="55"/>
@@ -21328,7 +21343,7 @@
       <c r="T733" s="9"/>
       <c r="U733" s="9"/>
     </row>
-    <row r="734" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A734" s="9"/>
       <c r="B734" s="55"/>
       <c r="C734" s="55"/>
@@ -21351,7 +21366,7 @@
       <c r="T734" s="9"/>
       <c r="U734" s="9"/>
     </row>
-    <row r="735" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A735" s="9"/>
       <c r="B735" s="55"/>
       <c r="C735" s="55"/>
@@ -21374,7 +21389,7 @@
       <c r="T735" s="9"/>
       <c r="U735" s="9"/>
     </row>
-    <row r="736" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A736" s="9"/>
       <c r="B736" s="55"/>
       <c r="C736" s="55"/>
@@ -21397,7 +21412,7 @@
       <c r="T736" s="9"/>
       <c r="U736" s="9"/>
     </row>
-    <row r="737" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A737" s="9"/>
       <c r="B737" s="55"/>
       <c r="C737" s="55"/>
@@ -21420,7 +21435,7 @@
       <c r="T737" s="9"/>
       <c r="U737" s="9"/>
     </row>
-    <row r="738" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A738" s="9"/>
       <c r="B738" s="55"/>
       <c r="C738" s="55"/>
@@ -21443,7 +21458,7 @@
       <c r="T738" s="9"/>
       <c r="U738" s="9"/>
     </row>
-    <row r="739" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A739" s="9"/>
       <c r="B739" s="55"/>
       <c r="C739" s="55"/>
@@ -21466,7 +21481,7 @@
       <c r="T739" s="9"/>
       <c r="U739" s="9"/>
     </row>
-    <row r="740" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A740" s="9"/>
       <c r="B740" s="55"/>
       <c r="C740" s="55"/>
@@ -21489,7 +21504,7 @@
       <c r="T740" s="9"/>
       <c r="U740" s="9"/>
     </row>
-    <row r="741" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A741" s="9"/>
       <c r="B741" s="55"/>
       <c r="C741" s="55"/>
@@ -21512,7 +21527,7 @@
       <c r="T741" s="9"/>
       <c r="U741" s="9"/>
     </row>
-    <row r="742" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A742" s="9"/>
       <c r="B742" s="55"/>
       <c r="C742" s="55"/>
@@ -21535,7 +21550,7 @@
       <c r="T742" s="9"/>
       <c r="U742" s="9"/>
     </row>
-    <row r="743" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A743" s="9"/>
       <c r="B743" s="55"/>
       <c r="C743" s="55"/>
@@ -21558,7 +21573,7 @@
       <c r="T743" s="9"/>
       <c r="U743" s="9"/>
     </row>
-    <row r="744" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A744" s="9"/>
       <c r="B744" s="55"/>
       <c r="C744" s="55"/>
@@ -21581,7 +21596,7 @@
       <c r="T744" s="9"/>
       <c r="U744" s="9"/>
     </row>
-    <row r="745" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A745" s="9"/>
       <c r="B745" s="55"/>
       <c r="C745" s="55"/>
@@ -21604,7 +21619,7 @@
       <c r="T745" s="9"/>
       <c r="U745" s="9"/>
     </row>
-    <row r="746" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A746" s="9"/>
       <c r="B746" s="55"/>
       <c r="C746" s="55"/>
@@ -21627,7 +21642,7 @@
       <c r="T746" s="9"/>
       <c r="U746" s="9"/>
     </row>
-    <row r="747" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A747" s="9"/>
       <c r="B747" s="55"/>
       <c r="C747" s="55"/>
@@ -21650,7 +21665,7 @@
       <c r="T747" s="9"/>
       <c r="U747" s="9"/>
     </row>
-    <row r="748" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A748" s="9"/>
       <c r="B748" s="55"/>
       <c r="C748" s="55"/>
@@ -21673,7 +21688,7 @@
       <c r="T748" s="9"/>
       <c r="U748" s="9"/>
     </row>
-    <row r="749" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A749" s="9"/>
       <c r="B749" s="55"/>
       <c r="C749" s="55"/>
@@ -21696,7 +21711,7 @@
       <c r="T749" s="9"/>
       <c r="U749" s="9"/>
     </row>
-    <row r="750" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A750" s="9"/>
       <c r="B750" s="55"/>
       <c r="C750" s="55"/>
@@ -21719,7 +21734,7 @@
       <c r="T750" s="9"/>
       <c r="U750" s="9"/>
     </row>
-    <row r="751" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A751" s="9"/>
       <c r="B751" s="55"/>
       <c r="C751" s="55"/>
@@ -21742,7 +21757,7 @@
       <c r="T751" s="9"/>
       <c r="U751" s="9"/>
     </row>
-    <row r="752" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A752" s="9"/>
       <c r="B752" s="55"/>
       <c r="C752" s="55"/>
@@ -21765,7 +21780,7 @@
       <c r="T752" s="9"/>
       <c r="U752" s="9"/>
     </row>
-    <row r="753" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A753" s="9"/>
       <c r="B753" s="55"/>
       <c r="C753" s="55"/>
@@ -21788,7 +21803,7 @@
       <c r="T753" s="9"/>
       <c r="U753" s="9"/>
     </row>
-    <row r="754" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A754" s="9"/>
       <c r="B754" s="55"/>
       <c r="C754" s="55"/>
@@ -21811,7 +21826,7 @@
       <c r="T754" s="9"/>
       <c r="U754" s="9"/>
     </row>
-    <row r="755" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A755" s="9"/>
       <c r="B755" s="55"/>
       <c r="C755" s="55"/>
@@ -21834,7 +21849,7 @@
       <c r="T755" s="9"/>
       <c r="U755" s="9"/>
     </row>
-    <row r="756" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A756" s="9"/>
       <c r="B756" s="55"/>
       <c r="C756" s="55"/>
@@ -21857,7 +21872,7 @@
       <c r="T756" s="9"/>
       <c r="U756" s="9"/>
     </row>
-    <row r="757" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A757" s="9"/>
       <c r="B757" s="55"/>
       <c r="C757" s="55"/>
@@ -21880,7 +21895,7 @@
       <c r="T757" s="9"/>
       <c r="U757" s="9"/>
     </row>
-    <row r="758" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A758" s="9"/>
       <c r="B758" s="55"/>
       <c r="C758" s="55"/>
@@ -21903,7 +21918,7 @@
       <c r="T758" s="9"/>
       <c r="U758" s="9"/>
     </row>
-    <row r="759" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A759" s="9"/>
       <c r="B759" s="55"/>
       <c r="C759" s="55"/>
@@ -21926,7 +21941,7 @@
       <c r="T759" s="9"/>
       <c r="U759" s="9"/>
     </row>
-    <row r="760" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A760" s="9"/>
       <c r="B760" s="55"/>
       <c r="C760" s="55"/>
@@ -21949,7 +21964,7 @@
       <c r="T760" s="9"/>
       <c r="U760" s="9"/>
     </row>
-    <row r="761" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A761" s="9"/>
       <c r="B761" s="55"/>
       <c r="C761" s="55"/>
@@ -21972,7 +21987,7 @@
       <c r="T761" s="9"/>
       <c r="U761" s="9"/>
     </row>
-    <row r="762" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A762" s="9"/>
       <c r="B762" s="55"/>
       <c r="C762" s="55"/>
@@ -21995,7 +22010,7 @@
       <c r="T762" s="9"/>
       <c r="U762" s="9"/>
     </row>
-    <row r="763" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A763" s="9"/>
       <c r="B763" s="55"/>
       <c r="C763" s="55"/>
@@ -22018,7 +22033,7 @@
       <c r="T763" s="9"/>
       <c r="U763" s="9"/>
     </row>
-    <row r="764" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A764" s="9"/>
       <c r="B764" s="55"/>
       <c r="C764" s="55"/>
@@ -22041,7 +22056,7 @@
       <c r="T764" s="9"/>
       <c r="U764" s="9"/>
     </row>
-    <row r="765" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A765" s="9"/>
       <c r="B765" s="55"/>
       <c r="C765" s="55"/>
@@ -22064,7 +22079,7 @@
       <c r="T765" s="9"/>
       <c r="U765" s="9"/>
     </row>
-    <row r="766" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A766" s="9"/>
       <c r="B766" s="55"/>
       <c r="C766" s="55"/>
@@ -22087,7 +22102,7 @@
       <c r="T766" s="9"/>
       <c r="U766" s="9"/>
     </row>
-    <row r="767" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A767" s="9"/>
       <c r="B767" s="55"/>
       <c r="C767" s="55"/>
@@ -22110,7 +22125,7 @@
       <c r="T767" s="9"/>
       <c r="U767" s="9"/>
     </row>
-    <row r="768" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A768" s="9"/>
       <c r="B768" s="55"/>
       <c r="C768" s="55"/>
@@ -22133,7 +22148,7 @@
       <c r="T768" s="9"/>
       <c r="U768" s="9"/>
     </row>
-    <row r="769" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A769" s="9"/>
       <c r="B769" s="55"/>
       <c r="C769" s="55"/>
@@ -22156,7 +22171,7 @@
       <c r="T769" s="9"/>
       <c r="U769" s="9"/>
     </row>
-    <row r="770" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A770" s="9"/>
       <c r="B770" s="55"/>
       <c r="C770" s="55"/>
@@ -22179,7 +22194,7 @@
       <c r="T770" s="9"/>
       <c r="U770" s="9"/>
     </row>
-    <row r="771" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A771" s="9"/>
       <c r="B771" s="55"/>
       <c r="C771" s="55"/>
@@ -22202,7 +22217,7 @@
       <c r="T771" s="9"/>
       <c r="U771" s="9"/>
     </row>
-    <row r="772" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A772" s="9"/>
       <c r="B772" s="55"/>
       <c r="C772" s="55"/>
@@ -22225,7 +22240,7 @@
       <c r="T772" s="9"/>
       <c r="U772" s="9"/>
     </row>
-    <row r="773" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A773" s="9"/>
       <c r="B773" s="55"/>
       <c r="C773" s="55"/>
@@ -22248,7 +22263,7 @@
       <c r="T773" s="9"/>
       <c r="U773" s="9"/>
     </row>
-    <row r="774" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A774" s="9"/>
       <c r="B774" s="55"/>
       <c r="C774" s="55"/>
@@ -22271,7 +22286,7 @@
       <c r="T774" s="9"/>
       <c r="U774" s="9"/>
     </row>
-    <row r="775" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A775" s="9"/>
       <c r="B775" s="55"/>
       <c r="C775" s="55"/>
@@ -22294,7 +22309,7 @@
       <c r="T775" s="9"/>
       <c r="U775" s="9"/>
     </row>
-    <row r="776" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A776" s="9"/>
       <c r="B776" s="55"/>
       <c r="C776" s="55"/>
@@ -22317,7 +22332,7 @@
       <c r="T776" s="9"/>
       <c r="U776" s="9"/>
     </row>
-    <row r="777" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A777" s="9"/>
       <c r="B777" s="55"/>
       <c r="C777" s="55"/>
@@ -22340,7 +22355,7 @@
       <c r="T777" s="9"/>
       <c r="U777" s="9"/>
     </row>
-    <row r="778" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A778" s="9"/>
       <c r="B778" s="55"/>
       <c r="C778" s="55"/>
@@ -22363,7 +22378,7 @@
       <c r="T778" s="9"/>
       <c r="U778" s="9"/>
     </row>
-    <row r="779" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A779" s="9"/>
       <c r="B779" s="55"/>
       <c r="C779" s="55"/>
@@ -22386,7 +22401,7 @@
       <c r="T779" s="9"/>
       <c r="U779" s="9"/>
     </row>
-    <row r="780" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A780" s="9"/>
       <c r="B780" s="55"/>
       <c r="C780" s="55"/>
@@ -22409,7 +22424,7 @@
       <c r="T780" s="9"/>
       <c r="U780" s="9"/>
     </row>
-    <row r="781" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A781" s="9"/>
       <c r="B781" s="55"/>
       <c r="C781" s="55"/>
@@ -22432,7 +22447,7 @@
       <c r="T781" s="9"/>
       <c r="U781" s="9"/>
     </row>
-    <row r="782" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A782" s="9"/>
       <c r="B782" s="55"/>
       <c r="C782" s="55"/>
@@ -22455,7 +22470,7 @@
       <c r="T782" s="9"/>
       <c r="U782" s="9"/>
     </row>
-    <row r="783" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A783" s="9"/>
       <c r="B783" s="55"/>
       <c r="C783" s="55"/>
@@ -22478,7 +22493,7 @@
       <c r="T783" s="9"/>
       <c r="U783" s="9"/>
     </row>
-    <row r="784" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A784" s="9"/>
       <c r="B784" s="55"/>
       <c r="C784" s="55"/>
@@ -22501,7 +22516,7 @@
       <c r="T784" s="9"/>
       <c r="U784" s="9"/>
     </row>
-    <row r="785" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A785" s="9"/>
       <c r="B785" s="55"/>
       <c r="C785" s="55"/>
@@ -22524,7 +22539,7 @@
       <c r="T785" s="9"/>
       <c r="U785" s="9"/>
     </row>
-    <row r="786" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A786" s="9"/>
       <c r="B786" s="55"/>
       <c r="C786" s="55"/>
@@ -22547,7 +22562,7 @@
       <c r="T786" s="9"/>
       <c r="U786" s="9"/>
     </row>
-    <row r="787" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A787" s="9"/>
       <c r="B787" s="55"/>
       <c r="C787" s="55"/>
@@ -22570,7 +22585,7 @@
       <c r="T787" s="9"/>
       <c r="U787" s="9"/>
     </row>
-    <row r="788" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A788" s="9"/>
       <c r="B788" s="55"/>
       <c r="C788" s="55"/>
@@ -22593,7 +22608,7 @@
       <c r="T788" s="9"/>
       <c r="U788" s="9"/>
     </row>
-    <row r="789" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A789" s="9"/>
       <c r="B789" s="55"/>
       <c r="C789" s="55"/>
@@ -22616,7 +22631,7 @@
       <c r="T789" s="9"/>
       <c r="U789" s="9"/>
     </row>
-    <row r="790" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A790" s="9"/>
       <c r="B790" s="55"/>
       <c r="C790" s="55"/>
@@ -22639,7 +22654,7 @@
       <c r="T790" s="9"/>
       <c r="U790" s="9"/>
     </row>
-    <row r="791" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A791" s="9"/>
       <c r="B791" s="55"/>
       <c r="C791" s="55"/>
@@ -22662,7 +22677,7 @@
       <c r="T791" s="9"/>
       <c r="U791" s="9"/>
     </row>
-    <row r="792" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A792" s="9"/>
       <c r="B792" s="55"/>
       <c r="C792" s="55"/>
@@ -22685,7 +22700,7 @@
       <c r="T792" s="9"/>
       <c r="U792" s="9"/>
     </row>
-    <row r="793" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A793" s="9"/>
       <c r="B793" s="55"/>
       <c r="C793" s="55"/>
@@ -22708,7 +22723,7 @@
       <c r="T793" s="9"/>
       <c r="U793" s="9"/>
     </row>
-    <row r="794" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A794" s="9"/>
       <c r="B794" s="55"/>
       <c r="C794" s="55"/>
@@ -22731,7 +22746,7 @@
       <c r="T794" s="9"/>
       <c r="U794" s="9"/>
     </row>
-    <row r="795" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A795" s="9"/>
       <c r="B795" s="55"/>
       <c r="C795" s="55"/>
@@ -22754,7 +22769,7 @@
       <c r="T795" s="9"/>
       <c r="U795" s="9"/>
     </row>
-    <row r="796" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A796" s="9"/>
       <c r="B796" s="55"/>
       <c r="C796" s="55"/>
@@ -22777,7 +22792,7 @@
       <c r="T796" s="9"/>
       <c r="U796" s="9"/>
     </row>
-    <row r="797" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A797" s="9"/>
       <c r="B797" s="55"/>
       <c r="C797" s="55"/>
@@ -22800,7 +22815,7 @@
       <c r="T797" s="9"/>
       <c r="U797" s="9"/>
     </row>
-    <row r="798" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A798" s="9"/>
       <c r="B798" s="55"/>
       <c r="C798" s="55"/>
@@ -22823,7 +22838,7 @@
       <c r="T798" s="9"/>
       <c r="U798" s="9"/>
     </row>
-    <row r="799" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A799" s="9"/>
       <c r="B799" s="55"/>
       <c r="C799" s="55"/>
@@ -22846,7 +22861,7 @@
       <c r="T799" s="9"/>
       <c r="U799" s="9"/>
     </row>
-    <row r="800" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A800" s="9"/>
       <c r="B800" s="55"/>
       <c r="C800" s="55"/>
@@ -22869,7 +22884,7 @@
       <c r="T800" s="9"/>
       <c r="U800" s="9"/>
     </row>
-    <row r="801" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A801" s="9"/>
       <c r="B801" s="55"/>
       <c r="C801" s="55"/>
@@ -22892,7 +22907,7 @@
       <c r="T801" s="9"/>
       <c r="U801" s="9"/>
     </row>
-    <row r="802" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A802" s="9"/>
       <c r="B802" s="55"/>
       <c r="C802" s="55"/>
@@ -22915,7 +22930,7 @@
       <c r="T802" s="9"/>
       <c r="U802" s="9"/>
     </row>
-    <row r="803" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A803" s="9"/>
       <c r="B803" s="55"/>
       <c r="C803" s="55"/>
@@ -22938,7 +22953,7 @@
       <c r="T803" s="9"/>
       <c r="U803" s="9"/>
     </row>
-    <row r="804" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A804" s="9"/>
       <c r="B804" s="55"/>
       <c r="C804" s="55"/>
@@ -22961,7 +22976,7 @@
       <c r="T804" s="9"/>
       <c r="U804" s="9"/>
     </row>
-    <row r="805" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A805" s="9"/>
       <c r="B805" s="55"/>
       <c r="C805" s="55"/>
@@ -22984,7 +22999,7 @@
       <c r="T805" s="9"/>
       <c r="U805" s="9"/>
     </row>
-    <row r="806" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A806" s="9"/>
       <c r="B806" s="55"/>
       <c r="C806" s="55"/>
@@ -23007,7 +23022,7 @@
       <c r="T806" s="9"/>
       <c r="U806" s="9"/>
     </row>
-    <row r="807" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A807" s="9"/>
       <c r="B807" s="55"/>
       <c r="C807" s="55"/>
@@ -23030,7 +23045,7 @@
       <c r="T807" s="9"/>
       <c r="U807" s="9"/>
     </row>
-    <row r="808" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A808" s="9"/>
       <c r="B808" s="55"/>
       <c r="C808" s="55"/>
@@ -23053,7 +23068,7 @@
       <c r="T808" s="9"/>
       <c r="U808" s="9"/>
     </row>
-    <row r="809" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A809" s="9"/>
       <c r="B809" s="55"/>
       <c r="C809" s="55"/>
@@ -23076,7 +23091,7 @@
       <c r="T809" s="9"/>
       <c r="U809" s="9"/>
     </row>
-    <row r="810" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A810" s="9"/>
       <c r="B810" s="55"/>
       <c r="C810" s="55"/>
@@ -23099,7 +23114,7 @@
       <c r="T810" s="9"/>
       <c r="U810" s="9"/>
     </row>
-    <row r="811" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A811" s="9"/>
       <c r="B811" s="55"/>
       <c r="C811" s="55"/>
@@ -23122,7 +23137,7 @@
       <c r="T811" s="9"/>
       <c r="U811" s="9"/>
     </row>
-    <row r="812" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A812" s="9"/>
       <c r="B812" s="55"/>
       <c r="C812" s="55"/>
@@ -23145,7 +23160,7 @@
       <c r="T812" s="9"/>
       <c r="U812" s="9"/>
     </row>
-    <row r="813" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A813" s="9"/>
       <c r="B813" s="55"/>
       <c r="C813" s="55"/>
@@ -23168,7 +23183,7 @@
       <c r="T813" s="9"/>
       <c r="U813" s="9"/>
     </row>
-    <row r="814" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A814" s="9"/>
       <c r="B814" s="55"/>
       <c r="C814" s="55"/>
@@ -23191,7 +23206,7 @@
       <c r="T814" s="9"/>
       <c r="U814" s="9"/>
     </row>
-    <row r="815" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A815" s="9"/>
       <c r="B815" s="55"/>
       <c r="C815" s="55"/>
@@ -23214,7 +23229,7 @@
       <c r="T815" s="9"/>
       <c r="U815" s="9"/>
     </row>
-    <row r="816" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A816" s="9"/>
       <c r="B816" s="55"/>
       <c r="C816" s="55"/>
@@ -23237,7 +23252,7 @@
       <c r="T816" s="9"/>
       <c r="U816" s="9"/>
     </row>
-    <row r="817" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A817" s="9"/>
       <c r="B817" s="55"/>
       <c r="C817" s="55"/>
@@ -23260,7 +23275,7 @@
       <c r="T817" s="9"/>
       <c r="U817" s="9"/>
     </row>
-    <row r="818" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A818" s="9"/>
       <c r="B818" s="55"/>
       <c r="C818" s="55"/>
@@ -23283,7 +23298,7 @@
       <c r="T818" s="9"/>
       <c r="U818" s="9"/>
     </row>
-    <row r="819" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A819" s="9"/>
       <c r="B819" s="55"/>
       <c r="C819" s="55"/>
@@ -23306,7 +23321,7 @@
       <c r="T819" s="9"/>
       <c r="U819" s="9"/>
     </row>
-    <row r="820" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A820" s="9"/>
       <c r="B820" s="55"/>
       <c r="C820" s="55"/>
@@ -23329,7 +23344,7 @@
       <c r="T820" s="9"/>
       <c r="U820" s="9"/>
     </row>
-    <row r="821" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A821" s="9"/>
       <c r="B821" s="55"/>
       <c r="C821" s="55"/>
@@ -23352,7 +23367,7 @@
       <c r="T821" s="9"/>
       <c r="U821" s="9"/>
     </row>
-    <row r="822" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A822" s="9"/>
       <c r="B822" s="55"/>
       <c r="C822" s="55"/>
@@ -23375,7 +23390,7 @@
       <c r="T822" s="9"/>
       <c r="U822" s="9"/>
     </row>
-    <row r="823" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A823" s="9"/>
       <c r="B823" s="55"/>
       <c r="C823" s="55"/>
@@ -23398,7 +23413,7 @@
       <c r="T823" s="9"/>
       <c r="U823" s="9"/>
     </row>
-    <row r="824" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A824" s="9"/>
       <c r="B824" s="55"/>
       <c r="C824" s="55"/>
@@ -23421,7 +23436,7 @@
       <c r="T824" s="9"/>
       <c r="U824" s="9"/>
     </row>
-    <row r="825" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A825" s="9"/>
       <c r="B825" s="55"/>
       <c r="C825" s="55"/>
@@ -23444,7 +23459,7 @@
       <c r="T825" s="9"/>
       <c r="U825" s="9"/>
     </row>
-    <row r="826" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A826" s="9"/>
       <c r="B826" s="55"/>
       <c r="C826" s="55"/>
@@ -23467,7 +23482,7 @@
       <c r="T826" s="9"/>
       <c r="U826" s="9"/>
     </row>
-    <row r="827" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A827" s="9"/>
       <c r="B827" s="55"/>
       <c r="C827" s="55"/>
@@ -23490,7 +23505,7 @@
       <c r="T827" s="9"/>
       <c r="U827" s="9"/>
     </row>
-    <row r="828" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A828" s="9"/>
       <c r="B828" s="55"/>
       <c r="C828" s="55"/>
@@ -23513,7 +23528,7 @@
       <c r="T828" s="9"/>
       <c r="U828" s="9"/>
     </row>
-    <row r="829" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A829" s="9"/>
       <c r="B829" s="55"/>
       <c r="C829" s="55"/>
@@ -23536,7 +23551,7 @@
       <c r="T829" s="9"/>
       <c r="U829" s="9"/>
     </row>
-    <row r="830" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A830" s="9"/>
       <c r="B830" s="55"/>
       <c r="C830" s="55"/>
@@ -23559,7 +23574,7 @@
       <c r="T830" s="9"/>
       <c r="U830" s="9"/>
     </row>
-    <row r="831" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A831" s="9"/>
       <c r="B831" s="55"/>
       <c r="C831" s="55"/>
@@ -23582,7 +23597,7 @@
       <c r="T831" s="9"/>
       <c r="U831" s="9"/>
     </row>
-    <row r="832" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A832" s="9"/>
       <c r="B832" s="55"/>
       <c r="C832" s="55"/>
@@ -23605,7 +23620,7 @@
       <c r="T832" s="9"/>
       <c r="U832" s="9"/>
     </row>
-    <row r="833" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A833" s="9"/>
       <c r="B833" s="55"/>
       <c r="C833" s="55"/>
@@ -23628,7 +23643,7 @@
       <c r="T833" s="9"/>
       <c r="U833" s="9"/>
     </row>
-    <row r="834" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A834" s="9"/>
       <c r="B834" s="55"/>
       <c r="C834" s="55"/>
@@ -23651,7 +23666,7 @@
       <c r="T834" s="9"/>
       <c r="U834" s="9"/>
     </row>
-    <row r="835" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A835" s="9"/>
       <c r="B835" s="55"/>
       <c r="C835" s="55"/>
@@ -23674,7 +23689,7 @@
       <c r="T835" s="9"/>
       <c r="U835" s="9"/>
     </row>
-    <row r="836" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A836" s="9"/>
       <c r="B836" s="55"/>
       <c r="C836" s="55"/>
@@ -23697,7 +23712,7 @@
       <c r="T836" s="9"/>
       <c r="U836" s="9"/>
     </row>
-    <row r="837" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A837" s="9"/>
       <c r="B837" s="55"/>
       <c r="C837" s="55"/>
@@ -23720,7 +23735,7 @@
       <c r="T837" s="9"/>
       <c r="U837" s="9"/>
     </row>
-    <row r="838" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A838" s="9"/>
       <c r="B838" s="55"/>
       <c r="C838" s="55"/>
@@ -23743,7 +23758,7 @@
       <c r="T838" s="9"/>
       <c r="U838" s="9"/>
     </row>
-    <row r="839" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A839" s="9"/>
       <c r="B839" s="55"/>
       <c r="C839" s="55"/>
@@ -23766,7 +23781,7 @@
       <c r="T839" s="9"/>
       <c r="U839" s="9"/>
     </row>
-    <row r="840" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A840" s="9"/>
       <c r="B840" s="55"/>
       <c r="C840" s="55"/>
@@ -23789,7 +23804,7 @@
       <c r="T840" s="9"/>
       <c r="U840" s="9"/>
     </row>
-    <row r="841" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A841" s="9"/>
       <c r="B841" s="55"/>
       <c r="C841" s="55"/>
@@ -23812,7 +23827,7 @@
       <c r="T841" s="9"/>
       <c r="U841" s="9"/>
     </row>
-    <row r="842" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A842" s="9"/>
       <c r="B842" s="55"/>
       <c r="C842" s="55"/>
@@ -23835,7 +23850,7 @@
       <c r="T842" s="9"/>
       <c r="U842" s="9"/>
     </row>
-    <row r="843" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A843" s="9"/>
       <c r="B843" s="55"/>
       <c r="C843" s="55"/>
@@ -23858,7 +23873,7 @@
       <c r="T843" s="9"/>
       <c r="U843" s="9"/>
     </row>
-    <row r="844" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A844" s="9"/>
       <c r="B844" s="55"/>
       <c r="C844" s="55"/>
@@ -23881,7 +23896,7 @@
       <c r="T844" s="9"/>
       <c r="U844" s="9"/>
     </row>
-    <row r="845" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A845" s="9"/>
       <c r="B845" s="55"/>
       <c r="C845" s="55"/>
@@ -23904,7 +23919,7 @@
       <c r="T845" s="9"/>
       <c r="U845" s="9"/>
     </row>
-    <row r="846" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A846" s="9"/>
       <c r="B846" s="55"/>
       <c r="C846" s="55"/>
@@ -23927,7 +23942,7 @@
       <c r="T846" s="9"/>
       <c r="U846" s="9"/>
     </row>
-    <row r="847" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A847" s="9"/>
       <c r="B847" s="55"/>
       <c r="C847" s="55"/>
@@ -23950,7 +23965,7 @@
       <c r="T847" s="9"/>
       <c r="U847" s="9"/>
     </row>
-    <row r="848" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A848" s="9"/>
       <c r="B848" s="55"/>
       <c r="C848" s="55"/>
@@ -23973,7 +23988,7 @@
       <c r="T848" s="9"/>
       <c r="U848" s="9"/>
     </row>
-    <row r="849" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A849" s="9"/>
       <c r="B849" s="55"/>
       <c r="C849" s="55"/>
@@ -23996,7 +24011,7 @@
       <c r="T849" s="9"/>
       <c r="U849" s="9"/>
     </row>
-    <row r="850" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A850" s="9"/>
       <c r="B850" s="55"/>
       <c r="C850" s="55"/>
@@ -24019,7 +24034,7 @@
       <c r="T850" s="9"/>
       <c r="U850" s="9"/>
     </row>
-    <row r="851" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A851" s="9"/>
       <c r="B851" s="55"/>
       <c r="C851" s="55"/>
@@ -24042,7 +24057,7 @@
       <c r="T851" s="9"/>
       <c r="U851" s="9"/>
     </row>
-    <row r="852" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A852" s="9"/>
       <c r="B852" s="55"/>
       <c r="C852" s="55"/>
@@ -24065,7 +24080,7 @@
       <c r="T852" s="9"/>
       <c r="U852" s="9"/>
     </row>
-    <row r="853" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A853" s="9"/>
       <c r="B853" s="55"/>
       <c r="C853" s="55"/>
@@ -24088,7 +24103,7 @@
       <c r="T853" s="9"/>
       <c r="U853" s="9"/>
     </row>
-    <row r="854" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A854" s="9"/>
       <c r="B854" s="55"/>
       <c r="C854" s="55"/>
@@ -24111,7 +24126,7 @@
       <c r="T854" s="9"/>
       <c r="U854" s="9"/>
     </row>
-    <row r="855" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A855" s="9"/>
       <c r="B855" s="55"/>
       <c r="C855" s="55"/>
@@ -24134,7 +24149,7 @@
       <c r="T855" s="9"/>
       <c r="U855" s="9"/>
     </row>
-    <row r="856" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A856" s="9"/>
       <c r="B856" s="55"/>
       <c r="C856" s="55"/>
@@ -24157,7 +24172,7 @@
       <c r="T856" s="9"/>
       <c r="U856" s="9"/>
     </row>
-    <row r="857" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A857" s="9"/>
       <c r="B857" s="55"/>
       <c r="C857" s="55"/>
@@ -24180,7 +24195,7 @@
       <c r="T857" s="9"/>
       <c r="U857" s="9"/>
     </row>
-    <row r="858" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A858" s="9"/>
       <c r="B858" s="55"/>
       <c r="C858" s="55"/>
@@ -24203,7 +24218,7 @@
       <c r="T858" s="9"/>
       <c r="U858" s="9"/>
     </row>
-    <row r="859" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A859" s="9"/>
       <c r="B859" s="55"/>
       <c r="C859" s="55"/>
@@ -24226,7 +24241,7 @@
       <c r="T859" s="9"/>
       <c r="U859" s="9"/>
     </row>
-    <row r="860" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A860" s="9"/>
       <c r="B860" s="55"/>
       <c r="C860" s="55"/>
@@ -24249,7 +24264,7 @@
       <c r="T860" s="9"/>
       <c r="U860" s="9"/>
     </row>
-    <row r="861" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A861" s="9"/>
       <c r="B861" s="55"/>
       <c r="C861" s="55"/>
@@ -24272,7 +24287,7 @@
       <c r="T861" s="9"/>
       <c r="U861" s="9"/>
     </row>
-    <row r="862" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A862" s="9"/>
       <c r="B862" s="55"/>
       <c r="C862" s="55"/>
@@ -24295,7 +24310,7 @@
       <c r="T862" s="9"/>
       <c r="U862" s="9"/>
     </row>
-    <row r="863" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A863" s="9"/>
       <c r="B863" s="55"/>
       <c r="C863" s="55"/>
@@ -24318,7 +24333,7 @@
       <c r="T863" s="9"/>
       <c r="U863" s="9"/>
     </row>
-    <row r="864" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A864" s="9"/>
       <c r="B864" s="55"/>
       <c r="C864" s="55"/>
@@ -24341,7 +24356,7 @@
       <c r="T864" s="9"/>
       <c r="U864" s="9"/>
     </row>
-    <row r="865" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A865" s="9"/>
       <c r="B865" s="55"/>
       <c r="C865" s="55"/>
@@ -24364,7 +24379,7 @@
       <c r="T865" s="9"/>
       <c r="U865" s="9"/>
     </row>
-    <row r="866" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A866" s="9"/>
       <c r="B866" s="55"/>
       <c r="C866" s="55"/>
@@ -24387,7 +24402,7 @@
       <c r="T866" s="9"/>
       <c r="U866" s="9"/>
     </row>
-    <row r="867" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A867" s="9"/>
       <c r="B867" s="55"/>
       <c r="C867" s="55"/>
@@ -24410,7 +24425,7 @@
       <c r="T867" s="9"/>
       <c r="U867" s="9"/>
     </row>
-    <row r="868" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A868" s="9"/>
       <c r="B868" s="55"/>
       <c r="C868" s="55"/>
@@ -24433,7 +24448,7 @@
       <c r="T868" s="9"/>
       <c r="U868" s="9"/>
     </row>
-    <row r="869" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A869" s="9"/>
       <c r="B869" s="55"/>
       <c r="C869" s="55"/>
@@ -24456,7 +24471,7 @@
       <c r="T869" s="9"/>
       <c r="U869" s="9"/>
     </row>
-    <row r="870" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A870" s="9"/>
       <c r="B870" s="55"/>
       <c r="C870" s="55"/>
@@ -24479,7 +24494,7 @@
       <c r="T870" s="9"/>
       <c r="U870" s="9"/>
     </row>
-    <row r="871" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A871" s="9"/>
       <c r="B871" s="55"/>
       <c r="C871" s="55"/>
@@ -24502,7 +24517,7 @@
       <c r="T871" s="9"/>
       <c r="U871" s="9"/>
     </row>
-    <row r="872" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A872" s="9"/>
       <c r="B872" s="55"/>
       <c r="C872" s="55"/>
@@ -24525,7 +24540,7 @@
       <c r="T872" s="9"/>
       <c r="U872" s="9"/>
     </row>
-    <row r="873" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A873" s="9"/>
       <c r="B873" s="55"/>
       <c r="C873" s="55"/>
@@ -24548,7 +24563,7 @@
       <c r="T873" s="9"/>
       <c r="U873" s="9"/>
     </row>
-    <row r="874" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A874" s="9"/>
       <c r="B874" s="55"/>
       <c r="C874" s="55"/>
@@ -24571,7 +24586,7 @@
       <c r="T874" s="9"/>
       <c r="U874" s="9"/>
     </row>
-    <row r="875" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A875" s="9"/>
       <c r="B875" s="55"/>
       <c r="C875" s="55"/>
@@ -24594,7 +24609,7 @@
       <c r="T875" s="9"/>
       <c r="U875" s="9"/>
     </row>
-    <row r="876" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A876" s="9"/>
       <c r="B876" s="55"/>
       <c r="C876" s="55"/>
@@ -24617,7 +24632,7 @@
       <c r="T876" s="9"/>
       <c r="U876" s="9"/>
     </row>
-    <row r="877" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A877" s="9"/>
       <c r="B877" s="55"/>
       <c r="C877" s="55"/>
@@ -24640,7 +24655,7 @@
       <c r="T877" s="9"/>
       <c r="U877" s="9"/>
     </row>
-    <row r="878" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A878" s="9"/>
       <c r="B878" s="55"/>
       <c r="C878" s="55"/>
@@ -24663,7 +24678,7 @@
       <c r="T878" s="9"/>
       <c r="U878" s="9"/>
     </row>
-    <row r="879" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A879" s="9"/>
       <c r="B879" s="55"/>
       <c r="C879" s="55"/>
@@ -24686,7 +24701,7 @@
       <c r="T879" s="9"/>
       <c r="U879" s="9"/>
     </row>
-    <row r="880" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A880" s="9"/>
       <c r="B880" s="55"/>
       <c r="C880" s="55"/>
@@ -24709,7 +24724,7 @@
       <c r="T880" s="9"/>
       <c r="U880" s="9"/>
     </row>
-    <row r="881" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A881" s="9"/>
       <c r="B881" s="55"/>
       <c r="C881" s="55"/>
@@ -24732,7 +24747,7 @@
       <c r="T881" s="9"/>
       <c r="U881" s="9"/>
     </row>
-    <row r="882" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A882" s="9"/>
       <c r="B882" s="55"/>
       <c r="C882" s="55"/>
@@ -24755,7 +24770,7 @@
       <c r="T882" s="9"/>
       <c r="U882" s="9"/>
     </row>
-    <row r="883" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A883" s="9"/>
       <c r="B883" s="55"/>
       <c r="C883" s="55"/>
@@ -24778,7 +24793,7 @@
       <c r="T883" s="9"/>
       <c r="U883" s="9"/>
     </row>
-    <row r="884" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A884" s="9"/>
       <c r="B884" s="55"/>
       <c r="C884" s="55"/>
@@ -24801,7 +24816,7 @@
       <c r="T884" s="9"/>
       <c r="U884" s="9"/>
     </row>
-    <row r="885" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A885" s="9"/>
       <c r="B885" s="55"/>
       <c r="C885" s="55"/>
@@ -24824,7 +24839,7 @@
       <c r="T885" s="9"/>
       <c r="U885" s="9"/>
     </row>
-    <row r="886" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A886" s="9"/>
       <c r="B886" s="55"/>
       <c r="C886" s="55"/>
@@ -24847,7 +24862,7 @@
       <c r="T886" s="9"/>
       <c r="U886" s="9"/>
     </row>
-    <row r="887" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A887" s="9"/>
       <c r="B887" s="55"/>
       <c r="C887" s="55"/>
@@ -24870,7 +24885,7 @@
       <c r="T887" s="9"/>
       <c r="U887" s="9"/>
     </row>
-    <row r="888" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A888" s="9"/>
       <c r="B888" s="55"/>
       <c r="C888" s="55"/>
@@ -24893,7 +24908,7 @@
       <c r="T888" s="9"/>
       <c r="U888" s="9"/>
     </row>
-    <row r="889" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A889" s="9"/>
       <c r="B889" s="55"/>
       <c r="C889" s="55"/>
@@ -24916,7 +24931,7 @@
       <c r="T889" s="9"/>
       <c r="U889" s="9"/>
     </row>
-    <row r="890" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A890" s="9"/>
       <c r="B890" s="55"/>
       <c r="C890" s="55"/>
@@ -24939,7 +24954,7 @@
       <c r="T890" s="9"/>
       <c r="U890" s="9"/>
     </row>
-    <row r="891" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A891" s="9"/>
       <c r="B891" s="55"/>
       <c r="C891" s="55"/>
@@ -24962,7 +24977,7 @@
       <c r="T891" s="9"/>
       <c r="U891" s="9"/>
     </row>
-    <row r="892" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A892" s="9"/>
       <c r="B892" s="55"/>
       <c r="C892" s="55"/>
@@ -24985,7 +25000,7 @@
       <c r="T892" s="9"/>
       <c r="U892" s="9"/>
     </row>
-    <row r="893" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A893" s="9"/>
       <c r="B893" s="55"/>
       <c r="C893" s="55"/>
@@ -25008,7 +25023,7 @@
       <c r="T893" s="9"/>
       <c r="U893" s="9"/>
     </row>
-    <row r="894" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A894" s="9"/>
       <c r="B894" s="55"/>
       <c r="C894" s="55"/>
@@ -25031,7 +25046,7 @@
       <c r="T894" s="9"/>
       <c r="U894" s="9"/>
     </row>
-    <row r="895" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A895" s="9"/>
       <c r="B895" s="55"/>
       <c r="C895" s="55"/>
@@ -25054,7 +25069,7 @@
       <c r="T895" s="9"/>
       <c r="U895" s="9"/>
     </row>
-    <row r="896" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A896" s="9"/>
       <c r="B896" s="55"/>
       <c r="C896" s="55"/>
@@ -25077,7 +25092,7 @@
       <c r="T896" s="9"/>
       <c r="U896" s="9"/>
     </row>
-    <row r="897" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A897" s="9"/>
       <c r="B897" s="55"/>
       <c r="C897" s="55"/>
@@ -25100,7 +25115,7 @@
       <c r="T897" s="9"/>
       <c r="U897" s="9"/>
     </row>
-    <row r="898" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A898" s="9"/>
       <c r="B898" s="55"/>
       <c r="C898" s="55"/>
@@ -25123,7 +25138,7 @@
       <c r="T898" s="9"/>
       <c r="U898" s="9"/>
     </row>
-    <row r="899" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A899" s="9"/>
       <c r="B899" s="55"/>
       <c r="C899" s="55"/>
@@ -25146,7 +25161,7 @@
       <c r="T899" s="9"/>
       <c r="U899" s="9"/>
     </row>
-    <row r="900" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A900" s="9"/>
       <c r="B900" s="55"/>
       <c r="C900" s="55"/>
@@ -25169,7 +25184,7 @@
       <c r="T900" s="9"/>
       <c r="U900" s="9"/>
     </row>
-    <row r="901" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A901" s="9"/>
       <c r="B901" s="55"/>
       <c r="C901" s="55"/>
@@ -25192,7 +25207,7 @@
       <c r="T901" s="9"/>
       <c r="U901" s="9"/>
     </row>
-    <row r="902" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A902" s="9"/>
       <c r="B902" s="55"/>
       <c r="C902" s="55"/>
@@ -25215,7 +25230,7 @@
       <c r="T902" s="9"/>
       <c r="U902" s="9"/>
     </row>
-    <row r="903" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A903" s="9"/>
       <c r="B903" s="55"/>
       <c r="C903" s="55"/>
@@ -25238,7 +25253,7 @@
       <c r="T903" s="9"/>
       <c r="U903" s="9"/>
     </row>
-    <row r="904" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A904" s="9"/>
       <c r="B904" s="55"/>
       <c r="C904" s="55"/>
@@ -25261,7 +25276,7 @@
       <c r="T904" s="9"/>
       <c r="U904" s="9"/>
     </row>
-    <row r="905" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A905" s="9"/>
       <c r="B905" s="55"/>
       <c r="C905" s="55"/>
@@ -25284,7 +25299,7 @@
       <c r="T905" s="9"/>
       <c r="U905" s="9"/>
     </row>
-    <row r="906" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A906" s="9"/>
       <c r="B906" s="55"/>
       <c r="C906" s="55"/>
@@ -25307,7 +25322,7 @@
       <c r="T906" s="9"/>
       <c r="U906" s="9"/>
     </row>
-    <row r="907" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A907" s="9"/>
       <c r="B907" s="55"/>
       <c r="C907" s="55"/>
@@ -25330,7 +25345,7 @@
       <c r="T907" s="9"/>
       <c r="U907" s="9"/>
     </row>
-    <row r="908" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A908" s="9"/>
       <c r="B908" s="55"/>
       <c r="C908" s="55"/>
@@ -25353,7 +25368,7 @@
       <c r="T908" s="9"/>
       <c r="U908" s="9"/>
     </row>
-    <row r="909" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A909" s="9"/>
       <c r="B909" s="55"/>
       <c r="C909" s="55"/>
@@ -25376,7 +25391,7 @@
       <c r="T909" s="9"/>
       <c r="U909" s="9"/>
     </row>
-    <row r="910" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A910" s="9"/>
       <c r="B910" s="55"/>
       <c r="C910" s="55"/>
@@ -25399,7 +25414,7 @@
       <c r="T910" s="9"/>
       <c r="U910" s="9"/>
     </row>
-    <row r="911" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A911" s="9"/>
       <c r="B911" s="55"/>
       <c r="C911" s="55"/>
@@ -25422,7 +25437,7 @@
       <c r="T911" s="9"/>
       <c r="U911" s="9"/>
     </row>
-    <row r="912" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A912" s="9"/>
       <c r="B912" s="55"/>
       <c r="C912" s="55"/>
@@ -25445,7 +25460,7 @@
       <c r="T912" s="9"/>
       <c r="U912" s="9"/>
     </row>
-    <row r="913" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A913" s="9"/>
       <c r="B913" s="55"/>
       <c r="C913" s="55"/>
@@ -25468,7 +25483,7 @@
       <c r="T913" s="9"/>
       <c r="U913" s="9"/>
     </row>
-    <row r="914" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A914" s="9"/>
       <c r="B914" s="55"/>
       <c r="C914" s="55"/>
@@ -25491,7 +25506,7 @@
       <c r="T914" s="9"/>
       <c r="U914" s="9"/>
     </row>
-    <row r="915" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A915" s="9"/>
       <c r="B915" s="55"/>
       <c r="C915" s="55"/>
@@ -25514,7 +25529,7 @@
       <c r="T915" s="9"/>
       <c r="U915" s="9"/>
     </row>
-    <row r="916" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A916" s="9"/>
       <c r="B916" s="55"/>
       <c r="C916" s="55"/>
@@ -25537,7 +25552,7 @@
       <c r="T916" s="9"/>
       <c r="U916" s="9"/>
     </row>
-    <row r="917" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A917" s="9"/>
       <c r="B917" s="55"/>
       <c r="C917" s="55"/>
@@ -25560,7 +25575,7 @@
       <c r="T917" s="9"/>
       <c r="U917" s="9"/>
     </row>
-    <row r="918" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A918" s="9"/>
       <c r="B918" s="55"/>
       <c r="C918" s="55"/>
@@ -25583,7 +25598,7 @@
       <c r="T918" s="9"/>
       <c r="U918" s="9"/>
     </row>
-    <row r="919" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A919" s="9"/>
       <c r="B919" s="55"/>
       <c r="C919" s="55"/>
@@ -25606,7 +25621,7 @@
       <c r="T919" s="9"/>
       <c r="U919" s="9"/>
     </row>
-    <row r="920" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A920" s="9"/>
       <c r="B920" s="55"/>
       <c r="C920" s="55"/>
@@ -25629,7 +25644,7 @@
       <c r="T920" s="9"/>
       <c r="U920" s="9"/>
     </row>
-    <row r="921" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A921" s="9"/>
       <c r="B921" s="55"/>
       <c r="C921" s="55"/>
@@ -25652,7 +25667,7 @@
       <c r="T921" s="9"/>
       <c r="U921" s="9"/>
     </row>
-    <row r="922" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A922" s="9"/>
       <c r="B922" s="55"/>
       <c r="C922" s="55"/>
@@ -25675,7 +25690,7 @@
       <c r="T922" s="9"/>
       <c r="U922" s="9"/>
     </row>
-    <row r="923" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A923" s="9"/>
       <c r="B923" s="55"/>
       <c r="C923" s="55"/>
@@ -25698,7 +25713,7 @@
       <c r="T923" s="9"/>
       <c r="U923" s="9"/>
     </row>
-    <row r="924" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A924" s="9"/>
       <c r="B924" s="55"/>
       <c r="C924" s="55"/>
@@ -25721,7 +25736,7 @@
       <c r="T924" s="9"/>
       <c r="U924" s="9"/>
     </row>
-    <row r="925" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A925" s="9"/>
       <c r="B925" s="55"/>
       <c r="C925" s="55"/>
@@ -25744,7 +25759,7 @@
       <c r="T925" s="9"/>
       <c r="U925" s="9"/>
     </row>
-    <row r="926" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A926" s="9"/>
       <c r="B926" s="55"/>
       <c r="C926" s="55"/>
@@ -25767,7 +25782,7 @@
       <c r="T926" s="9"/>
       <c r="U926" s="9"/>
     </row>
-    <row r="927" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A927" s="9"/>
       <c r="B927" s="55"/>
       <c r="C927" s="55"/>
@@ -25790,7 +25805,7 @@
       <c r="T927" s="9"/>
       <c r="U927" s="9"/>
     </row>
-    <row r="928" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A928" s="9"/>
       <c r="B928" s="55"/>
       <c r="C928" s="55"/>
@@ -25813,7 +25828,7 @@
       <c r="T928" s="9"/>
       <c r="U928" s="9"/>
     </row>
-    <row r="929" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A929" s="9"/>
       <c r="B929" s="55"/>
       <c r="C929" s="55"/>
@@ -25836,7 +25851,7 @@
       <c r="T929" s="9"/>
       <c r="U929" s="9"/>
     </row>
-    <row r="930" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A930" s="9"/>
       <c r="B930" s="55"/>
       <c r="C930" s="55"/>
@@ -25859,7 +25874,7 @@
       <c r="T930" s="9"/>
       <c r="U930" s="9"/>
     </row>
-    <row r="931" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A931" s="9"/>
       <c r="B931" s="55"/>
       <c r="C931" s="55"/>
@@ -25882,7 +25897,7 @@
       <c r="T931" s="9"/>
       <c r="U931" s="9"/>
     </row>
-    <row r="932" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A932" s="9"/>
       <c r="B932" s="55"/>
       <c r="C932" s="55"/>
@@ -25905,7 +25920,7 @@
       <c r="T932" s="9"/>
       <c r="U932" s="9"/>
     </row>
-    <row r="933" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A933" s="9"/>
       <c r="B933" s="55"/>
       <c r="C933" s="55"/>
@@ -25928,7 +25943,7 @@
       <c r="T933" s="9"/>
       <c r="U933" s="9"/>
     </row>
-    <row r="934" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A934" s="9"/>
       <c r="B934" s="55"/>
       <c r="C934" s="55"/>
@@ -25951,7 +25966,7 @@
       <c r="T934" s="9"/>
       <c r="U934" s="9"/>
     </row>
-    <row r="935" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A935" s="9"/>
       <c r="B935" s="55"/>
       <c r="C935" s="55"/>
@@ -25974,7 +25989,7 @@
       <c r="T935" s="9"/>
       <c r="U935" s="9"/>
     </row>
-    <row r="936" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A936" s="9"/>
       <c r="B936" s="55"/>
       <c r="C936" s="55"/>
@@ -25997,7 +26012,7 @@
       <c r="T936" s="9"/>
       <c r="U936" s="9"/>
     </row>
-    <row r="937" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A937" s="9"/>
       <c r="B937" s="55"/>
       <c r="C937" s="55"/>
@@ -26020,7 +26035,7 @@
       <c r="T937" s="9"/>
       <c r="U937" s="9"/>
     </row>
-    <row r="938" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A938" s="9"/>
       <c r="B938" s="55"/>
       <c r="C938" s="55"/>
@@ -26043,7 +26058,7 @@
       <c r="T938" s="9"/>
       <c r="U938" s="9"/>
     </row>
-    <row r="939" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A939" s="9"/>
       <c r="B939" s="55"/>
       <c r="C939" s="55"/>
@@ -26066,7 +26081,7 @@
       <c r="T939" s="9"/>
       <c r="U939" s="9"/>
     </row>
-    <row r="940" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A940" s="9"/>
       <c r="B940" s="55"/>
       <c r="C940" s="55"/>
@@ -26089,7 +26104,7 @@
       <c r="T940" s="9"/>
       <c r="U940" s="9"/>
     </row>
-    <row r="941" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A941" s="9"/>
       <c r="B941" s="55"/>
       <c r="C941" s="55"/>
@@ -26112,7 +26127,7 @@
       <c r="T941" s="9"/>
       <c r="U941" s="9"/>
     </row>
-    <row r="942" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A942" s="9"/>
       <c r="B942" s="55"/>
       <c r="C942" s="55"/>
@@ -26135,7 +26150,7 @@
       <c r="T942" s="9"/>
       <c r="U942" s="9"/>
     </row>
-    <row r="943" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A943" s="9"/>
       <c r="B943" s="55"/>
       <c r="C943" s="55"/>
@@ -26158,7 +26173,7 @@
       <c r="T943" s="9"/>
       <c r="U943" s="9"/>
     </row>
-    <row r="944" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A944" s="9"/>
       <c r="B944" s="55"/>
       <c r="C944" s="55"/>
@@ -26181,7 +26196,7 @@
       <c r="T944" s="9"/>
       <c r="U944" s="9"/>
     </row>
-    <row r="945" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A945" s="9"/>
       <c r="B945" s="55"/>
       <c r="C945" s="55"/>
@@ -26204,7 +26219,7 @@
       <c r="T945" s="9"/>
       <c r="U945" s="9"/>
     </row>
-    <row r="946" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A946" s="9"/>
       <c r="B946" s="55"/>
       <c r="C946" s="55"/>
@@ -26227,7 +26242,7 @@
       <c r="T946" s="9"/>
       <c r="U946" s="9"/>
     </row>
-    <row r="947" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A947" s="9"/>
       <c r="B947" s="55"/>
       <c r="C947" s="55"/>
@@ -26250,7 +26265,7 @@
       <c r="T947" s="9"/>
       <c r="U947" s="9"/>
     </row>
-    <row r="948" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A948" s="9"/>
       <c r="B948" s="55"/>
       <c r="C948" s="55"/>
@@ -26273,7 +26288,7 @@
       <c r="T948" s="9"/>
       <c r="U948" s="9"/>
     </row>
-    <row r="949" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A949" s="9"/>
       <c r="B949" s="55"/>
       <c r="C949" s="55"/>
@@ -26296,7 +26311,7 @@
       <c r="T949" s="9"/>
       <c r="U949" s="9"/>
     </row>
-    <row r="950" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A950" s="9"/>
       <c r="B950" s="55"/>
       <c r="C950" s="55"/>
@@ -26319,7 +26334,7 @@
       <c r="T950" s="9"/>
       <c r="U950" s="9"/>
     </row>
-    <row r="951" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A951" s="9"/>
       <c r="B951" s="55"/>
       <c r="C951" s="55"/>
@@ -26342,7 +26357,7 @@
       <c r="T951" s="9"/>
       <c r="U951" s="9"/>
     </row>
-    <row r="952" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="952" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A952" s="9"/>
       <c r="B952" s="55"/>
       <c r="C952" s="55"/>
@@ -26365,7 +26380,7 @@
       <c r="T952" s="9"/>
       <c r="U952" s="9"/>
     </row>
-    <row r="953" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A953" s="9"/>
       <c r="B953" s="55"/>
       <c r="C953" s="55"/>
@@ -26388,7 +26403,7 @@
       <c r="T953" s="9"/>
       <c r="U953" s="9"/>
     </row>
-    <row r="954" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A954" s="9"/>
       <c r="B954" s="55"/>
       <c r="C954" s="55"/>
@@ -26411,7 +26426,7 @@
       <c r="T954" s="9"/>
       <c r="U954" s="9"/>
     </row>
-    <row r="955" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="955" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A955" s="9"/>
       <c r="B955" s="55"/>
       <c r="C955" s="55"/>
@@ -26434,7 +26449,7 @@
       <c r="T955" s="9"/>
       <c r="U955" s="9"/>
     </row>
-    <row r="956" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="956" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A956" s="9"/>
       <c r="B956" s="55"/>
       <c r="C956" s="55"/>
@@ -26457,7 +26472,7 @@
       <c r="T956" s="9"/>
       <c r="U956" s="9"/>
     </row>
-    <row r="957" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="957" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A957" s="9"/>
       <c r="B957" s="55"/>
       <c r="C957" s="55"/>
@@ -26480,7 +26495,7 @@
       <c r="T957" s="9"/>
       <c r="U957" s="9"/>
     </row>
-    <row r="958" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="958" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A958" s="9"/>
       <c r="B958" s="55"/>
       <c r="C958" s="55"/>
@@ -26503,7 +26518,7 @@
       <c r="T958" s="9"/>
       <c r="U958" s="9"/>
     </row>
-    <row r="959" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="959" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A959" s="9"/>
       <c r="B959" s="55"/>
       <c r="C959" s="55"/>
@@ -26526,7 +26541,7 @@
       <c r="T959" s="9"/>
       <c r="U959" s="9"/>
     </row>
-    <row r="960" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A960" s="9"/>
       <c r="B960" s="55"/>
       <c r="C960" s="55"/>
@@ -26549,7 +26564,7 @@
       <c r="T960" s="9"/>
       <c r="U960" s="9"/>
     </row>
-    <row r="961" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="961" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A961" s="9"/>
       <c r="B961" s="55"/>
       <c r="C961" s="55"/>
@@ -26572,7 +26587,7 @@
       <c r="T961" s="9"/>
       <c r="U961" s="9"/>
     </row>
-    <row r="962" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A962" s="9"/>
       <c r="B962" s="55"/>
       <c r="C962" s="55"/>
@@ -26595,7 +26610,7 @@
       <c r="T962" s="9"/>
       <c r="U962" s="9"/>
     </row>
-    <row r="963" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A963" s="9"/>
       <c r="B963" s="55"/>
       <c r="C963" s="55"/>
@@ -26618,7 +26633,7 @@
       <c r="T963" s="9"/>
       <c r="U963" s="9"/>
     </row>
-    <row r="964" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="964" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A964" s="9"/>
       <c r="B964" s="55"/>
       <c r="C964" s="55"/>
@@ -26641,7 +26656,7 @@
       <c r="T964" s="9"/>
       <c r="U964" s="9"/>
     </row>
-    <row r="965" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="965" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A965" s="9"/>
       <c r="B965" s="55"/>
       <c r="C965" s="55"/>
@@ -26664,7 +26679,7 @@
       <c r="T965" s="9"/>
       <c r="U965" s="9"/>
     </row>
-    <row r="966" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="966" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A966" s="9"/>
       <c r="B966" s="55"/>
       <c r="C966" s="55"/>
@@ -26687,7 +26702,7 @@
       <c r="T966" s="9"/>
       <c r="U966" s="9"/>
     </row>
-    <row r="967" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="967" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A967" s="9"/>
       <c r="B967" s="55"/>
       <c r="C967" s="55"/>
@@ -26710,7 +26725,7 @@
       <c r="T967" s="9"/>
       <c r="U967" s="9"/>
     </row>
-    <row r="968" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A968" s="9"/>
       <c r="B968" s="55"/>
       <c r="C968" s="55"/>
@@ -26733,7 +26748,7 @@
       <c r="T968" s="9"/>
       <c r="U968" s="9"/>
     </row>
-    <row r="969" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="969" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A969" s="9"/>
       <c r="B969" s="55"/>
       <c r="C969" s="55"/>
@@ -26756,7 +26771,7 @@
       <c r="T969" s="9"/>
       <c r="U969" s="9"/>
     </row>
-    <row r="970" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="970" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A970" s="9"/>
       <c r="B970" s="55"/>
       <c r="C970" s="55"/>
@@ -26779,7 +26794,7 @@
       <c r="T970" s="9"/>
       <c r="U970" s="9"/>
     </row>
-    <row r="971" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="971" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A971" s="9"/>
       <c r="B971" s="55"/>
       <c r="C971" s="55"/>
@@ -26802,7 +26817,7 @@
       <c r="T971" s="9"/>
       <c r="U971" s="9"/>
     </row>
-    <row r="972" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="972" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A972" s="9"/>
       <c r="B972" s="55"/>
       <c r="C972" s="55"/>
@@ -26825,7 +26840,7 @@
       <c r="T972" s="9"/>
       <c r="U972" s="9"/>
     </row>
-    <row r="973" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="973" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A973" s="9"/>
       <c r="B973" s="55"/>
       <c r="C973" s="55"/>
@@ -26848,7 +26863,7 @@
       <c r="T973" s="9"/>
       <c r="U973" s="9"/>
     </row>
-    <row r="974" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="974" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A974" s="9"/>
       <c r="B974" s="55"/>
       <c r="C974" s="55"/>
@@ -26871,7 +26886,7 @@
       <c r="T974" s="9"/>
       <c r="U974" s="9"/>
     </row>
-    <row r="975" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="975" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A975" s="9"/>
       <c r="B975" s="55"/>
       <c r="C975" s="55"/>
@@ -26894,7 +26909,7 @@
       <c r="T975" s="9"/>
       <c r="U975" s="9"/>
     </row>
-    <row r="976" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A976" s="9"/>
       <c r="B976" s="55"/>
       <c r="C976" s="55"/>
@@ -26917,7 +26932,7 @@
       <c r="T976" s="9"/>
       <c r="U976" s="9"/>
     </row>
-    <row r="977" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A977" s="9"/>
       <c r="B977" s="55"/>
       <c r="C977" s="55"/>
@@ -26940,7 +26955,7 @@
       <c r="T977" s="9"/>
       <c r="U977" s="9"/>
     </row>
-    <row r="978" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A978" s="9"/>
       <c r="B978" s="55"/>
       <c r="C978" s="55"/>
@@ -26963,7 +26978,7 @@
       <c r="T978" s="9"/>
       <c r="U978" s="9"/>
     </row>
-    <row r="979" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="979" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A979" s="9"/>
       <c r="B979" s="55"/>
       <c r="C979" s="55"/>
@@ -26986,7 +27001,7 @@
       <c r="T979" s="9"/>
       <c r="U979" s="9"/>
     </row>
-    <row r="980" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="980" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A980" s="9"/>
       <c r="B980" s="55"/>
       <c r="C980" s="55"/>
@@ -27009,7 +27024,7 @@
       <c r="T980" s="9"/>
       <c r="U980" s="9"/>
     </row>
-    <row r="981" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="981" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A981" s="9"/>
       <c r="B981" s="55"/>
       <c r="C981" s="55"/>
@@ -27032,7 +27047,7 @@
       <c r="T981" s="9"/>
       <c r="U981" s="9"/>
     </row>
-    <row r="982" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="982" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A982" s="9"/>
       <c r="B982" s="55"/>
       <c r="C982" s="55"/>
@@ -27055,7 +27070,7 @@
       <c r="T982" s="9"/>
       <c r="U982" s="9"/>
     </row>
-    <row r="983" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="983" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A983" s="9"/>
       <c r="B983" s="55"/>
       <c r="C983" s="55"/>
@@ -27078,7 +27093,7 @@
       <c r="T983" s="9"/>
       <c r="U983" s="9"/>
     </row>
-    <row r="984" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A984" s="9"/>
       <c r="B984" s="55"/>
       <c r="C984" s="55"/>
@@ -27101,7 +27116,7 @@
       <c r="T984" s="9"/>
       <c r="U984" s="9"/>
     </row>
-    <row r="985" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A985" s="9"/>
       <c r="B985" s="55"/>
       <c r="C985" s="55"/>
@@ -27124,7 +27139,7 @@
       <c r="T985" s="9"/>
       <c r="U985" s="9"/>
     </row>
-    <row r="986" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A986" s="9"/>
       <c r="B986" s="55"/>
       <c r="C986" s="55"/>
@@ -27147,7 +27162,7 @@
       <c r="T986" s="9"/>
       <c r="U986" s="9"/>
     </row>
-    <row r="987" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="987" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A987" s="9"/>
       <c r="B987" s="55"/>
       <c r="C987" s="55"/>
@@ -27170,7 +27185,7 @@
       <c r="T987" s="9"/>
       <c r="U987" s="9"/>
     </row>
-    <row r="988" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A988" s="9"/>
       <c r="B988" s="55"/>
       <c r="C988" s="55"/>
@@ -27193,7 +27208,7 @@
       <c r="T988" s="9"/>
       <c r="U988" s="9"/>
     </row>
-    <row r="989" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="989" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A989" s="9"/>
       <c r="B989" s="55"/>
       <c r="C989" s="55"/>
@@ -27216,7 +27231,7 @@
       <c r="T989" s="9"/>
       <c r="U989" s="9"/>
     </row>
-    <row r="990" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A990" s="9"/>
       <c r="B990" s="55"/>
       <c r="C990" s="55"/>
@@ -27239,7 +27254,7 @@
       <c r="T990" s="9"/>
       <c r="U990" s="9"/>
     </row>
-    <row r="991" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="991" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A991" s="9"/>
       <c r="B991" s="55"/>
       <c r="C991" s="55"/>
@@ -27262,7 +27277,7 @@
       <c r="T991" s="9"/>
       <c r="U991" s="9"/>
     </row>
-    <row r="992" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="992" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A992" s="9"/>
       <c r="B992" s="55"/>
       <c r="C992" s="55"/>
@@ -27285,7 +27300,7 @@
       <c r="T992" s="9"/>
       <c r="U992" s="9"/>
     </row>
-    <row r="993" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A993" s="9"/>
       <c r="B993" s="55"/>
       <c r="C993" s="55"/>
@@ -27308,7 +27323,7 @@
       <c r="T993" s="9"/>
       <c r="U993" s="9"/>
     </row>
-    <row r="994" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A994" s="9"/>
       <c r="B994" s="55"/>
       <c r="C994" s="55"/>
@@ -27331,7 +27346,7 @@
       <c r="T994" s="9"/>
       <c r="U994" s="9"/>
     </row>
-    <row r="995" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A995" s="9"/>
       <c r="B995" s="55"/>
       <c r="C995" s="55"/>
@@ -27354,7 +27369,7 @@
       <c r="T995" s="9"/>
       <c r="U995" s="9"/>
     </row>
-    <row r="996" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="996" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A996" s="9"/>
       <c r="B996" s="55"/>
       <c r="C996" s="55"/>
@@ -27377,7 +27392,7 @@
       <c r="T996" s="9"/>
       <c r="U996" s="9"/>
     </row>
-    <row r="997" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="997" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A997" s="9"/>
       <c r="B997" s="55"/>
       <c r="C997" s="55"/>
@@ -27400,7 +27415,7 @@
       <c r="T997" s="9"/>
       <c r="U997" s="9"/>
     </row>
-    <row r="998" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="998" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A998" s="9"/>
       <c r="B998" s="55"/>
       <c r="C998" s="55"/>
@@ -27423,7 +27438,7 @@
       <c r="T998" s="9"/>
       <c r="U998" s="9"/>
     </row>
-    <row r="999" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="999" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A999" s="9"/>
       <c r="B999" s="55"/>
       <c r="C999" s="55"/>
@@ -27446,7 +27461,7 @@
       <c r="T999" s="9"/>
       <c r="U999" s="9"/>
     </row>
-    <row r="1000" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="1000" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1000" s="9"/>
       <c r="B1000" s="55"/>
       <c r="C1000" s="55"/>
@@ -27469,7 +27484,7 @@
       <c r="T1000" s="9"/>
       <c r="U1000" s="9"/>
     </row>
-    <row r="1001" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="1001" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1001" s="9"/>
       <c r="B1001" s="55"/>
       <c r="C1001" s="55"/>
@@ -27493,6 +27508,15 @@
       <c r="U1001" s="9"/>
     </row>
   </sheetData>
+  <autoFilter ref="S1:S1001" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="$MethodDefinition.schema:instrument.schema:hasPart[]"/>
+        <filter val="$MethodDefinition.schema:instrument.schema:manufacturer.schema:Organization.schema:name"/>
+        <filter val="$MethodDefinition.schema:instrument.schema:model.schema:name"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="6">
     <mergeCell ref="A58:E58"/>
     <mergeCell ref="A12:E12"/>

--- a/docs/TAPP_EPMA_filled.xlsx
+++ b/docs/TAPP_EPMA_filled.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/944a82e2ddcde9eb/Documents/GithubC/USGIN/geochemBuildingBlocks/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="324" documentId="11_3C209AD99577444EEF615C96566D1EBF266D99FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41ED8E6A-55F5-4C5A-8FFF-A2266BC2973F}"/>
+  <xr:revisionPtr revIDLastSave="334" documentId="11_3C209AD99577444EEF615C96566D1EBF266D99FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BF90C6C-0D91-457C-AEDC-A3D2C7D20707}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1365" windowWidth="27330" windowHeight="14610" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="165" yWindow="1335" windowWidth="22350" windowHeight="14610" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TAPP" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TAPP!$S$1:$S$1001</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TAPP!$U$1:$U$1001</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="465">
   <si>
     <t>Metadata Item</t>
   </si>
@@ -1177,18 +1177,10 @@
     <t>Sample preparation is a dedicated step (typically schema:position=1) in the actionProcess; schema:object is input, mostly likely the original sample. Schema:result is the product that will be used directly for analysis, e.g. polished thin section or epoxy mount; describe procedure in schema:step/schema:description</t>
   </si>
   <si>
-    <t>schema:object (readOnly false)
-schema:result {readOnly true)
-schema:description (readOnly ? True?)</t>
-  </si>
-  <si>
     <t>toolRole = acquisition</t>
   </si>
   <si>
     <t>toolRole = data reduction</t>
-  </si>
-  <si>
-    <t>parameter: DriftCorrection</t>
   </si>
   <si>
     <t>analyteColumn : spectrometerNumber 
@@ -1199,14 +1191,6 @@
     <t>analyteColumn : analysisOrder 
   datatype: positive integer
   readOnly:true</t>
-  </si>
-  <si>
-    <t>method-level property: beamCurrentDefault 
-  data:type PropertyValue 
-  readOnly:true
-analyteColumn item: beamCurrent
-  datatype: PropertyValue
-  readOnly: false</t>
   </si>
   <si>
     <t>analyteColumn : epmaTechnique 
@@ -1606,9 +1590,6 @@
     <t>match. schema:creator is a Person or Organization; schema:name carries the author name (plus schema:identifier for ORCID).</t>
   </si>
   <si>
-    <t>schema:instrument.schema.hasPart.</t>
-  </si>
-  <si>
     <t>parameter: wdsDeadTimeCorrection
    datatype: enum {Default constant 3µs (Cameca) | Adjusted constant (Cameca) | Default constant (JEOL) | Adjusted constant (JEOL) | High-precision (Probe for EPMA) | Logarithmic | Super-precision | Simple | Other | Unknown}
    readOnly: true</t>
@@ -1621,6 +1602,23 @@
   </si>
   <si>
     <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType = 'edsDetector'</t>
+  </si>
+  <si>
+    <t>parameter: DriftCorrection
+  dataType:  text
+  readOnly: True</t>
+  </si>
+  <si>
+    <t>schema:description
+  readOnly: true</t>
+  </si>
+  <si>
+    <t>method-level property: beamCurrentDefault 
+  data:type PropertyValue 
+  readOnly:true
+analyteColumn item: beamCurrent
+  datatype: PropertyValue
+  readOnly: true</t>
   </si>
 </sst>
 </file>
@@ -2950,7 +2948,7 @@
     <col min="22" max="16384" width="12.7109375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2967,7 +2965,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="G1" s="2"/>
       <c r="H1" s="112" t="s">
@@ -3010,10 +3008,10 @@
         <v>17</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="13.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="177" t="s">
         <v>18</v>
       </c>
@@ -3038,7 +3036,7 @@
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
     </row>
-    <row r="3" spans="1:21" s="64" customFormat="1" ht="57" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" s="64" customFormat="1" ht="57.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="59" t="s">
         <v>19</v>
       </c>
@@ -3091,14 +3089,14 @@
         <v>1</v>
       </c>
       <c r="S3" s="63" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="T3" s="169" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="U3" s="63"/>
     </row>
-    <row r="4" spans="1:21" s="70" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" s="70" customFormat="1" ht="51.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="65" t="s">
         <v>29</v>
       </c>
@@ -3151,16 +3149,16 @@
         <v>1</v>
       </c>
       <c r="S4" s="69" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="T4" s="170" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="U4" s="69" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" s="70" customFormat="1" ht="38.25" hidden="1" x14ac:dyDescent="0.2">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" s="70" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="65" t="s">
         <v>34</v>
       </c>
@@ -3213,14 +3211,14 @@
         <v>1</v>
       </c>
       <c r="S5" s="69" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="T5" s="170" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="U5" s="69"/>
     </row>
-    <row r="6" spans="1:21" s="70" customFormat="1" ht="57" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" s="70" customFormat="1" ht="57.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65" t="s">
         <v>46</v>
       </c>
@@ -3273,14 +3271,14 @@
         <v>1</v>
       </c>
       <c r="S6" s="69" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="T6" s="170" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="U6" s="69"/>
     </row>
-    <row r="7" spans="1:21" s="70" customFormat="1" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" s="70" customFormat="1" ht="29.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="71" t="s">
         <v>58</v>
       </c>
@@ -3313,14 +3311,14 @@
         <v>0</v>
       </c>
       <c r="S7" s="69" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="T7" s="170" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="U7" s="69"/>
     </row>
-    <row r="8" spans="1:21" s="70" customFormat="1" ht="42.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" s="70" customFormat="1" ht="43.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
         <v>63</v>
       </c>
@@ -3353,14 +3351,14 @@
         <v>0</v>
       </c>
       <c r="S8" s="69" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="T8" s="170" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="U8" s="69"/>
     </row>
-    <row r="9" spans="1:21" s="70" customFormat="1" ht="42.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" s="70" customFormat="1" ht="43.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="71" t="s">
         <v>66</v>
       </c>
@@ -3393,16 +3391,16 @@
         <v>0</v>
       </c>
       <c r="S9" s="69" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="T9" s="170" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="U9" s="69" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" s="70" customFormat="1" ht="42.75" hidden="1" x14ac:dyDescent="0.2">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" s="70" customFormat="1" ht="43.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="71" t="s">
         <v>69</v>
       </c>
@@ -3435,14 +3433,14 @@
         <v>0</v>
       </c>
       <c r="S10" s="69" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="T10" s="170" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="U10" s="69"/>
     </row>
-    <row r="11" spans="1:21" s="70" customFormat="1" ht="14.25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" s="70" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="77"/>
       <c r="B11" s="78"/>
       <c r="C11" s="78"/>
@@ -3465,7 +3463,7 @@
       <c r="T11" s="69"/>
       <c r="U11" s="69"/>
     </row>
-    <row r="12" spans="1:21" s="70" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" s="70" customFormat="1" ht="13.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="175" t="s">
         <v>73</v>
       </c>
@@ -3490,7 +3488,7 @@
       <c r="T12" s="69"/>
       <c r="U12" s="69"/>
     </row>
-    <row r="13" spans="1:21" s="70" customFormat="1" ht="85.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" s="70" customFormat="1" ht="86.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="80" t="s">
         <v>74</v>
       </c>
@@ -3512,7 +3510,7 @@
         <v>78</v>
       </c>
       <c r="I13" s="81" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="J13" s="81" t="s">
         <v>79</v>
@@ -3543,14 +3541,14 @@
         <v>1</v>
       </c>
       <c r="S13" s="69" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="T13" s="69" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="U13" s="69"/>
     </row>
-    <row r="14" spans="1:21" s="70" customFormat="1" ht="89.25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" s="70" customFormat="1" ht="90" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="84" t="s">
         <v>87</v>
       </c>
@@ -3603,16 +3601,16 @@
         <v>1</v>
       </c>
       <c r="S14" s="69" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="T14" s="69" t="s">
         <v>356</v>
       </c>
       <c r="U14" s="69" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" s="70" customFormat="1" ht="14.25" hidden="1" x14ac:dyDescent="0.2">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" s="70" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="77"/>
       <c r="B15" s="78"/>
       <c r="C15" s="78"/>
@@ -3635,7 +3633,7 @@
       <c r="T15" s="69"/>
       <c r="U15" s="69"/>
     </row>
-    <row r="16" spans="1:21" s="70" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" s="70" customFormat="1" ht="13.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="178" t="s">
         <v>100</v>
       </c>
@@ -3660,7 +3658,7 @@
       <c r="T16" s="69"/>
       <c r="U16" s="69"/>
     </row>
-    <row r="17" spans="1:21" s="70" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:21" s="70" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="88" t="s">
         <v>101</v>
       </c>
@@ -3713,14 +3711,14 @@
         <v>1</v>
       </c>
       <c r="S17" s="69" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="T17" s="170" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="U17" s="69"/>
     </row>
-    <row r="18" spans="1:21" s="70" customFormat="1" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:21" s="70" customFormat="1" ht="72" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="88" t="s">
         <v>108</v>
       </c>
@@ -3773,14 +3771,14 @@
         <v>1</v>
       </c>
       <c r="S18" s="69" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="T18" s="170" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="U18" s="69"/>
     </row>
-    <row r="19" spans="1:21" s="70" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:21" s="70" customFormat="1" ht="51.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="88" t="s">
         <v>119</v>
       </c>
@@ -3817,16 +3815,14 @@
         <v>0.2</v>
       </c>
       <c r="S19" s="69" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="T19" s="69" t="s">
-        <v>427</v>
-      </c>
-      <c r="U19" s="69" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" s="70" customFormat="1" ht="57" hidden="1" x14ac:dyDescent="0.2">
+        <v>424</v>
+      </c>
+      <c r="U19" s="69"/>
+    </row>
+    <row r="20" spans="1:21" s="70" customFormat="1" ht="57.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="88" t="s">
         <v>123</v>
       </c>
@@ -3867,16 +3863,16 @@
         <v>0.4</v>
       </c>
       <c r="S20" s="69" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="T20" s="170" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="U20" s="69" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" s="70" customFormat="1" ht="57" hidden="1" x14ac:dyDescent="0.2">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" s="70" customFormat="1" ht="57.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="88" t="s">
         <v>128</v>
       </c>
@@ -3921,16 +3917,16 @@
         <v>0.6</v>
       </c>
       <c r="S21" s="69" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="T21" s="170" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="U21" s="69" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" s="70" customFormat="1" ht="57" x14ac:dyDescent="0.2">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" s="70" customFormat="1" ht="57.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="92" t="s">
         <v>136</v>
       </c>
@@ -3965,16 +3961,16 @@
         <v>0.1</v>
       </c>
       <c r="S22" s="69" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="T22" s="69" t="s">
         <v>140</v>
       </c>
       <c r="U22" s="69" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" s="70" customFormat="1" ht="57" x14ac:dyDescent="0.2">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" s="70" customFormat="1" ht="57.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="92" t="s">
         <v>141</v>
       </c>
@@ -4009,16 +4005,16 @@
         <v>0.1</v>
       </c>
       <c r="S23" s="69" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="T23" s="69" t="s">
         <v>145</v>
       </c>
       <c r="U23" s="69" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" s="70" customFormat="1" ht="14.25" hidden="1" x14ac:dyDescent="0.2">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" s="70" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="77"/>
       <c r="B24" s="78"/>
       <c r="C24" s="78"/>
@@ -4041,7 +4037,7 @@
       <c r="T24" s="69"/>
       <c r="U24" s="69"/>
     </row>
-    <row r="25" spans="1:21" s="70" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:21" s="70" customFormat="1" ht="13.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="179" t="s">
         <v>146</v>
       </c>
@@ -4066,7 +4062,7 @@
       <c r="T25" s="69"/>
       <c r="U25" s="69"/>
     </row>
-    <row r="26" spans="1:21" s="70" customFormat="1" ht="71.25" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:21" s="70" customFormat="1" ht="72" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="96" t="s">
         <v>147</v>
       </c>
@@ -4119,16 +4115,16 @@
         <v>1</v>
       </c>
       <c r="S26" s="69" t="s">
+        <v>438</v>
+      </c>
+      <c r="T26" s="170" t="s">
         <v>441</v>
       </c>
-      <c r="T26" s="170" t="s">
-        <v>444</v>
-      </c>
       <c r="U26" s="171" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" s="70" customFormat="1" ht="76.5" hidden="1" x14ac:dyDescent="0.2">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" s="70" customFormat="1" ht="77.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="96" t="s">
         <v>157</v>
       </c>
@@ -4181,16 +4177,16 @@
         <v>1</v>
       </c>
       <c r="S27" s="101" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="T27" s="170" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="U27" s="171" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" s="70" customFormat="1" ht="76.5" hidden="1" x14ac:dyDescent="0.2">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" s="70" customFormat="1" ht="77.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="96" t="s">
         <v>164</v>
       </c>
@@ -4241,16 +4237,16 @@
         <v>0.9</v>
       </c>
       <c r="S28" s="101" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="T28" s="170" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="U28" s="171" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" s="70" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" s="70" customFormat="1" ht="51.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="102" t="s">
         <v>175</v>
       </c>
@@ -4289,10 +4285,10 @@
         <v>179</v>
       </c>
       <c r="U29" s="69" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" s="70" customFormat="1" ht="85.5" hidden="1" x14ac:dyDescent="0.2">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" s="70" customFormat="1" ht="86.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="102" t="s">
         <v>180</v>
       </c>
@@ -4335,10 +4331,10 @@
         <v>186</v>
       </c>
       <c r="U30" s="69" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" s="111" customFormat="1" ht="99.75" hidden="1" x14ac:dyDescent="0.2">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" s="111" customFormat="1" ht="100.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="106" t="s">
         <v>187</v>
       </c>
@@ -4377,7 +4373,7 @@
         <v>190</v>
       </c>
       <c r="U31" s="110" t="s">
-        <v>360</v>
+        <v>462</v>
       </c>
     </row>
     <row r="32" spans="1:21" ht="234" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -4418,13 +4414,13 @@
         <v>195</v>
       </c>
       <c r="T32" s="3" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="U32" s="3" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="33" spans="1:21" ht="77.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" ht="77.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
         <v>196</v>
       </c>
@@ -4441,7 +4437,7 @@
         <v>199</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="143" t="s">
@@ -4451,7 +4447,7 @@
         <v>201</v>
       </c>
       <c r="J33" s="36" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K33" s="36" t="s">
         <v>200</v>
@@ -4466,10 +4462,10 @@
         <v>203</v>
       </c>
       <c r="O33" s="36" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="P33" s="36" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="Q33" s="36" t="s">
         <v>203</v>
@@ -4482,13 +4478,13 @@
         <v>163</v>
       </c>
       <c r="T33" s="3" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="U33" s="3" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
         <v>204</v>
       </c>
@@ -4505,7 +4501,7 @@
         <v>206</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="143" t="s">
@@ -4549,10 +4545,10 @@
         <v>209</v>
       </c>
       <c r="U34" s="3" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
         <v>210</v>
       </c>
@@ -4569,7 +4565,7 @@
         <v>213</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="145"/>
@@ -4593,10 +4589,10 @@
         <v>214</v>
       </c>
       <c r="U35" s="3" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="36" spans="1:21" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
         <v>215</v>
       </c>
@@ -4613,7 +4609,7 @@
         <v>213</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="145"/>
@@ -4637,10 +4633,10 @@
         <v>217</v>
       </c>
       <c r="U36" s="3" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" ht="86.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" ht="86.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
         <v>218</v>
       </c>
@@ -4657,7 +4653,7 @@
         <v>220</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="143"/>
@@ -4683,10 +4679,10 @@
         <v>222</v>
       </c>
       <c r="U37" s="3" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" ht="57.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
         <v>223</v>
       </c>
@@ -4703,7 +4699,7 @@
         <v>225</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="145"/>
@@ -4727,10 +4723,10 @@
         <v>226</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
         <v>227</v>
       </c>
@@ -4747,7 +4743,7 @@
         <v>229</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="145"/>
@@ -4771,10 +4767,10 @@
         <v>230</v>
       </c>
       <c r="U39" s="3" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="40" spans="1:21" ht="129" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" ht="129" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
         <v>231</v>
       </c>
@@ -4791,16 +4787,16 @@
         <v>233</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="143" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="I40" s="36"/>
       <c r="J40" s="36"/>
       <c r="K40" s="36" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="L40" s="36"/>
       <c r="M40" s="36"/>
@@ -4819,10 +4815,10 @@
         <v>236</v>
       </c>
       <c r="U40" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="41" spans="1:21" ht="57.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
         <v>237</v>
       </c>
@@ -4839,7 +4835,7 @@
         <v>240</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="143" t="s">
@@ -4873,10 +4869,10 @@
         <v>245</v>
       </c>
       <c r="U41" s="3" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="42" spans="1:21" ht="57.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
         <v>246</v>
       </c>
@@ -4893,7 +4889,7 @@
         <v>248</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="143" t="s">
@@ -4925,10 +4921,10 @@
         <v>251</v>
       </c>
       <c r="U42" s="3" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="43" spans="1:21" ht="72" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" ht="72" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
         <v>252</v>
       </c>
@@ -4945,7 +4941,7 @@
         <v>255</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="145"/>
@@ -4969,10 +4965,10 @@
         <v>256</v>
       </c>
       <c r="U43" s="3" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="44" spans="1:21" ht="14.25" hidden="1" x14ac:dyDescent="0.2">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
       <c r="B44" s="34"/>
       <c r="C44" s="34"/>
@@ -4995,7 +4991,7 @@
       <c r="T44" s="3"/>
       <c r="U44" s="3"/>
     </row>
-    <row r="45" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:21" ht="13.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="180" t="s">
         <v>257</v>
       </c>
@@ -5020,7 +5016,7 @@
       <c r="T45" s="3"/>
       <c r="U45" s="3"/>
     </row>
-    <row r="46" spans="1:21" ht="142.5" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:21" ht="143.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>258</v>
       </c>
@@ -5067,16 +5063,16 @@
         <v>0.7</v>
       </c>
       <c r="S46" s="11" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="T46" s="3" t="s">
         <v>264</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="47" spans="1:21" ht="57" hidden="1" x14ac:dyDescent="0.2">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" ht="57.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
         <v>265</v>
       </c>
@@ -5115,10 +5111,10 @@
         <v>268</v>
       </c>
       <c r="U47" s="3" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="48" spans="1:21" ht="57" hidden="1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" ht="57.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
         <v>269</v>
       </c>
@@ -5161,10 +5157,10 @@
         <v>275</v>
       </c>
       <c r="U48" s="3" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="49" spans="1:21" ht="128.25" hidden="1" x14ac:dyDescent="0.2">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" ht="129" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>276</v>
       </c>
@@ -5203,10 +5199,10 @@
         <v>279</v>
       </c>
       <c r="U49" s="3" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="50" spans="1:21" ht="57" hidden="1" x14ac:dyDescent="0.2">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" ht="57.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>280</v>
       </c>
@@ -5245,10 +5241,10 @@
         <v>283</v>
       </c>
       <c r="U50" s="3" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="51" spans="1:21" ht="43.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="14" t="s">
         <v>284</v>
       </c>
@@ -5265,7 +5261,7 @@
         <v>286</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G51" s="3"/>
       <c r="H51" s="151"/>
@@ -5286,13 +5282,13 @@
         <v>208</v>
       </c>
       <c r="T51" s="3" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="U51" s="3" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="52" spans="1:21" ht="43.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
         <v>287</v>
       </c>
@@ -5309,7 +5305,7 @@
         <v>289</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="151"/>
@@ -5333,10 +5329,10 @@
         <v>290</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="53" spans="1:21" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="15" t="s">
         <v>291</v>
       </c>
@@ -5353,7 +5349,7 @@
         <v>293</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G53" s="3"/>
       <c r="H53" s="153"/>
@@ -5374,13 +5370,13 @@
         <v>208</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="54" spans="1:21" ht="143.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" ht="143.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A54" s="16" t="s">
         <v>294</v>
       </c>
@@ -5397,7 +5393,7 @@
         <v>296</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="155"/>
@@ -5420,13 +5416,13 @@
         <v>208</v>
       </c>
       <c r="T54" s="3" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="U54" s="3" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="55" spans="1:21" ht="51.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A55" s="14" t="s">
         <v>298</v>
       </c>
@@ -5443,7 +5439,7 @@
         <v>300</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="151"/>
@@ -5464,13 +5460,13 @@
         <v>208</v>
       </c>
       <c r="T55" s="3" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="U55" s="3" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="56" spans="1:21" ht="57.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A56" s="14" t="s">
         <v>301</v>
       </c>
@@ -5487,7 +5483,7 @@
         <v>303</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="151"/>
@@ -5508,13 +5504,13 @@
         <v>208</v>
       </c>
       <c r="T56" s="3" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="U56" s="3" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="57" spans="1:21" ht="14.25" hidden="1" x14ac:dyDescent="0.2">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
       <c r="B57" s="34"/>
       <c r="C57" s="34"/>
@@ -5537,7 +5533,7 @@
       <c r="T57" s="3"/>
       <c r="U57" s="3"/>
     </row>
-    <row r="58" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:21" ht="13.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A58" s="172" t="s">
         <v>304</v>
       </c>
@@ -5562,7 +5558,7 @@
       <c r="T58" s="3"/>
       <c r="U58" s="3"/>
     </row>
-    <row r="59" spans="1:21" ht="91.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:21" ht="91.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A59" s="17" t="s">
         <v>305</v>
       </c>
@@ -5579,7 +5575,7 @@
         <v>307</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G59" s="3"/>
       <c r="H59" s="160" t="s">
@@ -5618,13 +5614,13 @@
         <v>208</v>
       </c>
       <c r="T59" s="3" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="U59" s="3" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="60" spans="1:21" ht="57.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A60" s="17" t="s">
         <v>315</v>
       </c>
@@ -5641,7 +5637,7 @@
         <v>317</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G60" s="3"/>
       <c r="H60" s="160"/>
@@ -5668,13 +5664,13 @@
         <v>208</v>
       </c>
       <c r="T60" s="3" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="U60" s="3" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="61" spans="1:21" ht="43.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A61" s="17" t="s">
         <v>321</v>
       </c>
@@ -5691,7 +5687,7 @@
         <v>323</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G61" s="3"/>
       <c r="H61" s="160"/>
@@ -5715,10 +5711,10 @@
         <v>324</v>
       </c>
       <c r="U61" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="62" spans="1:21" ht="43.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A62" s="18" t="s">
         <v>325</v>
       </c>
@@ -5735,7 +5731,7 @@
         <v>327</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G62" s="3"/>
       <c r="H62" s="162"/>
@@ -5759,10 +5755,10 @@
         <v>328</v>
       </c>
       <c r="U62" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="63" spans="1:21" ht="43.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A63" s="18" t="s">
         <v>329</v>
       </c>
@@ -5779,7 +5775,7 @@
         <v>331</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G63" s="3"/>
       <c r="H63" s="162"/>
@@ -5800,13 +5796,13 @@
         <v>208</v>
       </c>
       <c r="T63" s="3" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="U63" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="64" spans="1:21" ht="171.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" ht="171.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A64" s="18" t="s">
         <v>332</v>
       </c>
@@ -5823,7 +5819,7 @@
         <v>335</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="162"/>
@@ -5854,13 +5850,13 @@
         <v>208</v>
       </c>
       <c r="T64" s="3" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="U64" s="3" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="65" spans="1:21" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A65" s="18" t="s">
         <v>341</v>
       </c>
@@ -5877,7 +5873,7 @@
         <v>343</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G65" s="3"/>
       <c r="H65" s="162"/>
@@ -5899,10 +5895,10 @@
       </c>
       <c r="T65" s="3"/>
       <c r="U65" s="3" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="66" spans="1:21" ht="72" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" ht="72" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A66" s="18" t="s">
         <v>344</v>
       </c>
@@ -5919,7 +5915,7 @@
         <v>346</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G66" s="8"/>
       <c r="H66" s="162"/>
@@ -5940,13 +5936,13 @@
         <v>208</v>
       </c>
       <c r="T66" s="3" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="U66" s="3" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="67" spans="1:21" ht="57.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A67" s="18" t="s">
         <v>347</v>
       </c>
@@ -5963,7 +5959,7 @@
         <v>349</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G67" s="8"/>
       <c r="H67" s="162"/>
@@ -5984,13 +5980,13 @@
         <v>208</v>
       </c>
       <c r="T67" s="9" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="U67" s="3" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="68" spans="1:21" ht="43.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A68" s="18" t="s">
         <v>350</v>
       </c>
@@ -6007,7 +6003,7 @@
         <v>352</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G68" s="8"/>
       <c r="H68" s="162"/>
@@ -6028,10 +6024,10 @@
         <v>208</v>
       </c>
       <c r="T68" s="9" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="U68" s="3" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="69" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
@@ -6088,10 +6084,10 @@
         <v>355</v>
       </c>
       <c r="T70" s="3" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="U70" s="3" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="71" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
@@ -27508,12 +27504,68 @@
       <c r="U1001" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="S1:S1001" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" ref="U1:U1001" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="$MethodDefinition.schema:instrument.schema:hasPart[]"/>
-        <filter val="$MethodDefinition.schema:instrument.schema:manufacturer.schema:Organization.schema:name"/>
-        <filter val="$MethodDefinition.schema:instrument.schema:model.schema:name"/>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <x14:filter val="analyteColumn : analysisOrder _x000a_  datatype: positive integer_x000a_  readOnly:true"/>
+            <x14:filter val="analyteColumn : backgroundCorrectionMethod _x000a_  datatype: enum {2-point off-peak linear | 2-point off-peak exponential | 2-point off-peak polynomial | 1-point high with slope factor | 1-point low with slope factor | Multi-point linear | Multi-point exponential | Mean Atomic Number (MAN) | EDS background fit | other | N/A }_x000a_  readOnly:true"/>
+            <x14:filter val="analyteColumn : backgroundCountingPosition _x000a_  datatype: text_x000a_  readOnly:true"/>
+            <x14:filter val="analyteColumn : backgroundCountingTime _x000a_  datatype: numeric_x000a_  readOnly:true"/>
+            <x14:filter val="analyteColumn : blankCorrection _x000a_  datatype: text_x000a_  readOnly:true"/>
+            <x14:filter val="analyteColumn : edsDeadTime _x000a_  datatype: text_x000a_  readOnly:true"/>
+            <x14:filter val="analyteColumn : elementEstimationMethod _x000a_  datatype: enum {Direct (measured) | Estimated via cation stoichiometry | Unknown }_x000a_  readOnly:true"/>
+            <x14:filter val="analyteColumn : epmaTechnique _x000a_  datatype: enum {WDS | EDS} _x000a_  readOnly:true"/>
+            <x14:filter val="analyteColumn : interferenceCorrection _x000a_  datatype: boolean_x000a_  readOnly:true"/>
+            <x14:filter val="analyteColumn : interferenceCorrectionStandard _x000a_  datatype: text_x000a_  readOnly:true"/>
+            <x14:filter val="analyteColumn : interferingElements _x000a_  datatype: text_x000a_  readOnly:true"/>
+            <x14:filter val="analyteColumn : monochromatorCrystal _x000a_  datatype: enum {LIF | LLIF | LIFL | LIFH | PET | LPET | PETL | PETH | PETJ | TAP | TAPL | TAPH | LTAP | LDE1 | LDE2 | LDE3 | RAP | KAP | ADP | Other}_x000a_  readOnly:true"/>
+            <x14:filter val="analyteColumn : normalization-standardsCorrection _x000a_  datatype: text_x000a_  readOnly:true"/>
+            <x14:filter val="analyteColumn : peakCountingTime _x000a_  datatype: numeric_x000a_  readOnly:true"/>
+            <x14:filter val="analyteColumn : primaryCalibrationStandard _x000a_  datatype: text_x000a_  readOnly:true"/>
+            <x14:filter val="analyteColumn : pulseHeightAnalyzeSetting _x000a_  datatype: enum {Integral | Differential)_x000a_  readOnly:true"/>
+            <x14:filter val="analyteColumn : secondaryReferenceMaterial _x000a_  datatype: text_x000a_  readOnly:true"/>
+            <x14:filter val="analyteColumn : spectrometerNumber _x000a_  datatype: positive integer_x000a_  readOnly:true"/>
+            <x14:filter val="analyteColumn : timeDependentIntensityCorrection _x000a_  datatype: enum {None | Linear | Exponential | Double exponential | Other | Unknown }_x000a_  readOnly:true"/>
+            <x14:filter val="analyteColumn : typicalDetectionLimit _x000a_  datatype: text_x000a_  readOnly:true"/>
+            <x14:filter val="analyteColumn : wdsDetectorType _x000a_  datatype: enum {High Pressure P10 Flow | Low Pressure P10 Flow | Xe Sealed | SDD | Si(Li) | Other | Unknown}_x000a_  readOnly:true"/>
+            <x14:filter val="analyteColumn : xrayEmissionLine _x000a_  datatype: enum {Kalpha | Kbeta | Lalpha | Lbeta | Lgamma | Malpha | Mbeta | Other)_x000a_  readOnly:true"/>
+            <x14:filter val="analyteColumn :detectionLimitMethod_x000a_  datatype: text_x000a_  readOnly:true"/>
+            <x14:filter val="analyteColumn :typicalAnalyticalAccuracy_x000a_  datatype: text_x000a_  readOnly:true"/>
+            <x14:filter val="analyteColumn :typicalAnalyticalPrecision_x000a_  datatype: text_x000a_  readOnly:true"/>
+            <x14:filter val="analyteColumn :typicalCountingStatisticsError_x000a_  datatype: text_x000a_  readOnly:true"/>
+            <x14:filter val="method-level property: beamCurrentDefault _x000a_  data:type PropertyValue _x000a_  readOnly:true_x000a_analyteColumn item: beamCurrent_x000a_  datatype: PropertyValue_x000a_  readOnly: false"/>
+          </mc:Choice>
+          <mc:Fallback>
+            <filter val="analyteColumn : analysisOrder _x000a_  datatype: positive integer_x000a_  readOnly:true"/>
+            <filter val="analyteColumn : backgroundCountingPosition _x000a_  datatype: text_x000a_  readOnly:true"/>
+            <filter val="analyteColumn : backgroundCountingTime _x000a_  datatype: numeric_x000a_  readOnly:true"/>
+            <filter val="analyteColumn : blankCorrection _x000a_  datatype: text_x000a_  readOnly:true"/>
+            <filter val="analyteColumn : edsDeadTime _x000a_  datatype: text_x000a_  readOnly:true"/>
+            <filter val="analyteColumn : elementEstimationMethod _x000a_  datatype: enum {Direct (measured) | Estimated via cation stoichiometry | Unknown }_x000a_  readOnly:true"/>
+            <filter val="analyteColumn : epmaTechnique _x000a_  datatype: enum {WDS | EDS} _x000a_  readOnly:true"/>
+            <filter val="analyteColumn : interferenceCorrection _x000a_  datatype: boolean_x000a_  readOnly:true"/>
+            <filter val="analyteColumn : interferenceCorrectionStandard _x000a_  datatype: text_x000a_  readOnly:true"/>
+            <filter val="analyteColumn : interferingElements _x000a_  datatype: text_x000a_  readOnly:true"/>
+            <filter val="analyteColumn : monochromatorCrystal _x000a_  datatype: enum {LIF | LLIF | LIFL | LIFH | PET | LPET | PETL | PETH | PETJ | TAP | TAPL | TAPH | LTAP | LDE1 | LDE2 | LDE3 | RAP | KAP | ADP | Other}_x000a_  readOnly:true"/>
+            <filter val="analyteColumn : normalization-standardsCorrection _x000a_  datatype: text_x000a_  readOnly:true"/>
+            <filter val="analyteColumn : peakCountingTime _x000a_  datatype: numeric_x000a_  readOnly:true"/>
+            <filter val="analyteColumn : primaryCalibrationStandard _x000a_  datatype: text_x000a_  readOnly:true"/>
+            <filter val="analyteColumn : pulseHeightAnalyzeSetting _x000a_  datatype: enum {Integral | Differential)_x000a_  readOnly:true"/>
+            <filter val="analyteColumn : secondaryReferenceMaterial _x000a_  datatype: text_x000a_  readOnly:true"/>
+            <filter val="analyteColumn : spectrometerNumber _x000a_  datatype: positive integer_x000a_  readOnly:true"/>
+            <filter val="analyteColumn : timeDependentIntensityCorrection _x000a_  datatype: enum {None | Linear | Exponential | Double exponential | Other | Unknown }_x000a_  readOnly:true"/>
+            <filter val="analyteColumn : typicalDetectionLimit _x000a_  datatype: text_x000a_  readOnly:true"/>
+            <filter val="analyteColumn : wdsDetectorType _x000a_  datatype: enum {High Pressure P10 Flow | Low Pressure P10 Flow | Xe Sealed | SDD | Si(Li) | Other | Unknown}_x000a_  readOnly:true"/>
+            <filter val="analyteColumn : xrayEmissionLine _x000a_  datatype: enum {Kalpha | Kbeta | Lalpha | Lbeta | Lgamma | Malpha | Mbeta | Other)_x000a_  readOnly:true"/>
+            <filter val="analyteColumn :detectionLimitMethod_x000a_  datatype: text_x000a_  readOnly:true"/>
+            <filter val="analyteColumn :typicalAnalyticalAccuracy_x000a_  datatype: text_x000a_  readOnly:true"/>
+            <filter val="analyteColumn :typicalAnalyticalPrecision_x000a_  datatype: text_x000a_  readOnly:true"/>
+            <filter val="analyteColumn :typicalCountingStatisticsError_x000a_  datatype: text_x000a_  readOnly:true"/>
+            <filter val="method-level property: beamCurrentDefault _x000a_  data:type PropertyValue _x000a_  readOnly:true_x000a_analyteColumn item: beamCurrent_x000a_  datatype: PropertyValue_x000a_  readOnly: false"/>
+          </mc:Fallback>
+        </mc:AlternateContent>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/docs/TAPP_EPMA_filled.xlsx
+++ b/docs/TAPP_EPMA_filled.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/944a82e2ddcde9eb/Documents/GithubC/USGIN/geochemBuildingBlocks/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="334" documentId="11_3C209AD99577444EEF615C96566D1EBF266D99FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BF90C6C-0D91-457C-AEDC-A3D2C7D20707}"/>
+  <xr:revisionPtr revIDLastSave="337" documentId="11_3C209AD99577444EEF615C96566D1EBF266D99FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFCCCE89-5B1D-4910-A98A-75EB0BAE74D6}"/>
   <bookViews>
     <workbookView xWindow="165" yWindow="1335" windowWidth="22350" windowHeight="14610" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1471,11 +1471,6 @@
     <t>MethodParameter (ada:fieldScope='method') , ada:dataType='number', schema:unitText='um'.</t>
   </si>
   <si>
-    <t>parameter: BeamRasterDimenstion. 
-  dataType: schema:PropertyValue
-  readOnly: False</t>
-  </si>
-  <si>
     <t>parameter:  BeamDamageMinimization. 
   dataType:  text
   readOnly: True</t>
@@ -1619,6 +1614,11 @@
 analyteColumn item: beamCurrent
   datatype: PropertyValue
   readOnly: true</t>
+  </si>
+  <si>
+    <t>parameter: BeamRasterDimension
+  dataType: schema:PropertyValue
+  readOnly: False</t>
   </si>
 </sst>
 </file>
@@ -2744,10 +2744,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -2924,7 +2920,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:U1001"/>
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2948,7 +2943,7 @@
     <col min="22" max="16384" width="12.7109375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3011,7 +3006,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="13.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="177" t="s">
         <v>18</v>
       </c>
@@ -3036,7 +3031,7 @@
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
     </row>
-    <row r="3" spans="1:21" s="64" customFormat="1" ht="57.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" s="64" customFormat="1" ht="57" x14ac:dyDescent="0.2">
       <c r="A3" s="59" t="s">
         <v>19</v>
       </c>
@@ -3096,7 +3091,7 @@
       </c>
       <c r="U3" s="63"/>
     </row>
-    <row r="4" spans="1:21" s="70" customFormat="1" ht="51.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" s="70" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A4" s="65" t="s">
         <v>29</v>
       </c>
@@ -3158,7 +3153,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="5" spans="1:21" s="70" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" s="70" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A5" s="65" t="s">
         <v>34</v>
       </c>
@@ -3211,14 +3206,14 @@
         <v>1</v>
       </c>
       <c r="S5" s="69" t="s">
+        <v>455</v>
+      </c>
+      <c r="T5" s="170" t="s">
         <v>456</v>
       </c>
-      <c r="T5" s="170" t="s">
-        <v>457</v>
-      </c>
       <c r="U5" s="69"/>
     </row>
-    <row r="6" spans="1:21" s="70" customFormat="1" ht="57.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" s="70" customFormat="1" ht="57" x14ac:dyDescent="0.2">
       <c r="A6" s="65" t="s">
         <v>46</v>
       </c>
@@ -3278,7 +3273,7 @@
       </c>
       <c r="U6" s="69"/>
     </row>
-    <row r="7" spans="1:21" s="70" customFormat="1" ht="29.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" s="70" customFormat="1" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7" s="71" t="s">
         <v>58</v>
       </c>
@@ -3318,7 +3313,7 @@
       </c>
       <c r="U7" s="69"/>
     </row>
-    <row r="8" spans="1:21" s="70" customFormat="1" ht="43.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" s="70" customFormat="1" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A8" s="65" t="s">
         <v>63</v>
       </c>
@@ -3358,7 +3353,7 @@
       </c>
       <c r="U8" s="69"/>
     </row>
-    <row r="9" spans="1:21" s="70" customFormat="1" ht="43.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" s="70" customFormat="1" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A9" s="71" t="s">
         <v>66</v>
       </c>
@@ -3400,7 +3395,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="10" spans="1:21" s="70" customFormat="1" ht="43.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" s="70" customFormat="1" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A10" s="71" t="s">
         <v>69</v>
       </c>
@@ -3440,7 +3435,7 @@
       </c>
       <c r="U10" s="69"/>
     </row>
-    <row r="11" spans="1:21" s="70" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" s="70" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A11" s="77"/>
       <c r="B11" s="78"/>
       <c r="C11" s="78"/>
@@ -3463,7 +3458,7 @@
       <c r="T11" s="69"/>
       <c r="U11" s="69"/>
     </row>
-    <row r="12" spans="1:21" s="70" customFormat="1" ht="13.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" s="70" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="175" t="s">
         <v>73</v>
       </c>
@@ -3488,7 +3483,7 @@
       <c r="T12" s="69"/>
       <c r="U12" s="69"/>
     </row>
-    <row r="13" spans="1:21" s="70" customFormat="1" ht="86.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" s="70" customFormat="1" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A13" s="80" t="s">
         <v>74</v>
       </c>
@@ -3510,7 +3505,7 @@
         <v>78</v>
       </c>
       <c r="I13" s="81" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J13" s="81" t="s">
         <v>79</v>
@@ -3548,7 +3543,7 @@
       </c>
       <c r="U13" s="69"/>
     </row>
-    <row r="14" spans="1:21" s="70" customFormat="1" ht="90" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" s="70" customFormat="1" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A14" s="84" t="s">
         <v>87</v>
       </c>
@@ -3607,10 +3602,10 @@
         <v>356</v>
       </c>
       <c r="U14" s="69" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" s="70" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" s="70" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A15" s="77"/>
       <c r="B15" s="78"/>
       <c r="C15" s="78"/>
@@ -3633,7 +3628,7 @@
       <c r="T15" s="69"/>
       <c r="U15" s="69"/>
     </row>
-    <row r="16" spans="1:21" s="70" customFormat="1" ht="13.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" s="70" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="178" t="s">
         <v>100</v>
       </c>
@@ -3658,7 +3653,7 @@
       <c r="T16" s="69"/>
       <c r="U16" s="69"/>
     </row>
-    <row r="17" spans="1:21" s="70" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" s="70" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A17" s="88" t="s">
         <v>101</v>
       </c>
@@ -3718,7 +3713,7 @@
       </c>
       <c r="U17" s="69"/>
     </row>
-    <row r="18" spans="1:21" s="70" customFormat="1" ht="72" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" s="70" customFormat="1" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A18" s="88" t="s">
         <v>108</v>
       </c>
@@ -3778,7 +3773,7 @@
       </c>
       <c r="U18" s="69"/>
     </row>
-    <row r="19" spans="1:21" s="70" customFormat="1" ht="51.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" s="70" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A19" s="88" t="s">
         <v>119</v>
       </c>
@@ -3815,14 +3810,14 @@
         <v>0.2</v>
       </c>
       <c r="S19" s="69" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="T19" s="69" t="s">
         <v>424</v>
       </c>
       <c r="U19" s="69"/>
     </row>
-    <row r="20" spans="1:21" s="70" customFormat="1" ht="57.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" s="70" customFormat="1" ht="57" x14ac:dyDescent="0.2">
       <c r="A20" s="88" t="s">
         <v>123</v>
       </c>
@@ -3872,7 +3867,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="21" spans="1:21" s="70" customFormat="1" ht="57.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" s="70" customFormat="1" ht="57" x14ac:dyDescent="0.2">
       <c r="A21" s="88" t="s">
         <v>128</v>
       </c>
@@ -3926,7 +3921,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="22" spans="1:21" s="70" customFormat="1" ht="57.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" s="70" customFormat="1" ht="57" x14ac:dyDescent="0.2">
       <c r="A22" s="92" t="s">
         <v>136</v>
       </c>
@@ -3961,7 +3956,7 @@
         <v>0.1</v>
       </c>
       <c r="S22" s="69" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="T22" s="69" t="s">
         <v>140</v>
@@ -3970,7 +3965,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="23" spans="1:21" s="70" customFormat="1" ht="57.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" s="70" customFormat="1" ht="57" x14ac:dyDescent="0.2">
       <c r="A23" s="92" t="s">
         <v>141</v>
       </c>
@@ -4005,7 +4000,7 @@
         <v>0.1</v>
       </c>
       <c r="S23" s="69" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="T23" s="69" t="s">
         <v>145</v>
@@ -4014,7 +4009,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="24" spans="1:21" s="70" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" s="70" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A24" s="77"/>
       <c r="B24" s="78"/>
       <c r="C24" s="78"/>
@@ -4037,7 +4032,7 @@
       <c r="T24" s="69"/>
       <c r="U24" s="69"/>
     </row>
-    <row r="25" spans="1:21" s="70" customFormat="1" ht="13.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" s="70" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="179" t="s">
         <v>146</v>
       </c>
@@ -4062,7 +4057,7 @@
       <c r="T25" s="69"/>
       <c r="U25" s="69"/>
     </row>
-    <row r="26" spans="1:21" s="70" customFormat="1" ht="72" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" s="70" customFormat="1" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A26" s="96" t="s">
         <v>147</v>
       </c>
@@ -4115,16 +4110,16 @@
         <v>1</v>
       </c>
       <c r="S26" s="69" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="T26" s="170" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="U26" s="171" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="27" spans="1:21" s="70" customFormat="1" ht="77.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" s="70" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A27" s="96" t="s">
         <v>157</v>
       </c>
@@ -4177,16 +4172,16 @@
         <v>1</v>
       </c>
       <c r="S27" s="101" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="T27" s="170" t="s">
         <v>432</v>
       </c>
       <c r="U27" s="171" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" s="70" customFormat="1" ht="77.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" s="70" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A28" s="96" t="s">
         <v>164</v>
       </c>
@@ -4237,16 +4232,16 @@
         <v>0.9</v>
       </c>
       <c r="S28" s="101" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="T28" s="170" t="s">
         <v>433</v>
       </c>
       <c r="U28" s="171" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" s="70" customFormat="1" ht="51.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" s="70" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A29" s="102" t="s">
         <v>175</v>
       </c>
@@ -4285,10 +4280,10 @@
         <v>179</v>
       </c>
       <c r="U29" s="69" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" s="70" customFormat="1" ht="86.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" s="70" customFormat="1" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A30" s="102" t="s">
         <v>180</v>
       </c>
@@ -4331,10 +4326,10 @@
         <v>186</v>
       </c>
       <c r="U30" s="69" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" s="111" customFormat="1" ht="100.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" s="111" customFormat="1" ht="100.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="106" t="s">
         <v>187</v>
       </c>
@@ -4373,10 +4368,10 @@
         <v>190</v>
       </c>
       <c r="U31" s="110" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" ht="234" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" ht="234" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
         <v>191</v>
       </c>
@@ -4414,10 +4409,10 @@
         <v>195</v>
       </c>
       <c r="T32" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="U32" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="33" spans="1:21" ht="77.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -4437,7 +4432,7 @@
         <v>199</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="143" t="s">
@@ -4447,7 +4442,7 @@
         <v>201</v>
       </c>
       <c r="J33" s="36" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="K33" s="36" t="s">
         <v>200</v>
@@ -4462,10 +4457,10 @@
         <v>203</v>
       </c>
       <c r="O33" s="36" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="P33" s="36" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="Q33" s="36" t="s">
         <v>203</v>
@@ -4478,10 +4473,10 @@
         <v>163</v>
       </c>
       <c r="T33" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="U33" s="3" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
@@ -4501,7 +4496,7 @@
         <v>206</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="143" t="s">
@@ -4565,7 +4560,7 @@
         <v>213</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="145"/>
@@ -4609,7 +4604,7 @@
         <v>213</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="145"/>
@@ -4653,7 +4648,7 @@
         <v>220</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="143"/>
@@ -4699,7 +4694,7 @@
         <v>225</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="145"/>
@@ -4743,7 +4738,7 @@
         <v>229</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="145"/>
@@ -4787,16 +4782,16 @@
         <v>233</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="143" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="I40" s="36"/>
       <c r="J40" s="36"/>
       <c r="K40" s="36" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L40" s="36"/>
       <c r="M40" s="36"/>
@@ -4835,7 +4830,7 @@
         <v>240</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="143" t="s">
@@ -4889,7 +4884,7 @@
         <v>248</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="143" t="s">
@@ -4941,7 +4936,7 @@
         <v>255</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="145"/>
@@ -4968,7 +4963,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="44" spans="1:21" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A44" s="5"/>
       <c r="B44" s="34"/>
       <c r="C44" s="34"/>
@@ -4991,7 +4986,7 @@
       <c r="T44" s="3"/>
       <c r="U44" s="3"/>
     </row>
-    <row r="45" spans="1:21" ht="13.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A45" s="180" t="s">
         <v>257</v>
       </c>
@@ -5016,7 +5011,7 @@
       <c r="T45" s="3"/>
       <c r="U45" s="3"/>
     </row>
-    <row r="46" spans="1:21" ht="143.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:21" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
         <v>258</v>
       </c>
@@ -5063,16 +5058,16 @@
         <v>0.7</v>
       </c>
       <c r="S46" s="11" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="T46" s="3" t="s">
         <v>264</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="47" spans="1:21" ht="57.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
         <v>265</v>
       </c>
@@ -5114,7 +5109,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="48" spans="1:21" ht="57.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A48" s="7" t="s">
         <v>269</v>
       </c>
@@ -5160,7 +5155,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="49" spans="1:21" ht="129" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:21" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>276</v>
       </c>
@@ -5199,10 +5194,10 @@
         <v>279</v>
       </c>
       <c r="U49" s="3" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="50" spans="1:21" ht="57.75" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>280</v>
       </c>
@@ -5261,7 +5256,7 @@
         <v>286</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G51" s="3"/>
       <c r="H51" s="151"/>
@@ -5282,7 +5277,7 @@
         <v>208</v>
       </c>
       <c r="T51" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="U51" s="3" t="s">
         <v>372</v>
@@ -5305,7 +5300,7 @@
         <v>289</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="151"/>
@@ -5349,7 +5344,7 @@
         <v>293</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G53" s="3"/>
       <c r="H53" s="153"/>
@@ -5370,7 +5365,7 @@
         <v>208</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="U53" s="3" t="s">
         <v>374</v>
@@ -5393,7 +5388,7 @@
         <v>296</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="155"/>
@@ -5439,7 +5434,7 @@
         <v>300</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="151"/>
@@ -5483,7 +5478,7 @@
         <v>303</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="151"/>
@@ -5510,7 +5505,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="57" spans="1:21" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:21" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A57" s="5"/>
       <c r="B57" s="34"/>
       <c r="C57" s="34"/>
@@ -5533,7 +5528,7 @@
       <c r="T57" s="3"/>
       <c r="U57" s="3"/>
     </row>
-    <row r="58" spans="1:21" ht="13.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A58" s="172" t="s">
         <v>304</v>
       </c>
@@ -5575,7 +5570,7 @@
         <v>307</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G59" s="3"/>
       <c r="H59" s="160" t="s">
@@ -5637,7 +5632,7 @@
         <v>317</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G60" s="3"/>
       <c r="H60" s="160"/>
@@ -5687,7 +5682,7 @@
         <v>323</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G61" s="3"/>
       <c r="H61" s="160"/>
@@ -5731,7 +5726,7 @@
         <v>327</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G62" s="3"/>
       <c r="H62" s="162"/>
@@ -5775,7 +5770,7 @@
         <v>331</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G63" s="3"/>
       <c r="H63" s="162"/>
@@ -5819,7 +5814,7 @@
         <v>335</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="162"/>
@@ -5873,7 +5868,7 @@
         <v>343</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G65" s="3"/>
       <c r="H65" s="162"/>
@@ -5915,7 +5910,7 @@
         <v>346</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G66" s="8"/>
       <c r="H66" s="162"/>
@@ -5959,7 +5954,7 @@
         <v>349</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G67" s="8"/>
       <c r="H67" s="162"/>
@@ -6003,7 +5998,7 @@
         <v>352</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G68" s="8"/>
       <c r="H68" s="162"/>
@@ -6030,7 +6025,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="69" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A69" s="9"/>
       <c r="B69" s="55"/>
       <c r="C69" s="55"/>
@@ -6053,7 +6048,7 @@
       <c r="T69" s="9"/>
       <c r="U69" s="9"/>
     </row>
-    <row r="70" spans="1:21" ht="42.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:21" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A70" s="10" t="s">
         <v>353</v>
       </c>
@@ -6090,7 +6085,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="71" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A71" s="9"/>
       <c r="B71" s="55"/>
       <c r="C71" s="55"/>
@@ -6113,7 +6108,7 @@
       <c r="T71" s="9"/>
       <c r="U71" s="9"/>
     </row>
-    <row r="72" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A72" s="9"/>
       <c r="B72" s="55"/>
       <c r="C72" s="55"/>
@@ -6136,7 +6131,7 @@
       <c r="T72" s="9"/>
       <c r="U72" s="9"/>
     </row>
-    <row r="73" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A73" s="9"/>
       <c r="B73" s="55"/>
       <c r="C73" s="55"/>
@@ -6159,7 +6154,7 @@
       <c r="T73" s="9"/>
       <c r="U73" s="9"/>
     </row>
-    <row r="74" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A74" s="9"/>
       <c r="B74" s="55"/>
       <c r="C74" s="55"/>
@@ -6182,7 +6177,7 @@
       <c r="T74" s="9"/>
       <c r="U74" s="9"/>
     </row>
-    <row r="75" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A75" s="9"/>
       <c r="B75" s="55"/>
       <c r="C75" s="55"/>
@@ -6205,7 +6200,7 @@
       <c r="T75" s="9"/>
       <c r="U75" s="9"/>
     </row>
-    <row r="76" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A76" s="9"/>
       <c r="B76" s="55"/>
       <c r="C76" s="55"/>
@@ -6228,7 +6223,7 @@
       <c r="T76" s="9"/>
       <c r="U76" s="9"/>
     </row>
-    <row r="77" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A77" s="9"/>
       <c r="B77" s="55"/>
       <c r="C77" s="55"/>
@@ -6251,7 +6246,7 @@
       <c r="T77" s="9"/>
       <c r="U77" s="9"/>
     </row>
-    <row r="78" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A78" s="9"/>
       <c r="B78" s="55"/>
       <c r="C78" s="55"/>
@@ -6274,7 +6269,7 @@
       <c r="T78" s="9"/>
       <c r="U78" s="9"/>
     </row>
-    <row r="79" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A79" s="9"/>
       <c r="B79" s="55"/>
       <c r="C79" s="55"/>
@@ -6297,7 +6292,7 @@
       <c r="T79" s="9"/>
       <c r="U79" s="9"/>
     </row>
-    <row r="80" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A80" s="9"/>
       <c r="B80" s="55"/>
       <c r="C80" s="55"/>
@@ -6320,7 +6315,7 @@
       <c r="T80" s="9"/>
       <c r="U80" s="9"/>
     </row>
-    <row r="81" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A81" s="9"/>
       <c r="B81" s="55"/>
       <c r="C81" s="55"/>
@@ -6343,7 +6338,7 @@
       <c r="T81" s="9"/>
       <c r="U81" s="9"/>
     </row>
-    <row r="82" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A82" s="9"/>
       <c r="B82" s="55"/>
       <c r="C82" s="55"/>
@@ -6366,7 +6361,7 @@
       <c r="T82" s="9"/>
       <c r="U82" s="9"/>
     </row>
-    <row r="83" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A83" s="9"/>
       <c r="B83" s="55"/>
       <c r="C83" s="55"/>
@@ -6389,7 +6384,7 @@
       <c r="T83" s="9"/>
       <c r="U83" s="9"/>
     </row>
-    <row r="84" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A84" s="9"/>
       <c r="B84" s="55"/>
       <c r="C84" s="55"/>
@@ -6412,7 +6407,7 @@
       <c r="T84" s="9"/>
       <c r="U84" s="9"/>
     </row>
-    <row r="85" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A85" s="9"/>
       <c r="B85" s="55"/>
       <c r="C85" s="55"/>
@@ -6435,7 +6430,7 @@
       <c r="T85" s="9"/>
       <c r="U85" s="9"/>
     </row>
-    <row r="86" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A86" s="9"/>
       <c r="B86" s="55"/>
       <c r="C86" s="55"/>
@@ -6458,7 +6453,7 @@
       <c r="T86" s="9"/>
       <c r="U86" s="9"/>
     </row>
-    <row r="87" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A87" s="9"/>
       <c r="B87" s="55"/>
       <c r="C87" s="55"/>
@@ -6481,7 +6476,7 @@
       <c r="T87" s="9"/>
       <c r="U87" s="9"/>
     </row>
-    <row r="88" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A88" s="9"/>
       <c r="B88" s="55"/>
       <c r="C88" s="55"/>
@@ -6504,7 +6499,7 @@
       <c r="T88" s="9"/>
       <c r="U88" s="9"/>
     </row>
-    <row r="89" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A89" s="9"/>
       <c r="B89" s="55"/>
       <c r="C89" s="55"/>
@@ -6527,7 +6522,7 @@
       <c r="T89" s="9"/>
       <c r="U89" s="9"/>
     </row>
-    <row r="90" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A90" s="9"/>
       <c r="B90" s="55"/>
       <c r="C90" s="55"/>
@@ -6550,7 +6545,7 @@
       <c r="T90" s="9"/>
       <c r="U90" s="9"/>
     </row>
-    <row r="91" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A91" s="9"/>
       <c r="B91" s="55"/>
       <c r="C91" s="55"/>
@@ -6573,7 +6568,7 @@
       <c r="T91" s="9"/>
       <c r="U91" s="9"/>
     </row>
-    <row r="92" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A92" s="9"/>
       <c r="B92" s="55"/>
       <c r="C92" s="55"/>
@@ -6596,7 +6591,7 @@
       <c r="T92" s="9"/>
       <c r="U92" s="9"/>
     </row>
-    <row r="93" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A93" s="9"/>
       <c r="B93" s="55"/>
       <c r="C93" s="55"/>
@@ -6619,7 +6614,7 @@
       <c r="T93" s="9"/>
       <c r="U93" s="9"/>
     </row>
-    <row r="94" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A94" s="9"/>
       <c r="B94" s="55"/>
       <c r="C94" s="55"/>
@@ -6642,7 +6637,7 @@
       <c r="T94" s="9"/>
       <c r="U94" s="9"/>
     </row>
-    <row r="95" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A95" s="9"/>
       <c r="B95" s="55"/>
       <c r="C95" s="55"/>
@@ -6665,7 +6660,7 @@
       <c r="T95" s="9"/>
       <c r="U95" s="9"/>
     </row>
-    <row r="96" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A96" s="9"/>
       <c r="B96" s="55"/>
       <c r="C96" s="55"/>
@@ -6688,7 +6683,7 @@
       <c r="T96" s="9"/>
       <c r="U96" s="9"/>
     </row>
-    <row r="97" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A97" s="9"/>
       <c r="B97" s="55"/>
       <c r="C97" s="55"/>
@@ -6711,7 +6706,7 @@
       <c r="T97" s="9"/>
       <c r="U97" s="9"/>
     </row>
-    <row r="98" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A98" s="9"/>
       <c r="B98" s="55"/>
       <c r="C98" s="55"/>
@@ -6734,7 +6729,7 @@
       <c r="T98" s="9"/>
       <c r="U98" s="9"/>
     </row>
-    <row r="99" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A99" s="9"/>
       <c r="B99" s="55"/>
       <c r="C99" s="55"/>
@@ -6757,7 +6752,7 @@
       <c r="T99" s="9"/>
       <c r="U99" s="9"/>
     </row>
-    <row r="100" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A100" s="9"/>
       <c r="B100" s="55"/>
       <c r="C100" s="55"/>
@@ -6780,7 +6775,7 @@
       <c r="T100" s="9"/>
       <c r="U100" s="9"/>
     </row>
-    <row r="101" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A101" s="9"/>
       <c r="B101" s="55"/>
       <c r="C101" s="55"/>
@@ -6803,7 +6798,7 @@
       <c r="T101" s="9"/>
       <c r="U101" s="9"/>
     </row>
-    <row r="102" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A102" s="9"/>
       <c r="B102" s="55"/>
       <c r="C102" s="55"/>
@@ -6826,7 +6821,7 @@
       <c r="T102" s="9"/>
       <c r="U102" s="9"/>
     </row>
-    <row r="103" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A103" s="9"/>
       <c r="B103" s="55"/>
       <c r="C103" s="55"/>
@@ -6849,7 +6844,7 @@
       <c r="T103" s="9"/>
       <c r="U103" s="9"/>
     </row>
-    <row r="104" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A104" s="9"/>
       <c r="B104" s="55"/>
       <c r="C104" s="55"/>
@@ -6872,7 +6867,7 @@
       <c r="T104" s="9"/>
       <c r="U104" s="9"/>
     </row>
-    <row r="105" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A105" s="9"/>
       <c r="B105" s="55"/>
       <c r="C105" s="55"/>
@@ -6895,7 +6890,7 @@
       <c r="T105" s="9"/>
       <c r="U105" s="9"/>
     </row>
-    <row r="106" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A106" s="9"/>
       <c r="B106" s="55"/>
       <c r="C106" s="55"/>
@@ -6918,7 +6913,7 @@
       <c r="T106" s="9"/>
       <c r="U106" s="9"/>
     </row>
-    <row r="107" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A107" s="9"/>
       <c r="B107" s="55"/>
       <c r="C107" s="55"/>
@@ -6941,7 +6936,7 @@
       <c r="T107" s="9"/>
       <c r="U107" s="9"/>
     </row>
-    <row r="108" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A108" s="9"/>
       <c r="B108" s="55"/>
       <c r="C108" s="55"/>
@@ -6964,7 +6959,7 @@
       <c r="T108" s="9"/>
       <c r="U108" s="9"/>
     </row>
-    <row r="109" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A109" s="9"/>
       <c r="B109" s="55"/>
       <c r="C109" s="55"/>
@@ -6987,7 +6982,7 @@
       <c r="T109" s="9"/>
       <c r="U109" s="9"/>
     </row>
-    <row r="110" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A110" s="9"/>
       <c r="B110" s="55"/>
       <c r="C110" s="55"/>
@@ -7010,7 +7005,7 @@
       <c r="T110" s="9"/>
       <c r="U110" s="9"/>
     </row>
-    <row r="111" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A111" s="9"/>
       <c r="B111" s="55"/>
       <c r="C111" s="55"/>
@@ -7033,7 +7028,7 @@
       <c r="T111" s="9"/>
       <c r="U111" s="9"/>
     </row>
-    <row r="112" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A112" s="9"/>
       <c r="B112" s="55"/>
       <c r="C112" s="55"/>
@@ -7056,7 +7051,7 @@
       <c r="T112" s="9"/>
       <c r="U112" s="9"/>
     </row>
-    <row r="113" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A113" s="9"/>
       <c r="B113" s="55"/>
       <c r="C113" s="55"/>
@@ -7079,7 +7074,7 @@
       <c r="T113" s="9"/>
       <c r="U113" s="9"/>
     </row>
-    <row r="114" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A114" s="9"/>
       <c r="B114" s="55"/>
       <c r="C114" s="55"/>
@@ -7102,7 +7097,7 @@
       <c r="T114" s="9"/>
       <c r="U114" s="9"/>
     </row>
-    <row r="115" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A115" s="9"/>
       <c r="B115" s="55"/>
       <c r="C115" s="55"/>
@@ -7125,7 +7120,7 @@
       <c r="T115" s="9"/>
       <c r="U115" s="9"/>
     </row>
-    <row r="116" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A116" s="9"/>
       <c r="B116" s="55"/>
       <c r="C116" s="55"/>
@@ -7148,7 +7143,7 @@
       <c r="T116" s="9"/>
       <c r="U116" s="9"/>
     </row>
-    <row r="117" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A117" s="9"/>
       <c r="B117" s="55"/>
       <c r="C117" s="55"/>
@@ -7171,7 +7166,7 @@
       <c r="T117" s="9"/>
       <c r="U117" s="9"/>
     </row>
-    <row r="118" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A118" s="9"/>
       <c r="B118" s="55"/>
       <c r="C118" s="55"/>
@@ -7194,7 +7189,7 @@
       <c r="T118" s="9"/>
       <c r="U118" s="9"/>
     </row>
-    <row r="119" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A119" s="9"/>
       <c r="B119" s="55"/>
       <c r="C119" s="55"/>
@@ -7217,7 +7212,7 @@
       <c r="T119" s="9"/>
       <c r="U119" s="9"/>
     </row>
-    <row r="120" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A120" s="9"/>
       <c r="B120" s="55"/>
       <c r="C120" s="55"/>
@@ -7240,7 +7235,7 @@
       <c r="T120" s="9"/>
       <c r="U120" s="9"/>
     </row>
-    <row r="121" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A121" s="9"/>
       <c r="B121" s="55"/>
       <c r="C121" s="55"/>
@@ -7263,7 +7258,7 @@
       <c r="T121" s="9"/>
       <c r="U121" s="9"/>
     </row>
-    <row r="122" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A122" s="9"/>
       <c r="B122" s="55"/>
       <c r="C122" s="55"/>
@@ -7286,7 +7281,7 @@
       <c r="T122" s="9"/>
       <c r="U122" s="9"/>
     </row>
-    <row r="123" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A123" s="9"/>
       <c r="B123" s="55"/>
       <c r="C123" s="55"/>
@@ -7309,7 +7304,7 @@
       <c r="T123" s="9"/>
       <c r="U123" s="9"/>
     </row>
-    <row r="124" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A124" s="9"/>
       <c r="B124" s="55"/>
       <c r="C124" s="55"/>
@@ -7332,7 +7327,7 @@
       <c r="T124" s="9"/>
       <c r="U124" s="9"/>
     </row>
-    <row r="125" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A125" s="9"/>
       <c r="B125" s="55"/>
       <c r="C125" s="55"/>
@@ -7355,7 +7350,7 @@
       <c r="T125" s="9"/>
       <c r="U125" s="9"/>
     </row>
-    <row r="126" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A126" s="9"/>
       <c r="B126" s="55"/>
       <c r="C126" s="55"/>
@@ -7378,7 +7373,7 @@
       <c r="T126" s="9"/>
       <c r="U126" s="9"/>
     </row>
-    <row r="127" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A127" s="9"/>
       <c r="B127" s="55"/>
       <c r="C127" s="55"/>
@@ -7401,7 +7396,7 @@
       <c r="T127" s="9"/>
       <c r="U127" s="9"/>
     </row>
-    <row r="128" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A128" s="9"/>
       <c r="B128" s="55"/>
       <c r="C128" s="55"/>
@@ -7424,7 +7419,7 @@
       <c r="T128" s="9"/>
       <c r="U128" s="9"/>
     </row>
-    <row r="129" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A129" s="9"/>
       <c r="B129" s="55"/>
       <c r="C129" s="55"/>
@@ -7447,7 +7442,7 @@
       <c r="T129" s="9"/>
       <c r="U129" s="9"/>
     </row>
-    <row r="130" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A130" s="9"/>
       <c r="B130" s="55"/>
       <c r="C130" s="55"/>
@@ -7470,7 +7465,7 @@
       <c r="T130" s="9"/>
       <c r="U130" s="9"/>
     </row>
-    <row r="131" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A131" s="9"/>
       <c r="B131" s="55"/>
       <c r="C131" s="55"/>
@@ -7493,7 +7488,7 @@
       <c r="T131" s="9"/>
       <c r="U131" s="9"/>
     </row>
-    <row r="132" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A132" s="9"/>
       <c r="B132" s="55"/>
       <c r="C132" s="55"/>
@@ -7516,7 +7511,7 @@
       <c r="T132" s="9"/>
       <c r="U132" s="9"/>
     </row>
-    <row r="133" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A133" s="9"/>
       <c r="B133" s="55"/>
       <c r="C133" s="55"/>
@@ -7539,7 +7534,7 @@
       <c r="T133" s="9"/>
       <c r="U133" s="9"/>
     </row>
-    <row r="134" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A134" s="9"/>
       <c r="B134" s="55"/>
       <c r="C134" s="55"/>
@@ -7562,7 +7557,7 @@
       <c r="T134" s="9"/>
       <c r="U134" s="9"/>
     </row>
-    <row r="135" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A135" s="9"/>
       <c r="B135" s="55"/>
       <c r="C135" s="55"/>
@@ -7585,7 +7580,7 @@
       <c r="T135" s="9"/>
       <c r="U135" s="9"/>
     </row>
-    <row r="136" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A136" s="9"/>
       <c r="B136" s="55"/>
       <c r="C136" s="55"/>
@@ -7608,7 +7603,7 @@
       <c r="T136" s="9"/>
       <c r="U136" s="9"/>
     </row>
-    <row r="137" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A137" s="9"/>
       <c r="B137" s="55"/>
       <c r="C137" s="55"/>
@@ -7631,7 +7626,7 @@
       <c r="T137" s="9"/>
       <c r="U137" s="9"/>
     </row>
-    <row r="138" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A138" s="9"/>
       <c r="B138" s="55"/>
       <c r="C138" s="55"/>
@@ -7654,7 +7649,7 @@
       <c r="T138" s="9"/>
       <c r="U138" s="9"/>
     </row>
-    <row r="139" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A139" s="9"/>
       <c r="B139" s="55"/>
       <c r="C139" s="55"/>
@@ -7677,7 +7672,7 @@
       <c r="T139" s="9"/>
       <c r="U139" s="9"/>
     </row>
-    <row r="140" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A140" s="9"/>
       <c r="B140" s="55"/>
       <c r="C140" s="55"/>
@@ -7700,7 +7695,7 @@
       <c r="T140" s="9"/>
       <c r="U140" s="9"/>
     </row>
-    <row r="141" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A141" s="9"/>
       <c r="B141" s="55"/>
       <c r="C141" s="55"/>
@@ -7723,7 +7718,7 @@
       <c r="T141" s="9"/>
       <c r="U141" s="9"/>
     </row>
-    <row r="142" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A142" s="9"/>
       <c r="B142" s="55"/>
       <c r="C142" s="55"/>
@@ -7746,7 +7741,7 @@
       <c r="T142" s="9"/>
       <c r="U142" s="9"/>
     </row>
-    <row r="143" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A143" s="9"/>
       <c r="B143" s="55"/>
       <c r="C143" s="55"/>
@@ -7769,7 +7764,7 @@
       <c r="T143" s="9"/>
       <c r="U143" s="9"/>
     </row>
-    <row r="144" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A144" s="9"/>
       <c r="B144" s="55"/>
       <c r="C144" s="55"/>
@@ -7792,7 +7787,7 @@
       <c r="T144" s="9"/>
       <c r="U144" s="9"/>
     </row>
-    <row r="145" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A145" s="9"/>
       <c r="B145" s="55"/>
       <c r="C145" s="55"/>
@@ -7815,7 +7810,7 @@
       <c r="T145" s="9"/>
       <c r="U145" s="9"/>
     </row>
-    <row r="146" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A146" s="9"/>
       <c r="B146" s="55"/>
       <c r="C146" s="55"/>
@@ -7838,7 +7833,7 @@
       <c r="T146" s="9"/>
       <c r="U146" s="9"/>
     </row>
-    <row r="147" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A147" s="9"/>
       <c r="B147" s="55"/>
       <c r="C147" s="55"/>
@@ -7861,7 +7856,7 @@
       <c r="T147" s="9"/>
       <c r="U147" s="9"/>
     </row>
-    <row r="148" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A148" s="9"/>
       <c r="B148" s="55"/>
       <c r="C148" s="55"/>
@@ -7884,7 +7879,7 @@
       <c r="T148" s="9"/>
       <c r="U148" s="9"/>
     </row>
-    <row r="149" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A149" s="9"/>
       <c r="B149" s="55"/>
       <c r="C149" s="55"/>
@@ -7907,7 +7902,7 @@
       <c r="T149" s="9"/>
       <c r="U149" s="9"/>
     </row>
-    <row r="150" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A150" s="9"/>
       <c r="B150" s="55"/>
       <c r="C150" s="55"/>
@@ -7930,7 +7925,7 @@
       <c r="T150" s="9"/>
       <c r="U150" s="9"/>
     </row>
-    <row r="151" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A151" s="9"/>
       <c r="B151" s="55"/>
       <c r="C151" s="55"/>
@@ -7953,7 +7948,7 @@
       <c r="T151" s="9"/>
       <c r="U151" s="9"/>
     </row>
-    <row r="152" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A152" s="9"/>
       <c r="B152" s="55"/>
       <c r="C152" s="55"/>
@@ -7976,7 +7971,7 @@
       <c r="T152" s="9"/>
       <c r="U152" s="9"/>
     </row>
-    <row r="153" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A153" s="9"/>
       <c r="B153" s="55"/>
       <c r="C153" s="55"/>
@@ -7999,7 +7994,7 @@
       <c r="T153" s="9"/>
       <c r="U153" s="9"/>
     </row>
-    <row r="154" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A154" s="9"/>
       <c r="B154" s="55"/>
       <c r="C154" s="55"/>
@@ -8022,7 +8017,7 @@
       <c r="T154" s="9"/>
       <c r="U154" s="9"/>
     </row>
-    <row r="155" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A155" s="9"/>
       <c r="B155" s="55"/>
       <c r="C155" s="55"/>
@@ -8045,7 +8040,7 @@
       <c r="T155" s="9"/>
       <c r="U155" s="9"/>
     </row>
-    <row r="156" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A156" s="9"/>
       <c r="B156" s="55"/>
       <c r="C156" s="55"/>
@@ -8068,7 +8063,7 @@
       <c r="T156" s="9"/>
       <c r="U156" s="9"/>
     </row>
-    <row r="157" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A157" s="9"/>
       <c r="B157" s="55"/>
       <c r="C157" s="55"/>
@@ -8091,7 +8086,7 @@
       <c r="T157" s="9"/>
       <c r="U157" s="9"/>
     </row>
-    <row r="158" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A158" s="9"/>
       <c r="B158" s="55"/>
       <c r="C158" s="55"/>
@@ -8114,7 +8109,7 @@
       <c r="T158" s="9"/>
       <c r="U158" s="9"/>
     </row>
-    <row r="159" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A159" s="9"/>
       <c r="B159" s="55"/>
       <c r="C159" s="55"/>
@@ -8137,7 +8132,7 @@
       <c r="T159" s="9"/>
       <c r="U159" s="9"/>
     </row>
-    <row r="160" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A160" s="9"/>
       <c r="B160" s="55"/>
       <c r="C160" s="55"/>
@@ -8160,7 +8155,7 @@
       <c r="T160" s="9"/>
       <c r="U160" s="9"/>
     </row>
-    <row r="161" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A161" s="9"/>
       <c r="B161" s="55"/>
       <c r="C161" s="55"/>
@@ -8183,7 +8178,7 @@
       <c r="T161" s="9"/>
       <c r="U161" s="9"/>
     </row>
-    <row r="162" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A162" s="9"/>
       <c r="B162" s="55"/>
       <c r="C162" s="55"/>
@@ -8206,7 +8201,7 @@
       <c r="T162" s="9"/>
       <c r="U162" s="9"/>
     </row>
-    <row r="163" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A163" s="9"/>
       <c r="B163" s="55"/>
       <c r="C163" s="55"/>
@@ -8229,7 +8224,7 @@
       <c r="T163" s="9"/>
       <c r="U163" s="9"/>
     </row>
-    <row r="164" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A164" s="9"/>
       <c r="B164" s="55"/>
       <c r="C164" s="55"/>
@@ -8252,7 +8247,7 @@
       <c r="T164" s="9"/>
       <c r="U164" s="9"/>
     </row>
-    <row r="165" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A165" s="9"/>
       <c r="B165" s="55"/>
       <c r="C165" s="55"/>
@@ -8275,7 +8270,7 @@
       <c r="T165" s="9"/>
       <c r="U165" s="9"/>
     </row>
-    <row r="166" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A166" s="9"/>
       <c r="B166" s="55"/>
       <c r="C166" s="55"/>
@@ -8298,7 +8293,7 @@
       <c r="T166" s="9"/>
       <c r="U166" s="9"/>
     </row>
-    <row r="167" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A167" s="9"/>
       <c r="B167" s="55"/>
       <c r="C167" s="55"/>
@@ -8321,7 +8316,7 @@
       <c r="T167" s="9"/>
       <c r="U167" s="9"/>
     </row>
-    <row r="168" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A168" s="9"/>
       <c r="B168" s="55"/>
       <c r="C168" s="55"/>
@@ -8344,7 +8339,7 @@
       <c r="T168" s="9"/>
       <c r="U168" s="9"/>
     </row>
-    <row r="169" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A169" s="9"/>
       <c r="B169" s="55"/>
       <c r="C169" s="55"/>
@@ -8367,7 +8362,7 @@
       <c r="T169" s="9"/>
       <c r="U169" s="9"/>
     </row>
-    <row r="170" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A170" s="9"/>
       <c r="B170" s="55"/>
       <c r="C170" s="55"/>
@@ -8390,7 +8385,7 @@
       <c r="T170" s="9"/>
       <c r="U170" s="9"/>
     </row>
-    <row r="171" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A171" s="9"/>
       <c r="B171" s="55"/>
       <c r="C171" s="55"/>
@@ -8413,7 +8408,7 @@
       <c r="T171" s="9"/>
       <c r="U171" s="9"/>
     </row>
-    <row r="172" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A172" s="9"/>
       <c r="B172" s="55"/>
       <c r="C172" s="55"/>
@@ -8436,7 +8431,7 @@
       <c r="T172" s="9"/>
       <c r="U172" s="9"/>
     </row>
-    <row r="173" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A173" s="9"/>
       <c r="B173" s="55"/>
       <c r="C173" s="55"/>
@@ -8459,7 +8454,7 @@
       <c r="T173" s="9"/>
       <c r="U173" s="9"/>
     </row>
-    <row r="174" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A174" s="9"/>
       <c r="B174" s="55"/>
       <c r="C174" s="55"/>
@@ -8482,7 +8477,7 @@
       <c r="T174" s="9"/>
       <c r="U174" s="9"/>
     </row>
-    <row r="175" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A175" s="9"/>
       <c r="B175" s="55"/>
       <c r="C175" s="55"/>
@@ -8505,7 +8500,7 @@
       <c r="T175" s="9"/>
       <c r="U175" s="9"/>
     </row>
-    <row r="176" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A176" s="9"/>
       <c r="B176" s="55"/>
       <c r="C176" s="55"/>
@@ -8528,7 +8523,7 @@
       <c r="T176" s="9"/>
       <c r="U176" s="9"/>
     </row>
-    <row r="177" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A177" s="9"/>
       <c r="B177" s="55"/>
       <c r="C177" s="55"/>
@@ -8551,7 +8546,7 @@
       <c r="T177" s="9"/>
       <c r="U177" s="9"/>
     </row>
-    <row r="178" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A178" s="9"/>
       <c r="B178" s="55"/>
       <c r="C178" s="55"/>
@@ -8574,7 +8569,7 @@
       <c r="T178" s="9"/>
       <c r="U178" s="9"/>
     </row>
-    <row r="179" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A179" s="9"/>
       <c r="B179" s="55"/>
       <c r="C179" s="55"/>
@@ -8597,7 +8592,7 @@
       <c r="T179" s="9"/>
       <c r="U179" s="9"/>
     </row>
-    <row r="180" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A180" s="9"/>
       <c r="B180" s="55"/>
       <c r="C180" s="55"/>
@@ -8620,7 +8615,7 @@
       <c r="T180" s="9"/>
       <c r="U180" s="9"/>
     </row>
-    <row r="181" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A181" s="9"/>
       <c r="B181" s="55"/>
       <c r="C181" s="55"/>
@@ -8643,7 +8638,7 @@
       <c r="T181" s="9"/>
       <c r="U181" s="9"/>
     </row>
-    <row r="182" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A182" s="9"/>
       <c r="B182" s="55"/>
       <c r="C182" s="55"/>
@@ -8666,7 +8661,7 @@
       <c r="T182" s="9"/>
       <c r="U182" s="9"/>
     </row>
-    <row r="183" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A183" s="9"/>
       <c r="B183" s="55"/>
       <c r="C183" s="55"/>
@@ -8689,7 +8684,7 @@
       <c r="T183" s="9"/>
       <c r="U183" s="9"/>
     </row>
-    <row r="184" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A184" s="9"/>
       <c r="B184" s="55"/>
       <c r="C184" s="55"/>
@@ -8712,7 +8707,7 @@
       <c r="T184" s="9"/>
       <c r="U184" s="9"/>
     </row>
-    <row r="185" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A185" s="9"/>
       <c r="B185" s="55"/>
       <c r="C185" s="55"/>
@@ -8735,7 +8730,7 @@
       <c r="T185" s="9"/>
       <c r="U185" s="9"/>
     </row>
-    <row r="186" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A186" s="9"/>
       <c r="B186" s="55"/>
       <c r="C186" s="55"/>
@@ -8758,7 +8753,7 @@
       <c r="T186" s="9"/>
       <c r="U186" s="9"/>
     </row>
-    <row r="187" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A187" s="9"/>
       <c r="B187" s="55"/>
       <c r="C187" s="55"/>
@@ -8781,7 +8776,7 @@
       <c r="T187" s="9"/>
       <c r="U187" s="9"/>
     </row>
-    <row r="188" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A188" s="9"/>
       <c r="B188" s="55"/>
       <c r="C188" s="55"/>
@@ -8804,7 +8799,7 @@
       <c r="T188" s="9"/>
       <c r="U188" s="9"/>
     </row>
-    <row r="189" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A189" s="9"/>
       <c r="B189" s="55"/>
       <c r="C189" s="55"/>
@@ -8827,7 +8822,7 @@
       <c r="T189" s="9"/>
       <c r="U189" s="9"/>
     </row>
-    <row r="190" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A190" s="9"/>
       <c r="B190" s="55"/>
       <c r="C190" s="55"/>
@@ -8850,7 +8845,7 @@
       <c r="T190" s="9"/>
       <c r="U190" s="9"/>
     </row>
-    <row r="191" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A191" s="9"/>
       <c r="B191" s="55"/>
       <c r="C191" s="55"/>
@@ -8873,7 +8868,7 @@
       <c r="T191" s="9"/>
       <c r="U191" s="9"/>
     </row>
-    <row r="192" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A192" s="9"/>
       <c r="B192" s="55"/>
       <c r="C192" s="55"/>
@@ -8896,7 +8891,7 @@
       <c r="T192" s="9"/>
       <c r="U192" s="9"/>
     </row>
-    <row r="193" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A193" s="9"/>
       <c r="B193" s="55"/>
       <c r="C193" s="55"/>
@@ -8919,7 +8914,7 @@
       <c r="T193" s="9"/>
       <c r="U193" s="9"/>
     </row>
-    <row r="194" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A194" s="9"/>
       <c r="B194" s="55"/>
       <c r="C194" s="55"/>
@@ -8942,7 +8937,7 @@
       <c r="T194" s="9"/>
       <c r="U194" s="9"/>
     </row>
-    <row r="195" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A195" s="9"/>
       <c r="B195" s="55"/>
       <c r="C195" s="55"/>
@@ -8965,7 +8960,7 @@
       <c r="T195" s="9"/>
       <c r="U195" s="9"/>
     </row>
-    <row r="196" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A196" s="9"/>
       <c r="B196" s="55"/>
       <c r="C196" s="55"/>
@@ -8988,7 +8983,7 @@
       <c r="T196" s="9"/>
       <c r="U196" s="9"/>
     </row>
-    <row r="197" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A197" s="9"/>
       <c r="B197" s="55"/>
       <c r="C197" s="55"/>
@@ -9011,7 +9006,7 @@
       <c r="T197" s="9"/>
       <c r="U197" s="9"/>
     </row>
-    <row r="198" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A198" s="9"/>
       <c r="B198" s="55"/>
       <c r="C198" s="55"/>
@@ -9034,7 +9029,7 @@
       <c r="T198" s="9"/>
       <c r="U198" s="9"/>
     </row>
-    <row r="199" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A199" s="9"/>
       <c r="B199" s="55"/>
       <c r="C199" s="55"/>
@@ -9057,7 +9052,7 @@
       <c r="T199" s="9"/>
       <c r="U199" s="9"/>
     </row>
-    <row r="200" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A200" s="9"/>
       <c r="B200" s="55"/>
       <c r="C200" s="55"/>
@@ -9080,7 +9075,7 @@
       <c r="T200" s="9"/>
       <c r="U200" s="9"/>
     </row>
-    <row r="201" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A201" s="9"/>
       <c r="B201" s="55"/>
       <c r="C201" s="55"/>
@@ -9103,7 +9098,7 @@
       <c r="T201" s="9"/>
       <c r="U201" s="9"/>
     </row>
-    <row r="202" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A202" s="9"/>
       <c r="B202" s="55"/>
       <c r="C202" s="55"/>
@@ -9126,7 +9121,7 @@
       <c r="T202" s="9"/>
       <c r="U202" s="9"/>
     </row>
-    <row r="203" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A203" s="9"/>
       <c r="B203" s="55"/>
       <c r="C203" s="55"/>
@@ -9149,7 +9144,7 @@
       <c r="T203" s="9"/>
       <c r="U203" s="9"/>
     </row>
-    <row r="204" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A204" s="9"/>
       <c r="B204" s="55"/>
       <c r="C204" s="55"/>
@@ -9172,7 +9167,7 @@
       <c r="T204" s="9"/>
       <c r="U204" s="9"/>
     </row>
-    <row r="205" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A205" s="9"/>
       <c r="B205" s="55"/>
       <c r="C205" s="55"/>
@@ -9195,7 +9190,7 @@
       <c r="T205" s="9"/>
       <c r="U205" s="9"/>
     </row>
-    <row r="206" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A206" s="9"/>
       <c r="B206" s="55"/>
       <c r="C206" s="55"/>
@@ -9218,7 +9213,7 @@
       <c r="T206" s="9"/>
       <c r="U206" s="9"/>
     </row>
-    <row r="207" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A207" s="9"/>
       <c r="B207" s="55"/>
       <c r="C207" s="55"/>
@@ -9241,7 +9236,7 @@
       <c r="T207" s="9"/>
       <c r="U207" s="9"/>
     </row>
-    <row r="208" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A208" s="9"/>
       <c r="B208" s="55"/>
       <c r="C208" s="55"/>
@@ -9264,7 +9259,7 @@
       <c r="T208" s="9"/>
       <c r="U208" s="9"/>
     </row>
-    <row r="209" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A209" s="9"/>
       <c r="B209" s="55"/>
       <c r="C209" s="55"/>
@@ -9287,7 +9282,7 @@
       <c r="T209" s="9"/>
       <c r="U209" s="9"/>
     </row>
-    <row r="210" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A210" s="9"/>
       <c r="B210" s="55"/>
       <c r="C210" s="55"/>
@@ -9310,7 +9305,7 @@
       <c r="T210" s="9"/>
       <c r="U210" s="9"/>
     </row>
-    <row r="211" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A211" s="9"/>
       <c r="B211" s="55"/>
       <c r="C211" s="55"/>
@@ -9333,7 +9328,7 @@
       <c r="T211" s="9"/>
       <c r="U211" s="9"/>
     </row>
-    <row r="212" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A212" s="9"/>
       <c r="B212" s="55"/>
       <c r="C212" s="55"/>
@@ -9356,7 +9351,7 @@
       <c r="T212" s="9"/>
       <c r="U212" s="9"/>
     </row>
-    <row r="213" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A213" s="9"/>
       <c r="B213" s="55"/>
       <c r="C213" s="55"/>
@@ -9379,7 +9374,7 @@
       <c r="T213" s="9"/>
       <c r="U213" s="9"/>
     </row>
-    <row r="214" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A214" s="9"/>
       <c r="B214" s="55"/>
       <c r="C214" s="55"/>
@@ -9402,7 +9397,7 @@
       <c r="T214" s="9"/>
       <c r="U214" s="9"/>
     </row>
-    <row r="215" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A215" s="9"/>
       <c r="B215" s="55"/>
       <c r="C215" s="55"/>
@@ -9425,7 +9420,7 @@
       <c r="T215" s="9"/>
       <c r="U215" s="9"/>
     </row>
-    <row r="216" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A216" s="9"/>
       <c r="B216" s="55"/>
       <c r="C216" s="55"/>
@@ -9448,7 +9443,7 @@
       <c r="T216" s="9"/>
       <c r="U216" s="9"/>
     </row>
-    <row r="217" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A217" s="9"/>
       <c r="B217" s="55"/>
       <c r="C217" s="55"/>
@@ -9471,7 +9466,7 @@
       <c r="T217" s="9"/>
       <c r="U217" s="9"/>
     </row>
-    <row r="218" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A218" s="9"/>
       <c r="B218" s="55"/>
       <c r="C218" s="55"/>
@@ -9494,7 +9489,7 @@
       <c r="T218" s="9"/>
       <c r="U218" s="9"/>
     </row>
-    <row r="219" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A219" s="9"/>
       <c r="B219" s="55"/>
       <c r="C219" s="55"/>
@@ -9517,7 +9512,7 @@
       <c r="T219" s="9"/>
       <c r="U219" s="9"/>
     </row>
-    <row r="220" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A220" s="9"/>
       <c r="B220" s="55"/>
       <c r="C220" s="55"/>
@@ -9540,7 +9535,7 @@
       <c r="T220" s="9"/>
       <c r="U220" s="9"/>
     </row>
-    <row r="221" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A221" s="9"/>
       <c r="B221" s="55"/>
       <c r="C221" s="55"/>
@@ -9563,7 +9558,7 @@
       <c r="T221" s="9"/>
       <c r="U221" s="9"/>
     </row>
-    <row r="222" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A222" s="9"/>
       <c r="B222" s="55"/>
       <c r="C222" s="55"/>
@@ -9586,7 +9581,7 @@
       <c r="T222" s="9"/>
       <c r="U222" s="9"/>
     </row>
-    <row r="223" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A223" s="9"/>
       <c r="B223" s="55"/>
       <c r="C223" s="55"/>
@@ -9609,7 +9604,7 @@
       <c r="T223" s="9"/>
       <c r="U223" s="9"/>
     </row>
-    <row r="224" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A224" s="9"/>
       <c r="B224" s="55"/>
       <c r="C224" s="55"/>
@@ -9632,7 +9627,7 @@
       <c r="T224" s="9"/>
       <c r="U224" s="9"/>
     </row>
-    <row r="225" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A225" s="9"/>
       <c r="B225" s="55"/>
       <c r="C225" s="55"/>
@@ -9655,7 +9650,7 @@
       <c r="T225" s="9"/>
       <c r="U225" s="9"/>
     </row>
-    <row r="226" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A226" s="9"/>
       <c r="B226" s="55"/>
       <c r="C226" s="55"/>
@@ -9678,7 +9673,7 @@
       <c r="T226" s="9"/>
       <c r="U226" s="9"/>
     </row>
-    <row r="227" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A227" s="9"/>
       <c r="B227" s="55"/>
       <c r="C227" s="55"/>
@@ -9701,7 +9696,7 @@
       <c r="T227" s="9"/>
       <c r="U227" s="9"/>
     </row>
-    <row r="228" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A228" s="9"/>
       <c r="B228" s="55"/>
       <c r="C228" s="55"/>
@@ -9724,7 +9719,7 @@
       <c r="T228" s="9"/>
       <c r="U228" s="9"/>
     </row>
-    <row r="229" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A229" s="9"/>
       <c r="B229" s="55"/>
       <c r="C229" s="55"/>
@@ -9747,7 +9742,7 @@
       <c r="T229" s="9"/>
       <c r="U229" s="9"/>
     </row>
-    <row r="230" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A230" s="9"/>
       <c r="B230" s="55"/>
       <c r="C230" s="55"/>
@@ -9770,7 +9765,7 @@
       <c r="T230" s="9"/>
       <c r="U230" s="9"/>
     </row>
-    <row r="231" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A231" s="9"/>
       <c r="B231" s="55"/>
       <c r="C231" s="55"/>
@@ -9793,7 +9788,7 @@
       <c r="T231" s="9"/>
       <c r="U231" s="9"/>
     </row>
-    <row r="232" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A232" s="9"/>
       <c r="B232" s="55"/>
       <c r="C232" s="55"/>
@@ -9816,7 +9811,7 @@
       <c r="T232" s="9"/>
       <c r="U232" s="9"/>
     </row>
-    <row r="233" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A233" s="9"/>
       <c r="B233" s="55"/>
       <c r="C233" s="55"/>
@@ -9839,7 +9834,7 @@
       <c r="T233" s="9"/>
       <c r="U233" s="9"/>
     </row>
-    <row r="234" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A234" s="9"/>
       <c r="B234" s="55"/>
       <c r="C234" s="55"/>
@@ -9862,7 +9857,7 @@
       <c r="T234" s="9"/>
       <c r="U234" s="9"/>
     </row>
-    <row r="235" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A235" s="9"/>
       <c r="B235" s="55"/>
       <c r="C235" s="55"/>
@@ -9885,7 +9880,7 @@
       <c r="T235" s="9"/>
       <c r="U235" s="9"/>
     </row>
-    <row r="236" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A236" s="9"/>
       <c r="B236" s="55"/>
       <c r="C236" s="55"/>
@@ -9908,7 +9903,7 @@
       <c r="T236" s="9"/>
       <c r="U236" s="9"/>
     </row>
-    <row r="237" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A237" s="9"/>
       <c r="B237" s="55"/>
       <c r="C237" s="55"/>
@@ -9931,7 +9926,7 @@
       <c r="T237" s="9"/>
       <c r="U237" s="9"/>
     </row>
-    <row r="238" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A238" s="9"/>
       <c r="B238" s="55"/>
       <c r="C238" s="55"/>
@@ -9954,7 +9949,7 @@
       <c r="T238" s="9"/>
       <c r="U238" s="9"/>
     </row>
-    <row r="239" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A239" s="9"/>
       <c r="B239" s="55"/>
       <c r="C239" s="55"/>
@@ -9977,7 +9972,7 @@
       <c r="T239" s="9"/>
       <c r="U239" s="9"/>
     </row>
-    <row r="240" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A240" s="9"/>
       <c r="B240" s="55"/>
       <c r="C240" s="55"/>
@@ -10000,7 +9995,7 @@
       <c r="T240" s="9"/>
       <c r="U240" s="9"/>
     </row>
-    <row r="241" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A241" s="9"/>
       <c r="B241" s="55"/>
       <c r="C241" s="55"/>
@@ -10023,7 +10018,7 @@
       <c r="T241" s="9"/>
       <c r="U241" s="9"/>
     </row>
-    <row r="242" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A242" s="9"/>
       <c r="B242" s="55"/>
       <c r="C242" s="55"/>
@@ -10046,7 +10041,7 @@
       <c r="T242" s="9"/>
       <c r="U242" s="9"/>
     </row>
-    <row r="243" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A243" s="9"/>
       <c r="B243" s="55"/>
       <c r="C243" s="55"/>
@@ -10069,7 +10064,7 @@
       <c r="T243" s="9"/>
       <c r="U243" s="9"/>
     </row>
-    <row r="244" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A244" s="9"/>
       <c r="B244" s="55"/>
       <c r="C244" s="55"/>
@@ -10092,7 +10087,7 @@
       <c r="T244" s="9"/>
       <c r="U244" s="9"/>
     </row>
-    <row r="245" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A245" s="9"/>
       <c r="B245" s="55"/>
       <c r="C245" s="55"/>
@@ -10115,7 +10110,7 @@
       <c r="T245" s="9"/>
       <c r="U245" s="9"/>
     </row>
-    <row r="246" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A246" s="9"/>
       <c r="B246" s="55"/>
       <c r="C246" s="55"/>
@@ -10138,7 +10133,7 @@
       <c r="T246" s="9"/>
       <c r="U246" s="9"/>
     </row>
-    <row r="247" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A247" s="9"/>
       <c r="B247" s="55"/>
       <c r="C247" s="55"/>
@@ -10161,7 +10156,7 @@
       <c r="T247" s="9"/>
       <c r="U247" s="9"/>
     </row>
-    <row r="248" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A248" s="9"/>
       <c r="B248" s="55"/>
       <c r="C248" s="55"/>
@@ -10184,7 +10179,7 @@
       <c r="T248" s="9"/>
       <c r="U248" s="9"/>
     </row>
-    <row r="249" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A249" s="9"/>
       <c r="B249" s="55"/>
       <c r="C249" s="55"/>
@@ -10207,7 +10202,7 @@
       <c r="T249" s="9"/>
       <c r="U249" s="9"/>
     </row>
-    <row r="250" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A250" s="9"/>
       <c r="B250" s="55"/>
       <c r="C250" s="55"/>
@@ -10230,7 +10225,7 @@
       <c r="T250" s="9"/>
       <c r="U250" s="9"/>
     </row>
-    <row r="251" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A251" s="9"/>
       <c r="B251" s="55"/>
       <c r="C251" s="55"/>
@@ -10253,7 +10248,7 @@
       <c r="T251" s="9"/>
       <c r="U251" s="9"/>
     </row>
-    <row r="252" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A252" s="9"/>
       <c r="B252" s="55"/>
       <c r="C252" s="55"/>
@@ -10276,7 +10271,7 @@
       <c r="T252" s="9"/>
       <c r="U252" s="9"/>
     </row>
-    <row r="253" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A253" s="9"/>
       <c r="B253" s="55"/>
       <c r="C253" s="55"/>
@@ -10299,7 +10294,7 @@
       <c r="T253" s="9"/>
       <c r="U253" s="9"/>
     </row>
-    <row r="254" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A254" s="9"/>
       <c r="B254" s="55"/>
       <c r="C254" s="55"/>
@@ -10322,7 +10317,7 @@
       <c r="T254" s="9"/>
       <c r="U254" s="9"/>
     </row>
-    <row r="255" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A255" s="9"/>
       <c r="B255" s="55"/>
       <c r="C255" s="55"/>
@@ -10345,7 +10340,7 @@
       <c r="T255" s="9"/>
       <c r="U255" s="9"/>
     </row>
-    <row r="256" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A256" s="9"/>
       <c r="B256" s="55"/>
       <c r="C256" s="55"/>
@@ -10368,7 +10363,7 @@
       <c r="T256" s="9"/>
       <c r="U256" s="9"/>
     </row>
-    <row r="257" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A257" s="9"/>
       <c r="B257" s="55"/>
       <c r="C257" s="55"/>
@@ -10391,7 +10386,7 @@
       <c r="T257" s="9"/>
       <c r="U257" s="9"/>
     </row>
-    <row r="258" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A258" s="9"/>
       <c r="B258" s="55"/>
       <c r="C258" s="55"/>
@@ -10414,7 +10409,7 @@
       <c r="T258" s="9"/>
       <c r="U258" s="9"/>
     </row>
-    <row r="259" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A259" s="9"/>
       <c r="B259" s="55"/>
       <c r="C259" s="55"/>
@@ -10437,7 +10432,7 @@
       <c r="T259" s="9"/>
       <c r="U259" s="9"/>
     </row>
-    <row r="260" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A260" s="9"/>
       <c r="B260" s="55"/>
       <c r="C260" s="55"/>
@@ -10460,7 +10455,7 @@
       <c r="T260" s="9"/>
       <c r="U260" s="9"/>
     </row>
-    <row r="261" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A261" s="9"/>
       <c r="B261" s="55"/>
       <c r="C261" s="55"/>
@@ -10483,7 +10478,7 @@
       <c r="T261" s="9"/>
       <c r="U261" s="9"/>
     </row>
-    <row r="262" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A262" s="9"/>
       <c r="B262" s="55"/>
       <c r="C262" s="55"/>
@@ -10506,7 +10501,7 @@
       <c r="T262" s="9"/>
       <c r="U262" s="9"/>
     </row>
-    <row r="263" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A263" s="9"/>
       <c r="B263" s="55"/>
       <c r="C263" s="55"/>
@@ -10529,7 +10524,7 @@
       <c r="T263" s="9"/>
       <c r="U263" s="9"/>
     </row>
-    <row r="264" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A264" s="9"/>
       <c r="B264" s="55"/>
       <c r="C264" s="55"/>
@@ -10552,7 +10547,7 @@
       <c r="T264" s="9"/>
       <c r="U264" s="9"/>
     </row>
-    <row r="265" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A265" s="9"/>
       <c r="B265" s="55"/>
       <c r="C265" s="55"/>
@@ -10575,7 +10570,7 @@
       <c r="T265" s="9"/>
       <c r="U265" s="9"/>
     </row>
-    <row r="266" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A266" s="9"/>
       <c r="B266" s="55"/>
       <c r="C266" s="55"/>
@@ -10598,7 +10593,7 @@
       <c r="T266" s="9"/>
       <c r="U266" s="9"/>
     </row>
-    <row r="267" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A267" s="9"/>
       <c r="B267" s="55"/>
       <c r="C267" s="55"/>
@@ -10621,7 +10616,7 @@
       <c r="T267" s="9"/>
       <c r="U267" s="9"/>
     </row>
-    <row r="268" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A268" s="9"/>
       <c r="B268" s="55"/>
       <c r="C268" s="55"/>
@@ -10644,7 +10639,7 @@
       <c r="T268" s="9"/>
       <c r="U268" s="9"/>
     </row>
-    <row r="269" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A269" s="9"/>
       <c r="B269" s="55"/>
       <c r="C269" s="55"/>
@@ -10667,7 +10662,7 @@
       <c r="T269" s="9"/>
       <c r="U269" s="9"/>
     </row>
-    <row r="270" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A270" s="9"/>
       <c r="B270" s="55"/>
       <c r="C270" s="55"/>
@@ -10690,7 +10685,7 @@
       <c r="T270" s="9"/>
       <c r="U270" s="9"/>
     </row>
-    <row r="271" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A271" s="9"/>
       <c r="B271" s="55"/>
       <c r="C271" s="55"/>
@@ -10713,7 +10708,7 @@
       <c r="T271" s="9"/>
       <c r="U271" s="9"/>
     </row>
-    <row r="272" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A272" s="9"/>
       <c r="B272" s="55"/>
       <c r="C272" s="55"/>
@@ -10736,7 +10731,7 @@
       <c r="T272" s="9"/>
       <c r="U272" s="9"/>
     </row>
-    <row r="273" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A273" s="9"/>
       <c r="B273" s="55"/>
       <c r="C273" s="55"/>
@@ -10759,7 +10754,7 @@
       <c r="T273" s="9"/>
       <c r="U273" s="9"/>
     </row>
-    <row r="274" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A274" s="9"/>
       <c r="B274" s="55"/>
       <c r="C274" s="55"/>
@@ -10782,7 +10777,7 @@
       <c r="T274" s="9"/>
       <c r="U274" s="9"/>
     </row>
-    <row r="275" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A275" s="9"/>
       <c r="B275" s="55"/>
       <c r="C275" s="55"/>
@@ -10805,7 +10800,7 @@
       <c r="T275" s="9"/>
       <c r="U275" s="9"/>
     </row>
-    <row r="276" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A276" s="9"/>
       <c r="B276" s="55"/>
       <c r="C276" s="55"/>
@@ -10828,7 +10823,7 @@
       <c r="T276" s="9"/>
       <c r="U276" s="9"/>
     </row>
-    <row r="277" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A277" s="9"/>
       <c r="B277" s="55"/>
       <c r="C277" s="55"/>
@@ -10851,7 +10846,7 @@
       <c r="T277" s="9"/>
       <c r="U277" s="9"/>
     </row>
-    <row r="278" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A278" s="9"/>
       <c r="B278" s="55"/>
       <c r="C278" s="55"/>
@@ -10874,7 +10869,7 @@
       <c r="T278" s="9"/>
       <c r="U278" s="9"/>
     </row>
-    <row r="279" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A279" s="9"/>
       <c r="B279" s="55"/>
       <c r="C279" s="55"/>
@@ -10897,7 +10892,7 @@
       <c r="T279" s="9"/>
       <c r="U279" s="9"/>
     </row>
-    <row r="280" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A280" s="9"/>
       <c r="B280" s="55"/>
       <c r="C280" s="55"/>
@@ -10920,7 +10915,7 @@
       <c r="T280" s="9"/>
       <c r="U280" s="9"/>
     </row>
-    <row r="281" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A281" s="9"/>
       <c r="B281" s="55"/>
       <c r="C281" s="55"/>
@@ -10943,7 +10938,7 @@
       <c r="T281" s="9"/>
       <c r="U281" s="9"/>
     </row>
-    <row r="282" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A282" s="9"/>
       <c r="B282" s="55"/>
       <c r="C282" s="55"/>
@@ -10966,7 +10961,7 @@
       <c r="T282" s="9"/>
       <c r="U282" s="9"/>
     </row>
-    <row r="283" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A283" s="9"/>
       <c r="B283" s="55"/>
       <c r="C283" s="55"/>
@@ -10989,7 +10984,7 @@
       <c r="T283" s="9"/>
       <c r="U283" s="9"/>
     </row>
-    <row r="284" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A284" s="9"/>
       <c r="B284" s="55"/>
       <c r="C284" s="55"/>
@@ -11012,7 +11007,7 @@
       <c r="T284" s="9"/>
       <c r="U284" s="9"/>
     </row>
-    <row r="285" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A285" s="9"/>
       <c r="B285" s="55"/>
       <c r="C285" s="55"/>
@@ -11035,7 +11030,7 @@
       <c r="T285" s="9"/>
       <c r="U285" s="9"/>
     </row>
-    <row r="286" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A286" s="9"/>
       <c r="B286" s="55"/>
       <c r="C286" s="55"/>
@@ -11058,7 +11053,7 @@
       <c r="T286" s="9"/>
       <c r="U286" s="9"/>
     </row>
-    <row r="287" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A287" s="9"/>
       <c r="B287" s="55"/>
       <c r="C287" s="55"/>
@@ -11081,7 +11076,7 @@
       <c r="T287" s="9"/>
       <c r="U287" s="9"/>
     </row>
-    <row r="288" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A288" s="9"/>
       <c r="B288" s="55"/>
       <c r="C288" s="55"/>
@@ -11104,7 +11099,7 @@
       <c r="T288" s="9"/>
       <c r="U288" s="9"/>
     </row>
-    <row r="289" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A289" s="9"/>
       <c r="B289" s="55"/>
       <c r="C289" s="55"/>
@@ -11127,7 +11122,7 @@
       <c r="T289" s="9"/>
       <c r="U289" s="9"/>
     </row>
-    <row r="290" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A290" s="9"/>
       <c r="B290" s="55"/>
       <c r="C290" s="55"/>
@@ -11150,7 +11145,7 @@
       <c r="T290" s="9"/>
       <c r="U290" s="9"/>
     </row>
-    <row r="291" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A291" s="9"/>
       <c r="B291" s="55"/>
       <c r="C291" s="55"/>
@@ -11173,7 +11168,7 @@
       <c r="T291" s="9"/>
       <c r="U291" s="9"/>
     </row>
-    <row r="292" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A292" s="9"/>
       <c r="B292" s="55"/>
       <c r="C292" s="55"/>
@@ -11196,7 +11191,7 @@
       <c r="T292" s="9"/>
       <c r="U292" s="9"/>
     </row>
-    <row r="293" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A293" s="9"/>
       <c r="B293" s="55"/>
       <c r="C293" s="55"/>
@@ -11219,7 +11214,7 @@
       <c r="T293" s="9"/>
       <c r="U293" s="9"/>
     </row>
-    <row r="294" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A294" s="9"/>
       <c r="B294" s="55"/>
       <c r="C294" s="55"/>
@@ -11242,7 +11237,7 @@
       <c r="T294" s="9"/>
       <c r="U294" s="9"/>
     </row>
-    <row r="295" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A295" s="9"/>
       <c r="B295" s="55"/>
       <c r="C295" s="55"/>
@@ -11265,7 +11260,7 @@
       <c r="T295" s="9"/>
       <c r="U295" s="9"/>
     </row>
-    <row r="296" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A296" s="9"/>
       <c r="B296" s="55"/>
       <c r="C296" s="55"/>
@@ -11288,7 +11283,7 @@
       <c r="T296" s="9"/>
       <c r="U296" s="9"/>
     </row>
-    <row r="297" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A297" s="9"/>
       <c r="B297" s="55"/>
       <c r="C297" s="55"/>
@@ -11311,7 +11306,7 @@
       <c r="T297" s="9"/>
       <c r="U297" s="9"/>
     </row>
-    <row r="298" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A298" s="9"/>
       <c r="B298" s="55"/>
       <c r="C298" s="55"/>
@@ -11334,7 +11329,7 @@
       <c r="T298" s="9"/>
       <c r="U298" s="9"/>
     </row>
-    <row r="299" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A299" s="9"/>
       <c r="B299" s="55"/>
       <c r="C299" s="55"/>
@@ -11357,7 +11352,7 @@
       <c r="T299" s="9"/>
       <c r="U299" s="9"/>
     </row>
-    <row r="300" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A300" s="9"/>
       <c r="B300" s="55"/>
       <c r="C300" s="55"/>
@@ -11380,7 +11375,7 @@
       <c r="T300" s="9"/>
       <c r="U300" s="9"/>
     </row>
-    <row r="301" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A301" s="9"/>
       <c r="B301" s="55"/>
       <c r="C301" s="55"/>
@@ -11403,7 +11398,7 @@
       <c r="T301" s="9"/>
       <c r="U301" s="9"/>
     </row>
-    <row r="302" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A302" s="9"/>
       <c r="B302" s="55"/>
       <c r="C302" s="55"/>
@@ -11426,7 +11421,7 @@
       <c r="T302" s="9"/>
       <c r="U302" s="9"/>
     </row>
-    <row r="303" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A303" s="9"/>
       <c r="B303" s="55"/>
       <c r="C303" s="55"/>
@@ -11449,7 +11444,7 @@
       <c r="T303" s="9"/>
       <c r="U303" s="9"/>
     </row>
-    <row r="304" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A304" s="9"/>
       <c r="B304" s="55"/>
       <c r="C304" s="55"/>
@@ -11472,7 +11467,7 @@
       <c r="T304" s="9"/>
       <c r="U304" s="9"/>
     </row>
-    <row r="305" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A305" s="9"/>
       <c r="B305" s="55"/>
       <c r="C305" s="55"/>
@@ -11495,7 +11490,7 @@
       <c r="T305" s="9"/>
       <c r="U305" s="9"/>
     </row>
-    <row r="306" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A306" s="9"/>
       <c r="B306" s="55"/>
       <c r="C306" s="55"/>
@@ -11518,7 +11513,7 @@
       <c r="T306" s="9"/>
       <c r="U306" s="9"/>
     </row>
-    <row r="307" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A307" s="9"/>
       <c r="B307" s="55"/>
       <c r="C307" s="55"/>
@@ -11541,7 +11536,7 @@
       <c r="T307" s="9"/>
       <c r="U307" s="9"/>
     </row>
-    <row r="308" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A308" s="9"/>
       <c r="B308" s="55"/>
       <c r="C308" s="55"/>
@@ -11564,7 +11559,7 @@
       <c r="T308" s="9"/>
       <c r="U308" s="9"/>
     </row>
-    <row r="309" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A309" s="9"/>
       <c r="B309" s="55"/>
       <c r="C309" s="55"/>
@@ -11587,7 +11582,7 @@
       <c r="T309" s="9"/>
       <c r="U309" s="9"/>
     </row>
-    <row r="310" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A310" s="9"/>
       <c r="B310" s="55"/>
       <c r="C310" s="55"/>
@@ -11610,7 +11605,7 @@
       <c r="T310" s="9"/>
       <c r="U310" s="9"/>
     </row>
-    <row r="311" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A311" s="9"/>
       <c r="B311" s="55"/>
       <c r="C311" s="55"/>
@@ -11633,7 +11628,7 @@
       <c r="T311" s="9"/>
       <c r="U311" s="9"/>
     </row>
-    <row r="312" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A312" s="9"/>
       <c r="B312" s="55"/>
       <c r="C312" s="55"/>
@@ -11656,7 +11651,7 @@
       <c r="T312" s="9"/>
       <c r="U312" s="9"/>
     </row>
-    <row r="313" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A313" s="9"/>
       <c r="B313" s="55"/>
       <c r="C313" s="55"/>
@@ -11679,7 +11674,7 @@
       <c r="T313" s="9"/>
       <c r="U313" s="9"/>
     </row>
-    <row r="314" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A314" s="9"/>
       <c r="B314" s="55"/>
       <c r="C314" s="55"/>
@@ -11702,7 +11697,7 @@
       <c r="T314" s="9"/>
       <c r="U314" s="9"/>
     </row>
-    <row r="315" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A315" s="9"/>
       <c r="B315" s="55"/>
       <c r="C315" s="55"/>
@@ -11725,7 +11720,7 @@
       <c r="T315" s="9"/>
       <c r="U315" s="9"/>
     </row>
-    <row r="316" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A316" s="9"/>
       <c r="B316" s="55"/>
       <c r="C316" s="55"/>
@@ -11748,7 +11743,7 @@
       <c r="T316" s="9"/>
       <c r="U316" s="9"/>
     </row>
-    <row r="317" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A317" s="9"/>
       <c r="B317" s="55"/>
       <c r="C317" s="55"/>
@@ -11771,7 +11766,7 @@
       <c r="T317" s="9"/>
       <c r="U317" s="9"/>
     </row>
-    <row r="318" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A318" s="9"/>
       <c r="B318" s="55"/>
       <c r="C318" s="55"/>
@@ -11794,7 +11789,7 @@
       <c r="T318" s="9"/>
       <c r="U318" s="9"/>
     </row>
-    <row r="319" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A319" s="9"/>
       <c r="B319" s="55"/>
       <c r="C319" s="55"/>
@@ -11817,7 +11812,7 @@
       <c r="T319" s="9"/>
       <c r="U319" s="9"/>
     </row>
-    <row r="320" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A320" s="9"/>
       <c r="B320" s="55"/>
       <c r="C320" s="55"/>
@@ -11840,7 +11835,7 @@
       <c r="T320" s="9"/>
       <c r="U320" s="9"/>
     </row>
-    <row r="321" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A321" s="9"/>
       <c r="B321" s="55"/>
       <c r="C321" s="55"/>
@@ -11863,7 +11858,7 @@
       <c r="T321" s="9"/>
       <c r="U321" s="9"/>
     </row>
-    <row r="322" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A322" s="9"/>
       <c r="B322" s="55"/>
       <c r="C322" s="55"/>
@@ -11886,7 +11881,7 @@
       <c r="T322" s="9"/>
       <c r="U322" s="9"/>
     </row>
-    <row r="323" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A323" s="9"/>
       <c r="B323" s="55"/>
       <c r="C323" s="55"/>
@@ -11909,7 +11904,7 @@
       <c r="T323" s="9"/>
       <c r="U323" s="9"/>
     </row>
-    <row r="324" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A324" s="9"/>
       <c r="B324" s="55"/>
       <c r="C324" s="55"/>
@@ -11932,7 +11927,7 @@
       <c r="T324" s="9"/>
       <c r="U324" s="9"/>
     </row>
-    <row r="325" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A325" s="9"/>
       <c r="B325" s="55"/>
       <c r="C325" s="55"/>
@@ -11955,7 +11950,7 @@
       <c r="T325" s="9"/>
       <c r="U325" s="9"/>
     </row>
-    <row r="326" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A326" s="9"/>
       <c r="B326" s="55"/>
       <c r="C326" s="55"/>
@@ -11978,7 +11973,7 @@
       <c r="T326" s="9"/>
       <c r="U326" s="9"/>
     </row>
-    <row r="327" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A327" s="9"/>
       <c r="B327" s="55"/>
       <c r="C327" s="55"/>
@@ -12001,7 +11996,7 @@
       <c r="T327" s="9"/>
       <c r="U327" s="9"/>
     </row>
-    <row r="328" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A328" s="9"/>
       <c r="B328" s="55"/>
       <c r="C328" s="55"/>
@@ -12024,7 +12019,7 @@
       <c r="T328" s="9"/>
       <c r="U328" s="9"/>
     </row>
-    <row r="329" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A329" s="9"/>
       <c r="B329" s="55"/>
       <c r="C329" s="55"/>
@@ -12047,7 +12042,7 @@
       <c r="T329" s="9"/>
       <c r="U329" s="9"/>
     </row>
-    <row r="330" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A330" s="9"/>
       <c r="B330" s="55"/>
       <c r="C330" s="55"/>
@@ -12070,7 +12065,7 @@
       <c r="T330" s="9"/>
       <c r="U330" s="9"/>
     </row>
-    <row r="331" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A331" s="9"/>
       <c r="B331" s="55"/>
       <c r="C331" s="55"/>
@@ -12093,7 +12088,7 @@
       <c r="T331" s="9"/>
       <c r="U331" s="9"/>
     </row>
-    <row r="332" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A332" s="9"/>
       <c r="B332" s="55"/>
       <c r="C332" s="55"/>
@@ -12116,7 +12111,7 @@
       <c r="T332" s="9"/>
       <c r="U332" s="9"/>
     </row>
-    <row r="333" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A333" s="9"/>
       <c r="B333" s="55"/>
       <c r="C333" s="55"/>
@@ -12139,7 +12134,7 @@
       <c r="T333" s="9"/>
       <c r="U333" s="9"/>
     </row>
-    <row r="334" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A334" s="9"/>
       <c r="B334" s="55"/>
       <c r="C334" s="55"/>
@@ -12162,7 +12157,7 @@
       <c r="T334" s="9"/>
       <c r="U334" s="9"/>
     </row>
-    <row r="335" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A335" s="9"/>
       <c r="B335" s="55"/>
       <c r="C335" s="55"/>
@@ -12185,7 +12180,7 @@
       <c r="T335" s="9"/>
       <c r="U335" s="9"/>
     </row>
-    <row r="336" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A336" s="9"/>
       <c r="B336" s="55"/>
       <c r="C336" s="55"/>
@@ -12208,7 +12203,7 @@
       <c r="T336" s="9"/>
       <c r="U336" s="9"/>
     </row>
-    <row r="337" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A337" s="9"/>
       <c r="B337" s="55"/>
       <c r="C337" s="55"/>
@@ -12231,7 +12226,7 @@
       <c r="T337" s="9"/>
       <c r="U337" s="9"/>
     </row>
-    <row r="338" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A338" s="9"/>
       <c r="B338" s="55"/>
       <c r="C338" s="55"/>
@@ -12254,7 +12249,7 @@
       <c r="T338" s="9"/>
       <c r="U338" s="9"/>
     </row>
-    <row r="339" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A339" s="9"/>
       <c r="B339" s="55"/>
       <c r="C339" s="55"/>
@@ -12277,7 +12272,7 @@
       <c r="T339" s="9"/>
       <c r="U339" s="9"/>
     </row>
-    <row r="340" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A340" s="9"/>
       <c r="B340" s="55"/>
       <c r="C340" s="55"/>
@@ -12300,7 +12295,7 @@
       <c r="T340" s="9"/>
       <c r="U340" s="9"/>
     </row>
-    <row r="341" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A341" s="9"/>
       <c r="B341" s="55"/>
       <c r="C341" s="55"/>
@@ -12323,7 +12318,7 @@
       <c r="T341" s="9"/>
       <c r="U341" s="9"/>
     </row>
-    <row r="342" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A342" s="9"/>
       <c r="B342" s="55"/>
       <c r="C342" s="55"/>
@@ -12346,7 +12341,7 @@
       <c r="T342" s="9"/>
       <c r="U342" s="9"/>
     </row>
-    <row r="343" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A343" s="9"/>
       <c r="B343" s="55"/>
       <c r="C343" s="55"/>
@@ -12369,7 +12364,7 @@
       <c r="T343" s="9"/>
       <c r="U343" s="9"/>
     </row>
-    <row r="344" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A344" s="9"/>
       <c r="B344" s="55"/>
       <c r="C344" s="55"/>
@@ -12392,7 +12387,7 @@
       <c r="T344" s="9"/>
       <c r="U344" s="9"/>
     </row>
-    <row r="345" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A345" s="9"/>
       <c r="B345" s="55"/>
       <c r="C345" s="55"/>
@@ -12415,7 +12410,7 @@
       <c r="T345" s="9"/>
       <c r="U345" s="9"/>
     </row>
-    <row r="346" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A346" s="9"/>
       <c r="B346" s="55"/>
       <c r="C346" s="55"/>
@@ -12438,7 +12433,7 @@
       <c r="T346" s="9"/>
       <c r="U346" s="9"/>
     </row>
-    <row r="347" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A347" s="9"/>
       <c r="B347" s="55"/>
       <c r="C347" s="55"/>
@@ -12461,7 +12456,7 @@
       <c r="T347" s="9"/>
       <c r="U347" s="9"/>
     </row>
-    <row r="348" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A348" s="9"/>
       <c r="B348" s="55"/>
       <c r="C348" s="55"/>
@@ -12484,7 +12479,7 @@
       <c r="T348" s="9"/>
       <c r="U348" s="9"/>
     </row>
-    <row r="349" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A349" s="9"/>
       <c r="B349" s="55"/>
       <c r="C349" s="55"/>
@@ -12507,7 +12502,7 @@
       <c r="T349" s="9"/>
       <c r="U349" s="9"/>
     </row>
-    <row r="350" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A350" s="9"/>
       <c r="B350" s="55"/>
       <c r="C350" s="55"/>
@@ -12530,7 +12525,7 @@
       <c r="T350" s="9"/>
       <c r="U350" s="9"/>
     </row>
-    <row r="351" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A351" s="9"/>
       <c r="B351" s="55"/>
       <c r="C351" s="55"/>
@@ -12553,7 +12548,7 @@
       <c r="T351" s="9"/>
       <c r="U351" s="9"/>
     </row>
-    <row r="352" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A352" s="9"/>
       <c r="B352" s="55"/>
       <c r="C352" s="55"/>
@@ -12576,7 +12571,7 @@
       <c r="T352" s="9"/>
       <c r="U352" s="9"/>
     </row>
-    <row r="353" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A353" s="9"/>
       <c r="B353" s="55"/>
       <c r="C353" s="55"/>
@@ -12599,7 +12594,7 @@
       <c r="T353" s="9"/>
       <c r="U353" s="9"/>
     </row>
-    <row r="354" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A354" s="9"/>
       <c r="B354" s="55"/>
       <c r="C354" s="55"/>
@@ -12622,7 +12617,7 @@
       <c r="T354" s="9"/>
       <c r="U354" s="9"/>
     </row>
-    <row r="355" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A355" s="9"/>
       <c r="B355" s="55"/>
       <c r="C355" s="55"/>
@@ -12645,7 +12640,7 @@
       <c r="T355" s="9"/>
       <c r="U355" s="9"/>
     </row>
-    <row r="356" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A356" s="9"/>
       <c r="B356" s="55"/>
       <c r="C356" s="55"/>
@@ -12668,7 +12663,7 @@
       <c r="T356" s="9"/>
       <c r="U356" s="9"/>
     </row>
-    <row r="357" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A357" s="9"/>
       <c r="B357" s="55"/>
       <c r="C357" s="55"/>
@@ -12691,7 +12686,7 @@
       <c r="T357" s="9"/>
       <c r="U357" s="9"/>
     </row>
-    <row r="358" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A358" s="9"/>
       <c r="B358" s="55"/>
       <c r="C358" s="55"/>
@@ -12714,7 +12709,7 @@
       <c r="T358" s="9"/>
       <c r="U358" s="9"/>
     </row>
-    <row r="359" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A359" s="9"/>
       <c r="B359" s="55"/>
       <c r="C359" s="55"/>
@@ -12737,7 +12732,7 @@
       <c r="T359" s="9"/>
       <c r="U359" s="9"/>
     </row>
-    <row r="360" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A360" s="9"/>
       <c r="B360" s="55"/>
       <c r="C360" s="55"/>
@@ -12760,7 +12755,7 @@
       <c r="T360" s="9"/>
       <c r="U360" s="9"/>
     </row>
-    <row r="361" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A361" s="9"/>
       <c r="B361" s="55"/>
       <c r="C361" s="55"/>
@@ -12783,7 +12778,7 @@
       <c r="T361" s="9"/>
       <c r="U361" s="9"/>
     </row>
-    <row r="362" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A362" s="9"/>
       <c r="B362" s="55"/>
       <c r="C362" s="55"/>
@@ -12806,7 +12801,7 @@
       <c r="T362" s="9"/>
       <c r="U362" s="9"/>
     </row>
-    <row r="363" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A363" s="9"/>
       <c r="B363" s="55"/>
       <c r="C363" s="55"/>
@@ -12829,7 +12824,7 @@
       <c r="T363" s="9"/>
       <c r="U363" s="9"/>
     </row>
-    <row r="364" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A364" s="9"/>
       <c r="B364" s="55"/>
       <c r="C364" s="55"/>
@@ -12852,7 +12847,7 @@
       <c r="T364" s="9"/>
       <c r="U364" s="9"/>
     </row>
-    <row r="365" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A365" s="9"/>
       <c r="B365" s="55"/>
       <c r="C365" s="55"/>
@@ -12875,7 +12870,7 @@
       <c r="T365" s="9"/>
       <c r="U365" s="9"/>
     </row>
-    <row r="366" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A366" s="9"/>
       <c r="B366" s="55"/>
       <c r="C366" s="55"/>
@@ -12898,7 +12893,7 @@
       <c r="T366" s="9"/>
       <c r="U366" s="9"/>
     </row>
-    <row r="367" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A367" s="9"/>
       <c r="B367" s="55"/>
       <c r="C367" s="55"/>
@@ -12921,7 +12916,7 @@
       <c r="T367" s="9"/>
       <c r="U367" s="9"/>
     </row>
-    <row r="368" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A368" s="9"/>
       <c r="B368" s="55"/>
       <c r="C368" s="55"/>
@@ -12944,7 +12939,7 @@
       <c r="T368" s="9"/>
       <c r="U368" s="9"/>
     </row>
-    <row r="369" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A369" s="9"/>
       <c r="B369" s="55"/>
       <c r="C369" s="55"/>
@@ -12967,7 +12962,7 @@
       <c r="T369" s="9"/>
       <c r="U369" s="9"/>
     </row>
-    <row r="370" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A370" s="9"/>
       <c r="B370" s="55"/>
       <c r="C370" s="55"/>
@@ -12990,7 +12985,7 @@
       <c r="T370" s="9"/>
       <c r="U370" s="9"/>
     </row>
-    <row r="371" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A371" s="9"/>
       <c r="B371" s="55"/>
       <c r="C371" s="55"/>
@@ -13013,7 +13008,7 @@
       <c r="T371" s="9"/>
       <c r="U371" s="9"/>
     </row>
-    <row r="372" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A372" s="9"/>
       <c r="B372" s="55"/>
       <c r="C372" s="55"/>
@@ -13036,7 +13031,7 @@
       <c r="T372" s="9"/>
       <c r="U372" s="9"/>
     </row>
-    <row r="373" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A373" s="9"/>
       <c r="B373" s="55"/>
       <c r="C373" s="55"/>
@@ -13059,7 +13054,7 @@
       <c r="T373" s="9"/>
       <c r="U373" s="9"/>
     </row>
-    <row r="374" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A374" s="9"/>
       <c r="B374" s="55"/>
       <c r="C374" s="55"/>
@@ -13082,7 +13077,7 @@
       <c r="T374" s="9"/>
       <c r="U374" s="9"/>
     </row>
-    <row r="375" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A375" s="9"/>
       <c r="B375" s="55"/>
       <c r="C375" s="55"/>
@@ -13105,7 +13100,7 @@
       <c r="T375" s="9"/>
       <c r="U375" s="9"/>
     </row>
-    <row r="376" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A376" s="9"/>
       <c r="B376" s="55"/>
       <c r="C376" s="55"/>
@@ -13128,7 +13123,7 @@
       <c r="T376" s="9"/>
       <c r="U376" s="9"/>
     </row>
-    <row r="377" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A377" s="9"/>
       <c r="B377" s="55"/>
       <c r="C377" s="55"/>
@@ -13151,7 +13146,7 @@
       <c r="T377" s="9"/>
       <c r="U377" s="9"/>
     </row>
-    <row r="378" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A378" s="9"/>
       <c r="B378" s="55"/>
       <c r="C378" s="55"/>
@@ -13174,7 +13169,7 @@
       <c r="T378" s="9"/>
       <c r="U378" s="9"/>
     </row>
-    <row r="379" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A379" s="9"/>
       <c r="B379" s="55"/>
       <c r="C379" s="55"/>
@@ -13197,7 +13192,7 @@
       <c r="T379" s="9"/>
       <c r="U379" s="9"/>
     </row>
-    <row r="380" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A380" s="9"/>
       <c r="B380" s="55"/>
       <c r="C380" s="55"/>
@@ -13220,7 +13215,7 @@
       <c r="T380" s="9"/>
       <c r="U380" s="9"/>
     </row>
-    <row r="381" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A381" s="9"/>
       <c r="B381" s="55"/>
       <c r="C381" s="55"/>
@@ -13243,7 +13238,7 @@
       <c r="T381" s="9"/>
       <c r="U381" s="9"/>
     </row>
-    <row r="382" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A382" s="9"/>
       <c r="B382" s="55"/>
       <c r="C382" s="55"/>
@@ -13266,7 +13261,7 @@
       <c r="T382" s="9"/>
       <c r="U382" s="9"/>
     </row>
-    <row r="383" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A383" s="9"/>
       <c r="B383" s="55"/>
       <c r="C383" s="55"/>
@@ -13289,7 +13284,7 @@
       <c r="T383" s="9"/>
       <c r="U383" s="9"/>
     </row>
-    <row r="384" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A384" s="9"/>
       <c r="B384" s="55"/>
       <c r="C384" s="55"/>
@@ -13312,7 +13307,7 @@
       <c r="T384" s="9"/>
       <c r="U384" s="9"/>
     </row>
-    <row r="385" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A385" s="9"/>
       <c r="B385" s="55"/>
       <c r="C385" s="55"/>
@@ -13335,7 +13330,7 @@
       <c r="T385" s="9"/>
       <c r="U385" s="9"/>
     </row>
-    <row r="386" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A386" s="9"/>
       <c r="B386" s="55"/>
       <c r="C386" s="55"/>
@@ -13358,7 +13353,7 @@
       <c r="T386" s="9"/>
       <c r="U386" s="9"/>
     </row>
-    <row r="387" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A387" s="9"/>
       <c r="B387" s="55"/>
       <c r="C387" s="55"/>
@@ -13381,7 +13376,7 @@
       <c r="T387" s="9"/>
       <c r="U387" s="9"/>
     </row>
-    <row r="388" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A388" s="9"/>
       <c r="B388" s="55"/>
       <c r="C388" s="55"/>
@@ -13404,7 +13399,7 @@
       <c r="T388" s="9"/>
       <c r="U388" s="9"/>
     </row>
-    <row r="389" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A389" s="9"/>
       <c r="B389" s="55"/>
       <c r="C389" s="55"/>
@@ -13427,7 +13422,7 @@
       <c r="T389" s="9"/>
       <c r="U389" s="9"/>
     </row>
-    <row r="390" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A390" s="9"/>
       <c r="B390" s="55"/>
       <c r="C390" s="55"/>
@@ -13450,7 +13445,7 @@
       <c r="T390" s="9"/>
       <c r="U390" s="9"/>
     </row>
-    <row r="391" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A391" s="9"/>
       <c r="B391" s="55"/>
       <c r="C391" s="55"/>
@@ -13473,7 +13468,7 @@
       <c r="T391" s="9"/>
       <c r="U391" s="9"/>
     </row>
-    <row r="392" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A392" s="9"/>
       <c r="B392" s="55"/>
       <c r="C392" s="55"/>
@@ -13496,7 +13491,7 @@
       <c r="T392" s="9"/>
       <c r="U392" s="9"/>
     </row>
-    <row r="393" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A393" s="9"/>
       <c r="B393" s="55"/>
       <c r="C393" s="55"/>
@@ -13519,7 +13514,7 @@
       <c r="T393" s="9"/>
       <c r="U393" s="9"/>
     </row>
-    <row r="394" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A394" s="9"/>
       <c r="B394" s="55"/>
       <c r="C394" s="55"/>
@@ -13542,7 +13537,7 @@
       <c r="T394" s="9"/>
       <c r="U394" s="9"/>
     </row>
-    <row r="395" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A395" s="9"/>
       <c r="B395" s="55"/>
       <c r="C395" s="55"/>
@@ -13565,7 +13560,7 @@
       <c r="T395" s="9"/>
       <c r="U395" s="9"/>
     </row>
-    <row r="396" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A396" s="9"/>
       <c r="B396" s="55"/>
       <c r="C396" s="55"/>
@@ -13588,7 +13583,7 @@
       <c r="T396" s="9"/>
       <c r="U396" s="9"/>
     </row>
-    <row r="397" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A397" s="9"/>
       <c r="B397" s="55"/>
       <c r="C397" s="55"/>
@@ -13611,7 +13606,7 @@
       <c r="T397" s="9"/>
       <c r="U397" s="9"/>
     </row>
-    <row r="398" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A398" s="9"/>
       <c r="B398" s="55"/>
       <c r="C398" s="55"/>
@@ -13634,7 +13629,7 @@
       <c r="T398" s="9"/>
       <c r="U398" s="9"/>
     </row>
-    <row r="399" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A399" s="9"/>
       <c r="B399" s="55"/>
       <c r="C399" s="55"/>
@@ -13657,7 +13652,7 @@
       <c r="T399" s="9"/>
       <c r="U399" s="9"/>
     </row>
-    <row r="400" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A400" s="9"/>
       <c r="B400" s="55"/>
       <c r="C400" s="55"/>
@@ -13680,7 +13675,7 @@
       <c r="T400" s="9"/>
       <c r="U400" s="9"/>
     </row>
-    <row r="401" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A401" s="9"/>
       <c r="B401" s="55"/>
       <c r="C401" s="55"/>
@@ -13703,7 +13698,7 @@
       <c r="T401" s="9"/>
       <c r="U401" s="9"/>
     </row>
-    <row r="402" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A402" s="9"/>
       <c r="B402" s="55"/>
       <c r="C402" s="55"/>
@@ -13726,7 +13721,7 @@
       <c r="T402" s="9"/>
       <c r="U402" s="9"/>
     </row>
-    <row r="403" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A403" s="9"/>
       <c r="B403" s="55"/>
       <c r="C403" s="55"/>
@@ -13749,7 +13744,7 @@
       <c r="T403" s="9"/>
       <c r="U403" s="9"/>
     </row>
-    <row r="404" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A404" s="9"/>
       <c r="B404" s="55"/>
       <c r="C404" s="55"/>
@@ -13772,7 +13767,7 @@
       <c r="T404" s="9"/>
       <c r="U404" s="9"/>
     </row>
-    <row r="405" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A405" s="9"/>
       <c r="B405" s="55"/>
       <c r="C405" s="55"/>
@@ -13795,7 +13790,7 @@
       <c r="T405" s="9"/>
       <c r="U405" s="9"/>
     </row>
-    <row r="406" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A406" s="9"/>
       <c r="B406" s="55"/>
       <c r="C406" s="55"/>
@@ -13818,7 +13813,7 @@
       <c r="T406" s="9"/>
       <c r="U406" s="9"/>
     </row>
-    <row r="407" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A407" s="9"/>
       <c r="B407" s="55"/>
       <c r="C407" s="55"/>
@@ -13841,7 +13836,7 @@
       <c r="T407" s="9"/>
       <c r="U407" s="9"/>
     </row>
-    <row r="408" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A408" s="9"/>
       <c r="B408" s="55"/>
       <c r="C408" s="55"/>
@@ -13864,7 +13859,7 @@
       <c r="T408" s="9"/>
       <c r="U408" s="9"/>
     </row>
-    <row r="409" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A409" s="9"/>
       <c r="B409" s="55"/>
       <c r="C409" s="55"/>
@@ -13887,7 +13882,7 @@
       <c r="T409" s="9"/>
       <c r="U409" s="9"/>
     </row>
-    <row r="410" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A410" s="9"/>
       <c r="B410" s="55"/>
       <c r="C410" s="55"/>
@@ -13910,7 +13905,7 @@
       <c r="T410" s="9"/>
       <c r="U410" s="9"/>
     </row>
-    <row r="411" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A411" s="9"/>
       <c r="B411" s="55"/>
       <c r="C411" s="55"/>
@@ -13933,7 +13928,7 @@
       <c r="T411" s="9"/>
       <c r="U411" s="9"/>
     </row>
-    <row r="412" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A412" s="9"/>
       <c r="B412" s="55"/>
       <c r="C412" s="55"/>
@@ -13956,7 +13951,7 @@
       <c r="T412" s="9"/>
       <c r="U412" s="9"/>
     </row>
-    <row r="413" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A413" s="9"/>
       <c r="B413" s="55"/>
       <c r="C413" s="55"/>
@@ -13979,7 +13974,7 @@
       <c r="T413" s="9"/>
       <c r="U413" s="9"/>
     </row>
-    <row r="414" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A414" s="9"/>
       <c r="B414" s="55"/>
       <c r="C414" s="55"/>
@@ -14002,7 +13997,7 @@
       <c r="T414" s="9"/>
       <c r="U414" s="9"/>
     </row>
-    <row r="415" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A415" s="9"/>
       <c r="B415" s="55"/>
       <c r="C415" s="55"/>
@@ -14025,7 +14020,7 @@
       <c r="T415" s="9"/>
       <c r="U415" s="9"/>
     </row>
-    <row r="416" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A416" s="9"/>
       <c r="B416" s="55"/>
       <c r="C416" s="55"/>
@@ -14048,7 +14043,7 @@
       <c r="T416" s="9"/>
       <c r="U416" s="9"/>
     </row>
-    <row r="417" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A417" s="9"/>
       <c r="B417" s="55"/>
       <c r="C417" s="55"/>
@@ -14071,7 +14066,7 @@
       <c r="T417" s="9"/>
       <c r="U417" s="9"/>
     </row>
-    <row r="418" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A418" s="9"/>
       <c r="B418" s="55"/>
       <c r="C418" s="55"/>
@@ -14094,7 +14089,7 @@
       <c r="T418" s="9"/>
       <c r="U418" s="9"/>
     </row>
-    <row r="419" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A419" s="9"/>
       <c r="B419" s="55"/>
       <c r="C419" s="55"/>
@@ -14117,7 +14112,7 @@
       <c r="T419" s="9"/>
       <c r="U419" s="9"/>
     </row>
-    <row r="420" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A420" s="9"/>
       <c r="B420" s="55"/>
       <c r="C420" s="55"/>
@@ -14140,7 +14135,7 @@
       <c r="T420" s="9"/>
       <c r="U420" s="9"/>
     </row>
-    <row r="421" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A421" s="9"/>
       <c r="B421" s="55"/>
       <c r="C421" s="55"/>
@@ -14163,7 +14158,7 @@
       <c r="T421" s="9"/>
       <c r="U421" s="9"/>
     </row>
-    <row r="422" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A422" s="9"/>
       <c r="B422" s="55"/>
       <c r="C422" s="55"/>
@@ -14186,7 +14181,7 @@
       <c r="T422" s="9"/>
       <c r="U422" s="9"/>
     </row>
-    <row r="423" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A423" s="9"/>
       <c r="B423" s="55"/>
       <c r="C423" s="55"/>
@@ -14209,7 +14204,7 @@
       <c r="T423" s="9"/>
       <c r="U423" s="9"/>
     </row>
-    <row r="424" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A424" s="9"/>
       <c r="B424" s="55"/>
       <c r="C424" s="55"/>
@@ -14232,7 +14227,7 @@
       <c r="T424" s="9"/>
       <c r="U424" s="9"/>
     </row>
-    <row r="425" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A425" s="9"/>
       <c r="B425" s="55"/>
       <c r="C425" s="55"/>
@@ -14255,7 +14250,7 @@
       <c r="T425" s="9"/>
       <c r="U425" s="9"/>
     </row>
-    <row r="426" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A426" s="9"/>
       <c r="B426" s="55"/>
       <c r="C426" s="55"/>
@@ -14278,7 +14273,7 @@
       <c r="T426" s="9"/>
       <c r="U426" s="9"/>
     </row>
-    <row r="427" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A427" s="9"/>
       <c r="B427" s="55"/>
       <c r="C427" s="55"/>
@@ -14301,7 +14296,7 @@
       <c r="T427" s="9"/>
       <c r="U427" s="9"/>
     </row>
-    <row r="428" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A428" s="9"/>
       <c r="B428" s="55"/>
       <c r="C428" s="55"/>
@@ -14324,7 +14319,7 @@
       <c r="T428" s="9"/>
       <c r="U428" s="9"/>
     </row>
-    <row r="429" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A429" s="9"/>
       <c r="B429" s="55"/>
       <c r="C429" s="55"/>
@@ -14347,7 +14342,7 @@
       <c r="T429" s="9"/>
       <c r="U429" s="9"/>
     </row>
-    <row r="430" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A430" s="9"/>
       <c r="B430" s="55"/>
       <c r="C430" s="55"/>
@@ -14370,7 +14365,7 @@
       <c r="T430" s="9"/>
       <c r="U430" s="9"/>
     </row>
-    <row r="431" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A431" s="9"/>
       <c r="B431" s="55"/>
       <c r="C431" s="55"/>
@@ -14393,7 +14388,7 @@
       <c r="T431" s="9"/>
       <c r="U431" s="9"/>
     </row>
-    <row r="432" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A432" s="9"/>
       <c r="B432" s="55"/>
       <c r="C432" s="55"/>
@@ -14416,7 +14411,7 @@
       <c r="T432" s="9"/>
       <c r="U432" s="9"/>
     </row>
-    <row r="433" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A433" s="9"/>
       <c r="B433" s="55"/>
       <c r="C433" s="55"/>
@@ -14439,7 +14434,7 @@
       <c r="T433" s="9"/>
       <c r="U433" s="9"/>
     </row>
-    <row r="434" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A434" s="9"/>
       <c r="B434" s="55"/>
       <c r="C434" s="55"/>
@@ -14462,7 +14457,7 @@
       <c r="T434" s="9"/>
       <c r="U434" s="9"/>
     </row>
-    <row r="435" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A435" s="9"/>
       <c r="B435" s="55"/>
       <c r="C435" s="55"/>
@@ -14485,7 +14480,7 @@
       <c r="T435" s="9"/>
       <c r="U435" s="9"/>
     </row>
-    <row r="436" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A436" s="9"/>
       <c r="B436" s="55"/>
       <c r="C436" s="55"/>
@@ -14508,7 +14503,7 @@
       <c r="T436" s="9"/>
       <c r="U436" s="9"/>
     </row>
-    <row r="437" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A437" s="9"/>
       <c r="B437" s="55"/>
       <c r="C437" s="55"/>
@@ -14531,7 +14526,7 @@
       <c r="T437" s="9"/>
       <c r="U437" s="9"/>
     </row>
-    <row r="438" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A438" s="9"/>
       <c r="B438" s="55"/>
       <c r="C438" s="55"/>
@@ -14554,7 +14549,7 @@
       <c r="T438" s="9"/>
       <c r="U438" s="9"/>
     </row>
-    <row r="439" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A439" s="9"/>
       <c r="B439" s="55"/>
       <c r="C439" s="55"/>
@@ -14577,7 +14572,7 @@
       <c r="T439" s="9"/>
       <c r="U439" s="9"/>
     </row>
-    <row r="440" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A440" s="9"/>
       <c r="B440" s="55"/>
       <c r="C440" s="55"/>
@@ -14600,7 +14595,7 @@
       <c r="T440" s="9"/>
       <c r="U440" s="9"/>
     </row>
-    <row r="441" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A441" s="9"/>
       <c r="B441" s="55"/>
       <c r="C441" s="55"/>
@@ -14623,7 +14618,7 @@
       <c r="T441" s="9"/>
       <c r="U441" s="9"/>
     </row>
-    <row r="442" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A442" s="9"/>
       <c r="B442" s="55"/>
       <c r="C442" s="55"/>
@@ -14646,7 +14641,7 @@
       <c r="T442" s="9"/>
       <c r="U442" s="9"/>
     </row>
-    <row r="443" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A443" s="9"/>
       <c r="B443" s="55"/>
       <c r="C443" s="55"/>
@@ -14669,7 +14664,7 @@
       <c r="T443" s="9"/>
       <c r="U443" s="9"/>
     </row>
-    <row r="444" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A444" s="9"/>
       <c r="B444" s="55"/>
       <c r="C444" s="55"/>
@@ -14692,7 +14687,7 @@
       <c r="T444" s="9"/>
       <c r="U444" s="9"/>
     </row>
-    <row r="445" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A445" s="9"/>
       <c r="B445" s="55"/>
       <c r="C445" s="55"/>
@@ -14715,7 +14710,7 @@
       <c r="T445" s="9"/>
       <c r="U445" s="9"/>
     </row>
-    <row r="446" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A446" s="9"/>
       <c r="B446" s="55"/>
       <c r="C446" s="55"/>
@@ -14738,7 +14733,7 @@
       <c r="T446" s="9"/>
       <c r="U446" s="9"/>
     </row>
-    <row r="447" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A447" s="9"/>
       <c r="B447" s="55"/>
       <c r="C447" s="55"/>
@@ -14761,7 +14756,7 @@
       <c r="T447" s="9"/>
       <c r="U447" s="9"/>
     </row>
-    <row r="448" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A448" s="9"/>
       <c r="B448" s="55"/>
       <c r="C448" s="55"/>
@@ -14784,7 +14779,7 @@
       <c r="T448" s="9"/>
       <c r="U448" s="9"/>
     </row>
-    <row r="449" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A449" s="9"/>
       <c r="B449" s="55"/>
       <c r="C449" s="55"/>
@@ -14807,7 +14802,7 @@
       <c r="T449" s="9"/>
       <c r="U449" s="9"/>
     </row>
-    <row r="450" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A450" s="9"/>
       <c r="B450" s="55"/>
       <c r="C450" s="55"/>
@@ -14830,7 +14825,7 @@
       <c r="T450" s="9"/>
       <c r="U450" s="9"/>
     </row>
-    <row r="451" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A451" s="9"/>
       <c r="B451" s="55"/>
       <c r="C451" s="55"/>
@@ -14853,7 +14848,7 @@
       <c r="T451" s="9"/>
       <c r="U451" s="9"/>
     </row>
-    <row r="452" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A452" s="9"/>
       <c r="B452" s="55"/>
       <c r="C452" s="55"/>
@@ -14876,7 +14871,7 @@
       <c r="T452" s="9"/>
       <c r="U452" s="9"/>
     </row>
-    <row r="453" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A453" s="9"/>
       <c r="B453" s="55"/>
       <c r="C453" s="55"/>
@@ -14899,7 +14894,7 @@
       <c r="T453" s="9"/>
       <c r="U453" s="9"/>
     </row>
-    <row r="454" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A454" s="9"/>
       <c r="B454" s="55"/>
       <c r="C454" s="55"/>
@@ -14922,7 +14917,7 @@
       <c r="T454" s="9"/>
       <c r="U454" s="9"/>
     </row>
-    <row r="455" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A455" s="9"/>
       <c r="B455" s="55"/>
       <c r="C455" s="55"/>
@@ -14945,7 +14940,7 @@
       <c r="T455" s="9"/>
       <c r="U455" s="9"/>
     </row>
-    <row r="456" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A456" s="9"/>
       <c r="B456" s="55"/>
       <c r="C456" s="55"/>
@@ -14968,7 +14963,7 @@
       <c r="T456" s="9"/>
       <c r="U456" s="9"/>
     </row>
-    <row r="457" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A457" s="9"/>
       <c r="B457" s="55"/>
       <c r="C457" s="55"/>
@@ -14991,7 +14986,7 @@
       <c r="T457" s="9"/>
       <c r="U457" s="9"/>
     </row>
-    <row r="458" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A458" s="9"/>
       <c r="B458" s="55"/>
       <c r="C458" s="55"/>
@@ -15014,7 +15009,7 @@
       <c r="T458" s="9"/>
       <c r="U458" s="9"/>
     </row>
-    <row r="459" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A459" s="9"/>
       <c r="B459" s="55"/>
       <c r="C459" s="55"/>
@@ -15037,7 +15032,7 @@
       <c r="T459" s="9"/>
       <c r="U459" s="9"/>
     </row>
-    <row r="460" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A460" s="9"/>
       <c r="B460" s="55"/>
       <c r="C460" s="55"/>
@@ -15060,7 +15055,7 @@
       <c r="T460" s="9"/>
       <c r="U460" s="9"/>
     </row>
-    <row r="461" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A461" s="9"/>
       <c r="B461" s="55"/>
       <c r="C461" s="55"/>
@@ -15083,7 +15078,7 @@
       <c r="T461" s="9"/>
       <c r="U461" s="9"/>
     </row>
-    <row r="462" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A462" s="9"/>
       <c r="B462" s="55"/>
       <c r="C462" s="55"/>
@@ -15106,7 +15101,7 @@
       <c r="T462" s="9"/>
       <c r="U462" s="9"/>
     </row>
-    <row r="463" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A463" s="9"/>
       <c r="B463" s="55"/>
       <c r="C463" s="55"/>
@@ -15129,7 +15124,7 @@
       <c r="T463" s="9"/>
       <c r="U463" s="9"/>
     </row>
-    <row r="464" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A464" s="9"/>
       <c r="B464" s="55"/>
       <c r="C464" s="55"/>
@@ -15152,7 +15147,7 @@
       <c r="T464" s="9"/>
       <c r="U464" s="9"/>
     </row>
-    <row r="465" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A465" s="9"/>
       <c r="B465" s="55"/>
       <c r="C465" s="55"/>
@@ -15175,7 +15170,7 @@
       <c r="T465" s="9"/>
       <c r="U465" s="9"/>
     </row>
-    <row r="466" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A466" s="9"/>
       <c r="B466" s="55"/>
       <c r="C466" s="55"/>
@@ -15198,7 +15193,7 @@
       <c r="T466" s="9"/>
       <c r="U466" s="9"/>
     </row>
-    <row r="467" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A467" s="9"/>
       <c r="B467" s="55"/>
       <c r="C467" s="55"/>
@@ -15221,7 +15216,7 @@
       <c r="T467" s="9"/>
       <c r="U467" s="9"/>
     </row>
-    <row r="468" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A468" s="9"/>
       <c r="B468" s="55"/>
       <c r="C468" s="55"/>
@@ -15244,7 +15239,7 @@
       <c r="T468" s="9"/>
       <c r="U468" s="9"/>
     </row>
-    <row r="469" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A469" s="9"/>
       <c r="B469" s="55"/>
       <c r="C469" s="55"/>
@@ -15267,7 +15262,7 @@
       <c r="T469" s="9"/>
       <c r="U469" s="9"/>
     </row>
-    <row r="470" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A470" s="9"/>
       <c r="B470" s="55"/>
       <c r="C470" s="55"/>
@@ -15290,7 +15285,7 @@
       <c r="T470" s="9"/>
       <c r="U470" s="9"/>
     </row>
-    <row r="471" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A471" s="9"/>
       <c r="B471" s="55"/>
       <c r="C471" s="55"/>
@@ -15313,7 +15308,7 @@
       <c r="T471" s="9"/>
       <c r="U471" s="9"/>
     </row>
-    <row r="472" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A472" s="9"/>
       <c r="B472" s="55"/>
       <c r="C472" s="55"/>
@@ -15336,7 +15331,7 @@
       <c r="T472" s="9"/>
       <c r="U472" s="9"/>
     </row>
-    <row r="473" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A473" s="9"/>
       <c r="B473" s="55"/>
       <c r="C473" s="55"/>
@@ -15359,7 +15354,7 @@
       <c r="T473" s="9"/>
       <c r="U473" s="9"/>
     </row>
-    <row r="474" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A474" s="9"/>
       <c r="B474" s="55"/>
       <c r="C474" s="55"/>
@@ -15382,7 +15377,7 @@
       <c r="T474" s="9"/>
       <c r="U474" s="9"/>
     </row>
-    <row r="475" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A475" s="9"/>
       <c r="B475" s="55"/>
       <c r="C475" s="55"/>
@@ -15405,7 +15400,7 @@
       <c r="T475" s="9"/>
       <c r="U475" s="9"/>
     </row>
-    <row r="476" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A476" s="9"/>
       <c r="B476" s="55"/>
       <c r="C476" s="55"/>
@@ -15428,7 +15423,7 @@
       <c r="T476" s="9"/>
       <c r="U476" s="9"/>
     </row>
-    <row r="477" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A477" s="9"/>
       <c r="B477" s="55"/>
       <c r="C477" s="55"/>
@@ -15451,7 +15446,7 @@
       <c r="T477" s="9"/>
       <c r="U477" s="9"/>
     </row>
-    <row r="478" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A478" s="9"/>
       <c r="B478" s="55"/>
       <c r="C478" s="55"/>
@@ -15474,7 +15469,7 @@
       <c r="T478" s="9"/>
       <c r="U478" s="9"/>
     </row>
-    <row r="479" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A479" s="9"/>
       <c r="B479" s="55"/>
       <c r="C479" s="55"/>
@@ -15497,7 +15492,7 @@
       <c r="T479" s="9"/>
       <c r="U479" s="9"/>
     </row>
-    <row r="480" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A480" s="9"/>
       <c r="B480" s="55"/>
       <c r="C480" s="55"/>
@@ -15520,7 +15515,7 @@
       <c r="T480" s="9"/>
       <c r="U480" s="9"/>
     </row>
-    <row r="481" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A481" s="9"/>
       <c r="B481" s="55"/>
       <c r="C481" s="55"/>
@@ -15543,7 +15538,7 @@
       <c r="T481" s="9"/>
       <c r="U481" s="9"/>
     </row>
-    <row r="482" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A482" s="9"/>
       <c r="B482" s="55"/>
       <c r="C482" s="55"/>
@@ -15566,7 +15561,7 @@
       <c r="T482" s="9"/>
       <c r="U482" s="9"/>
     </row>
-    <row r="483" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A483" s="9"/>
       <c r="B483" s="55"/>
       <c r="C483" s="55"/>
@@ -15589,7 +15584,7 @@
       <c r="T483" s="9"/>
       <c r="U483" s="9"/>
     </row>
-    <row r="484" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A484" s="9"/>
       <c r="B484" s="55"/>
       <c r="C484" s="55"/>
@@ -15612,7 +15607,7 @@
       <c r="T484" s="9"/>
       <c r="U484" s="9"/>
     </row>
-    <row r="485" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A485" s="9"/>
       <c r="B485" s="55"/>
       <c r="C485" s="55"/>
@@ -15635,7 +15630,7 @@
       <c r="T485" s="9"/>
       <c r="U485" s="9"/>
     </row>
-    <row r="486" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A486" s="9"/>
       <c r="B486" s="55"/>
       <c r="C486" s="55"/>
@@ -15658,7 +15653,7 @@
       <c r="T486" s="9"/>
       <c r="U486" s="9"/>
     </row>
-    <row r="487" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A487" s="9"/>
       <c r="B487" s="55"/>
       <c r="C487" s="55"/>
@@ -15681,7 +15676,7 @@
       <c r="T487" s="9"/>
       <c r="U487" s="9"/>
     </row>
-    <row r="488" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A488" s="9"/>
       <c r="B488" s="55"/>
       <c r="C488" s="55"/>
@@ -15704,7 +15699,7 @@
       <c r="T488" s="9"/>
       <c r="U488" s="9"/>
     </row>
-    <row r="489" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A489" s="9"/>
       <c r="B489" s="55"/>
       <c r="C489" s="55"/>
@@ -15727,7 +15722,7 @@
       <c r="T489" s="9"/>
       <c r="U489" s="9"/>
     </row>
-    <row r="490" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A490" s="9"/>
       <c r="B490" s="55"/>
       <c r="C490" s="55"/>
@@ -15750,7 +15745,7 @@
       <c r="T490" s="9"/>
       <c r="U490" s="9"/>
     </row>
-    <row r="491" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A491" s="9"/>
       <c r="B491" s="55"/>
       <c r="C491" s="55"/>
@@ -15773,7 +15768,7 @@
       <c r="T491" s="9"/>
       <c r="U491" s="9"/>
     </row>
-    <row r="492" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A492" s="9"/>
       <c r="B492" s="55"/>
       <c r="C492" s="55"/>
@@ -15796,7 +15791,7 @@
       <c r="T492" s="9"/>
       <c r="U492" s="9"/>
     </row>
-    <row r="493" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A493" s="9"/>
       <c r="B493" s="55"/>
       <c r="C493" s="55"/>
@@ -15819,7 +15814,7 @@
       <c r="T493" s="9"/>
       <c r="U493" s="9"/>
     </row>
-    <row r="494" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A494" s="9"/>
       <c r="B494" s="55"/>
       <c r="C494" s="55"/>
@@ -15842,7 +15837,7 @@
       <c r="T494" s="9"/>
       <c r="U494" s="9"/>
     </row>
-    <row r="495" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A495" s="9"/>
       <c r="B495" s="55"/>
       <c r="C495" s="55"/>
@@ -15865,7 +15860,7 @@
       <c r="T495" s="9"/>
       <c r="U495" s="9"/>
     </row>
-    <row r="496" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A496" s="9"/>
       <c r="B496" s="55"/>
       <c r="C496" s="55"/>
@@ -15888,7 +15883,7 @@
       <c r="T496" s="9"/>
       <c r="U496" s="9"/>
     </row>
-    <row r="497" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A497" s="9"/>
       <c r="B497" s="55"/>
       <c r="C497" s="55"/>
@@ -15911,7 +15906,7 @@
       <c r="T497" s="9"/>
       <c r="U497" s="9"/>
     </row>
-    <row r="498" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A498" s="9"/>
       <c r="B498" s="55"/>
       <c r="C498" s="55"/>
@@ -15934,7 +15929,7 @@
       <c r="T498" s="9"/>
       <c r="U498" s="9"/>
     </row>
-    <row r="499" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A499" s="9"/>
       <c r="B499" s="55"/>
       <c r="C499" s="55"/>
@@ -15957,7 +15952,7 @@
       <c r="T499" s="9"/>
       <c r="U499" s="9"/>
     </row>
-    <row r="500" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A500" s="9"/>
       <c r="B500" s="55"/>
       <c r="C500" s="55"/>
@@ -15980,7 +15975,7 @@
       <c r="T500" s="9"/>
       <c r="U500" s="9"/>
     </row>
-    <row r="501" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A501" s="9"/>
       <c r="B501" s="55"/>
       <c r="C501" s="55"/>
@@ -16003,7 +15998,7 @@
       <c r="T501" s="9"/>
       <c r="U501" s="9"/>
     </row>
-    <row r="502" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A502" s="9"/>
       <c r="B502" s="55"/>
       <c r="C502" s="55"/>
@@ -16026,7 +16021,7 @@
       <c r="T502" s="9"/>
       <c r="U502" s="9"/>
     </row>
-    <row r="503" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A503" s="9"/>
       <c r="B503" s="55"/>
       <c r="C503" s="55"/>
@@ -16049,7 +16044,7 @@
       <c r="T503" s="9"/>
       <c r="U503" s="9"/>
     </row>
-    <row r="504" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A504" s="9"/>
       <c r="B504" s="55"/>
       <c r="C504" s="55"/>
@@ -16072,7 +16067,7 @@
       <c r="T504" s="9"/>
       <c r="U504" s="9"/>
     </row>
-    <row r="505" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A505" s="9"/>
       <c r="B505" s="55"/>
       <c r="C505" s="55"/>
@@ -16095,7 +16090,7 @@
       <c r="T505" s="9"/>
       <c r="U505" s="9"/>
     </row>
-    <row r="506" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A506" s="9"/>
       <c r="B506" s="55"/>
       <c r="C506" s="55"/>
@@ -16118,7 +16113,7 @@
       <c r="T506" s="9"/>
       <c r="U506" s="9"/>
     </row>
-    <row r="507" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A507" s="9"/>
       <c r="B507" s="55"/>
       <c r="C507" s="55"/>
@@ -16141,7 +16136,7 @@
       <c r="T507" s="9"/>
       <c r="U507" s="9"/>
     </row>
-    <row r="508" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A508" s="9"/>
       <c r="B508" s="55"/>
       <c r="C508" s="55"/>
@@ -16164,7 +16159,7 @@
       <c r="T508" s="9"/>
       <c r="U508" s="9"/>
     </row>
-    <row r="509" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A509" s="9"/>
       <c r="B509" s="55"/>
       <c r="C509" s="55"/>
@@ -16187,7 +16182,7 @@
       <c r="T509" s="9"/>
       <c r="U509" s="9"/>
     </row>
-    <row r="510" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A510" s="9"/>
       <c r="B510" s="55"/>
       <c r="C510" s="55"/>
@@ -16210,7 +16205,7 @@
       <c r="T510" s="9"/>
       <c r="U510" s="9"/>
     </row>
-    <row r="511" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A511" s="9"/>
       <c r="B511" s="55"/>
       <c r="C511" s="55"/>
@@ -16233,7 +16228,7 @@
       <c r="T511" s="9"/>
       <c r="U511" s="9"/>
     </row>
-    <row r="512" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A512" s="9"/>
       <c r="B512" s="55"/>
       <c r="C512" s="55"/>
@@ -16256,7 +16251,7 @@
       <c r="T512" s="9"/>
       <c r="U512" s="9"/>
     </row>
-    <row r="513" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A513" s="9"/>
       <c r="B513" s="55"/>
       <c r="C513" s="55"/>
@@ -16279,7 +16274,7 @@
       <c r="T513" s="9"/>
       <c r="U513" s="9"/>
     </row>
-    <row r="514" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A514" s="9"/>
       <c r="B514" s="55"/>
       <c r="C514" s="55"/>
@@ -16302,7 +16297,7 @@
       <c r="T514" s="9"/>
       <c r="U514" s="9"/>
     </row>
-    <row r="515" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A515" s="9"/>
       <c r="B515" s="55"/>
       <c r="C515" s="55"/>
@@ -16325,7 +16320,7 @@
       <c r="T515" s="9"/>
       <c r="U515" s="9"/>
     </row>
-    <row r="516" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A516" s="9"/>
       <c r="B516" s="55"/>
       <c r="C516" s="55"/>
@@ -16348,7 +16343,7 @@
       <c r="T516" s="9"/>
       <c r="U516" s="9"/>
     </row>
-    <row r="517" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A517" s="9"/>
       <c r="B517" s="55"/>
       <c r="C517" s="55"/>
@@ -16371,7 +16366,7 @@
       <c r="T517" s="9"/>
       <c r="U517" s="9"/>
     </row>
-    <row r="518" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A518" s="9"/>
       <c r="B518" s="55"/>
       <c r="C518" s="55"/>
@@ -16394,7 +16389,7 @@
       <c r="T518" s="9"/>
       <c r="U518" s="9"/>
     </row>
-    <row r="519" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A519" s="9"/>
       <c r="B519" s="55"/>
       <c r="C519" s="55"/>
@@ -16417,7 +16412,7 @@
       <c r="T519" s="9"/>
       <c r="U519" s="9"/>
     </row>
-    <row r="520" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A520" s="9"/>
       <c r="B520" s="55"/>
       <c r="C520" s="55"/>
@@ -16440,7 +16435,7 @@
       <c r="T520" s="9"/>
       <c r="U520" s="9"/>
     </row>
-    <row r="521" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A521" s="9"/>
       <c r="B521" s="55"/>
       <c r="C521" s="55"/>
@@ -16463,7 +16458,7 @@
       <c r="T521" s="9"/>
       <c r="U521" s="9"/>
     </row>
-    <row r="522" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A522" s="9"/>
       <c r="B522" s="55"/>
       <c r="C522" s="55"/>
@@ -16486,7 +16481,7 @@
       <c r="T522" s="9"/>
       <c r="U522" s="9"/>
     </row>
-    <row r="523" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A523" s="9"/>
       <c r="B523" s="55"/>
       <c r="C523" s="55"/>
@@ -16509,7 +16504,7 @@
       <c r="T523" s="9"/>
       <c r="U523" s="9"/>
     </row>
-    <row r="524" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A524" s="9"/>
       <c r="B524" s="55"/>
       <c r="C524" s="55"/>
@@ -16532,7 +16527,7 @@
       <c r="T524" s="9"/>
       <c r="U524" s="9"/>
     </row>
-    <row r="525" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A525" s="9"/>
       <c r="B525" s="55"/>
       <c r="C525" s="55"/>
@@ -16555,7 +16550,7 @@
       <c r="T525" s="9"/>
       <c r="U525" s="9"/>
     </row>
-    <row r="526" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A526" s="9"/>
       <c r="B526" s="55"/>
       <c r="C526" s="55"/>
@@ -16578,7 +16573,7 @@
       <c r="T526" s="9"/>
       <c r="U526" s="9"/>
     </row>
-    <row r="527" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A527" s="9"/>
       <c r="B527" s="55"/>
       <c r="C527" s="55"/>
@@ -16601,7 +16596,7 @@
       <c r="T527" s="9"/>
       <c r="U527" s="9"/>
     </row>
-    <row r="528" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A528" s="9"/>
       <c r="B528" s="55"/>
       <c r="C528" s="55"/>
@@ -16624,7 +16619,7 @@
       <c r="T528" s="9"/>
       <c r="U528" s="9"/>
     </row>
-    <row r="529" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A529" s="9"/>
       <c r="B529" s="55"/>
       <c r="C529" s="55"/>
@@ -16647,7 +16642,7 @@
       <c r="T529" s="9"/>
       <c r="U529" s="9"/>
     </row>
-    <row r="530" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A530" s="9"/>
       <c r="B530" s="55"/>
       <c r="C530" s="55"/>
@@ -16670,7 +16665,7 @@
       <c r="T530" s="9"/>
       <c r="U530" s="9"/>
     </row>
-    <row r="531" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A531" s="9"/>
       <c r="B531" s="55"/>
       <c r="C531" s="55"/>
@@ -16693,7 +16688,7 @@
       <c r="T531" s="9"/>
       <c r="U531" s="9"/>
     </row>
-    <row r="532" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A532" s="9"/>
       <c r="B532" s="55"/>
       <c r="C532" s="55"/>
@@ -16716,7 +16711,7 @@
       <c r="T532" s="9"/>
       <c r="U532" s="9"/>
     </row>
-    <row r="533" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A533" s="9"/>
       <c r="B533" s="55"/>
       <c r="C533" s="55"/>
@@ -16739,7 +16734,7 @@
       <c r="T533" s="9"/>
       <c r="U533" s="9"/>
     </row>
-    <row r="534" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A534" s="9"/>
       <c r="B534" s="55"/>
       <c r="C534" s="55"/>
@@ -16762,7 +16757,7 @@
       <c r="T534" s="9"/>
       <c r="U534" s="9"/>
     </row>
-    <row r="535" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A535" s="9"/>
       <c r="B535" s="55"/>
       <c r="C535" s="55"/>
@@ -16785,7 +16780,7 @@
       <c r="T535" s="9"/>
       <c r="U535" s="9"/>
     </row>
-    <row r="536" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A536" s="9"/>
       <c r="B536" s="55"/>
       <c r="C536" s="55"/>
@@ -16808,7 +16803,7 @@
       <c r="T536" s="9"/>
       <c r="U536" s="9"/>
     </row>
-    <row r="537" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A537" s="9"/>
       <c r="B537" s="55"/>
       <c r="C537" s="55"/>
@@ -16831,7 +16826,7 @@
       <c r="T537" s="9"/>
       <c r="U537" s="9"/>
     </row>
-    <row r="538" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A538" s="9"/>
       <c r="B538" s="55"/>
       <c r="C538" s="55"/>
@@ -16854,7 +16849,7 @@
       <c r="T538" s="9"/>
       <c r="U538" s="9"/>
     </row>
-    <row r="539" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A539" s="9"/>
       <c r="B539" s="55"/>
       <c r="C539" s="55"/>
@@ -16877,7 +16872,7 @@
       <c r="T539" s="9"/>
       <c r="U539" s="9"/>
     </row>
-    <row r="540" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A540" s="9"/>
       <c r="B540" s="55"/>
       <c r="C540" s="55"/>
@@ -16900,7 +16895,7 @@
       <c r="T540" s="9"/>
       <c r="U540" s="9"/>
     </row>
-    <row r="541" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A541" s="9"/>
       <c r="B541" s="55"/>
       <c r="C541" s="55"/>
@@ -16923,7 +16918,7 @@
       <c r="T541" s="9"/>
       <c r="U541" s="9"/>
     </row>
-    <row r="542" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A542" s="9"/>
       <c r="B542" s="55"/>
       <c r="C542" s="55"/>
@@ -16946,7 +16941,7 @@
       <c r="T542" s="9"/>
       <c r="U542" s="9"/>
     </row>
-    <row r="543" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A543" s="9"/>
       <c r="B543" s="55"/>
       <c r="C543" s="55"/>
@@ -16969,7 +16964,7 @@
       <c r="T543" s="9"/>
       <c r="U543" s="9"/>
     </row>
-    <row r="544" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A544" s="9"/>
       <c r="B544" s="55"/>
       <c r="C544" s="55"/>
@@ -16992,7 +16987,7 @@
       <c r="T544" s="9"/>
       <c r="U544" s="9"/>
     </row>
-    <row r="545" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A545" s="9"/>
       <c r="B545" s="55"/>
       <c r="C545" s="55"/>
@@ -17015,7 +17010,7 @@
       <c r="T545" s="9"/>
       <c r="U545" s="9"/>
     </row>
-    <row r="546" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A546" s="9"/>
       <c r="B546" s="55"/>
       <c r="C546" s="55"/>
@@ -17038,7 +17033,7 @@
       <c r="T546" s="9"/>
       <c r="U546" s="9"/>
     </row>
-    <row r="547" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A547" s="9"/>
       <c r="B547" s="55"/>
       <c r="C547" s="55"/>
@@ -17061,7 +17056,7 @@
       <c r="T547" s="9"/>
       <c r="U547" s="9"/>
     </row>
-    <row r="548" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A548" s="9"/>
       <c r="B548" s="55"/>
       <c r="C548" s="55"/>
@@ -17084,7 +17079,7 @@
       <c r="T548" s="9"/>
       <c r="U548" s="9"/>
     </row>
-    <row r="549" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A549" s="9"/>
       <c r="B549" s="55"/>
       <c r="C549" s="55"/>
@@ -17107,7 +17102,7 @@
       <c r="T549" s="9"/>
       <c r="U549" s="9"/>
     </row>
-    <row r="550" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A550" s="9"/>
       <c r="B550" s="55"/>
       <c r="C550" s="55"/>
@@ -17130,7 +17125,7 @@
       <c r="T550" s="9"/>
       <c r="U550" s="9"/>
     </row>
-    <row r="551" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A551" s="9"/>
       <c r="B551" s="55"/>
       <c r="C551" s="55"/>
@@ -17153,7 +17148,7 @@
       <c r="T551" s="9"/>
       <c r="U551" s="9"/>
     </row>
-    <row r="552" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A552" s="9"/>
       <c r="B552" s="55"/>
       <c r="C552" s="55"/>
@@ -17176,7 +17171,7 @@
       <c r="T552" s="9"/>
       <c r="U552" s="9"/>
     </row>
-    <row r="553" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A553" s="9"/>
       <c r="B553" s="55"/>
       <c r="C553" s="55"/>
@@ -17199,7 +17194,7 @@
       <c r="T553" s="9"/>
       <c r="U553" s="9"/>
     </row>
-    <row r="554" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A554" s="9"/>
       <c r="B554" s="55"/>
       <c r="C554" s="55"/>
@@ -17222,7 +17217,7 @@
       <c r="T554" s="9"/>
       <c r="U554" s="9"/>
     </row>
-    <row r="555" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A555" s="9"/>
       <c r="B555" s="55"/>
       <c r="C555" s="55"/>
@@ -17245,7 +17240,7 @@
       <c r="T555" s="9"/>
       <c r="U555" s="9"/>
     </row>
-    <row r="556" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A556" s="9"/>
       <c r="B556" s="55"/>
       <c r="C556" s="55"/>
@@ -17268,7 +17263,7 @@
       <c r="T556" s="9"/>
       <c r="U556" s="9"/>
     </row>
-    <row r="557" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A557" s="9"/>
       <c r="B557" s="55"/>
       <c r="C557" s="55"/>
@@ -17291,7 +17286,7 @@
       <c r="T557" s="9"/>
       <c r="U557" s="9"/>
     </row>
-    <row r="558" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A558" s="9"/>
       <c r="B558" s="55"/>
       <c r="C558" s="55"/>
@@ -17314,7 +17309,7 @@
       <c r="T558" s="9"/>
       <c r="U558" s="9"/>
     </row>
-    <row r="559" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A559" s="9"/>
       <c r="B559" s="55"/>
       <c r="C559" s="55"/>
@@ -17337,7 +17332,7 @@
       <c r="T559" s="9"/>
       <c r="U559" s="9"/>
     </row>
-    <row r="560" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A560" s="9"/>
       <c r="B560" s="55"/>
       <c r="C560" s="55"/>
@@ -17360,7 +17355,7 @@
       <c r="T560" s="9"/>
       <c r="U560" s="9"/>
     </row>
-    <row r="561" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A561" s="9"/>
       <c r="B561" s="55"/>
       <c r="C561" s="55"/>
@@ -17383,7 +17378,7 @@
       <c r="T561" s="9"/>
       <c r="U561" s="9"/>
     </row>
-    <row r="562" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A562" s="9"/>
       <c r="B562" s="55"/>
       <c r="C562" s="55"/>
@@ -17406,7 +17401,7 @@
       <c r="T562" s="9"/>
       <c r="U562" s="9"/>
     </row>
-    <row r="563" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A563" s="9"/>
       <c r="B563" s="55"/>
       <c r="C563" s="55"/>
@@ -17429,7 +17424,7 @@
       <c r="T563" s="9"/>
       <c r="U563" s="9"/>
     </row>
-    <row r="564" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A564" s="9"/>
       <c r="B564" s="55"/>
       <c r="C564" s="55"/>
@@ -17452,7 +17447,7 @@
       <c r="T564" s="9"/>
       <c r="U564" s="9"/>
     </row>
-    <row r="565" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A565" s="9"/>
       <c r="B565" s="55"/>
       <c r="C565" s="55"/>
@@ -17475,7 +17470,7 @@
       <c r="T565" s="9"/>
       <c r="U565" s="9"/>
     </row>
-    <row r="566" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A566" s="9"/>
       <c r="B566" s="55"/>
       <c r="C566" s="55"/>
@@ -17498,7 +17493,7 @@
       <c r="T566" s="9"/>
       <c r="U566" s="9"/>
     </row>
-    <row r="567" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A567" s="9"/>
       <c r="B567" s="55"/>
       <c r="C567" s="55"/>
@@ -17521,7 +17516,7 @@
       <c r="T567" s="9"/>
       <c r="U567" s="9"/>
     </row>
-    <row r="568" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A568" s="9"/>
       <c r="B568" s="55"/>
       <c r="C568" s="55"/>
@@ -17544,7 +17539,7 @@
       <c r="T568" s="9"/>
       <c r="U568" s="9"/>
     </row>
-    <row r="569" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A569" s="9"/>
       <c r="B569" s="55"/>
       <c r="C569" s="55"/>
@@ -17567,7 +17562,7 @@
       <c r="T569" s="9"/>
       <c r="U569" s="9"/>
     </row>
-    <row r="570" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A570" s="9"/>
       <c r="B570" s="55"/>
       <c r="C570" s="55"/>
@@ -17590,7 +17585,7 @@
       <c r="T570" s="9"/>
       <c r="U570" s="9"/>
     </row>
-    <row r="571" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A571" s="9"/>
       <c r="B571" s="55"/>
       <c r="C571" s="55"/>
@@ -17613,7 +17608,7 @@
       <c r="T571" s="9"/>
       <c r="U571" s="9"/>
     </row>
-    <row r="572" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A572" s="9"/>
       <c r="B572" s="55"/>
       <c r="C572" s="55"/>
@@ -17636,7 +17631,7 @@
       <c r="T572" s="9"/>
       <c r="U572" s="9"/>
     </row>
-    <row r="573" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A573" s="9"/>
       <c r="B573" s="55"/>
       <c r="C573" s="55"/>
@@ -17659,7 +17654,7 @@
       <c r="T573" s="9"/>
       <c r="U573" s="9"/>
     </row>
-    <row r="574" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A574" s="9"/>
       <c r="B574" s="55"/>
       <c r="C574" s="55"/>
@@ -17682,7 +17677,7 @@
       <c r="T574" s="9"/>
       <c r="U574" s="9"/>
     </row>
-    <row r="575" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A575" s="9"/>
       <c r="B575" s="55"/>
       <c r="C575" s="55"/>
@@ -17705,7 +17700,7 @@
       <c r="T575" s="9"/>
       <c r="U575" s="9"/>
     </row>
-    <row r="576" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A576" s="9"/>
       <c r="B576" s="55"/>
       <c r="C576" s="55"/>
@@ -17728,7 +17723,7 @@
       <c r="T576" s="9"/>
       <c r="U576" s="9"/>
     </row>
-    <row r="577" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A577" s="9"/>
       <c r="B577" s="55"/>
       <c r="C577" s="55"/>
@@ -17751,7 +17746,7 @@
       <c r="T577" s="9"/>
       <c r="U577" s="9"/>
     </row>
-    <row r="578" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A578" s="9"/>
       <c r="B578" s="55"/>
       <c r="C578" s="55"/>
@@ -17774,7 +17769,7 @@
       <c r="T578" s="9"/>
       <c r="U578" s="9"/>
     </row>
-    <row r="579" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A579" s="9"/>
       <c r="B579" s="55"/>
       <c r="C579" s="55"/>
@@ -17797,7 +17792,7 @@
       <c r="T579" s="9"/>
       <c r="U579" s="9"/>
     </row>
-    <row r="580" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A580" s="9"/>
       <c r="B580" s="55"/>
       <c r="C580" s="55"/>
@@ -17820,7 +17815,7 @@
       <c r="T580" s="9"/>
       <c r="U580" s="9"/>
     </row>
-    <row r="581" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A581" s="9"/>
       <c r="B581" s="55"/>
       <c r="C581" s="55"/>
@@ -17843,7 +17838,7 @@
       <c r="T581" s="9"/>
       <c r="U581" s="9"/>
     </row>
-    <row r="582" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A582" s="9"/>
       <c r="B582" s="55"/>
       <c r="C582" s="55"/>
@@ -17866,7 +17861,7 @@
       <c r="T582" s="9"/>
       <c r="U582" s="9"/>
     </row>
-    <row r="583" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A583" s="9"/>
       <c r="B583" s="55"/>
       <c r="C583" s="55"/>
@@ -17889,7 +17884,7 @@
       <c r="T583" s="9"/>
       <c r="U583" s="9"/>
     </row>
-    <row r="584" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A584" s="9"/>
       <c r="B584" s="55"/>
       <c r="C584" s="55"/>
@@ -17912,7 +17907,7 @@
       <c r="T584" s="9"/>
       <c r="U584" s="9"/>
     </row>
-    <row r="585" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A585" s="9"/>
       <c r="B585" s="55"/>
       <c r="C585" s="55"/>
@@ -17935,7 +17930,7 @@
       <c r="T585" s="9"/>
       <c r="U585" s="9"/>
     </row>
-    <row r="586" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A586" s="9"/>
       <c r="B586" s="55"/>
       <c r="C586" s="55"/>
@@ -17958,7 +17953,7 @@
       <c r="T586" s="9"/>
       <c r="U586" s="9"/>
     </row>
-    <row r="587" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A587" s="9"/>
       <c r="B587" s="55"/>
       <c r="C587" s="55"/>
@@ -17981,7 +17976,7 @@
       <c r="T587" s="9"/>
       <c r="U587" s="9"/>
     </row>
-    <row r="588" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A588" s="9"/>
       <c r="B588" s="55"/>
       <c r="C588" s="55"/>
@@ -18004,7 +17999,7 @@
       <c r="T588" s="9"/>
       <c r="U588" s="9"/>
     </row>
-    <row r="589" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A589" s="9"/>
       <c r="B589" s="55"/>
       <c r="C589" s="55"/>
@@ -18027,7 +18022,7 @@
       <c r="T589" s="9"/>
       <c r="U589" s="9"/>
     </row>
-    <row r="590" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A590" s="9"/>
       <c r="B590" s="55"/>
       <c r="C590" s="55"/>
@@ -18050,7 +18045,7 @@
       <c r="T590" s="9"/>
       <c r="U590" s="9"/>
     </row>
-    <row r="591" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A591" s="9"/>
       <c r="B591" s="55"/>
       <c r="C591" s="55"/>
@@ -18073,7 +18068,7 @@
       <c r="T591" s="9"/>
       <c r="U591" s="9"/>
     </row>
-    <row r="592" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A592" s="9"/>
       <c r="B592" s="55"/>
       <c r="C592" s="55"/>
@@ -18096,7 +18091,7 @@
       <c r="T592" s="9"/>
       <c r="U592" s="9"/>
     </row>
-    <row r="593" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A593" s="9"/>
       <c r="B593" s="55"/>
       <c r="C593" s="55"/>
@@ -18119,7 +18114,7 @@
       <c r="T593" s="9"/>
       <c r="U593" s="9"/>
     </row>
-    <row r="594" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A594" s="9"/>
       <c r="B594" s="55"/>
       <c r="C594" s="55"/>
@@ -18142,7 +18137,7 @@
       <c r="T594" s="9"/>
       <c r="U594" s="9"/>
     </row>
-    <row r="595" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A595" s="9"/>
       <c r="B595" s="55"/>
       <c r="C595" s="55"/>
@@ -18165,7 +18160,7 @@
       <c r="T595" s="9"/>
       <c r="U595" s="9"/>
     </row>
-    <row r="596" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A596" s="9"/>
       <c r="B596" s="55"/>
       <c r="C596" s="55"/>
@@ -18188,7 +18183,7 @@
       <c r="T596" s="9"/>
       <c r="U596" s="9"/>
     </row>
-    <row r="597" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A597" s="9"/>
       <c r="B597" s="55"/>
       <c r="C597" s="55"/>
@@ -18211,7 +18206,7 @@
       <c r="T597" s="9"/>
       <c r="U597" s="9"/>
     </row>
-    <row r="598" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A598" s="9"/>
       <c r="B598" s="55"/>
       <c r="C598" s="55"/>
@@ -18234,7 +18229,7 @@
       <c r="T598" s="9"/>
       <c r="U598" s="9"/>
     </row>
-    <row r="599" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A599" s="9"/>
       <c r="B599" s="55"/>
       <c r="C599" s="55"/>
@@ -18257,7 +18252,7 @@
       <c r="T599" s="9"/>
       <c r="U599" s="9"/>
     </row>
-    <row r="600" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A600" s="9"/>
       <c r="B600" s="55"/>
       <c r="C600" s="55"/>
@@ -18280,7 +18275,7 @@
       <c r="T600" s="9"/>
       <c r="U600" s="9"/>
     </row>
-    <row r="601" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A601" s="9"/>
       <c r="B601" s="55"/>
       <c r="C601" s="55"/>
@@ -18303,7 +18298,7 @@
       <c r="T601" s="9"/>
       <c r="U601" s="9"/>
     </row>
-    <row r="602" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A602" s="9"/>
       <c r="B602" s="55"/>
       <c r="C602" s="55"/>
@@ -18326,7 +18321,7 @@
       <c r="T602" s="9"/>
       <c r="U602" s="9"/>
     </row>
-    <row r="603" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A603" s="9"/>
       <c r="B603" s="55"/>
       <c r="C603" s="55"/>
@@ -18349,7 +18344,7 @@
       <c r="T603" s="9"/>
       <c r="U603" s="9"/>
     </row>
-    <row r="604" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A604" s="9"/>
       <c r="B604" s="55"/>
       <c r="C604" s="55"/>
@@ -18372,7 +18367,7 @@
       <c r="T604" s="9"/>
       <c r="U604" s="9"/>
     </row>
-    <row r="605" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A605" s="9"/>
       <c r="B605" s="55"/>
       <c r="C605" s="55"/>
@@ -18395,7 +18390,7 @@
       <c r="T605" s="9"/>
       <c r="U605" s="9"/>
     </row>
-    <row r="606" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A606" s="9"/>
       <c r="B606" s="55"/>
       <c r="C606" s="55"/>
@@ -18418,7 +18413,7 @@
       <c r="T606" s="9"/>
       <c r="U606" s="9"/>
     </row>
-    <row r="607" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A607" s="9"/>
       <c r="B607" s="55"/>
       <c r="C607" s="55"/>
@@ -18441,7 +18436,7 @@
       <c r="T607" s="9"/>
       <c r="U607" s="9"/>
     </row>
-    <row r="608" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A608" s="9"/>
       <c r="B608" s="55"/>
       <c r="C608" s="55"/>
@@ -18464,7 +18459,7 @@
       <c r="T608" s="9"/>
       <c r="U608" s="9"/>
     </row>
-    <row r="609" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A609" s="9"/>
       <c r="B609" s="55"/>
       <c r="C609" s="55"/>
@@ -18487,7 +18482,7 @@
       <c r="T609" s="9"/>
       <c r="U609" s="9"/>
     </row>
-    <row r="610" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A610" s="9"/>
       <c r="B610" s="55"/>
       <c r="C610" s="55"/>
@@ -18510,7 +18505,7 @@
       <c r="T610" s="9"/>
       <c r="U610" s="9"/>
     </row>
-    <row r="611" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A611" s="9"/>
       <c r="B611" s="55"/>
       <c r="C611" s="55"/>
@@ -18533,7 +18528,7 @@
       <c r="T611" s="9"/>
       <c r="U611" s="9"/>
     </row>
-    <row r="612" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A612" s="9"/>
       <c r="B612" s="55"/>
       <c r="C612" s="55"/>
@@ -18556,7 +18551,7 @@
       <c r="T612" s="9"/>
       <c r="U612" s="9"/>
     </row>
-    <row r="613" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A613" s="9"/>
       <c r="B613" s="55"/>
       <c r="C613" s="55"/>
@@ -18579,7 +18574,7 @@
       <c r="T613" s="9"/>
       <c r="U613" s="9"/>
     </row>
-    <row r="614" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A614" s="9"/>
       <c r="B614" s="55"/>
       <c r="C614" s="55"/>
@@ -18602,7 +18597,7 @@
       <c r="T614" s="9"/>
       <c r="U614" s="9"/>
     </row>
-    <row r="615" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A615" s="9"/>
       <c r="B615" s="55"/>
       <c r="C615" s="55"/>
@@ -18625,7 +18620,7 @@
       <c r="T615" s="9"/>
       <c r="U615" s="9"/>
     </row>
-    <row r="616" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A616" s="9"/>
       <c r="B616" s="55"/>
       <c r="C616" s="55"/>
@@ -18648,7 +18643,7 @@
       <c r="T616" s="9"/>
       <c r="U616" s="9"/>
     </row>
-    <row r="617" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A617" s="9"/>
       <c r="B617" s="55"/>
       <c r="C617" s="55"/>
@@ -18671,7 +18666,7 @@
       <c r="T617" s="9"/>
       <c r="U617" s="9"/>
     </row>
-    <row r="618" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A618" s="9"/>
       <c r="B618" s="55"/>
       <c r="C618" s="55"/>
@@ -18694,7 +18689,7 @@
       <c r="T618" s="9"/>
       <c r="U618" s="9"/>
     </row>
-    <row r="619" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A619" s="9"/>
       <c r="B619" s="55"/>
       <c r="C619" s="55"/>
@@ -18717,7 +18712,7 @@
       <c r="T619" s="9"/>
       <c r="U619" s="9"/>
     </row>
-    <row r="620" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A620" s="9"/>
       <c r="B620" s="55"/>
       <c r="C620" s="55"/>
@@ -18740,7 +18735,7 @@
       <c r="T620" s="9"/>
       <c r="U620" s="9"/>
     </row>
-    <row r="621" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A621" s="9"/>
       <c r="B621" s="55"/>
       <c r="C621" s="55"/>
@@ -18763,7 +18758,7 @@
       <c r="T621" s="9"/>
       <c r="U621" s="9"/>
     </row>
-    <row r="622" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A622" s="9"/>
       <c r="B622" s="55"/>
       <c r="C622" s="55"/>
@@ -18786,7 +18781,7 @@
       <c r="T622" s="9"/>
       <c r="U622" s="9"/>
     </row>
-    <row r="623" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A623" s="9"/>
       <c r="B623" s="55"/>
       <c r="C623" s="55"/>
@@ -18809,7 +18804,7 @@
       <c r="T623" s="9"/>
       <c r="U623" s="9"/>
     </row>
-    <row r="624" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A624" s="9"/>
       <c r="B624" s="55"/>
       <c r="C624" s="55"/>
@@ -18832,7 +18827,7 @@
       <c r="T624" s="9"/>
       <c r="U624" s="9"/>
     </row>
-    <row r="625" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A625" s="9"/>
       <c r="B625" s="55"/>
       <c r="C625" s="55"/>
@@ -18855,7 +18850,7 @@
       <c r="T625" s="9"/>
       <c r="U625" s="9"/>
     </row>
-    <row r="626" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A626" s="9"/>
       <c r="B626" s="55"/>
       <c r="C626" s="55"/>
@@ -18878,7 +18873,7 @@
       <c r="T626" s="9"/>
       <c r="U626" s="9"/>
     </row>
-    <row r="627" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A627" s="9"/>
       <c r="B627" s="55"/>
       <c r="C627" s="55"/>
@@ -18901,7 +18896,7 @@
       <c r="T627" s="9"/>
       <c r="U627" s="9"/>
     </row>
-    <row r="628" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A628" s="9"/>
       <c r="B628" s="55"/>
       <c r="C628" s="55"/>
@@ -18924,7 +18919,7 @@
       <c r="T628" s="9"/>
       <c r="U628" s="9"/>
     </row>
-    <row r="629" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A629" s="9"/>
       <c r="B629" s="55"/>
       <c r="C629" s="55"/>
@@ -18947,7 +18942,7 @@
       <c r="T629" s="9"/>
       <c r="U629" s="9"/>
     </row>
-    <row r="630" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A630" s="9"/>
       <c r="B630" s="55"/>
       <c r="C630" s="55"/>
@@ -18970,7 +18965,7 @@
       <c r="T630" s="9"/>
       <c r="U630" s="9"/>
     </row>
-    <row r="631" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A631" s="9"/>
       <c r="B631" s="55"/>
       <c r="C631" s="55"/>
@@ -18993,7 +18988,7 @@
       <c r="T631" s="9"/>
       <c r="U631" s="9"/>
     </row>
-    <row r="632" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A632" s="9"/>
       <c r="B632" s="55"/>
       <c r="C632" s="55"/>
@@ -19016,7 +19011,7 @@
       <c r="T632" s="9"/>
       <c r="U632" s="9"/>
     </row>
-    <row r="633" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A633" s="9"/>
       <c r="B633" s="55"/>
       <c r="C633" s="55"/>
@@ -19039,7 +19034,7 @@
       <c r="T633" s="9"/>
       <c r="U633" s="9"/>
     </row>
-    <row r="634" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A634" s="9"/>
       <c r="B634" s="55"/>
       <c r="C634" s="55"/>
@@ -19062,7 +19057,7 @@
       <c r="T634" s="9"/>
       <c r="U634" s="9"/>
     </row>
-    <row r="635" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A635" s="9"/>
       <c r="B635" s="55"/>
       <c r="C635" s="55"/>
@@ -19085,7 +19080,7 @@
       <c r="T635" s="9"/>
       <c r="U635" s="9"/>
     </row>
-    <row r="636" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A636" s="9"/>
       <c r="B636" s="55"/>
       <c r="C636" s="55"/>
@@ -19108,7 +19103,7 @@
       <c r="T636" s="9"/>
       <c r="U636" s="9"/>
     </row>
-    <row r="637" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A637" s="9"/>
       <c r="B637" s="55"/>
       <c r="C637" s="55"/>
@@ -19131,7 +19126,7 @@
       <c r="T637" s="9"/>
       <c r="U637" s="9"/>
     </row>
-    <row r="638" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A638" s="9"/>
       <c r="B638" s="55"/>
       <c r="C638" s="55"/>
@@ -19154,7 +19149,7 @@
       <c r="T638" s="9"/>
       <c r="U638" s="9"/>
     </row>
-    <row r="639" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A639" s="9"/>
       <c r="B639" s="55"/>
       <c r="C639" s="55"/>
@@ -19177,7 +19172,7 @@
       <c r="T639" s="9"/>
       <c r="U639" s="9"/>
     </row>
-    <row r="640" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A640" s="9"/>
       <c r="B640" s="55"/>
       <c r="C640" s="55"/>
@@ -19200,7 +19195,7 @@
       <c r="T640" s="9"/>
       <c r="U640" s="9"/>
     </row>
-    <row r="641" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A641" s="9"/>
       <c r="B641" s="55"/>
       <c r="C641" s="55"/>
@@ -19223,7 +19218,7 @@
       <c r="T641" s="9"/>
       <c r="U641" s="9"/>
     </row>
-    <row r="642" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A642" s="9"/>
       <c r="B642" s="55"/>
       <c r="C642" s="55"/>
@@ -19246,7 +19241,7 @@
       <c r="T642" s="9"/>
       <c r="U642" s="9"/>
     </row>
-    <row r="643" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A643" s="9"/>
       <c r="B643" s="55"/>
       <c r="C643" s="55"/>
@@ -19269,7 +19264,7 @@
       <c r="T643" s="9"/>
       <c r="U643" s="9"/>
     </row>
-    <row r="644" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A644" s="9"/>
       <c r="B644" s="55"/>
       <c r="C644" s="55"/>
@@ -19292,7 +19287,7 @@
       <c r="T644" s="9"/>
       <c r="U644" s="9"/>
     </row>
-    <row r="645" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A645" s="9"/>
       <c r="B645" s="55"/>
       <c r="C645" s="55"/>
@@ -19315,7 +19310,7 @@
       <c r="T645" s="9"/>
       <c r="U645" s="9"/>
     </row>
-    <row r="646" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A646" s="9"/>
       <c r="B646" s="55"/>
       <c r="C646" s="55"/>
@@ -19338,7 +19333,7 @@
       <c r="T646" s="9"/>
       <c r="U646" s="9"/>
     </row>
-    <row r="647" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A647" s="9"/>
       <c r="B647" s="55"/>
       <c r="C647" s="55"/>
@@ -19361,7 +19356,7 @@
       <c r="T647" s="9"/>
       <c r="U647" s="9"/>
     </row>
-    <row r="648" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A648" s="9"/>
       <c r="B648" s="55"/>
       <c r="C648" s="55"/>
@@ -19384,7 +19379,7 @@
       <c r="T648" s="9"/>
       <c r="U648" s="9"/>
     </row>
-    <row r="649" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A649" s="9"/>
       <c r="B649" s="55"/>
       <c r="C649" s="55"/>
@@ -19407,7 +19402,7 @@
       <c r="T649" s="9"/>
       <c r="U649" s="9"/>
     </row>
-    <row r="650" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A650" s="9"/>
       <c r="B650" s="55"/>
       <c r="C650" s="55"/>
@@ -19430,7 +19425,7 @@
       <c r="T650" s="9"/>
       <c r="U650" s="9"/>
     </row>
-    <row r="651" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A651" s="9"/>
       <c r="B651" s="55"/>
       <c r="C651" s="55"/>
@@ -19453,7 +19448,7 @@
       <c r="T651" s="9"/>
       <c r="U651" s="9"/>
     </row>
-    <row r="652" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A652" s="9"/>
       <c r="B652" s="55"/>
       <c r="C652" s="55"/>
@@ -19476,7 +19471,7 @@
       <c r="T652" s="9"/>
       <c r="U652" s="9"/>
     </row>
-    <row r="653" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A653" s="9"/>
       <c r="B653" s="55"/>
       <c r="C653" s="55"/>
@@ -19499,7 +19494,7 @@
       <c r="T653" s="9"/>
       <c r="U653" s="9"/>
     </row>
-    <row r="654" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A654" s="9"/>
       <c r="B654" s="55"/>
       <c r="C654" s="55"/>
@@ -19522,7 +19517,7 @@
       <c r="T654" s="9"/>
       <c r="U654" s="9"/>
     </row>
-    <row r="655" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A655" s="9"/>
       <c r="B655" s="55"/>
       <c r="C655" s="55"/>
@@ -19545,7 +19540,7 @@
       <c r="T655" s="9"/>
       <c r="U655" s="9"/>
     </row>
-    <row r="656" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A656" s="9"/>
       <c r="B656" s="55"/>
       <c r="C656" s="55"/>
@@ -19568,7 +19563,7 @@
       <c r="T656" s="9"/>
       <c r="U656" s="9"/>
     </row>
-    <row r="657" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A657" s="9"/>
       <c r="B657" s="55"/>
       <c r="C657" s="55"/>
@@ -19591,7 +19586,7 @@
       <c r="T657" s="9"/>
       <c r="U657" s="9"/>
     </row>
-    <row r="658" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A658" s="9"/>
       <c r="B658" s="55"/>
       <c r="C658" s="55"/>
@@ -19614,7 +19609,7 @@
       <c r="T658" s="9"/>
       <c r="U658" s="9"/>
     </row>
-    <row r="659" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A659" s="9"/>
       <c r="B659" s="55"/>
       <c r="C659" s="55"/>
@@ -19637,7 +19632,7 @@
       <c r="T659" s="9"/>
       <c r="U659" s="9"/>
     </row>
-    <row r="660" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A660" s="9"/>
       <c r="B660" s="55"/>
       <c r="C660" s="55"/>
@@ -19660,7 +19655,7 @@
       <c r="T660" s="9"/>
       <c r="U660" s="9"/>
     </row>
-    <row r="661" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A661" s="9"/>
       <c r="B661" s="55"/>
       <c r="C661" s="55"/>
@@ -19683,7 +19678,7 @@
       <c r="T661" s="9"/>
       <c r="U661" s="9"/>
     </row>
-    <row r="662" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A662" s="9"/>
       <c r="B662" s="55"/>
       <c r="C662" s="55"/>
@@ -19706,7 +19701,7 @@
       <c r="T662" s="9"/>
       <c r="U662" s="9"/>
     </row>
-    <row r="663" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A663" s="9"/>
       <c r="B663" s="55"/>
       <c r="C663" s="55"/>
@@ -19729,7 +19724,7 @@
       <c r="T663" s="9"/>
       <c r="U663" s="9"/>
     </row>
-    <row r="664" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A664" s="9"/>
       <c r="B664" s="55"/>
       <c r="C664" s="55"/>
@@ -19752,7 +19747,7 @@
       <c r="T664" s="9"/>
       <c r="U664" s="9"/>
     </row>
-    <row r="665" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A665" s="9"/>
       <c r="B665" s="55"/>
       <c r="C665" s="55"/>
@@ -19775,7 +19770,7 @@
       <c r="T665" s="9"/>
       <c r="U665" s="9"/>
     </row>
-    <row r="666" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A666" s="9"/>
       <c r="B666" s="55"/>
       <c r="C666" s="55"/>
@@ -19798,7 +19793,7 @@
       <c r="T666" s="9"/>
       <c r="U666" s="9"/>
     </row>
-    <row r="667" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A667" s="9"/>
       <c r="B667" s="55"/>
       <c r="C667" s="55"/>
@@ -19821,7 +19816,7 @@
       <c r="T667" s="9"/>
       <c r="U667" s="9"/>
     </row>
-    <row r="668" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A668" s="9"/>
       <c r="B668" s="55"/>
       <c r="C668" s="55"/>
@@ -19844,7 +19839,7 @@
       <c r="T668" s="9"/>
       <c r="U668" s="9"/>
     </row>
-    <row r="669" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A669" s="9"/>
       <c r="B669" s="55"/>
       <c r="C669" s="55"/>
@@ -19867,7 +19862,7 @@
       <c r="T669" s="9"/>
       <c r="U669" s="9"/>
     </row>
-    <row r="670" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A670" s="9"/>
       <c r="B670" s="55"/>
       <c r="C670" s="55"/>
@@ -19890,7 +19885,7 @@
       <c r="T670" s="9"/>
       <c r="U670" s="9"/>
     </row>
-    <row r="671" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A671" s="9"/>
       <c r="B671" s="55"/>
       <c r="C671" s="55"/>
@@ -19913,7 +19908,7 @@
       <c r="T671" s="9"/>
       <c r="U671" s="9"/>
     </row>
-    <row r="672" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A672" s="9"/>
       <c r="B672" s="55"/>
       <c r="C672" s="55"/>
@@ -19936,7 +19931,7 @@
       <c r="T672" s="9"/>
       <c r="U672" s="9"/>
     </row>
-    <row r="673" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A673" s="9"/>
       <c r="B673" s="55"/>
       <c r="C673" s="55"/>
@@ -19959,7 +19954,7 @@
       <c r="T673" s="9"/>
       <c r="U673" s="9"/>
     </row>
-    <row r="674" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A674" s="9"/>
       <c r="B674" s="55"/>
       <c r="C674" s="55"/>
@@ -19982,7 +19977,7 @@
       <c r="T674" s="9"/>
       <c r="U674" s="9"/>
     </row>
-    <row r="675" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A675" s="9"/>
       <c r="B675" s="55"/>
       <c r="C675" s="55"/>
@@ -20005,7 +20000,7 @@
       <c r="T675" s="9"/>
       <c r="U675" s="9"/>
     </row>
-    <row r="676" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A676" s="9"/>
       <c r="B676" s="55"/>
       <c r="C676" s="55"/>
@@ -20028,7 +20023,7 @@
       <c r="T676" s="9"/>
       <c r="U676" s="9"/>
     </row>
-    <row r="677" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A677" s="9"/>
       <c r="B677" s="55"/>
       <c r="C677" s="55"/>
@@ -20051,7 +20046,7 @@
       <c r="T677" s="9"/>
       <c r="U677" s="9"/>
     </row>
-    <row r="678" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A678" s="9"/>
       <c r="B678" s="55"/>
       <c r="C678" s="55"/>
@@ -20074,7 +20069,7 @@
       <c r="T678" s="9"/>
       <c r="U678" s="9"/>
     </row>
-    <row r="679" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A679" s="9"/>
       <c r="B679" s="55"/>
       <c r="C679" s="55"/>
@@ -20097,7 +20092,7 @@
       <c r="T679" s="9"/>
       <c r="U679" s="9"/>
     </row>
-    <row r="680" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A680" s="9"/>
       <c r="B680" s="55"/>
       <c r="C680" s="55"/>
@@ -20120,7 +20115,7 @@
       <c r="T680" s="9"/>
       <c r="U680" s="9"/>
     </row>
-    <row r="681" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A681" s="9"/>
       <c r="B681" s="55"/>
       <c r="C681" s="55"/>
@@ -20143,7 +20138,7 @@
       <c r="T681" s="9"/>
       <c r="U681" s="9"/>
     </row>
-    <row r="682" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A682" s="9"/>
       <c r="B682" s="55"/>
       <c r="C682" s="55"/>
@@ -20166,7 +20161,7 @@
       <c r="T682" s="9"/>
       <c r="U682" s="9"/>
     </row>
-    <row r="683" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A683" s="9"/>
       <c r="B683" s="55"/>
       <c r="C683" s="55"/>
@@ -20189,7 +20184,7 @@
       <c r="T683" s="9"/>
       <c r="U683" s="9"/>
     </row>
-    <row r="684" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A684" s="9"/>
       <c r="B684" s="55"/>
       <c r="C684" s="55"/>
@@ -20212,7 +20207,7 @@
       <c r="T684" s="9"/>
       <c r="U684" s="9"/>
     </row>
-    <row r="685" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A685" s="9"/>
       <c r="B685" s="55"/>
       <c r="C685" s="55"/>
@@ -20235,7 +20230,7 @@
       <c r="T685" s="9"/>
       <c r="U685" s="9"/>
     </row>
-    <row r="686" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A686" s="9"/>
       <c r="B686" s="55"/>
       <c r="C686" s="55"/>
@@ -20258,7 +20253,7 @@
       <c r="T686" s="9"/>
       <c r="U686" s="9"/>
     </row>
-    <row r="687" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A687" s="9"/>
       <c r="B687" s="55"/>
       <c r="C687" s="55"/>
@@ -20281,7 +20276,7 @@
       <c r="T687" s="9"/>
       <c r="U687" s="9"/>
     </row>
-    <row r="688" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A688" s="9"/>
       <c r="B688" s="55"/>
       <c r="C688" s="55"/>
@@ -20304,7 +20299,7 @@
       <c r="T688" s="9"/>
       <c r="U688" s="9"/>
     </row>
-    <row r="689" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A689" s="9"/>
       <c r="B689" s="55"/>
       <c r="C689" s="55"/>
@@ -20327,7 +20322,7 @@
       <c r="T689" s="9"/>
       <c r="U689" s="9"/>
     </row>
-    <row r="690" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A690" s="9"/>
       <c r="B690" s="55"/>
       <c r="C690" s="55"/>
@@ -20350,7 +20345,7 @@
       <c r="T690" s="9"/>
       <c r="U690" s="9"/>
     </row>
-    <row r="691" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A691" s="9"/>
       <c r="B691" s="55"/>
       <c r="C691" s="55"/>
@@ -20373,7 +20368,7 @@
       <c r="T691" s="9"/>
       <c r="U691" s="9"/>
     </row>
-    <row r="692" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A692" s="9"/>
       <c r="B692" s="55"/>
       <c r="C692" s="55"/>
@@ -20396,7 +20391,7 @@
       <c r="T692" s="9"/>
       <c r="U692" s="9"/>
     </row>
-    <row r="693" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A693" s="9"/>
       <c r="B693" s="55"/>
       <c r="C693" s="55"/>
@@ -20419,7 +20414,7 @@
       <c r="T693" s="9"/>
       <c r="U693" s="9"/>
     </row>
-    <row r="694" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A694" s="9"/>
       <c r="B694" s="55"/>
       <c r="C694" s="55"/>
@@ -20442,7 +20437,7 @@
       <c r="T694" s="9"/>
       <c r="U694" s="9"/>
     </row>
-    <row r="695" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A695" s="9"/>
       <c r="B695" s="55"/>
       <c r="C695" s="55"/>
@@ -20465,7 +20460,7 @@
       <c r="T695" s="9"/>
       <c r="U695" s="9"/>
     </row>
-    <row r="696" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A696" s="9"/>
       <c r="B696" s="55"/>
       <c r="C696" s="55"/>
@@ -20488,7 +20483,7 @@
       <c r="T696" s="9"/>
       <c r="U696" s="9"/>
     </row>
-    <row r="697" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A697" s="9"/>
       <c r="B697" s="55"/>
       <c r="C697" s="55"/>
@@ -20511,7 +20506,7 @@
       <c r="T697" s="9"/>
       <c r="U697" s="9"/>
     </row>
-    <row r="698" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A698" s="9"/>
       <c r="B698" s="55"/>
       <c r="C698" s="55"/>
@@ -20534,7 +20529,7 @@
       <c r="T698" s="9"/>
       <c r="U698" s="9"/>
     </row>
-    <row r="699" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A699" s="9"/>
       <c r="B699" s="55"/>
       <c r="C699" s="55"/>
@@ -20557,7 +20552,7 @@
       <c r="T699" s="9"/>
       <c r="U699" s="9"/>
     </row>
-    <row r="700" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A700" s="9"/>
       <c r="B700" s="55"/>
       <c r="C700" s="55"/>
@@ -20580,7 +20575,7 @@
       <c r="T700" s="9"/>
       <c r="U700" s="9"/>
     </row>
-    <row r="701" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A701" s="9"/>
       <c r="B701" s="55"/>
       <c r="C701" s="55"/>
@@ -20603,7 +20598,7 @@
       <c r="T701" s="9"/>
       <c r="U701" s="9"/>
     </row>
-    <row r="702" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A702" s="9"/>
       <c r="B702" s="55"/>
       <c r="C702" s="55"/>
@@ -20626,7 +20621,7 @@
       <c r="T702" s="9"/>
       <c r="U702" s="9"/>
     </row>
-    <row r="703" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A703" s="9"/>
       <c r="B703" s="55"/>
       <c r="C703" s="55"/>
@@ -20649,7 +20644,7 @@
       <c r="T703" s="9"/>
       <c r="U703" s="9"/>
     </row>
-    <row r="704" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A704" s="9"/>
       <c r="B704" s="55"/>
       <c r="C704" s="55"/>
@@ -20672,7 +20667,7 @@
       <c r="T704" s="9"/>
       <c r="U704" s="9"/>
     </row>
-    <row r="705" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A705" s="9"/>
       <c r="B705" s="55"/>
       <c r="C705" s="55"/>
@@ -20695,7 +20690,7 @@
       <c r="T705" s="9"/>
       <c r="U705" s="9"/>
     </row>
-    <row r="706" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A706" s="9"/>
       <c r="B706" s="55"/>
       <c r="C706" s="55"/>
@@ -20718,7 +20713,7 @@
       <c r="T706" s="9"/>
       <c r="U706" s="9"/>
     </row>
-    <row r="707" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A707" s="9"/>
       <c r="B707" s="55"/>
       <c r="C707" s="55"/>
@@ -20741,7 +20736,7 @@
       <c r="T707" s="9"/>
       <c r="U707" s="9"/>
     </row>
-    <row r="708" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A708" s="9"/>
       <c r="B708" s="55"/>
       <c r="C708" s="55"/>
@@ -20764,7 +20759,7 @@
       <c r="T708" s="9"/>
       <c r="U708" s="9"/>
     </row>
-    <row r="709" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A709" s="9"/>
       <c r="B709" s="55"/>
       <c r="C709" s="55"/>
@@ -20787,7 +20782,7 @@
       <c r="T709" s="9"/>
       <c r="U709" s="9"/>
     </row>
-    <row r="710" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A710" s="9"/>
       <c r="B710" s="55"/>
       <c r="C710" s="55"/>
@@ -20810,7 +20805,7 @@
       <c r="T710" s="9"/>
       <c r="U710" s="9"/>
     </row>
-    <row r="711" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A711" s="9"/>
       <c r="B711" s="55"/>
       <c r="C711" s="55"/>
@@ -20833,7 +20828,7 @@
       <c r="T711" s="9"/>
       <c r="U711" s="9"/>
     </row>
-    <row r="712" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A712" s="9"/>
       <c r="B712" s="55"/>
       <c r="C712" s="55"/>
@@ -20856,7 +20851,7 @@
       <c r="T712" s="9"/>
       <c r="U712" s="9"/>
     </row>
-    <row r="713" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A713" s="9"/>
       <c r="B713" s="55"/>
       <c r="C713" s="55"/>
@@ -20879,7 +20874,7 @@
       <c r="T713" s="9"/>
       <c r="U713" s="9"/>
     </row>
-    <row r="714" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A714" s="9"/>
       <c r="B714" s="55"/>
       <c r="C714" s="55"/>
@@ -20902,7 +20897,7 @@
       <c r="T714" s="9"/>
       <c r="U714" s="9"/>
     </row>
-    <row r="715" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A715" s="9"/>
       <c r="B715" s="55"/>
       <c r="C715" s="55"/>
@@ -20925,7 +20920,7 @@
       <c r="T715" s="9"/>
       <c r="U715" s="9"/>
     </row>
-    <row r="716" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A716" s="9"/>
       <c r="B716" s="55"/>
       <c r="C716" s="55"/>
@@ -20948,7 +20943,7 @@
       <c r="T716" s="9"/>
       <c r="U716" s="9"/>
     </row>
-    <row r="717" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A717" s="9"/>
       <c r="B717" s="55"/>
       <c r="C717" s="55"/>
@@ -20971,7 +20966,7 @@
       <c r="T717" s="9"/>
       <c r="U717" s="9"/>
     </row>
-    <row r="718" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A718" s="9"/>
       <c r="B718" s="55"/>
       <c r="C718" s="55"/>
@@ -20994,7 +20989,7 @@
       <c r="T718" s="9"/>
       <c r="U718" s="9"/>
     </row>
-    <row r="719" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A719" s="9"/>
       <c r="B719" s="55"/>
       <c r="C719" s="55"/>
@@ -21017,7 +21012,7 @@
       <c r="T719" s="9"/>
       <c r="U719" s="9"/>
     </row>
-    <row r="720" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A720" s="9"/>
       <c r="B720" s="55"/>
       <c r="C720" s="55"/>
@@ -21040,7 +21035,7 @@
       <c r="T720" s="9"/>
       <c r="U720" s="9"/>
     </row>
-    <row r="721" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A721" s="9"/>
       <c r="B721" s="55"/>
       <c r="C721" s="55"/>
@@ -21063,7 +21058,7 @@
       <c r="T721" s="9"/>
       <c r="U721" s="9"/>
     </row>
-    <row r="722" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A722" s="9"/>
       <c r="B722" s="55"/>
       <c r="C722" s="55"/>
@@ -21086,7 +21081,7 @@
       <c r="T722" s="9"/>
       <c r="U722" s="9"/>
     </row>
-    <row r="723" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A723" s="9"/>
       <c r="B723" s="55"/>
       <c r="C723" s="55"/>
@@ -21109,7 +21104,7 @@
       <c r="T723" s="9"/>
       <c r="U723" s="9"/>
     </row>
-    <row r="724" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A724" s="9"/>
       <c r="B724" s="55"/>
       <c r="C724" s="55"/>
@@ -21132,7 +21127,7 @@
       <c r="T724" s="9"/>
       <c r="U724" s="9"/>
     </row>
-    <row r="725" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A725" s="9"/>
       <c r="B725" s="55"/>
       <c r="C725" s="55"/>
@@ -21155,7 +21150,7 @@
       <c r="T725" s="9"/>
       <c r="U725" s="9"/>
     </row>
-    <row r="726" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A726" s="9"/>
       <c r="B726" s="55"/>
       <c r="C726" s="55"/>
@@ -21178,7 +21173,7 @@
       <c r="T726" s="9"/>
       <c r="U726" s="9"/>
     </row>
-    <row r="727" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A727" s="9"/>
       <c r="B727" s="55"/>
       <c r="C727" s="55"/>
@@ -21201,7 +21196,7 @@
       <c r="T727" s="9"/>
       <c r="U727" s="9"/>
     </row>
-    <row r="728" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A728" s="9"/>
       <c r="B728" s="55"/>
       <c r="C728" s="55"/>
@@ -21224,7 +21219,7 @@
       <c r="T728" s="9"/>
       <c r="U728" s="9"/>
     </row>
-    <row r="729" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A729" s="9"/>
       <c r="B729" s="55"/>
       <c r="C729" s="55"/>
@@ -21247,7 +21242,7 @@
       <c r="T729" s="9"/>
       <c r="U729" s="9"/>
     </row>
-    <row r="730" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A730" s="9"/>
       <c r="B730" s="55"/>
       <c r="C730" s="55"/>
@@ -21270,7 +21265,7 @@
       <c r="T730" s="9"/>
       <c r="U730" s="9"/>
     </row>
-    <row r="731" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A731" s="9"/>
       <c r="B731" s="55"/>
       <c r="C731" s="55"/>
@@ -21293,7 +21288,7 @@
       <c r="T731" s="9"/>
       <c r="U731" s="9"/>
     </row>
-    <row r="732" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A732" s="9"/>
       <c r="B732" s="55"/>
       <c r="C732" s="55"/>
@@ -21316,7 +21311,7 @@
       <c r="T732" s="9"/>
       <c r="U732" s="9"/>
     </row>
-    <row r="733" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A733" s="9"/>
       <c r="B733" s="55"/>
       <c r="C733" s="55"/>
@@ -21339,7 +21334,7 @@
       <c r="T733" s="9"/>
       <c r="U733" s="9"/>
     </row>
-    <row r="734" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A734" s="9"/>
       <c r="B734" s="55"/>
       <c r="C734" s="55"/>
@@ -21362,7 +21357,7 @@
       <c r="T734" s="9"/>
       <c r="U734" s="9"/>
     </row>
-    <row r="735" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A735" s="9"/>
       <c r="B735" s="55"/>
       <c r="C735" s="55"/>
@@ -21385,7 +21380,7 @@
       <c r="T735" s="9"/>
       <c r="U735" s="9"/>
     </row>
-    <row r="736" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A736" s="9"/>
       <c r="B736" s="55"/>
       <c r="C736" s="55"/>
@@ -21408,7 +21403,7 @@
       <c r="T736" s="9"/>
       <c r="U736" s="9"/>
     </row>
-    <row r="737" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A737" s="9"/>
       <c r="B737" s="55"/>
       <c r="C737" s="55"/>
@@ -21431,7 +21426,7 @@
       <c r="T737" s="9"/>
       <c r="U737" s="9"/>
     </row>
-    <row r="738" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A738" s="9"/>
       <c r="B738" s="55"/>
       <c r="C738" s="55"/>
@@ -21454,7 +21449,7 @@
       <c r="T738" s="9"/>
       <c r="U738" s="9"/>
     </row>
-    <row r="739" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A739" s="9"/>
       <c r="B739" s="55"/>
       <c r="C739" s="55"/>
@@ -21477,7 +21472,7 @@
       <c r="T739" s="9"/>
       <c r="U739" s="9"/>
     </row>
-    <row r="740" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A740" s="9"/>
       <c r="B740" s="55"/>
       <c r="C740" s="55"/>
@@ -21500,7 +21495,7 @@
       <c r="T740" s="9"/>
       <c r="U740" s="9"/>
     </row>
-    <row r="741" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A741" s="9"/>
       <c r="B741" s="55"/>
       <c r="C741" s="55"/>
@@ -21523,7 +21518,7 @@
       <c r="T741" s="9"/>
       <c r="U741" s="9"/>
     </row>
-    <row r="742" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A742" s="9"/>
       <c r="B742" s="55"/>
       <c r="C742" s="55"/>
@@ -21546,7 +21541,7 @@
       <c r="T742" s="9"/>
       <c r="U742" s="9"/>
     </row>
-    <row r="743" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A743" s="9"/>
       <c r="B743" s="55"/>
       <c r="C743" s="55"/>
@@ -21569,7 +21564,7 @@
       <c r="T743" s="9"/>
       <c r="U743" s="9"/>
     </row>
-    <row r="744" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A744" s="9"/>
       <c r="B744" s="55"/>
       <c r="C744" s="55"/>
@@ -21592,7 +21587,7 @@
       <c r="T744" s="9"/>
       <c r="U744" s="9"/>
     </row>
-    <row r="745" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A745" s="9"/>
       <c r="B745" s="55"/>
       <c r="C745" s="55"/>
@@ -21615,7 +21610,7 @@
       <c r="T745" s="9"/>
       <c r="U745" s="9"/>
     </row>
-    <row r="746" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A746" s="9"/>
       <c r="B746" s="55"/>
       <c r="C746" s="55"/>
@@ -21638,7 +21633,7 @@
       <c r="T746" s="9"/>
       <c r="U746" s="9"/>
     </row>
-    <row r="747" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A747" s="9"/>
       <c r="B747" s="55"/>
       <c r="C747" s="55"/>
@@ -21661,7 +21656,7 @@
       <c r="T747" s="9"/>
       <c r="U747" s="9"/>
     </row>
-    <row r="748" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A748" s="9"/>
       <c r="B748" s="55"/>
       <c r="C748" s="55"/>
@@ -21684,7 +21679,7 @@
       <c r="T748" s="9"/>
       <c r="U748" s="9"/>
     </row>
-    <row r="749" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A749" s="9"/>
       <c r="B749" s="55"/>
       <c r="C749" s="55"/>
@@ -21707,7 +21702,7 @@
       <c r="T749" s="9"/>
       <c r="U749" s="9"/>
     </row>
-    <row r="750" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A750" s="9"/>
       <c r="B750" s="55"/>
       <c r="C750" s="55"/>
@@ -21730,7 +21725,7 @@
       <c r="T750" s="9"/>
       <c r="U750" s="9"/>
     </row>
-    <row r="751" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A751" s="9"/>
       <c r="B751" s="55"/>
       <c r="C751" s="55"/>
@@ -21753,7 +21748,7 @@
       <c r="T751" s="9"/>
       <c r="U751" s="9"/>
     </row>
-    <row r="752" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A752" s="9"/>
       <c r="B752" s="55"/>
       <c r="C752" s="55"/>
@@ -21776,7 +21771,7 @@
       <c r="T752" s="9"/>
       <c r="U752" s="9"/>
     </row>
-    <row r="753" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A753" s="9"/>
       <c r="B753" s="55"/>
       <c r="C753" s="55"/>
@@ -21799,7 +21794,7 @@
       <c r="T753" s="9"/>
       <c r="U753" s="9"/>
     </row>
-    <row r="754" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A754" s="9"/>
       <c r="B754" s="55"/>
       <c r="C754" s="55"/>
@@ -21822,7 +21817,7 @@
       <c r="T754" s="9"/>
       <c r="U754" s="9"/>
     </row>
-    <row r="755" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A755" s="9"/>
       <c r="B755" s="55"/>
       <c r="C755" s="55"/>
@@ -21845,7 +21840,7 @@
       <c r="T755" s="9"/>
       <c r="U755" s="9"/>
     </row>
-    <row r="756" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A756" s="9"/>
       <c r="B756" s="55"/>
       <c r="C756" s="55"/>
@@ -21868,7 +21863,7 @@
       <c r="T756" s="9"/>
       <c r="U756" s="9"/>
     </row>
-    <row r="757" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A757" s="9"/>
       <c r="B757" s="55"/>
       <c r="C757" s="55"/>
@@ -21891,7 +21886,7 @@
       <c r="T757" s="9"/>
       <c r="U757" s="9"/>
     </row>
-    <row r="758" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A758" s="9"/>
       <c r="B758" s="55"/>
       <c r="C758" s="55"/>
@@ -21914,7 +21909,7 @@
       <c r="T758" s="9"/>
       <c r="U758" s="9"/>
     </row>
-    <row r="759" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A759" s="9"/>
       <c r="B759" s="55"/>
       <c r="C759" s="55"/>
@@ -21937,7 +21932,7 @@
       <c r="T759" s="9"/>
       <c r="U759" s="9"/>
     </row>
-    <row r="760" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A760" s="9"/>
       <c r="B760" s="55"/>
       <c r="C760" s="55"/>
@@ -21960,7 +21955,7 @@
       <c r="T760" s="9"/>
       <c r="U760" s="9"/>
     </row>
-    <row r="761" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A761" s="9"/>
       <c r="B761" s="55"/>
       <c r="C761" s="55"/>
@@ -21983,7 +21978,7 @@
       <c r="T761" s="9"/>
       <c r="U761" s="9"/>
     </row>
-    <row r="762" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A762" s="9"/>
       <c r="B762" s="55"/>
       <c r="C762" s="55"/>
@@ -22006,7 +22001,7 @@
       <c r="T762" s="9"/>
       <c r="U762" s="9"/>
     </row>
-    <row r="763" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A763" s="9"/>
       <c r="B763" s="55"/>
       <c r="C763" s="55"/>
@@ -22029,7 +22024,7 @@
       <c r="T763" s="9"/>
       <c r="U763" s="9"/>
     </row>
-    <row r="764" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A764" s="9"/>
       <c r="B764" s="55"/>
       <c r="C764" s="55"/>
@@ -22052,7 +22047,7 @@
       <c r="T764" s="9"/>
       <c r="U764" s="9"/>
     </row>
-    <row r="765" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A765" s="9"/>
       <c r="B765" s="55"/>
       <c r="C765" s="55"/>
@@ -22075,7 +22070,7 @@
       <c r="T765" s="9"/>
       <c r="U765" s="9"/>
     </row>
-    <row r="766" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A766" s="9"/>
       <c r="B766" s="55"/>
       <c r="C766" s="55"/>
@@ -22098,7 +22093,7 @@
       <c r="T766" s="9"/>
       <c r="U766" s="9"/>
     </row>
-    <row r="767" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A767" s="9"/>
       <c r="B767" s="55"/>
       <c r="C767" s="55"/>
@@ -22121,7 +22116,7 @@
       <c r="T767" s="9"/>
       <c r="U767" s="9"/>
     </row>
-    <row r="768" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A768" s="9"/>
       <c r="B768" s="55"/>
       <c r="C768" s="55"/>
@@ -22144,7 +22139,7 @@
       <c r="T768" s="9"/>
       <c r="U768" s="9"/>
     </row>
-    <row r="769" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A769" s="9"/>
       <c r="B769" s="55"/>
       <c r="C769" s="55"/>
@@ -22167,7 +22162,7 @@
       <c r="T769" s="9"/>
       <c r="U769" s="9"/>
     </row>
-    <row r="770" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A770" s="9"/>
       <c r="B770" s="55"/>
       <c r="C770" s="55"/>
@@ -22190,7 +22185,7 @@
       <c r="T770" s="9"/>
       <c r="U770" s="9"/>
     </row>
-    <row r="771" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A771" s="9"/>
       <c r="B771" s="55"/>
       <c r="C771" s="55"/>
@@ -22213,7 +22208,7 @@
       <c r="T771" s="9"/>
       <c r="U771" s="9"/>
     </row>
-    <row r="772" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A772" s="9"/>
       <c r="B772" s="55"/>
       <c r="C772" s="55"/>
@@ -22236,7 +22231,7 @@
       <c r="T772" s="9"/>
       <c r="U772" s="9"/>
     </row>
-    <row r="773" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A773" s="9"/>
       <c r="B773" s="55"/>
       <c r="C773" s="55"/>
@@ -22259,7 +22254,7 @@
       <c r="T773" s="9"/>
       <c r="U773" s="9"/>
     </row>
-    <row r="774" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A774" s="9"/>
       <c r="B774" s="55"/>
       <c r="C774" s="55"/>
@@ -22282,7 +22277,7 @@
       <c r="T774" s="9"/>
       <c r="U774" s="9"/>
     </row>
-    <row r="775" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A775" s="9"/>
       <c r="B775" s="55"/>
       <c r="C775" s="55"/>
@@ -22305,7 +22300,7 @@
       <c r="T775" s="9"/>
       <c r="U775" s="9"/>
     </row>
-    <row r="776" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A776" s="9"/>
       <c r="B776" s="55"/>
       <c r="C776" s="55"/>
@@ -22328,7 +22323,7 @@
       <c r="T776" s="9"/>
       <c r="U776" s="9"/>
     </row>
-    <row r="777" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A777" s="9"/>
       <c r="B777" s="55"/>
       <c r="C777" s="55"/>
@@ -22351,7 +22346,7 @@
       <c r="T777" s="9"/>
       <c r="U777" s="9"/>
     </row>
-    <row r="778" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A778" s="9"/>
       <c r="B778" s="55"/>
       <c r="C778" s="55"/>
@@ -22374,7 +22369,7 @@
       <c r="T778" s="9"/>
       <c r="U778" s="9"/>
     </row>
-    <row r="779" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A779" s="9"/>
       <c r="B779" s="55"/>
       <c r="C779" s="55"/>
@@ -22397,7 +22392,7 @@
       <c r="T779" s="9"/>
       <c r="U779" s="9"/>
     </row>
-    <row r="780" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A780" s="9"/>
       <c r="B780" s="55"/>
       <c r="C780" s="55"/>
@@ -22420,7 +22415,7 @@
       <c r="T780" s="9"/>
       <c r="U780" s="9"/>
     </row>
-    <row r="781" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A781" s="9"/>
       <c r="B781" s="55"/>
       <c r="C781" s="55"/>
@@ -22443,7 +22438,7 @@
       <c r="T781" s="9"/>
       <c r="U781" s="9"/>
     </row>
-    <row r="782" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A782" s="9"/>
       <c r="B782" s="55"/>
       <c r="C782" s="55"/>
@@ -22466,7 +22461,7 @@
       <c r="T782" s="9"/>
       <c r="U782" s="9"/>
     </row>
-    <row r="783" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A783" s="9"/>
       <c r="B783" s="55"/>
       <c r="C783" s="55"/>
@@ -22489,7 +22484,7 @@
       <c r="T783" s="9"/>
       <c r="U783" s="9"/>
     </row>
-    <row r="784" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A784" s="9"/>
       <c r="B784" s="55"/>
       <c r="C784" s="55"/>
@@ -22512,7 +22507,7 @@
       <c r="T784" s="9"/>
       <c r="U784" s="9"/>
     </row>
-    <row r="785" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A785" s="9"/>
       <c r="B785" s="55"/>
       <c r="C785" s="55"/>
@@ -22535,7 +22530,7 @@
       <c r="T785" s="9"/>
       <c r="U785" s="9"/>
     </row>
-    <row r="786" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A786" s="9"/>
       <c r="B786" s="55"/>
       <c r="C786" s="55"/>
@@ -22558,7 +22553,7 @@
       <c r="T786" s="9"/>
       <c r="U786" s="9"/>
     </row>
-    <row r="787" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A787" s="9"/>
       <c r="B787" s="55"/>
       <c r="C787" s="55"/>
@@ -22581,7 +22576,7 @@
       <c r="T787" s="9"/>
       <c r="U787" s="9"/>
     </row>
-    <row r="788" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A788" s="9"/>
       <c r="B788" s="55"/>
       <c r="C788" s="55"/>
@@ -22604,7 +22599,7 @@
       <c r="T788" s="9"/>
       <c r="U788" s="9"/>
     </row>
-    <row r="789" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A789" s="9"/>
       <c r="B789" s="55"/>
       <c r="C789" s="55"/>
@@ -22627,7 +22622,7 @@
       <c r="T789" s="9"/>
       <c r="U789" s="9"/>
     </row>
-    <row r="790" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A790" s="9"/>
       <c r="B790" s="55"/>
       <c r="C790" s="55"/>
@@ -22650,7 +22645,7 @@
       <c r="T790" s="9"/>
       <c r="U790" s="9"/>
     </row>
-    <row r="791" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A791" s="9"/>
       <c r="B791" s="55"/>
       <c r="C791" s="55"/>
@@ -22673,7 +22668,7 @@
       <c r="T791" s="9"/>
       <c r="U791" s="9"/>
     </row>
-    <row r="792" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A792" s="9"/>
       <c r="B792" s="55"/>
       <c r="C792" s="55"/>
@@ -22696,7 +22691,7 @@
       <c r="T792" s="9"/>
       <c r="U792" s="9"/>
     </row>
-    <row r="793" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A793" s="9"/>
       <c r="B793" s="55"/>
       <c r="C793" s="55"/>
@@ -22719,7 +22714,7 @@
       <c r="T793" s="9"/>
       <c r="U793" s="9"/>
     </row>
-    <row r="794" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A794" s="9"/>
       <c r="B794" s="55"/>
       <c r="C794" s="55"/>
@@ -22742,7 +22737,7 @@
       <c r="T794" s="9"/>
       <c r="U794" s="9"/>
     </row>
-    <row r="795" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A795" s="9"/>
       <c r="B795" s="55"/>
       <c r="C795" s="55"/>
@@ -22765,7 +22760,7 @@
       <c r="T795" s="9"/>
       <c r="U795" s="9"/>
     </row>
-    <row r="796" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A796" s="9"/>
       <c r="B796" s="55"/>
       <c r="C796" s="55"/>
@@ -22788,7 +22783,7 @@
       <c r="T796" s="9"/>
       <c r="U796" s="9"/>
     </row>
-    <row r="797" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A797" s="9"/>
       <c r="B797" s="55"/>
       <c r="C797" s="55"/>
@@ -22811,7 +22806,7 @@
       <c r="T797" s="9"/>
       <c r="U797" s="9"/>
     </row>
-    <row r="798" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A798" s="9"/>
       <c r="B798" s="55"/>
       <c r="C798" s="55"/>
@@ -22834,7 +22829,7 @@
       <c r="T798" s="9"/>
       <c r="U798" s="9"/>
     </row>
-    <row r="799" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A799" s="9"/>
       <c r="B799" s="55"/>
       <c r="C799" s="55"/>
@@ -22857,7 +22852,7 @@
       <c r="T799" s="9"/>
       <c r="U799" s="9"/>
     </row>
-    <row r="800" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A800" s="9"/>
       <c r="B800" s="55"/>
       <c r="C800" s="55"/>
@@ -22880,7 +22875,7 @@
       <c r="T800" s="9"/>
       <c r="U800" s="9"/>
     </row>
-    <row r="801" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A801" s="9"/>
       <c r="B801" s="55"/>
       <c r="C801" s="55"/>
@@ -22903,7 +22898,7 @@
       <c r="T801" s="9"/>
       <c r="U801" s="9"/>
     </row>
-    <row r="802" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A802" s="9"/>
       <c r="B802" s="55"/>
       <c r="C802" s="55"/>
@@ -22926,7 +22921,7 @@
       <c r="T802" s="9"/>
       <c r="U802" s="9"/>
     </row>
-    <row r="803" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A803" s="9"/>
       <c r="B803" s="55"/>
       <c r="C803" s="55"/>
@@ -22949,7 +22944,7 @@
       <c r="T803" s="9"/>
       <c r="U803" s="9"/>
     </row>
-    <row r="804" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A804" s="9"/>
       <c r="B804" s="55"/>
       <c r="C804" s="55"/>
@@ -22972,7 +22967,7 @@
       <c r="T804" s="9"/>
       <c r="U804" s="9"/>
     </row>
-    <row r="805" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A805" s="9"/>
       <c r="B805" s="55"/>
       <c r="C805" s="55"/>
@@ -22995,7 +22990,7 @@
       <c r="T805" s="9"/>
       <c r="U805" s="9"/>
     </row>
-    <row r="806" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A806" s="9"/>
       <c r="B806" s="55"/>
       <c r="C806" s="55"/>
@@ -23018,7 +23013,7 @@
       <c r="T806" s="9"/>
       <c r="U806" s="9"/>
     </row>
-    <row r="807" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A807" s="9"/>
       <c r="B807" s="55"/>
       <c r="C807" s="55"/>
@@ -23041,7 +23036,7 @@
       <c r="T807" s="9"/>
       <c r="U807" s="9"/>
     </row>
-    <row r="808" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A808" s="9"/>
       <c r="B808" s="55"/>
       <c r="C808" s="55"/>
@@ -23064,7 +23059,7 @@
       <c r="T808" s="9"/>
       <c r="U808" s="9"/>
     </row>
-    <row r="809" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A809" s="9"/>
       <c r="B809" s="55"/>
       <c r="C809" s="55"/>
@@ -23087,7 +23082,7 @@
       <c r="T809" s="9"/>
       <c r="U809" s="9"/>
     </row>
-    <row r="810" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A810" s="9"/>
       <c r="B810" s="55"/>
       <c r="C810" s="55"/>
@@ -23110,7 +23105,7 @@
       <c r="T810" s="9"/>
       <c r="U810" s="9"/>
     </row>
-    <row r="811" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A811" s="9"/>
       <c r="B811" s="55"/>
       <c r="C811" s="55"/>
@@ -23133,7 +23128,7 @@
       <c r="T811" s="9"/>
       <c r="U811" s="9"/>
     </row>
-    <row r="812" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A812" s="9"/>
       <c r="B812" s="55"/>
       <c r="C812" s="55"/>
@@ -23156,7 +23151,7 @@
       <c r="T812" s="9"/>
       <c r="U812" s="9"/>
     </row>
-    <row r="813" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A813" s="9"/>
       <c r="B813" s="55"/>
       <c r="C813" s="55"/>
@@ -23179,7 +23174,7 @@
       <c r="T813" s="9"/>
       <c r="U813" s="9"/>
     </row>
-    <row r="814" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A814" s="9"/>
       <c r="B814" s="55"/>
       <c r="C814" s="55"/>
@@ -23202,7 +23197,7 @@
       <c r="T814" s="9"/>
       <c r="U814" s="9"/>
     </row>
-    <row r="815" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A815" s="9"/>
       <c r="B815" s="55"/>
       <c r="C815" s="55"/>
@@ -23225,7 +23220,7 @@
       <c r="T815" s="9"/>
       <c r="U815" s="9"/>
     </row>
-    <row r="816" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A816" s="9"/>
       <c r="B816" s="55"/>
       <c r="C816" s="55"/>
@@ -23248,7 +23243,7 @@
       <c r="T816" s="9"/>
       <c r="U816" s="9"/>
     </row>
-    <row r="817" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A817" s="9"/>
       <c r="B817" s="55"/>
       <c r="C817" s="55"/>
@@ -23271,7 +23266,7 @@
       <c r="T817" s="9"/>
       <c r="U817" s="9"/>
     </row>
-    <row r="818" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A818" s="9"/>
       <c r="B818" s="55"/>
       <c r="C818" s="55"/>
@@ -23294,7 +23289,7 @@
       <c r="T818" s="9"/>
       <c r="U818" s="9"/>
     </row>
-    <row r="819" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A819" s="9"/>
       <c r="B819" s="55"/>
       <c r="C819" s="55"/>
@@ -23317,7 +23312,7 @@
       <c r="T819" s="9"/>
       <c r="U819" s="9"/>
     </row>
-    <row r="820" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A820" s="9"/>
       <c r="B820" s="55"/>
       <c r="C820" s="55"/>
@@ -23340,7 +23335,7 @@
       <c r="T820" s="9"/>
       <c r="U820" s="9"/>
     </row>
-    <row r="821" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A821" s="9"/>
       <c r="B821" s="55"/>
       <c r="C821" s="55"/>
@@ -23363,7 +23358,7 @@
       <c r="T821" s="9"/>
       <c r="U821" s="9"/>
     </row>
-    <row r="822" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A822" s="9"/>
       <c r="B822" s="55"/>
       <c r="C822" s="55"/>
@@ -23386,7 +23381,7 @@
       <c r="T822" s="9"/>
       <c r="U822" s="9"/>
     </row>
-    <row r="823" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A823" s="9"/>
       <c r="B823" s="55"/>
       <c r="C823" s="55"/>
@@ -23409,7 +23404,7 @@
       <c r="T823" s="9"/>
       <c r="U823" s="9"/>
     </row>
-    <row r="824" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A824" s="9"/>
       <c r="B824" s="55"/>
       <c r="C824" s="55"/>
@@ -23432,7 +23427,7 @@
       <c r="T824" s="9"/>
       <c r="U824" s="9"/>
     </row>
-    <row r="825" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A825" s="9"/>
       <c r="B825" s="55"/>
       <c r="C825" s="55"/>
@@ -23455,7 +23450,7 @@
       <c r="T825" s="9"/>
       <c r="U825" s="9"/>
     </row>
-    <row r="826" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A826" s="9"/>
       <c r="B826" s="55"/>
       <c r="C826" s="55"/>
@@ -23478,7 +23473,7 @@
       <c r="T826" s="9"/>
       <c r="U826" s="9"/>
     </row>
-    <row r="827" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A827" s="9"/>
       <c r="B827" s="55"/>
       <c r="C827" s="55"/>
@@ -23501,7 +23496,7 @@
       <c r="T827" s="9"/>
       <c r="U827" s="9"/>
     </row>
-    <row r="828" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A828" s="9"/>
       <c r="B828" s="55"/>
       <c r="C828" s="55"/>
@@ -23524,7 +23519,7 @@
       <c r="T828" s="9"/>
       <c r="U828" s="9"/>
     </row>
-    <row r="829" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A829" s="9"/>
       <c r="B829" s="55"/>
       <c r="C829" s="55"/>
@@ -23547,7 +23542,7 @@
       <c r="T829" s="9"/>
       <c r="U829" s="9"/>
     </row>
-    <row r="830" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A830" s="9"/>
       <c r="B830" s="55"/>
       <c r="C830" s="55"/>
@@ -23570,7 +23565,7 @@
       <c r="T830" s="9"/>
       <c r="U830" s="9"/>
     </row>
-    <row r="831" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A831" s="9"/>
       <c r="B831" s="55"/>
       <c r="C831" s="55"/>
@@ -23593,7 +23588,7 @@
       <c r="T831" s="9"/>
       <c r="U831" s="9"/>
     </row>
-    <row r="832" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A832" s="9"/>
       <c r="B832" s="55"/>
       <c r="C832" s="55"/>
@@ -23616,7 +23611,7 @@
       <c r="T832" s="9"/>
       <c r="U832" s="9"/>
     </row>
-    <row r="833" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A833" s="9"/>
       <c r="B833" s="55"/>
       <c r="C833" s="55"/>
@@ -23639,7 +23634,7 @@
       <c r="T833" s="9"/>
       <c r="U833" s="9"/>
     </row>
-    <row r="834" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A834" s="9"/>
       <c r="B834" s="55"/>
       <c r="C834" s="55"/>
@@ -23662,7 +23657,7 @@
       <c r="T834" s="9"/>
       <c r="U834" s="9"/>
     </row>
-    <row r="835" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A835" s="9"/>
       <c r="B835" s="55"/>
       <c r="C835" s="55"/>
@@ -23685,7 +23680,7 @@
       <c r="T835" s="9"/>
       <c r="U835" s="9"/>
     </row>
-    <row r="836" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A836" s="9"/>
       <c r="B836" s="55"/>
       <c r="C836" s="55"/>
@@ -23708,7 +23703,7 @@
       <c r="T836" s="9"/>
       <c r="U836" s="9"/>
     </row>
-    <row r="837" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A837" s="9"/>
       <c r="B837" s="55"/>
       <c r="C837" s="55"/>
@@ -23731,7 +23726,7 @@
       <c r="T837" s="9"/>
       <c r="U837" s="9"/>
     </row>
-    <row r="838" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A838" s="9"/>
       <c r="B838" s="55"/>
       <c r="C838" s="55"/>
@@ -23754,7 +23749,7 @@
       <c r="T838" s="9"/>
       <c r="U838" s="9"/>
     </row>
-    <row r="839" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A839" s="9"/>
       <c r="B839" s="55"/>
       <c r="C839" s="55"/>
@@ -23777,7 +23772,7 @@
       <c r="T839" s="9"/>
       <c r="U839" s="9"/>
     </row>
-    <row r="840" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A840" s="9"/>
       <c r="B840" s="55"/>
       <c r="C840" s="55"/>
@@ -23800,7 +23795,7 @@
       <c r="T840" s="9"/>
       <c r="U840" s="9"/>
     </row>
-    <row r="841" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A841" s="9"/>
       <c r="B841" s="55"/>
       <c r="C841" s="55"/>
@@ -23823,7 +23818,7 @@
       <c r="T841" s="9"/>
       <c r="U841" s="9"/>
     </row>
-    <row r="842" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A842" s="9"/>
       <c r="B842" s="55"/>
       <c r="C842" s="55"/>
@@ -23846,7 +23841,7 @@
       <c r="T842" s="9"/>
       <c r="U842" s="9"/>
     </row>
-    <row r="843" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A843" s="9"/>
       <c r="B843" s="55"/>
       <c r="C843" s="55"/>
@@ -23869,7 +23864,7 @@
       <c r="T843" s="9"/>
       <c r="U843" s="9"/>
     </row>
-    <row r="844" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A844" s="9"/>
       <c r="B844" s="55"/>
       <c r="C844" s="55"/>
@@ -23892,7 +23887,7 @@
       <c r="T844" s="9"/>
       <c r="U844" s="9"/>
     </row>
-    <row r="845" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A845" s="9"/>
       <c r="B845" s="55"/>
       <c r="C845" s="55"/>
@@ -23915,7 +23910,7 @@
       <c r="T845" s="9"/>
       <c r="U845" s="9"/>
     </row>
-    <row r="846" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A846" s="9"/>
       <c r="B846" s="55"/>
       <c r="C846" s="55"/>
@@ -23938,7 +23933,7 @@
       <c r="T846" s="9"/>
       <c r="U846" s="9"/>
     </row>
-    <row r="847" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A847" s="9"/>
       <c r="B847" s="55"/>
       <c r="C847" s="55"/>
@@ -23961,7 +23956,7 @@
       <c r="T847" s="9"/>
       <c r="U847" s="9"/>
     </row>
-    <row r="848" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A848" s="9"/>
       <c r="B848" s="55"/>
       <c r="C848" s="55"/>
@@ -23984,7 +23979,7 @@
       <c r="T848" s="9"/>
       <c r="U848" s="9"/>
     </row>
-    <row r="849" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A849" s="9"/>
       <c r="B849" s="55"/>
       <c r="C849" s="55"/>
@@ -24007,7 +24002,7 @@
       <c r="T849" s="9"/>
       <c r="U849" s="9"/>
     </row>
-    <row r="850" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A850" s="9"/>
       <c r="B850" s="55"/>
       <c r="C850" s="55"/>
@@ -24030,7 +24025,7 @@
       <c r="T850" s="9"/>
       <c r="U850" s="9"/>
     </row>
-    <row r="851" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A851" s="9"/>
       <c r="B851" s="55"/>
       <c r="C851" s="55"/>
@@ -24053,7 +24048,7 @@
       <c r="T851" s="9"/>
       <c r="U851" s="9"/>
     </row>
-    <row r="852" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A852" s="9"/>
       <c r="B852" s="55"/>
       <c r="C852" s="55"/>
@@ -24076,7 +24071,7 @@
       <c r="T852" s="9"/>
       <c r="U852" s="9"/>
     </row>
-    <row r="853" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A853" s="9"/>
       <c r="B853" s="55"/>
       <c r="C853" s="55"/>
@@ -24099,7 +24094,7 @@
       <c r="T853" s="9"/>
       <c r="U853" s="9"/>
     </row>
-    <row r="854" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A854" s="9"/>
       <c r="B854" s="55"/>
       <c r="C854" s="55"/>
@@ -24122,7 +24117,7 @@
       <c r="T854" s="9"/>
       <c r="U854" s="9"/>
     </row>
-    <row r="855" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A855" s="9"/>
       <c r="B855" s="55"/>
       <c r="C855" s="55"/>
@@ -24145,7 +24140,7 @@
       <c r="T855" s="9"/>
       <c r="U855" s="9"/>
     </row>
-    <row r="856" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A856" s="9"/>
       <c r="B856" s="55"/>
       <c r="C856" s="55"/>
@@ -24168,7 +24163,7 @@
       <c r="T856" s="9"/>
       <c r="U856" s="9"/>
     </row>
-    <row r="857" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A857" s="9"/>
       <c r="B857" s="55"/>
       <c r="C857" s="55"/>
@@ -24191,7 +24186,7 @@
       <c r="T857" s="9"/>
       <c r="U857" s="9"/>
     </row>
-    <row r="858" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A858" s="9"/>
       <c r="B858" s="55"/>
       <c r="C858" s="55"/>
@@ -24214,7 +24209,7 @@
       <c r="T858" s="9"/>
       <c r="U858" s="9"/>
     </row>
-    <row r="859" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A859" s="9"/>
       <c r="B859" s="55"/>
       <c r="C859" s="55"/>
@@ -24237,7 +24232,7 @@
       <c r="T859" s="9"/>
       <c r="U859" s="9"/>
     </row>
-    <row r="860" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A860" s="9"/>
       <c r="B860" s="55"/>
       <c r="C860" s="55"/>
@@ -24260,7 +24255,7 @@
       <c r="T860" s="9"/>
       <c r="U860" s="9"/>
     </row>
-    <row r="861" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A861" s="9"/>
       <c r="B861" s="55"/>
       <c r="C861" s="55"/>
@@ -24283,7 +24278,7 @@
       <c r="T861" s="9"/>
       <c r="U861" s="9"/>
     </row>
-    <row r="862" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A862" s="9"/>
       <c r="B862" s="55"/>
       <c r="C862" s="55"/>
@@ -24306,7 +24301,7 @@
       <c r="T862" s="9"/>
       <c r="U862" s="9"/>
     </row>
-    <row r="863" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A863" s="9"/>
       <c r="B863" s="55"/>
       <c r="C863" s="55"/>
@@ -24329,7 +24324,7 @@
       <c r="T863" s="9"/>
       <c r="U863" s="9"/>
     </row>
-    <row r="864" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A864" s="9"/>
       <c r="B864" s="55"/>
       <c r="C864" s="55"/>
@@ -24352,7 +24347,7 @@
       <c r="T864" s="9"/>
       <c r="U864" s="9"/>
     </row>
-    <row r="865" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A865" s="9"/>
       <c r="B865" s="55"/>
       <c r="C865" s="55"/>
@@ -24375,7 +24370,7 @@
       <c r="T865" s="9"/>
       <c r="U865" s="9"/>
     </row>
-    <row r="866" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A866" s="9"/>
       <c r="B866" s="55"/>
       <c r="C866" s="55"/>
@@ -24398,7 +24393,7 @@
       <c r="T866" s="9"/>
       <c r="U866" s="9"/>
     </row>
-    <row r="867" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A867" s="9"/>
       <c r="B867" s="55"/>
       <c r="C867" s="55"/>
@@ -24421,7 +24416,7 @@
       <c r="T867" s="9"/>
       <c r="U867" s="9"/>
     </row>
-    <row r="868" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A868" s="9"/>
       <c r="B868" s="55"/>
       <c r="C868" s="55"/>
@@ -24444,7 +24439,7 @@
       <c r="T868" s="9"/>
       <c r="U868" s="9"/>
     </row>
-    <row r="869" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A869" s="9"/>
       <c r="B869" s="55"/>
       <c r="C869" s="55"/>
@@ -24467,7 +24462,7 @@
       <c r="T869" s="9"/>
       <c r="U869" s="9"/>
     </row>
-    <row r="870" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A870" s="9"/>
       <c r="B870" s="55"/>
       <c r="C870" s="55"/>
@@ -24490,7 +24485,7 @@
       <c r="T870" s="9"/>
       <c r="U870" s="9"/>
     </row>
-    <row r="871" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A871" s="9"/>
       <c r="B871" s="55"/>
       <c r="C871" s="55"/>
@@ -24513,7 +24508,7 @@
       <c r="T871" s="9"/>
       <c r="U871" s="9"/>
     </row>
-    <row r="872" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A872" s="9"/>
       <c r="B872" s="55"/>
       <c r="C872" s="55"/>
@@ -24536,7 +24531,7 @@
       <c r="T872" s="9"/>
       <c r="U872" s="9"/>
     </row>
-    <row r="873" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A873" s="9"/>
       <c r="B873" s="55"/>
       <c r="C873" s="55"/>
@@ -24559,7 +24554,7 @@
       <c r="T873" s="9"/>
       <c r="U873" s="9"/>
     </row>
-    <row r="874" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A874" s="9"/>
       <c r="B874" s="55"/>
       <c r="C874" s="55"/>
@@ -24582,7 +24577,7 @@
       <c r="T874" s="9"/>
       <c r="U874" s="9"/>
     </row>
-    <row r="875" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A875" s="9"/>
       <c r="B875" s="55"/>
       <c r="C875" s="55"/>
@@ -24605,7 +24600,7 @@
       <c r="T875" s="9"/>
       <c r="U875" s="9"/>
     </row>
-    <row r="876" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A876" s="9"/>
       <c r="B876" s="55"/>
       <c r="C876" s="55"/>
@@ -24628,7 +24623,7 @@
       <c r="T876" s="9"/>
       <c r="U876" s="9"/>
     </row>
-    <row r="877" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A877" s="9"/>
       <c r="B877" s="55"/>
       <c r="C877" s="55"/>
@@ -24651,7 +24646,7 @@
       <c r="T877" s="9"/>
       <c r="U877" s="9"/>
     </row>
-    <row r="878" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A878" s="9"/>
       <c r="B878" s="55"/>
       <c r="C878" s="55"/>
@@ -24674,7 +24669,7 @@
       <c r="T878" s="9"/>
       <c r="U878" s="9"/>
     </row>
-    <row r="879" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A879" s="9"/>
       <c r="B879" s="55"/>
       <c r="C879" s="55"/>
@@ -24697,7 +24692,7 @@
       <c r="T879" s="9"/>
       <c r="U879" s="9"/>
     </row>
-    <row r="880" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A880" s="9"/>
       <c r="B880" s="55"/>
       <c r="C880" s="55"/>
@@ -24720,7 +24715,7 @@
       <c r="T880" s="9"/>
       <c r="U880" s="9"/>
     </row>
-    <row r="881" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A881" s="9"/>
       <c r="B881" s="55"/>
       <c r="C881" s="55"/>
@@ -24743,7 +24738,7 @@
       <c r="T881" s="9"/>
       <c r="U881" s="9"/>
     </row>
-    <row r="882" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A882" s="9"/>
       <c r="B882" s="55"/>
       <c r="C882" s="55"/>
@@ -24766,7 +24761,7 @@
       <c r="T882" s="9"/>
       <c r="U882" s="9"/>
     </row>
-    <row r="883" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A883" s="9"/>
       <c r="B883" s="55"/>
       <c r="C883" s="55"/>
@@ -24789,7 +24784,7 @@
       <c r="T883" s="9"/>
       <c r="U883" s="9"/>
     </row>
-    <row r="884" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A884" s="9"/>
       <c r="B884" s="55"/>
       <c r="C884" s="55"/>
@@ -24812,7 +24807,7 @@
       <c r="T884" s="9"/>
       <c r="U884" s="9"/>
     </row>
-    <row r="885" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A885" s="9"/>
       <c r="B885" s="55"/>
       <c r="C885" s="55"/>
@@ -24835,7 +24830,7 @@
       <c r="T885" s="9"/>
       <c r="U885" s="9"/>
     </row>
-    <row r="886" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A886" s="9"/>
       <c r="B886" s="55"/>
       <c r="C886" s="55"/>
@@ -24858,7 +24853,7 @@
       <c r="T886" s="9"/>
       <c r="U886" s="9"/>
     </row>
-    <row r="887" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A887" s="9"/>
       <c r="B887" s="55"/>
       <c r="C887" s="55"/>
@@ -24881,7 +24876,7 @@
       <c r="T887" s="9"/>
       <c r="U887" s="9"/>
     </row>
-    <row r="888" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A888" s="9"/>
       <c r="B888" s="55"/>
       <c r="C888" s="55"/>
@@ -24904,7 +24899,7 @@
       <c r="T888" s="9"/>
       <c r="U888" s="9"/>
     </row>
-    <row r="889" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A889" s="9"/>
       <c r="B889" s="55"/>
       <c r="C889" s="55"/>
@@ -24927,7 +24922,7 @@
       <c r="T889" s="9"/>
       <c r="U889" s="9"/>
     </row>
-    <row r="890" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A890" s="9"/>
       <c r="B890" s="55"/>
       <c r="C890" s="55"/>
@@ -24950,7 +24945,7 @@
       <c r="T890" s="9"/>
       <c r="U890" s="9"/>
     </row>
-    <row r="891" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A891" s="9"/>
       <c r="B891" s="55"/>
       <c r="C891" s="55"/>
@@ -24973,7 +24968,7 @@
       <c r="T891" s="9"/>
       <c r="U891" s="9"/>
     </row>
-    <row r="892" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A892" s="9"/>
       <c r="B892" s="55"/>
       <c r="C892" s="55"/>
@@ -24996,7 +24991,7 @@
       <c r="T892" s="9"/>
       <c r="U892" s="9"/>
     </row>
-    <row r="893" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A893" s="9"/>
       <c r="B893" s="55"/>
       <c r="C893" s="55"/>
@@ -25019,7 +25014,7 @@
       <c r="T893" s="9"/>
       <c r="U893" s="9"/>
     </row>
-    <row r="894" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A894" s="9"/>
       <c r="B894" s="55"/>
       <c r="C894" s="55"/>
@@ -25042,7 +25037,7 @@
       <c r="T894" s="9"/>
       <c r="U894" s="9"/>
     </row>
-    <row r="895" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A895" s="9"/>
       <c r="B895" s="55"/>
       <c r="C895" s="55"/>
@@ -25065,7 +25060,7 @@
       <c r="T895" s="9"/>
       <c r="U895" s="9"/>
     </row>
-    <row r="896" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A896" s="9"/>
       <c r="B896" s="55"/>
       <c r="C896" s="55"/>
@@ -25088,7 +25083,7 @@
       <c r="T896" s="9"/>
       <c r="U896" s="9"/>
     </row>
-    <row r="897" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A897" s="9"/>
       <c r="B897" s="55"/>
       <c r="C897" s="55"/>
@@ -25111,7 +25106,7 @@
       <c r="T897" s="9"/>
       <c r="U897" s="9"/>
     </row>
-    <row r="898" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A898" s="9"/>
       <c r="B898" s="55"/>
       <c r="C898" s="55"/>
@@ -25134,7 +25129,7 @@
       <c r="T898" s="9"/>
       <c r="U898" s="9"/>
     </row>
-    <row r="899" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A899" s="9"/>
       <c r="B899" s="55"/>
       <c r="C899" s="55"/>
@@ -25157,7 +25152,7 @@
       <c r="T899" s="9"/>
       <c r="U899" s="9"/>
     </row>
-    <row r="900" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A900" s="9"/>
       <c r="B900" s="55"/>
       <c r="C900" s="55"/>
@@ -25180,7 +25175,7 @@
       <c r="T900" s="9"/>
       <c r="U900" s="9"/>
     </row>
-    <row r="901" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A901" s="9"/>
       <c r="B901" s="55"/>
       <c r="C901" s="55"/>
@@ -25203,7 +25198,7 @@
       <c r="T901" s="9"/>
       <c r="U901" s="9"/>
     </row>
-    <row r="902" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A902" s="9"/>
       <c r="B902" s="55"/>
       <c r="C902" s="55"/>
@@ -25226,7 +25221,7 @@
       <c r="T902" s="9"/>
       <c r="U902" s="9"/>
     </row>
-    <row r="903" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A903" s="9"/>
       <c r="B903" s="55"/>
       <c r="C903" s="55"/>
@@ -25249,7 +25244,7 @@
       <c r="T903" s="9"/>
       <c r="U903" s="9"/>
     </row>
-    <row r="904" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A904" s="9"/>
       <c r="B904" s="55"/>
       <c r="C904" s="55"/>
@@ -25272,7 +25267,7 @@
       <c r="T904" s="9"/>
       <c r="U904" s="9"/>
     </row>
-    <row r="905" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A905" s="9"/>
       <c r="B905" s="55"/>
       <c r="C905" s="55"/>
@@ -25295,7 +25290,7 @@
       <c r="T905" s="9"/>
       <c r="U905" s="9"/>
     </row>
-    <row r="906" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A906" s="9"/>
       <c r="B906" s="55"/>
       <c r="C906" s="55"/>
@@ -25318,7 +25313,7 @@
       <c r="T906" s="9"/>
       <c r="U906" s="9"/>
     </row>
-    <row r="907" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A907" s="9"/>
       <c r="B907" s="55"/>
       <c r="C907" s="55"/>
@@ -25341,7 +25336,7 @@
       <c r="T907" s="9"/>
       <c r="U907" s="9"/>
     </row>
-    <row r="908" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A908" s="9"/>
       <c r="B908" s="55"/>
       <c r="C908" s="55"/>
@@ -25364,7 +25359,7 @@
       <c r="T908" s="9"/>
       <c r="U908" s="9"/>
     </row>
-    <row r="909" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A909" s="9"/>
       <c r="B909" s="55"/>
       <c r="C909" s="55"/>
@@ -25387,7 +25382,7 @@
       <c r="T909" s="9"/>
       <c r="U909" s="9"/>
     </row>
-    <row r="910" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A910" s="9"/>
       <c r="B910" s="55"/>
       <c r="C910" s="55"/>
@@ -25410,7 +25405,7 @@
       <c r="T910" s="9"/>
       <c r="U910" s="9"/>
     </row>
-    <row r="911" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A911" s="9"/>
       <c r="B911" s="55"/>
       <c r="C911" s="55"/>
@@ -25433,7 +25428,7 @@
       <c r="T911" s="9"/>
       <c r="U911" s="9"/>
     </row>
-    <row r="912" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A912" s="9"/>
       <c r="B912" s="55"/>
       <c r="C912" s="55"/>
@@ -25456,7 +25451,7 @@
       <c r="T912" s="9"/>
       <c r="U912" s="9"/>
     </row>
-    <row r="913" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A913" s="9"/>
       <c r="B913" s="55"/>
       <c r="C913" s="55"/>
@@ -25479,7 +25474,7 @@
       <c r="T913" s="9"/>
       <c r="U913" s="9"/>
     </row>
-    <row r="914" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A914" s="9"/>
       <c r="B914" s="55"/>
       <c r="C914" s="55"/>
@@ -25502,7 +25497,7 @@
       <c r="T914" s="9"/>
       <c r="U914" s="9"/>
     </row>
-    <row r="915" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A915" s="9"/>
       <c r="B915" s="55"/>
       <c r="C915" s="55"/>
@@ -25525,7 +25520,7 @@
       <c r="T915" s="9"/>
       <c r="U915" s="9"/>
     </row>
-    <row r="916" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A916" s="9"/>
       <c r="B916" s="55"/>
       <c r="C916" s="55"/>
@@ -25548,7 +25543,7 @@
       <c r="T916" s="9"/>
       <c r="U916" s="9"/>
     </row>
-    <row r="917" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A917" s="9"/>
       <c r="B917" s="55"/>
       <c r="C917" s="55"/>
@@ -25571,7 +25566,7 @@
       <c r="T917" s="9"/>
       <c r="U917" s="9"/>
     </row>
-    <row r="918" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A918" s="9"/>
       <c r="B918" s="55"/>
       <c r="C918" s="55"/>
@@ -25594,7 +25589,7 @@
       <c r="T918" s="9"/>
       <c r="U918" s="9"/>
     </row>
-    <row r="919" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A919" s="9"/>
       <c r="B919" s="55"/>
       <c r="C919" s="55"/>
@@ -25617,7 +25612,7 @@
       <c r="T919" s="9"/>
       <c r="U919" s="9"/>
     </row>
-    <row r="920" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A920" s="9"/>
       <c r="B920" s="55"/>
       <c r="C920" s="55"/>
@@ -25640,7 +25635,7 @@
       <c r="T920" s="9"/>
       <c r="U920" s="9"/>
     </row>
-    <row r="921" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A921" s="9"/>
       <c r="B921" s="55"/>
       <c r="C921" s="55"/>
@@ -25663,7 +25658,7 @@
       <c r="T921" s="9"/>
       <c r="U921" s="9"/>
     </row>
-    <row r="922" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A922" s="9"/>
       <c r="B922" s="55"/>
       <c r="C922" s="55"/>
@@ -25686,7 +25681,7 @@
       <c r="T922" s="9"/>
       <c r="U922" s="9"/>
     </row>
-    <row r="923" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A923" s="9"/>
       <c r="B923" s="55"/>
       <c r="C923" s="55"/>
@@ -25709,7 +25704,7 @@
       <c r="T923" s="9"/>
       <c r="U923" s="9"/>
     </row>
-    <row r="924" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A924" s="9"/>
       <c r="B924" s="55"/>
       <c r="C924" s="55"/>
@@ -25732,7 +25727,7 @@
       <c r="T924" s="9"/>
       <c r="U924" s="9"/>
     </row>
-    <row r="925" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A925" s="9"/>
       <c r="B925" s="55"/>
       <c r="C925" s="55"/>
@@ -25755,7 +25750,7 @@
       <c r="T925" s="9"/>
       <c r="U925" s="9"/>
     </row>
-    <row r="926" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A926" s="9"/>
       <c r="B926" s="55"/>
       <c r="C926" s="55"/>
@@ -25778,7 +25773,7 @@
       <c r="T926" s="9"/>
       <c r="U926" s="9"/>
     </row>
-    <row r="927" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A927" s="9"/>
       <c r="B927" s="55"/>
       <c r="C927" s="55"/>
@@ -25801,7 +25796,7 @@
       <c r="T927" s="9"/>
       <c r="U927" s="9"/>
     </row>
-    <row r="928" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A928" s="9"/>
       <c r="B928" s="55"/>
       <c r="C928" s="55"/>
@@ -25824,7 +25819,7 @@
       <c r="T928" s="9"/>
       <c r="U928" s="9"/>
     </row>
-    <row r="929" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A929" s="9"/>
       <c r="B929" s="55"/>
       <c r="C929" s="55"/>
@@ -25847,7 +25842,7 @@
       <c r="T929" s="9"/>
       <c r="U929" s="9"/>
     </row>
-    <row r="930" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A930" s="9"/>
       <c r="B930" s="55"/>
       <c r="C930" s="55"/>
@@ -25870,7 +25865,7 @@
       <c r="T930" s="9"/>
       <c r="U930" s="9"/>
     </row>
-    <row r="931" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A931" s="9"/>
       <c r="B931" s="55"/>
       <c r="C931" s="55"/>
@@ -25893,7 +25888,7 @@
       <c r="T931" s="9"/>
       <c r="U931" s="9"/>
     </row>
-    <row r="932" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A932" s="9"/>
       <c r="B932" s="55"/>
       <c r="C932" s="55"/>
@@ -25916,7 +25911,7 @@
       <c r="T932" s="9"/>
       <c r="U932" s="9"/>
     </row>
-    <row r="933" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A933" s="9"/>
       <c r="B933" s="55"/>
       <c r="C933" s="55"/>
@@ -25939,7 +25934,7 @@
       <c r="T933" s="9"/>
       <c r="U933" s="9"/>
     </row>
-    <row r="934" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A934" s="9"/>
       <c r="B934" s="55"/>
       <c r="C934" s="55"/>
@@ -25962,7 +25957,7 @@
       <c r="T934" s="9"/>
       <c r="U934" s="9"/>
     </row>
-    <row r="935" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A935" s="9"/>
       <c r="B935" s="55"/>
       <c r="C935" s="55"/>
@@ -25985,7 +25980,7 @@
       <c r="T935" s="9"/>
       <c r="U935" s="9"/>
     </row>
-    <row r="936" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A936" s="9"/>
       <c r="B936" s="55"/>
       <c r="C936" s="55"/>
@@ -26008,7 +26003,7 @@
       <c r="T936" s="9"/>
       <c r="U936" s="9"/>
     </row>
-    <row r="937" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A937" s="9"/>
       <c r="B937" s="55"/>
       <c r="C937" s="55"/>
@@ -26031,7 +26026,7 @@
       <c r="T937" s="9"/>
       <c r="U937" s="9"/>
     </row>
-    <row r="938" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A938" s="9"/>
       <c r="B938" s="55"/>
       <c r="C938" s="55"/>
@@ -26054,7 +26049,7 @@
       <c r="T938" s="9"/>
       <c r="U938" s="9"/>
     </row>
-    <row r="939" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A939" s="9"/>
       <c r="B939" s="55"/>
       <c r="C939" s="55"/>
@@ -26077,7 +26072,7 @@
       <c r="T939" s="9"/>
       <c r="U939" s="9"/>
     </row>
-    <row r="940" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A940" s="9"/>
       <c r="B940" s="55"/>
       <c r="C940" s="55"/>
@@ -26100,7 +26095,7 @@
       <c r="T940" s="9"/>
       <c r="U940" s="9"/>
     </row>
-    <row r="941" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A941" s="9"/>
       <c r="B941" s="55"/>
       <c r="C941" s="55"/>
@@ -26123,7 +26118,7 @@
       <c r="T941" s="9"/>
       <c r="U941" s="9"/>
     </row>
-    <row r="942" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A942" s="9"/>
       <c r="B942" s="55"/>
       <c r="C942" s="55"/>
@@ -26146,7 +26141,7 @@
       <c r="T942" s="9"/>
       <c r="U942" s="9"/>
     </row>
-    <row r="943" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A943" s="9"/>
       <c r="B943" s="55"/>
       <c r="C943" s="55"/>
@@ -26169,7 +26164,7 @@
       <c r="T943" s="9"/>
       <c r="U943" s="9"/>
     </row>
-    <row r="944" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A944" s="9"/>
       <c r="B944" s="55"/>
       <c r="C944" s="55"/>
@@ -26192,7 +26187,7 @@
       <c r="T944" s="9"/>
       <c r="U944" s="9"/>
     </row>
-    <row r="945" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A945" s="9"/>
       <c r="B945" s="55"/>
       <c r="C945" s="55"/>
@@ -26215,7 +26210,7 @@
       <c r="T945" s="9"/>
       <c r="U945" s="9"/>
     </row>
-    <row r="946" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A946" s="9"/>
       <c r="B946" s="55"/>
       <c r="C946" s="55"/>
@@ -26238,7 +26233,7 @@
       <c r="T946" s="9"/>
       <c r="U946" s="9"/>
     </row>
-    <row r="947" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A947" s="9"/>
       <c r="B947" s="55"/>
       <c r="C947" s="55"/>
@@ -26261,7 +26256,7 @@
       <c r="T947" s="9"/>
       <c r="U947" s="9"/>
     </row>
-    <row r="948" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A948" s="9"/>
       <c r="B948" s="55"/>
       <c r="C948" s="55"/>
@@ -26284,7 +26279,7 @@
       <c r="T948" s="9"/>
       <c r="U948" s="9"/>
     </row>
-    <row r="949" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A949" s="9"/>
       <c r="B949" s="55"/>
       <c r="C949" s="55"/>
@@ -26307,7 +26302,7 @@
       <c r="T949" s="9"/>
       <c r="U949" s="9"/>
     </row>
-    <row r="950" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A950" s="9"/>
       <c r="B950" s="55"/>
       <c r="C950" s="55"/>
@@ -26330,7 +26325,7 @@
       <c r="T950" s="9"/>
       <c r="U950" s="9"/>
     </row>
-    <row r="951" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A951" s="9"/>
       <c r="B951" s="55"/>
       <c r="C951" s="55"/>
@@ -26353,7 +26348,7 @@
       <c r="T951" s="9"/>
       <c r="U951" s="9"/>
     </row>
-    <row r="952" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="952" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A952" s="9"/>
       <c r="B952" s="55"/>
       <c r="C952" s="55"/>
@@ -26376,7 +26371,7 @@
       <c r="T952" s="9"/>
       <c r="U952" s="9"/>
     </row>
-    <row r="953" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A953" s="9"/>
       <c r="B953" s="55"/>
       <c r="C953" s="55"/>
@@ -26399,7 +26394,7 @@
       <c r="T953" s="9"/>
       <c r="U953" s="9"/>
     </row>
-    <row r="954" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A954" s="9"/>
       <c r="B954" s="55"/>
       <c r="C954" s="55"/>
@@ -26422,7 +26417,7 @@
       <c r="T954" s="9"/>
       <c r="U954" s="9"/>
     </row>
-    <row r="955" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="955" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A955" s="9"/>
       <c r="B955" s="55"/>
       <c r="C955" s="55"/>
@@ -26445,7 +26440,7 @@
       <c r="T955" s="9"/>
       <c r="U955" s="9"/>
     </row>
-    <row r="956" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="956" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A956" s="9"/>
       <c r="B956" s="55"/>
       <c r="C956" s="55"/>
@@ -26468,7 +26463,7 @@
       <c r="T956" s="9"/>
       <c r="U956" s="9"/>
     </row>
-    <row r="957" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="957" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A957" s="9"/>
       <c r="B957" s="55"/>
       <c r="C957" s="55"/>
@@ -26491,7 +26486,7 @@
       <c r="T957" s="9"/>
       <c r="U957" s="9"/>
     </row>
-    <row r="958" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="958" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A958" s="9"/>
       <c r="B958" s="55"/>
       <c r="C958" s="55"/>
@@ -26514,7 +26509,7 @@
       <c r="T958" s="9"/>
       <c r="U958" s="9"/>
     </row>
-    <row r="959" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="959" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A959" s="9"/>
       <c r="B959" s="55"/>
       <c r="C959" s="55"/>
@@ -26537,7 +26532,7 @@
       <c r="T959" s="9"/>
       <c r="U959" s="9"/>
     </row>
-    <row r="960" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A960" s="9"/>
       <c r="B960" s="55"/>
       <c r="C960" s="55"/>
@@ -26560,7 +26555,7 @@
       <c r="T960" s="9"/>
       <c r="U960" s="9"/>
     </row>
-    <row r="961" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="961" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A961" s="9"/>
       <c r="B961" s="55"/>
       <c r="C961" s="55"/>
@@ -26583,7 +26578,7 @@
       <c r="T961" s="9"/>
       <c r="U961" s="9"/>
     </row>
-    <row r="962" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A962" s="9"/>
       <c r="B962" s="55"/>
       <c r="C962" s="55"/>
@@ -26606,7 +26601,7 @@
       <c r="T962" s="9"/>
       <c r="U962" s="9"/>
     </row>
-    <row r="963" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A963" s="9"/>
       <c r="B963" s="55"/>
       <c r="C963" s="55"/>
@@ -26629,7 +26624,7 @@
       <c r="T963" s="9"/>
       <c r="U963" s="9"/>
     </row>
-    <row r="964" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="964" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A964" s="9"/>
       <c r="B964" s="55"/>
       <c r="C964" s="55"/>
@@ -26652,7 +26647,7 @@
       <c r="T964" s="9"/>
       <c r="U964" s="9"/>
     </row>
-    <row r="965" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="965" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A965" s="9"/>
       <c r="B965" s="55"/>
       <c r="C965" s="55"/>
@@ -26675,7 +26670,7 @@
       <c r="T965" s="9"/>
       <c r="U965" s="9"/>
     </row>
-    <row r="966" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="966" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A966" s="9"/>
       <c r="B966" s="55"/>
       <c r="C966" s="55"/>
@@ -26698,7 +26693,7 @@
       <c r="T966" s="9"/>
       <c r="U966" s="9"/>
     </row>
-    <row r="967" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="967" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A967" s="9"/>
       <c r="B967" s="55"/>
       <c r="C967" s="55"/>
@@ -26721,7 +26716,7 @@
       <c r="T967" s="9"/>
       <c r="U967" s="9"/>
     </row>
-    <row r="968" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A968" s="9"/>
       <c r="B968" s="55"/>
       <c r="C968" s="55"/>
@@ -26744,7 +26739,7 @@
       <c r="T968" s="9"/>
       <c r="U968" s="9"/>
     </row>
-    <row r="969" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="969" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A969" s="9"/>
       <c r="B969" s="55"/>
       <c r="C969" s="55"/>
@@ -26767,7 +26762,7 @@
       <c r="T969" s="9"/>
       <c r="U969" s="9"/>
     </row>
-    <row r="970" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="970" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A970" s="9"/>
       <c r="B970" s="55"/>
       <c r="C970" s="55"/>
@@ -26790,7 +26785,7 @@
       <c r="T970" s="9"/>
       <c r="U970" s="9"/>
     </row>
-    <row r="971" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="971" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A971" s="9"/>
       <c r="B971" s="55"/>
       <c r="C971" s="55"/>
@@ -26813,7 +26808,7 @@
       <c r="T971" s="9"/>
       <c r="U971" s="9"/>
     </row>
-    <row r="972" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="972" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A972" s="9"/>
       <c r="B972" s="55"/>
       <c r="C972" s="55"/>
@@ -26836,7 +26831,7 @@
       <c r="T972" s="9"/>
       <c r="U972" s="9"/>
     </row>
-    <row r="973" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="973" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A973" s="9"/>
       <c r="B973" s="55"/>
       <c r="C973" s="55"/>
@@ -26859,7 +26854,7 @@
       <c r="T973" s="9"/>
       <c r="U973" s="9"/>
     </row>
-    <row r="974" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="974" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A974" s="9"/>
       <c r="B974" s="55"/>
       <c r="C974" s="55"/>
@@ -26882,7 +26877,7 @@
       <c r="T974" s="9"/>
       <c r="U974" s="9"/>
     </row>
-    <row r="975" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="975" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A975" s="9"/>
       <c r="B975" s="55"/>
       <c r="C975" s="55"/>
@@ -26905,7 +26900,7 @@
       <c r="T975" s="9"/>
       <c r="U975" s="9"/>
     </row>
-    <row r="976" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A976" s="9"/>
       <c r="B976" s="55"/>
       <c r="C976" s="55"/>
@@ -26928,7 +26923,7 @@
       <c r="T976" s="9"/>
       <c r="U976" s="9"/>
     </row>
-    <row r="977" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A977" s="9"/>
       <c r="B977" s="55"/>
       <c r="C977" s="55"/>
@@ -26951,7 +26946,7 @@
       <c r="T977" s="9"/>
       <c r="U977" s="9"/>
     </row>
-    <row r="978" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A978" s="9"/>
       <c r="B978" s="55"/>
       <c r="C978" s="55"/>
@@ -26974,7 +26969,7 @@
       <c r="T978" s="9"/>
       <c r="U978" s="9"/>
     </row>
-    <row r="979" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="979" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A979" s="9"/>
       <c r="B979" s="55"/>
       <c r="C979" s="55"/>
@@ -26997,7 +26992,7 @@
       <c r="T979" s="9"/>
       <c r="U979" s="9"/>
     </row>
-    <row r="980" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="980" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A980" s="9"/>
       <c r="B980" s="55"/>
       <c r="C980" s="55"/>
@@ -27020,7 +27015,7 @@
       <c r="T980" s="9"/>
       <c r="U980" s="9"/>
     </row>
-    <row r="981" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="981" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A981" s="9"/>
       <c r="B981" s="55"/>
       <c r="C981" s="55"/>
@@ -27043,7 +27038,7 @@
       <c r="T981" s="9"/>
       <c r="U981" s="9"/>
     </row>
-    <row r="982" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="982" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A982" s="9"/>
       <c r="B982" s="55"/>
       <c r="C982" s="55"/>
@@ -27066,7 +27061,7 @@
       <c r="T982" s="9"/>
       <c r="U982" s="9"/>
     </row>
-    <row r="983" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="983" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A983" s="9"/>
       <c r="B983" s="55"/>
       <c r="C983" s="55"/>
@@ -27089,7 +27084,7 @@
       <c r="T983" s="9"/>
       <c r="U983" s="9"/>
     </row>
-    <row r="984" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A984" s="9"/>
       <c r="B984" s="55"/>
       <c r="C984" s="55"/>
@@ -27112,7 +27107,7 @@
       <c r="T984" s="9"/>
       <c r="U984" s="9"/>
     </row>
-    <row r="985" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A985" s="9"/>
       <c r="B985" s="55"/>
       <c r="C985" s="55"/>
@@ -27135,7 +27130,7 @@
       <c r="T985" s="9"/>
       <c r="U985" s="9"/>
     </row>
-    <row r="986" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A986" s="9"/>
       <c r="B986" s="55"/>
       <c r="C986" s="55"/>
@@ -27158,7 +27153,7 @@
       <c r="T986" s="9"/>
       <c r="U986" s="9"/>
     </row>
-    <row r="987" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="987" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A987" s="9"/>
       <c r="B987" s="55"/>
       <c r="C987" s="55"/>
@@ -27181,7 +27176,7 @@
       <c r="T987" s="9"/>
       <c r="U987" s="9"/>
     </row>
-    <row r="988" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A988" s="9"/>
       <c r="B988" s="55"/>
       <c r="C988" s="55"/>
@@ -27204,7 +27199,7 @@
       <c r="T988" s="9"/>
       <c r="U988" s="9"/>
     </row>
-    <row r="989" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="989" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A989" s="9"/>
       <c r="B989" s="55"/>
       <c r="C989" s="55"/>
@@ -27227,7 +27222,7 @@
       <c r="T989" s="9"/>
       <c r="U989" s="9"/>
     </row>
-    <row r="990" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A990" s="9"/>
       <c r="B990" s="55"/>
       <c r="C990" s="55"/>
@@ -27250,7 +27245,7 @@
       <c r="T990" s="9"/>
       <c r="U990" s="9"/>
     </row>
-    <row r="991" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="991" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A991" s="9"/>
       <c r="B991" s="55"/>
       <c r="C991" s="55"/>
@@ -27273,7 +27268,7 @@
       <c r="T991" s="9"/>
       <c r="U991" s="9"/>
     </row>
-    <row r="992" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="992" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A992" s="9"/>
       <c r="B992" s="55"/>
       <c r="C992" s="55"/>
@@ -27296,7 +27291,7 @@
       <c r="T992" s="9"/>
       <c r="U992" s="9"/>
     </row>
-    <row r="993" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A993" s="9"/>
       <c r="B993" s="55"/>
       <c r="C993" s="55"/>
@@ -27319,7 +27314,7 @@
       <c r="T993" s="9"/>
       <c r="U993" s="9"/>
     </row>
-    <row r="994" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A994" s="9"/>
       <c r="B994" s="55"/>
       <c r="C994" s="55"/>
@@ -27342,7 +27337,7 @@
       <c r="T994" s="9"/>
       <c r="U994" s="9"/>
     </row>
-    <row r="995" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A995" s="9"/>
       <c r="B995" s="55"/>
       <c r="C995" s="55"/>
@@ -27365,7 +27360,7 @@
       <c r="T995" s="9"/>
       <c r="U995" s="9"/>
     </row>
-    <row r="996" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="996" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A996" s="9"/>
       <c r="B996" s="55"/>
       <c r="C996" s="55"/>
@@ -27388,7 +27383,7 @@
       <c r="T996" s="9"/>
       <c r="U996" s="9"/>
     </row>
-    <row r="997" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="997" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A997" s="9"/>
       <c r="B997" s="55"/>
       <c r="C997" s="55"/>
@@ -27411,7 +27406,7 @@
       <c r="T997" s="9"/>
       <c r="U997" s="9"/>
     </row>
-    <row r="998" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="998" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A998" s="9"/>
       <c r="B998" s="55"/>
       <c r="C998" s="55"/>
@@ -27434,7 +27429,7 @@
       <c r="T998" s="9"/>
       <c r="U998" s="9"/>
     </row>
-    <row r="999" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="999" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A999" s="9"/>
       <c r="B999" s="55"/>
       <c r="C999" s="55"/>
@@ -27457,7 +27452,7 @@
       <c r="T999" s="9"/>
       <c r="U999" s="9"/>
     </row>
-    <row r="1000" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1000" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1000" s="9"/>
       <c r="B1000" s="55"/>
       <c r="C1000" s="55"/>
@@ -27480,7 +27475,7 @@
       <c r="T1000" s="9"/>
       <c r="U1000" s="9"/>
     </row>
-    <row r="1001" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1001" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1001" s="9"/>
       <c r="B1001" s="55"/>
       <c r="C1001" s="55"/>
@@ -27504,71 +27499,7 @@
       <c r="U1001" s="9"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" ref="U1:U1001" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <x14:filter val="analyteColumn : analysisOrder _x000a_  datatype: positive integer_x000a_  readOnly:true"/>
-            <x14:filter val="analyteColumn : backgroundCorrectionMethod _x000a_  datatype: enum {2-point off-peak linear | 2-point off-peak exponential | 2-point off-peak polynomial | 1-point high with slope factor | 1-point low with slope factor | Multi-point linear | Multi-point exponential | Mean Atomic Number (MAN) | EDS background fit | other | N/A }_x000a_  readOnly:true"/>
-            <x14:filter val="analyteColumn : backgroundCountingPosition _x000a_  datatype: text_x000a_  readOnly:true"/>
-            <x14:filter val="analyteColumn : backgroundCountingTime _x000a_  datatype: numeric_x000a_  readOnly:true"/>
-            <x14:filter val="analyteColumn : blankCorrection _x000a_  datatype: text_x000a_  readOnly:true"/>
-            <x14:filter val="analyteColumn : edsDeadTime _x000a_  datatype: text_x000a_  readOnly:true"/>
-            <x14:filter val="analyteColumn : elementEstimationMethod _x000a_  datatype: enum {Direct (measured) | Estimated via cation stoichiometry | Unknown }_x000a_  readOnly:true"/>
-            <x14:filter val="analyteColumn : epmaTechnique _x000a_  datatype: enum {WDS | EDS} _x000a_  readOnly:true"/>
-            <x14:filter val="analyteColumn : interferenceCorrection _x000a_  datatype: boolean_x000a_  readOnly:true"/>
-            <x14:filter val="analyteColumn : interferenceCorrectionStandard _x000a_  datatype: text_x000a_  readOnly:true"/>
-            <x14:filter val="analyteColumn : interferingElements _x000a_  datatype: text_x000a_  readOnly:true"/>
-            <x14:filter val="analyteColumn : monochromatorCrystal _x000a_  datatype: enum {LIF | LLIF | LIFL | LIFH | PET | LPET | PETL | PETH | PETJ | TAP | TAPL | TAPH | LTAP | LDE1 | LDE2 | LDE3 | RAP | KAP | ADP | Other}_x000a_  readOnly:true"/>
-            <x14:filter val="analyteColumn : normalization-standardsCorrection _x000a_  datatype: text_x000a_  readOnly:true"/>
-            <x14:filter val="analyteColumn : peakCountingTime _x000a_  datatype: numeric_x000a_  readOnly:true"/>
-            <x14:filter val="analyteColumn : primaryCalibrationStandard _x000a_  datatype: text_x000a_  readOnly:true"/>
-            <x14:filter val="analyteColumn : pulseHeightAnalyzeSetting _x000a_  datatype: enum {Integral | Differential)_x000a_  readOnly:true"/>
-            <x14:filter val="analyteColumn : secondaryReferenceMaterial _x000a_  datatype: text_x000a_  readOnly:true"/>
-            <x14:filter val="analyteColumn : spectrometerNumber _x000a_  datatype: positive integer_x000a_  readOnly:true"/>
-            <x14:filter val="analyteColumn : timeDependentIntensityCorrection _x000a_  datatype: enum {None | Linear | Exponential | Double exponential | Other | Unknown }_x000a_  readOnly:true"/>
-            <x14:filter val="analyteColumn : typicalDetectionLimit _x000a_  datatype: text_x000a_  readOnly:true"/>
-            <x14:filter val="analyteColumn : wdsDetectorType _x000a_  datatype: enum {High Pressure P10 Flow | Low Pressure P10 Flow | Xe Sealed | SDD | Si(Li) | Other | Unknown}_x000a_  readOnly:true"/>
-            <x14:filter val="analyteColumn : xrayEmissionLine _x000a_  datatype: enum {Kalpha | Kbeta | Lalpha | Lbeta | Lgamma | Malpha | Mbeta | Other)_x000a_  readOnly:true"/>
-            <x14:filter val="analyteColumn :detectionLimitMethod_x000a_  datatype: text_x000a_  readOnly:true"/>
-            <x14:filter val="analyteColumn :typicalAnalyticalAccuracy_x000a_  datatype: text_x000a_  readOnly:true"/>
-            <x14:filter val="analyteColumn :typicalAnalyticalPrecision_x000a_  datatype: text_x000a_  readOnly:true"/>
-            <x14:filter val="analyteColumn :typicalCountingStatisticsError_x000a_  datatype: text_x000a_  readOnly:true"/>
-            <x14:filter val="method-level property: beamCurrentDefault _x000a_  data:type PropertyValue _x000a_  readOnly:true_x000a_analyteColumn item: beamCurrent_x000a_  datatype: PropertyValue_x000a_  readOnly: false"/>
-          </mc:Choice>
-          <mc:Fallback>
-            <filter val="analyteColumn : analysisOrder _x000a_  datatype: positive integer_x000a_  readOnly:true"/>
-            <filter val="analyteColumn : backgroundCountingPosition _x000a_  datatype: text_x000a_  readOnly:true"/>
-            <filter val="analyteColumn : backgroundCountingTime _x000a_  datatype: numeric_x000a_  readOnly:true"/>
-            <filter val="analyteColumn : blankCorrection _x000a_  datatype: text_x000a_  readOnly:true"/>
-            <filter val="analyteColumn : edsDeadTime _x000a_  datatype: text_x000a_  readOnly:true"/>
-            <filter val="analyteColumn : elementEstimationMethod _x000a_  datatype: enum {Direct (measured) | Estimated via cation stoichiometry | Unknown }_x000a_  readOnly:true"/>
-            <filter val="analyteColumn : epmaTechnique _x000a_  datatype: enum {WDS | EDS} _x000a_  readOnly:true"/>
-            <filter val="analyteColumn : interferenceCorrection _x000a_  datatype: boolean_x000a_  readOnly:true"/>
-            <filter val="analyteColumn : interferenceCorrectionStandard _x000a_  datatype: text_x000a_  readOnly:true"/>
-            <filter val="analyteColumn : interferingElements _x000a_  datatype: text_x000a_  readOnly:true"/>
-            <filter val="analyteColumn : monochromatorCrystal _x000a_  datatype: enum {LIF | LLIF | LIFL | LIFH | PET | LPET | PETL | PETH | PETJ | TAP | TAPL | TAPH | LTAP | LDE1 | LDE2 | LDE3 | RAP | KAP | ADP | Other}_x000a_  readOnly:true"/>
-            <filter val="analyteColumn : normalization-standardsCorrection _x000a_  datatype: text_x000a_  readOnly:true"/>
-            <filter val="analyteColumn : peakCountingTime _x000a_  datatype: numeric_x000a_  readOnly:true"/>
-            <filter val="analyteColumn : primaryCalibrationStandard _x000a_  datatype: text_x000a_  readOnly:true"/>
-            <filter val="analyteColumn : pulseHeightAnalyzeSetting _x000a_  datatype: enum {Integral | Differential)_x000a_  readOnly:true"/>
-            <filter val="analyteColumn : secondaryReferenceMaterial _x000a_  datatype: text_x000a_  readOnly:true"/>
-            <filter val="analyteColumn : spectrometerNumber _x000a_  datatype: positive integer_x000a_  readOnly:true"/>
-            <filter val="analyteColumn : timeDependentIntensityCorrection _x000a_  datatype: enum {None | Linear | Exponential | Double exponential | Other | Unknown }_x000a_  readOnly:true"/>
-            <filter val="analyteColumn : typicalDetectionLimit _x000a_  datatype: text_x000a_  readOnly:true"/>
-            <filter val="analyteColumn : wdsDetectorType _x000a_  datatype: enum {High Pressure P10 Flow | Low Pressure P10 Flow | Xe Sealed | SDD | Si(Li) | Other | Unknown}_x000a_  readOnly:true"/>
-            <filter val="analyteColumn : xrayEmissionLine _x000a_  datatype: enum {Kalpha | Kbeta | Lalpha | Lbeta | Lgamma | Malpha | Mbeta | Other)_x000a_  readOnly:true"/>
-            <filter val="analyteColumn :detectionLimitMethod_x000a_  datatype: text_x000a_  readOnly:true"/>
-            <filter val="analyteColumn :typicalAnalyticalAccuracy_x000a_  datatype: text_x000a_  readOnly:true"/>
-            <filter val="analyteColumn :typicalAnalyticalPrecision_x000a_  datatype: text_x000a_  readOnly:true"/>
-            <filter val="analyteColumn :typicalCountingStatisticsError_x000a_  datatype: text_x000a_  readOnly:true"/>
-            <filter val="method-level property: beamCurrentDefault _x000a_  data:type PropertyValue _x000a_  readOnly:true_x000a_analyteColumn item: beamCurrent_x000a_  datatype: PropertyValue_x000a_  readOnly: false"/>
-          </mc:Fallback>
-        </mc:AlternateContent>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="U1:U1001" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="6">
     <mergeCell ref="A58:E58"/>
     <mergeCell ref="A12:E12"/>

--- a/docs/TAPP_EPMA_filled.xlsx
+++ b/docs/TAPP_EPMA_filled.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/944a82e2ddcde9eb/Documents/GithubC/USGIN/geochemBuildingBlocks/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="337" documentId="11_3C209AD99577444EEF615C96566D1EBF266D99FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFCCCE89-5B1D-4910-A98A-75EB0BAE74D6}"/>
+  <xr:revisionPtr revIDLastSave="349" documentId="11_3C209AD99577444EEF615C96566D1EBF266D99FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6A35475-C27D-4DA8-B536-B98FBD718235}"/>
   <bookViews>
-    <workbookView xWindow="165" yWindow="1335" windowWidth="22350" windowHeight="14610" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="165" yWindow="1335" windowWidth="27615" windowHeight="14610" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TAPP" sheetId="1" r:id="rId1"/>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="469">
   <si>
     <t>Metadata Item</t>
   </si>
@@ -1619,6 +1619,19 @@
     <t>parameter: BeamRasterDimension
   dataType: schema:PropertyValue
   readOnly: False</t>
+  </si>
+  <si>
+    <t>P0: synthetic Example, 2026
+(Richard and Deng, 2026 )</t>
+  </si>
+  <si>
+    <t>EPMA-WDS major/minor element silicate and oxide, all properties</t>
+  </si>
+  <si>
+    <t>Richard, S.M. ORCID:0000-0001-6041-5302; Deng, Ruolin ORCID:0000-0001-5383-3039</t>
+  </si>
+  <si>
+    <t>IEDA, Columbia University</t>
   </si>
 </sst>
 </file>
@@ -2744,6 +2757,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -2929,13 +2946,13 @@
     <col min="4" max="4" width="16.85546875" style="58" customWidth="1"/>
     <col min="5" max="5" width="26.140625" style="32" customWidth="1"/>
     <col min="6" max="6" width="7.85546875" style="4" customWidth="1"/>
-    <col min="7" max="7" width="28.28515625" style="4" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="28.28515625" style="167" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="28.28515625" style="58" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="36.85546875" style="58" hidden="1" customWidth="1"/>
-    <col min="11" max="14" width="28.28515625" style="58" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="33.42578125" style="58" hidden="1" customWidth="1"/>
-    <col min="16" max="17" width="28.28515625" style="58" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="28.28515625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="28.28515625" style="167" customWidth="1"/>
+    <col min="9" max="9" width="28.28515625" style="58" customWidth="1"/>
+    <col min="10" max="10" width="36.85546875" style="58" customWidth="1"/>
+    <col min="11" max="14" width="28.28515625" style="58" customWidth="1"/>
+    <col min="15" max="15" width="33.42578125" style="58" customWidth="1"/>
+    <col min="16" max="17" width="28.28515625" style="58" customWidth="1"/>
     <col min="18" max="18" width="28.28515625" style="168" customWidth="1"/>
     <col min="19" max="19" width="37.140625" style="4" customWidth="1"/>
     <col min="20" max="20" width="49.140625" style="4" customWidth="1"/>
@@ -2962,7 +2979,9 @@
       <c r="F1" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="G1" s="2"/>
+      <c r="G1" s="112" t="s">
+        <v>465</v>
+      </c>
       <c r="H1" s="112" t="s">
         <v>5</v>
       </c>
@@ -3048,7 +3067,9 @@
         <v>23</v>
       </c>
       <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
+      <c r="G3" s="117" t="s">
+        <v>466</v>
+      </c>
       <c r="H3" s="117" t="s">
         <v>24</v>
       </c>
@@ -3108,7 +3129,9 @@
         <v>32</v>
       </c>
       <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
+      <c r="G4" s="119" t="s">
+        <v>33</v>
+      </c>
       <c r="H4" s="119" t="s">
         <v>33</v>
       </c>
@@ -3170,7 +3193,9 @@
         <v>36</v>
       </c>
       <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
+      <c r="G5" s="69" t="s">
+        <v>467</v>
+      </c>
       <c r="H5" s="119" t="s">
         <v>37</v>
       </c>
@@ -3230,7 +3255,9 @@
         <v>48</v>
       </c>
       <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
+      <c r="G6" s="68" t="s">
+        <v>468</v>
+      </c>
       <c r="H6" s="119" t="s">
         <v>49</v>
       </c>
@@ -27509,6 +27536,26 @@
     <mergeCell ref="A45:E45"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B66 A70:E70 C1:D68 E1:E7 E9:E66">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF57BB8A"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:R7 H9:R9">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF57BB8A"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H10:R10">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -27518,7 +27565,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:R7 H9:R9">
+  <conditionalFormatting sqref="H13:R14">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF57BB8A"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H17:R23">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -27528,7 +27585,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H10:R10">
+  <conditionalFormatting sqref="H26:R43">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -27538,7 +27595,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H13:R14">
+  <conditionalFormatting sqref="H46:R58">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -27548,7 +27605,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H17:R23">
+  <conditionalFormatting sqref="H59:R66">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -27558,7 +27615,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H26:R43">
+  <conditionalFormatting sqref="G3">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -27568,7 +27625,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H46:R58">
+  <conditionalFormatting sqref="G4">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -27578,7 +27635,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H59:R66">
+  <conditionalFormatting sqref="G6">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/docs/TAPP_EPMA_filled.xlsx
+++ b/docs/TAPP_EPMA_filled.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/944a82e2ddcde9eb/Documents/GithubC/USGIN/geochemBuildingBlocks/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="349" documentId="11_3C209AD99577444EEF615C96566D1EBF266D99FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6A35475-C27D-4DA8-B536-B98FBD718235}"/>
+  <xr:revisionPtr revIDLastSave="432" documentId="11_3C209AD99577444EEF615C96566D1EBF266D99FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E51B3F03-4ACE-4A76-B070-DA59C3677AFD}"/>
   <bookViews>
     <workbookView xWindow="165" yWindow="1335" windowWidth="27615" windowHeight="14610" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="508">
   <si>
     <t>Metadata Item</t>
   </si>
@@ -686,9 +686,6 @@
   </si>
   <si>
     <t>e.g., Si | Fe | Mn | Ti | Ba | Sr | ...</t>
-  </si>
-  <si>
-    <t>Specify what is measured, and in what format, or what kind of signal is being collected.</t>
   </si>
   <si>
     <t>$.ada:analyteTemplate.ada:defaultAnalytes[]</t>
@@ -1542,16 +1539,6 @@
 Synthetic Mn-olivine (Mn Kα)</t>
   </si>
   <si>
-    <t>Anorthite (Si Kα, Al Kα, Ca Kα); 
-Albite (Na Kα); 
-Fayalite (Fe Kα); 
-Forsterite (Mg Kα); 
-Mn2SiO4 (Mn Kα); 
-TiO2 (Ti Kα); 
-Cr2O3 (Cr Kα); 
-Microcline (K Kα)</t>
-  </si>
-  <si>
     <t>20 nA (X-ray maps/BSE); 
 20 nA silicates/sulfides/oxides;
 8 nA phosphates; 
@@ -1632,6 +1619,133 @@
   </si>
   <si>
     <t>IEDA, Columbia University</t>
+  </si>
+  <si>
+    <t>https://ror.org/02fjjnc15</t>
+  </si>
+  <si>
+    <t>NSF EAR-1234567</t>
+  </si>
+  <si>
+    <t>https://example.org/EMPA/WDS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feldspar, Pyroxene, Olivine </t>
+  </si>
+  <si>
+    <t>25 mm epoxy mount, polished to 0.25 µm diamond, 20 nm C coat</t>
+  </si>
+  <si>
+    <t>Probe for EPMA v12.9.5</t>
+  </si>
+  <si>
+    <t>Cameca PeakSight, CalcZAF</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SXFiveFE </t>
+  </si>
+  <si>
+    <t>Spectrometer number|Orientation|Crystals|Notes
+SP1|Inclined|LiF, PET, TAP, PC2|Less sensitive to specimen height; good for rough surfaces; low pressure
+SP2|Vertical|LLiF, LPET|High pressure for greater sensitivity; large crystals for trace/light elements
+SP3|Vertical|TAP, PC0|Low pressure; light element coverage
+SP4|Vertical|LPET, TAP|Low pressure</t>
+  </si>
+  <si>
+    <t>10 by 10</t>
+  </si>
+  <si>
+    <t>None required (anhydrous minerals)</t>
+  </si>
+  <si>
+    <t>Primary major element reference materials are run at beginning and end of every analytical session and the calibration is interpolated</t>
+  </si>
+  <si>
+    <t>Si,Al,K,Ca,Na,Fe,Mg,Ti,Cr,Mn</t>
+  </si>
+  <si>
+    <t>WDS</t>
+  </si>
+  <si>
+    <t>2,2,2,2,2,4,3,1,1,1</t>
+  </si>
+  <si>
+    <t>LPET,LPET,LLIF,LLIF,LPET,LPET,TAP,LiF,LiF,LiF</t>
+  </si>
+  <si>
+    <t>1,4,3,2</t>
+  </si>
+  <si>
+    <t>High Pressure P10 Flow,High Pressure P10 Flow,High Pressure P10 Flow,High Pressure P10 Flow,High Pressure P10 Flow, Low Pressure P10 Flow,Low Pressure P10 Flow,Low Pressure P10 Flow,Low Pressure P10 Flow,Low Pressure P10 Flow</t>
+  </si>
+  <si>
+    <t>Integral</t>
+  </si>
+  <si>
+    <t>+5 mm (High)</t>
+  </si>
+  <si>
+    <t>Kalpha</t>
+  </si>
+  <si>
+    <t>20,20,20,20,30,20,20,60,60,60</t>
+  </si>
+  <si>
+    <t>Armstrong/Love-Scott</t>
+  </si>
+  <si>
+    <t>MCMASTER</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Super-precision</t>
+  </si>
+  <si>
+    <t>single-sample mean; quartz</t>
+  </si>
+  <si>
+    <t>Single-sample normalization to JdF-D2 basalt glass</t>
+  </si>
+  <si>
+    <t>10-12 %</t>
+  </si>
+  <si>
+    <t>1-point low with slope factor</t>
+  </si>
+  <si>
+    <t>Linear, Linear, Linear, Linear, Linear,Exponential, Double exponential,Double exponential,Double exponential,Exponential</t>
+  </si>
+  <si>
+    <t>Direct (measured)</t>
+  </si>
+  <si>
+    <t>Anorthite,Anorthite,K-feldspar,Anorthite,Jadeite,Fayalite,Forsterite,Synthetic rutile,Cr2O3,Mn2SiO4</t>
+  </si>
+  <si>
+    <t>USNM 111240/52 VG-2</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>0.01 wt%</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A.B., 1997</t>
+  </si>
+  <si>
+    <t>0.5% (1σ, n=20 for SiO2),,,,,,,,,</t>
+  </si>
+  <si>
+    <t>1.2% relative to GeoReM preferred value for VG-2 SiO2,,,,,,,,,</t>
+  </si>
+  <si>
+    <t>Additional context about this method.</t>
   </si>
 </sst>
 </file>
@@ -1641,7 +1755,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1746,6 +1860,13 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -2157,11 +2278,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="181">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2671,8 +2793,15 @@
     <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -2945,8 +3074,8 @@
     <col min="3" max="3" width="14.7109375" style="58" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.85546875" style="58" customWidth="1"/>
     <col min="5" max="5" width="26.140625" style="32" customWidth="1"/>
-    <col min="6" max="6" width="7.85546875" style="4" customWidth="1"/>
-    <col min="7" max="7" width="28.28515625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="43.7109375" style="4" customWidth="1"/>
     <col min="8" max="8" width="28.28515625" style="167" customWidth="1"/>
     <col min="9" max="9" width="28.28515625" style="58" customWidth="1"/>
     <col min="10" max="10" width="36.85546875" style="58" customWidth="1"/>
@@ -2977,10 +3106,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G1" s="112" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="H1" s="112" t="s">
         <v>5</v>
@@ -3022,7 +3151,7 @@
         <v>17</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.2">
@@ -3068,7 +3197,7 @@
       </c>
       <c r="F3" s="63"/>
       <c r="G3" s="117" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="H3" s="117" t="s">
         <v>24</v>
@@ -3105,10 +3234,10 @@
         <v>1</v>
       </c>
       <c r="S3" s="63" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="T3" s="169" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="U3" s="63"/>
     </row>
@@ -3167,13 +3296,13 @@
         <v>1</v>
       </c>
       <c r="S4" s="69" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="T4" s="170" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="U4" s="69" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="5" spans="1:21" s="70" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
@@ -3194,7 +3323,7 @@
       </c>
       <c r="F5" s="69"/>
       <c r="G5" s="69" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H5" s="119" t="s">
         <v>37</v>
@@ -3231,10 +3360,10 @@
         <v>1</v>
       </c>
       <c r="S5" s="69" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="T5" s="170" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="U5" s="69"/>
     </row>
@@ -3256,7 +3385,7 @@
       </c>
       <c r="F6" s="69"/>
       <c r="G6" s="68" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="H6" s="119" t="s">
         <v>49</v>
@@ -3293,10 +3422,10 @@
         <v>1</v>
       </c>
       <c r="S6" s="69" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="T6" s="170" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="U6" s="69"/>
     </row>
@@ -3317,7 +3446,9 @@
         <v>62</v>
       </c>
       <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
+      <c r="G7" s="69" t="s">
+        <v>467</v>
+      </c>
       <c r="H7" s="121"/>
       <c r="I7" s="72"/>
       <c r="J7" s="72"/>
@@ -3333,10 +3464,10 @@
         <v>0</v>
       </c>
       <c r="S7" s="69" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="T7" s="170" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="U7" s="69"/>
     </row>
@@ -3357,7 +3488,9 @@
         <v>46082</v>
       </c>
       <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
+      <c r="G8" s="181">
+        <v>46140</v>
+      </c>
       <c r="H8" s="123"/>
       <c r="I8" s="124"/>
       <c r="J8" s="124"/>
@@ -3373,10 +3506,10 @@
         <v>0</v>
       </c>
       <c r="S8" s="69" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="T8" s="170" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="U8" s="69"/>
     </row>
@@ -3397,7 +3530,9 @@
         <v>68</v>
       </c>
       <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
+      <c r="G9" s="69" t="s">
+        <v>468</v>
+      </c>
       <c r="H9" s="121"/>
       <c r="I9" s="72"/>
       <c r="J9" s="72"/>
@@ -3413,13 +3548,13 @@
         <v>0</v>
       </c>
       <c r="S9" s="69" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="T9" s="170" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="U9" s="69" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="10" spans="1:21" s="70" customFormat="1" ht="42.75" x14ac:dyDescent="0.2">
@@ -3439,7 +3574,9 @@
         <v>72</v>
       </c>
       <c r="F10" s="69"/>
-      <c r="G10" s="69"/>
+      <c r="G10" s="182" t="s">
+        <v>469</v>
+      </c>
       <c r="H10" s="121"/>
       <c r="I10" s="72"/>
       <c r="J10" s="72"/>
@@ -3455,10 +3592,10 @@
         <v>0</v>
       </c>
       <c r="S10" s="69" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="T10" s="170" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="U10" s="69"/>
     </row>
@@ -3527,12 +3664,14 @@
         <v>77</v>
       </c>
       <c r="F13" s="69"/>
-      <c r="G13" s="69"/>
+      <c r="G13" s="69" t="s">
+        <v>470</v>
+      </c>
       <c r="H13" s="129" t="s">
         <v>78</v>
       </c>
       <c r="I13" s="81" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="J13" s="81" t="s">
         <v>79</v>
@@ -3563,10 +3702,10 @@
         <v>1</v>
       </c>
       <c r="S13" s="69" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="T13" s="69" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="U13" s="69"/>
     </row>
@@ -3587,7 +3726,9 @@
         <v>89</v>
       </c>
       <c r="F14" s="69"/>
-      <c r="G14" s="69"/>
+      <c r="G14" s="69" t="s">
+        <v>471</v>
+      </c>
       <c r="H14" s="131" t="s">
         <v>90</v>
       </c>
@@ -3623,13 +3764,13 @@
         <v>1</v>
       </c>
       <c r="S14" s="69" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="T14" s="69" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="U14" s="69" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="15" spans="1:21" s="70" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -3697,7 +3838,9 @@
         <v>103</v>
       </c>
       <c r="F17" s="69"/>
-      <c r="G17" s="69"/>
+      <c r="G17" s="69" t="s">
+        <v>106</v>
+      </c>
       <c r="H17" s="133" t="s">
         <v>104</v>
       </c>
@@ -3733,10 +3876,10 @@
         <v>1</v>
       </c>
       <c r="S17" s="69" t="s">
+        <v>419</v>
+      </c>
+      <c r="T17" s="170" t="s">
         <v>420</v>
-      </c>
-      <c r="T17" s="170" t="s">
-        <v>421</v>
       </c>
       <c r="U17" s="69"/>
     </row>
@@ -3757,7 +3900,9 @@
         <v>110</v>
       </c>
       <c r="F18" s="69"/>
-      <c r="G18" s="69"/>
+      <c r="G18" s="69" t="s">
+        <v>474</v>
+      </c>
       <c r="H18" s="133" t="s">
         <v>111</v>
       </c>
@@ -3793,10 +3938,10 @@
         <v>1</v>
       </c>
       <c r="S18" s="69" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="T18" s="170" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="U18" s="69"/>
     </row>
@@ -3817,7 +3962,9 @@
         <v>121</v>
       </c>
       <c r="F19" s="69"/>
-      <c r="G19" s="69"/>
+      <c r="G19" s="69" t="s">
+        <v>122</v>
+      </c>
       <c r="H19" s="133"/>
       <c r="I19" s="89"/>
       <c r="J19" s="89"/>
@@ -3837,10 +3984,10 @@
         <v>0.2</v>
       </c>
       <c r="S19" s="69" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="T19" s="69" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="U19" s="69"/>
     </row>
@@ -3861,7 +4008,9 @@
         <v>125</v>
       </c>
       <c r="F20" s="69"/>
-      <c r="G20" s="69"/>
+      <c r="G20" s="69" t="s">
+        <v>472</v>
+      </c>
       <c r="H20" s="133" t="s">
         <v>126</v>
       </c>
@@ -3885,13 +4034,13 @@
         <v>0.4</v>
       </c>
       <c r="S20" s="69" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="T20" s="170" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="U20" s="69" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="21" spans="1:21" s="70" customFormat="1" ht="57" x14ac:dyDescent="0.2">
@@ -3911,7 +4060,9 @@
         <v>131</v>
       </c>
       <c r="F21" s="69"/>
-      <c r="G21" s="69"/>
+      <c r="G21" s="69" t="s">
+        <v>473</v>
+      </c>
       <c r="H21" s="133" t="s">
         <v>132</v>
       </c>
@@ -3939,16 +4090,16 @@
         <v>0.6</v>
       </c>
       <c r="S21" s="69" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="T21" s="170" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="U21" s="69" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" s="70" customFormat="1" ht="57" x14ac:dyDescent="0.2">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" s="70" customFormat="1" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A22" s="92" t="s">
         <v>136</v>
       </c>
@@ -3965,7 +4116,9 @@
         <v>138</v>
       </c>
       <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
+      <c r="G22" s="69" t="s">
+        <v>475</v>
+      </c>
       <c r="H22" s="135"/>
       <c r="I22" s="93"/>
       <c r="J22" s="93"/>
@@ -3983,13 +4136,13 @@
         <v>0.1</v>
       </c>
       <c r="S22" s="69" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="T22" s="69" t="s">
         <v>140</v>
       </c>
       <c r="U22" s="69" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="23" spans="1:21" s="70" customFormat="1" ht="57" x14ac:dyDescent="0.2">
@@ -4027,13 +4180,13 @@
         <v>0.1</v>
       </c>
       <c r="S23" s="69" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="T23" s="69" t="s">
         <v>145</v>
       </c>
       <c r="U23" s="69" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="24" spans="1:21" s="70" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
@@ -4101,7 +4254,9 @@
         <v>149</v>
       </c>
       <c r="F26" s="69"/>
-      <c r="G26" s="69"/>
+      <c r="G26" s="69" t="s">
+        <v>150</v>
+      </c>
       <c r="H26" s="137" t="s">
         <v>150</v>
       </c>
@@ -4137,13 +4292,13 @@
         <v>1</v>
       </c>
       <c r="S26" s="69" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="T26" s="170" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="U26" s="171" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="27" spans="1:21" s="70" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
@@ -4163,7 +4318,9 @@
         <v>160</v>
       </c>
       <c r="F27" s="69"/>
-      <c r="G27" s="69"/>
+      <c r="G27" s="69">
+        <v>20</v>
+      </c>
       <c r="H27" s="137" t="s">
         <v>161</v>
       </c>
@@ -4199,13 +4356,13 @@
         <v>1</v>
       </c>
       <c r="S27" s="101" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="T27" s="170" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="U27" s="171" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="28" spans="1:21" s="70" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
@@ -4225,7 +4382,9 @@
         <v>167</v>
       </c>
       <c r="F28" s="69"/>
-      <c r="G28" s="69"/>
+      <c r="G28" s="69">
+        <v>5</v>
+      </c>
       <c r="H28" s="137" t="s">
         <v>168</v>
       </c>
@@ -4259,13 +4418,13 @@
         <v>0.9</v>
       </c>
       <c r="S28" s="101" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="T28" s="170" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="U28" s="171" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="29" spans="1:21" s="70" customFormat="1" ht="51" x14ac:dyDescent="0.2">
@@ -4285,7 +4444,9 @@
         <v>178</v>
       </c>
       <c r="F29" s="69"/>
-      <c r="G29" s="69"/>
+      <c r="G29" s="69" t="s">
+        <v>476</v>
+      </c>
       <c r="H29" s="139"/>
       <c r="I29" s="103"/>
       <c r="J29" s="103"/>
@@ -4307,7 +4468,7 @@
         <v>179</v>
       </c>
       <c r="U29" s="69" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="30" spans="1:21" s="70" customFormat="1" ht="85.5" x14ac:dyDescent="0.2">
@@ -4327,7 +4488,9 @@
         <v>182</v>
       </c>
       <c r="F30" s="69"/>
-      <c r="G30" s="69"/>
+      <c r="G30" s="69" t="s">
+        <v>477</v>
+      </c>
       <c r="H30" s="139"/>
       <c r="I30" s="103"/>
       <c r="J30" s="103"/>
@@ -4353,7 +4516,7 @@
         <v>186</v>
       </c>
       <c r="U30" s="69" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="31" spans="1:21" s="111" customFormat="1" ht="100.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -4373,7 +4536,9 @@
         <v>189</v>
       </c>
       <c r="F31" s="110"/>
-      <c r="G31" s="110"/>
+      <c r="G31" s="110" t="s">
+        <v>478</v>
+      </c>
       <c r="H31" s="141"/>
       <c r="I31" s="107"/>
       <c r="J31" s="107"/>
@@ -4395,7 +4560,7 @@
         <v>190</v>
       </c>
       <c r="U31" s="110" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="32" spans="1:21" ht="234" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -4416,7 +4581,7 @@
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>194</v>
+        <v>479</v>
       </c>
       <c r="H32" s="143"/>
       <c r="I32" s="36"/>
@@ -4433,64 +4598,66 @@
         <v>0</v>
       </c>
       <c r="S32" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="T32" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="U32" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="33" spans="1:21" ht="77.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="B33" s="36" t="s">
         <v>196</v>
-      </c>
-      <c r="B33" s="36" t="s">
-        <v>197</v>
       </c>
       <c r="C33" s="38" t="s">
         <v>21</v>
       </c>
       <c r="D33" s="36" t="s">
+        <v>197</v>
+      </c>
+      <c r="E33" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="E33" s="21" t="s">
+      <c r="F33" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="G33" s="3">
+        <v>10</v>
+      </c>
+      <c r="H33" s="143" t="s">
         <v>199</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="G33" s="3"/>
-      <c r="H33" s="143" t="s">
+      <c r="I33" s="36" t="s">
         <v>200</v>
       </c>
-      <c r="I33" s="36" t="s">
-        <v>201</v>
-      </c>
       <c r="J33" s="36" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="K33" s="36" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L33" s="36" t="s">
         <v>162</v>
       </c>
       <c r="M33" s="36" t="s">
+        <v>201</v>
+      </c>
+      <c r="N33" s="36" t="s">
         <v>202</v>
       </c>
-      <c r="N33" s="36" t="s">
-        <v>203</v>
-      </c>
       <c r="O33" s="36" t="s">
+        <v>447</v>
+      </c>
+      <c r="P33" s="36" t="s">
         <v>449</v>
       </c>
-      <c r="P33" s="36" t="s">
-        <v>451</v>
-      </c>
       <c r="Q33" s="36" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="R33" s="144">
         <f t="shared" si="2"/>
@@ -4500,18 +4667,18 @@
         <v>163</v>
       </c>
       <c r="T33" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="U33" s="3" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="B34" s="36" t="s">
         <v>204</v>
-      </c>
-      <c r="B34" s="36" t="s">
-        <v>205</v>
       </c>
       <c r="C34" s="38" t="s">
         <v>21</v>
@@ -4520,76 +4687,80 @@
         <v>31</v>
       </c>
       <c r="E34" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="H34" s="143" t="s">
         <v>206</v>
       </c>
-      <c r="F34" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="G34" s="3"/>
-      <c r="H34" s="143" t="s">
-        <v>207</v>
-      </c>
       <c r="I34" s="36" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J34" s="36" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K34" s="36" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L34" s="36" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M34" s="36" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="N34" s="36" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O34" s="36" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P34" s="36" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q34" s="36" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R34" s="144">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S34" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="T34" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="T34" s="3" t="s">
-        <v>209</v>
-      </c>
       <c r="U34" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="35" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="B35" s="39" t="s">
         <v>210</v>
-      </c>
-      <c r="B35" s="39" t="s">
-        <v>211</v>
       </c>
       <c r="C35" s="40" t="s">
         <v>60</v>
       </c>
       <c r="D35" s="39" t="s">
+        <v>211</v>
+      </c>
+      <c r="E35" s="22" t="s">
         <v>212</v>
       </c>
-      <c r="E35" s="22" t="s">
-        <v>213</v>
-      </c>
       <c r="F35" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="G35" s="3"/>
+        <v>441</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="H35" s="145"/>
       <c r="I35" s="39"/>
       <c r="J35" s="39"/>
@@ -4605,35 +4776,37 @@
         <v>0</v>
       </c>
       <c r="S35" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T35" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="U35" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="36" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="B36" s="39" t="s">
         <v>215</v>
-      </c>
-      <c r="B36" s="39" t="s">
-        <v>216</v>
       </c>
       <c r="C36" s="40" t="s">
         <v>60</v>
       </c>
       <c r="D36" s="39" t="s">
+        <v>211</v>
+      </c>
+      <c r="E36" s="22" t="s">
         <v>212</v>
       </c>
-      <c r="E36" s="22" t="s">
-        <v>213</v>
-      </c>
       <c r="F36" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="G36" s="3"/>
+        <v>441</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>483</v>
+      </c>
       <c r="H36" s="145"/>
       <c r="I36" s="39"/>
       <c r="J36" s="39"/>
@@ -4649,21 +4822,21 @@
         <v>0</v>
       </c>
       <c r="S36" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T36" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="U36" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="37" spans="1:21" ht="86.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="B37" s="36" t="s">
         <v>218</v>
-      </c>
-      <c r="B37" s="36" t="s">
-        <v>219</v>
       </c>
       <c r="C37" s="37" t="s">
         <v>21</v>
@@ -4672,19 +4845,21 @@
         <v>31</v>
       </c>
       <c r="E37" s="21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="G37" s="3"/>
+        <v>441</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>482</v>
+      </c>
       <c r="H37" s="143"/>
       <c r="I37" s="36"/>
       <c r="J37" s="36"/>
       <c r="K37" s="36"/>
       <c r="L37" s="36"/>
       <c r="M37" s="36" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="N37" s="36"/>
       <c r="O37" s="36"/>
@@ -4695,21 +4870,21 @@
         <v>0.1</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T37" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="U37" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" ht="77.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="U37" s="3" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="13" t="s">
+      <c r="B38" s="39" t="s">
         <v>223</v>
-      </c>
-      <c r="B38" s="39" t="s">
-        <v>224</v>
       </c>
       <c r="C38" s="40" t="s">
         <v>60</v>
@@ -4718,12 +4893,14 @@
         <v>31</v>
       </c>
       <c r="E38" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="G38" s="3"/>
+        <v>441</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>484</v>
+      </c>
       <c r="H38" s="145"/>
       <c r="I38" s="39"/>
       <c r="J38" s="39"/>
@@ -4739,21 +4916,21 @@
         <v>0</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T38" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="B39" s="39" t="s">
         <v>227</v>
-      </c>
-      <c r="B39" s="39" t="s">
-        <v>228</v>
       </c>
       <c r="C39" s="40" t="s">
         <v>60</v>
@@ -4762,12 +4939,14 @@
         <v>31</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="G39" s="3"/>
+        <v>441</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>485</v>
+      </c>
       <c r="H39" s="145"/>
       <c r="I39" s="39"/>
       <c r="J39" s="39"/>
@@ -4783,21 +4962,21 @@
         <v>0</v>
       </c>
       <c r="S39" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T39" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="U39" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="129" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="B40" s="36" t="s">
         <v>231</v>
-      </c>
-      <c r="B40" s="36" t="s">
-        <v>232</v>
       </c>
       <c r="C40" s="38" t="s">
         <v>21</v>
@@ -4806,19 +4985,19 @@
         <v>31</v>
       </c>
       <c r="E40" s="21" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="G40" s="3"/>
-      <c r="H40" s="143" t="s">
-        <v>448</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="H40" s="143"/>
       <c r="I40" s="36"/>
       <c r="J40" s="36"/>
       <c r="K40" s="36" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="L40" s="36"/>
       <c r="M40" s="36"/>
@@ -4828,38 +5007,40 @@
       <c r="Q40" s="36"/>
       <c r="R40" s="144">
         <f t="shared" si="2"/>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="S40" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="U40" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="41" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="B41" s="36" t="s">
         <v>237</v>
-      </c>
-      <c r="B41" s="36" t="s">
-        <v>238</v>
       </c>
       <c r="C41" s="38" t="s">
         <v>21</v>
       </c>
       <c r="D41" s="36" t="s">
+        <v>238</v>
+      </c>
+      <c r="E41" s="21" t="s">
         <v>239</v>
       </c>
-      <c r="E41" s="21" t="s">
-        <v>240</v>
-      </c>
       <c r="F41" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="G41" s="3"/>
+        <v>441</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>488</v>
+      </c>
       <c r="H41" s="143" t="s">
         <v>162</v>
       </c>
@@ -4869,14 +5050,14 @@
         <v>162</v>
       </c>
       <c r="L41" s="36" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M41" s="36"/>
       <c r="N41" s="36" t="s">
+        <v>241</v>
+      </c>
+      <c r="O41" s="36" t="s">
         <v>242</v>
-      </c>
-      <c r="O41" s="36" t="s">
-        <v>243</v>
       </c>
       <c r="P41" s="36"/>
       <c r="Q41" s="36"/>
@@ -4885,50 +5066,52 @@
         <v>0.5</v>
       </c>
       <c r="S41" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="T41" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>245</v>
-      </c>
       <c r="U41" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="B42" s="36" t="s">
         <v>246</v>
-      </c>
-      <c r="B42" s="36" t="s">
-        <v>247</v>
       </c>
       <c r="C42" s="38" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="36" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E42" s="21" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="G42" s="3"/>
+        <v>441</v>
+      </c>
+      <c r="G42" s="3">
+        <v>10</v>
+      </c>
       <c r="H42" s="143" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I42" s="36"/>
       <c r="J42" s="36"/>
       <c r="K42" s="36" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L42" s="36"/>
       <c r="M42" s="36"/>
       <c r="N42" s="36" t="s">
+        <v>248</v>
+      </c>
+      <c r="O42" s="36" t="s">
         <v>249</v>
-      </c>
-      <c r="O42" s="36" t="s">
-        <v>250</v>
       </c>
       <c r="P42" s="36"/>
       <c r="Q42" s="36"/>
@@ -4937,35 +5120,37 @@
         <v>0.4</v>
       </c>
       <c r="S42" s="11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="T42" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="U42" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="72" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="B43" s="39" t="s">
         <v>252</v>
-      </c>
-      <c r="B43" s="39" t="s">
-        <v>253</v>
       </c>
       <c r="C43" s="40" t="s">
         <v>60</v>
       </c>
       <c r="D43" s="39" t="s">
+        <v>253</v>
+      </c>
+      <c r="E43" s="22" t="s">
         <v>254</v>
       </c>
-      <c r="E43" s="22" t="s">
-        <v>255</v>
-      </c>
       <c r="F43" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="G43" s="3"/>
+        <v>441</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>486</v>
+      </c>
       <c r="H43" s="145"/>
       <c r="I43" s="39"/>
       <c r="J43" s="39"/>
@@ -4981,13 +5166,13 @@
         <v>0</v>
       </c>
       <c r="S43" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T43" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="U43" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="44" spans="1:21" ht="14.25" x14ac:dyDescent="0.2">
@@ -5015,7 +5200,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A45" s="180" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B45" s="173"/>
       <c r="C45" s="173"/>
@@ -5040,10 +5225,10 @@
     </row>
     <row r="46" spans="1:21" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="B46" s="41" t="s">
         <v>258</v>
-      </c>
-      <c r="B46" s="41" t="s">
-        <v>259</v>
       </c>
       <c r="C46" s="35" t="s">
         <v>21</v>
@@ -5052,54 +5237,56 @@
         <v>31</v>
       </c>
       <c r="E46" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="H46" s="147" t="s">
         <v>260</v>
       </c>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="147" t="s">
+      <c r="I46" s="41" t="s">
         <v>261</v>
-      </c>
-      <c r="I46" s="41" t="s">
-        <v>262</v>
       </c>
       <c r="J46" s="41"/>
       <c r="K46" s="41" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L46" s="41"/>
       <c r="M46" s="41" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="N46" s="41"/>
       <c r="O46" s="41" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P46" s="41" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q46" s="41" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="R46" s="148">
         <f t="shared" ref="R46:R56" si="3">COUNTA(H46:Q46)/10</f>
         <v>0.7</v>
       </c>
       <c r="S46" s="11" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="T46" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="47" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="B47" s="41" t="s">
         <v>265</v>
-      </c>
-      <c r="B47" s="41" t="s">
-        <v>266</v>
       </c>
       <c r="C47" s="42" t="s">
         <v>21</v>
@@ -5108,10 +5295,12 @@
         <v>31</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
+      <c r="G47" s="3" t="s">
+        <v>490</v>
+      </c>
       <c r="H47" s="147"/>
       <c r="I47" s="41"/>
       <c r="J47" s="41"/>
@@ -5130,40 +5319,42 @@
         <v>156</v>
       </c>
       <c r="T47" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="U47" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="48" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A48" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="B48" s="43" t="s">
         <v>269</v>
-      </c>
-      <c r="B48" s="43" t="s">
-        <v>270</v>
       </c>
       <c r="C48" s="44" t="s">
         <v>60</v>
       </c>
       <c r="D48" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="E48" s="24" t="s">
         <v>271</v>
       </c>
-      <c r="E48" s="24" t="s">
-        <v>272</v>
-      </c>
       <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
+      <c r="G48" s="3" t="s">
+        <v>491</v>
+      </c>
       <c r="H48" s="149"/>
       <c r="I48" s="43"/>
       <c r="J48" s="43"/>
       <c r="K48" s="43"/>
       <c r="L48" s="43"/>
       <c r="M48" s="43" t="s">
+        <v>272</v>
+      </c>
+      <c r="N48" s="43" t="s">
         <v>273</v>
-      </c>
-      <c r="N48" s="43" t="s">
-        <v>274</v>
       </c>
       <c r="O48" s="43"/>
       <c r="P48" s="43"/>
@@ -5176,18 +5367,18 @@
         <v>156</v>
       </c>
       <c r="T48" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="U48" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="49" spans="1:21" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="B49" s="41" t="s">
         <v>276</v>
-      </c>
-      <c r="B49" s="41" t="s">
-        <v>277</v>
       </c>
       <c r="C49" s="42" t="s">
         <v>21</v>
@@ -5196,10 +5387,12 @@
         <v>31</v>
       </c>
       <c r="E49" s="23" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
+      <c r="G49" s="3" t="s">
+        <v>492</v>
+      </c>
       <c r="H49" s="147"/>
       <c r="I49" s="41"/>
       <c r="J49" s="41"/>
@@ -5218,18 +5411,18 @@
         <v>156</v>
       </c>
       <c r="T49" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="U49" s="3" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="50" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="B50" s="43" t="s">
         <v>280</v>
-      </c>
-      <c r="B50" s="43" t="s">
-        <v>281</v>
       </c>
       <c r="C50" s="44" t="s">
         <v>60</v>
@@ -5238,7 +5431,7 @@
         <v>31</v>
       </c>
       <c r="E50" s="24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
@@ -5260,18 +5453,18 @@
         <v>156</v>
       </c>
       <c r="T50" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="U50" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="51" spans="1:21" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="B51" s="45" t="s">
         <v>284</v>
-      </c>
-      <c r="B51" s="45" t="s">
-        <v>285</v>
       </c>
       <c r="C51" s="46" t="s">
         <v>60</v>
@@ -5280,12 +5473,14 @@
         <v>22</v>
       </c>
       <c r="E51" s="25" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="G51" s="3"/>
+        <v>441</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>493</v>
+      </c>
       <c r="H51" s="151"/>
       <c r="I51" s="45"/>
       <c r="J51" s="45"/>
@@ -5301,21 +5496,21 @@
         <v>0</v>
       </c>
       <c r="S51" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T51" s="3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="U51" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="B52" s="45" t="s">
         <v>287</v>
-      </c>
-      <c r="B52" s="45" t="s">
-        <v>288</v>
       </c>
       <c r="C52" s="46" t="s">
         <v>60</v>
@@ -5324,12 +5519,14 @@
         <v>22</v>
       </c>
       <c r="E52" s="25" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="G52" s="3"/>
+        <v>441</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>494</v>
+      </c>
       <c r="H52" s="151"/>
       <c r="I52" s="45"/>
       <c r="J52" s="45"/>
@@ -5345,21 +5542,21 @@
         <v>0</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="53" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="B53" s="47" t="s">
         <v>291</v>
-      </c>
-      <c r="B53" s="47" t="s">
-        <v>292</v>
       </c>
       <c r="C53" s="48" t="s">
         <v>60</v>
@@ -5368,12 +5565,14 @@
         <v>22</v>
       </c>
       <c r="E53" s="26" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="G53" s="3"/>
+        <v>441</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>495</v>
+      </c>
       <c r="H53" s="153"/>
       <c r="I53" s="47"/>
       <c r="J53" s="47"/>
@@ -5389,21 +5588,21 @@
         <v>0</v>
       </c>
       <c r="S53" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="54" spans="1:21" ht="143.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A54" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="B54" s="49" t="s">
         <v>294</v>
-      </c>
-      <c r="B54" s="49" t="s">
-        <v>295</v>
       </c>
       <c r="C54" s="38" t="s">
         <v>21</v>
@@ -5412,19 +5611,21 @@
         <v>31</v>
       </c>
       <c r="E54" s="27" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="G54" s="3"/>
+        <v>441</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>496</v>
+      </c>
       <c r="H54" s="155"/>
       <c r="I54" s="49"/>
       <c r="J54" s="49"/>
       <c r="K54" s="49"/>
       <c r="L54" s="49"/>
       <c r="M54" s="49" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="N54" s="49"/>
       <c r="O54" s="49"/>
@@ -5435,21 +5636,21 @@
         <v>0.1</v>
       </c>
       <c r="S54" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T54" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="U54" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="55" spans="1:21" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A55" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="B55" s="45" t="s">
         <v>298</v>
-      </c>
-      <c r="B55" s="45" t="s">
-        <v>299</v>
       </c>
       <c r="C55" s="50" t="s">
         <v>60</v>
@@ -5458,12 +5659,14 @@
         <v>31</v>
       </c>
       <c r="E55" s="25" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="G55" s="3"/>
+        <v>441</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>497</v>
+      </c>
       <c r="H55" s="151"/>
       <c r="I55" s="45"/>
       <c r="J55" s="45"/>
@@ -5479,21 +5682,21 @@
         <v>0</v>
       </c>
       <c r="S55" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T55" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="U55" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="56" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A56" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="B56" s="45" t="s">
         <v>301</v>
-      </c>
-      <c r="B56" s="45" t="s">
-        <v>302</v>
       </c>
       <c r="C56" s="50" t="s">
         <v>60</v>
@@ -5502,12 +5705,14 @@
         <v>31</v>
       </c>
       <c r="E56" s="25" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="G56" s="3"/>
+        <v>441</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>498</v>
+      </c>
       <c r="H56" s="151"/>
       <c r="I56" s="45"/>
       <c r="J56" s="45"/>
@@ -5523,13 +5728,13 @@
         <v>0</v>
       </c>
       <c r="S56" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T56" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="U56" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="57" spans="1:21" ht="14.25" x14ac:dyDescent="0.2">
@@ -5557,7 +5762,7 @@
     </row>
     <row r="58" spans="1:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A58" s="172" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B58" s="173"/>
       <c r="C58" s="173"/>
@@ -5582,10 +5787,10 @@
     </row>
     <row r="59" spans="1:21" ht="91.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A59" s="17" t="s">
+        <v>304</v>
+      </c>
+      <c r="B59" s="51" t="s">
         <v>305</v>
-      </c>
-      <c r="B59" s="51" t="s">
-        <v>306</v>
       </c>
       <c r="C59" s="38" t="s">
         <v>21</v>
@@ -5594,60 +5799,62 @@
         <v>22</v>
       </c>
       <c r="E59" s="28" t="s">
+        <v>306</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="H59" s="160" t="s">
+        <v>233</v>
+      </c>
+      <c r="I59" s="51" t="s">
         <v>307</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="G59" s="3"/>
-      <c r="H59" s="160" t="s">
-        <v>234</v>
-      </c>
-      <c r="I59" s="51" t="s">
-        <v>308</v>
       </c>
       <c r="J59" s="51"/>
       <c r="K59" s="51" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L59" s="51" t="s">
+        <v>308</v>
+      </c>
+      <c r="M59" s="51" t="s">
         <v>309</v>
       </c>
-      <c r="M59" s="51" t="s">
+      <c r="N59" s="51" t="s">
         <v>310</v>
       </c>
-      <c r="N59" s="51" t="s">
+      <c r="O59" s="51" t="s">
         <v>311</v>
       </c>
-      <c r="O59" s="51" t="s">
+      <c r="P59" s="51" t="s">
         <v>312</v>
       </c>
-      <c r="P59" s="51" t="s">
+      <c r="Q59" s="51" t="s">
         <v>313</v>
-      </c>
-      <c r="Q59" s="51" t="s">
-        <v>314</v>
       </c>
       <c r="R59" s="161">
         <f t="shared" ref="R59:R68" si="4">COUNTA(H59:Q59)/10</f>
         <v>0.9</v>
       </c>
       <c r="S59" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T59" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="U59" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="60" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A60" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="B60" s="51" t="s">
         <v>315</v>
-      </c>
-      <c r="B60" s="51" t="s">
-        <v>316</v>
       </c>
       <c r="C60" s="52" t="s">
         <v>21</v>
@@ -5656,26 +5863,28 @@
         <v>22</v>
       </c>
       <c r="E60" s="28" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="G60" s="3"/>
+        <v>441</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>500</v>
+      </c>
       <c r="H60" s="160"/>
       <c r="I60" s="51"/>
       <c r="J60" s="51"/>
       <c r="K60" s="51"/>
       <c r="L60" s="51"/>
       <c r="M60" s="51" t="s">
+        <v>317</v>
+      </c>
+      <c r="N60" s="51" t="s">
         <v>318</v>
-      </c>
-      <c r="N60" s="51" t="s">
-        <v>319</v>
       </c>
       <c r="O60" s="51"/>
       <c r="P60" s="51" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Q60" s="51"/>
       <c r="R60" s="161">
@@ -5683,35 +5892,37 @@
         <v>0.3</v>
       </c>
       <c r="S60" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T60" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="U60" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="61" spans="1:21" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A61" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="B61" s="51" t="s">
         <v>321</v>
-      </c>
-      <c r="B61" s="51" t="s">
-        <v>322</v>
       </c>
       <c r="C61" s="38" t="s">
         <v>21</v>
       </c>
       <c r="D61" s="51" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E61" s="28" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="G61" s="3"/>
+        <v>441</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>501</v>
+      </c>
       <c r="H61" s="160"/>
       <c r="I61" s="51"/>
       <c r="J61" s="51"/>
@@ -5727,21 +5938,21 @@
         <v>0</v>
       </c>
       <c r="S61" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T61" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="U61" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="62" spans="1:21" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A62" s="18" t="s">
+        <v>324</v>
+      </c>
+      <c r="B62" s="53" t="s">
         <v>325</v>
-      </c>
-      <c r="B62" s="53" t="s">
-        <v>326</v>
       </c>
       <c r="C62" s="54" t="s">
         <v>60</v>
@@ -5750,12 +5961,14 @@
         <v>22</v>
       </c>
       <c r="E62" s="29" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="G62" s="3"/>
+        <v>441</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>502</v>
+      </c>
       <c r="H62" s="162"/>
       <c r="I62" s="53"/>
       <c r="J62" s="53"/>
@@ -5771,21 +5984,21 @@
         <v>0</v>
       </c>
       <c r="S62" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T62" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="U62" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="63" spans="1:21" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A63" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="B63" s="53" t="s">
         <v>329</v>
-      </c>
-      <c r="B63" s="53" t="s">
-        <v>330</v>
       </c>
       <c r="C63" s="54" t="s">
         <v>60</v>
@@ -5794,12 +6007,14 @@
         <v>22</v>
       </c>
       <c r="E63" s="29" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="G63" s="3"/>
+        <v>441</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>491</v>
+      </c>
       <c r="H63" s="162"/>
       <c r="I63" s="53"/>
       <c r="J63" s="53"/>
@@ -5815,75 +6030,77 @@
         <v>0</v>
       </c>
       <c r="S63" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T63" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="U63" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="64" spans="1:21" ht="171.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A64" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="B64" s="53" t="s">
         <v>332</v>
-      </c>
-      <c r="B64" s="53" t="s">
-        <v>333</v>
       </c>
       <c r="C64" s="54" t="s">
         <v>60</v>
       </c>
       <c r="D64" s="53" t="s">
+        <v>333</v>
+      </c>
+      <c r="E64" s="29" t="s">
         <v>334</v>
       </c>
-      <c r="E64" s="29" t="s">
-        <v>335</v>
-      </c>
       <c r="F64" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="G64" s="3"/>
+        <v>441</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>503</v>
+      </c>
       <c r="H64" s="162"/>
       <c r="I64" s="53" t="s">
+        <v>335</v>
+      </c>
+      <c r="J64" s="53" t="s">
         <v>336</v>
       </c>
-      <c r="J64" s="53" t="s">
+      <c r="K64" s="53" t="s">
         <v>337</v>
       </c>
-      <c r="K64" s="53" t="s">
+      <c r="L64" s="53" t="s">
         <v>338</v>
-      </c>
-      <c r="L64" s="53" t="s">
-        <v>339</v>
       </c>
       <c r="M64" s="53"/>
       <c r="N64" s="53"/>
       <c r="O64" s="53"/>
       <c r="P64" s="53"/>
       <c r="Q64" s="53" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="R64" s="163">
         <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="S64" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T64" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="U64" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="65" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A65" s="18" t="s">
+        <v>340</v>
+      </c>
+      <c r="B65" s="53" t="s">
         <v>341</v>
-      </c>
-      <c r="B65" s="53" t="s">
-        <v>342</v>
       </c>
       <c r="C65" s="54" t="s">
         <v>60</v>
@@ -5892,12 +6109,14 @@
         <v>130</v>
       </c>
       <c r="E65" s="29" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="G65" s="3"/>
+        <v>441</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>504</v>
+      </c>
       <c r="H65" s="162"/>
       <c r="I65" s="53"/>
       <c r="J65" s="53"/>
@@ -5913,19 +6132,19 @@
         <v>0</v>
       </c>
       <c r="S65" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T65" s="3"/>
       <c r="U65" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="66" spans="1:21" ht="72" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A66" s="18" t="s">
+        <v>343</v>
+      </c>
+      <c r="B66" s="53" t="s">
         <v>344</v>
-      </c>
-      <c r="B66" s="53" t="s">
-        <v>345</v>
       </c>
       <c r="C66" s="54" t="s">
         <v>60</v>
@@ -5934,12 +6153,14 @@
         <v>22</v>
       </c>
       <c r="E66" s="29" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>442</v>
-      </c>
-      <c r="G66" s="8"/>
+        <v>441</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>505</v>
+      </c>
       <c r="H66" s="162"/>
       <c r="I66" s="53"/>
       <c r="J66" s="53"/>
@@ -5955,21 +6176,21 @@
         <v>0</v>
       </c>
       <c r="S66" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T66" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="U66" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="67" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A67" s="18" t="s">
+        <v>346</v>
+      </c>
+      <c r="B67" s="53" t="s">
         <v>347</v>
-      </c>
-      <c r="B67" s="53" t="s">
-        <v>348</v>
       </c>
       <c r="C67" s="54" t="s">
         <v>60</v>
@@ -5978,12 +6199,14 @@
         <v>22</v>
       </c>
       <c r="E67" s="29" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>442</v>
-      </c>
-      <c r="G67" s="8"/>
+        <v>441</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>506</v>
+      </c>
       <c r="H67" s="162"/>
       <c r="I67" s="53"/>
       <c r="J67" s="53"/>
@@ -5999,21 +6222,21 @@
         <v>0</v>
       </c>
       <c r="S67" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T67" s="9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="U67" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="68" spans="1:21" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A68" s="18" t="s">
+        <v>349</v>
+      </c>
+      <c r="B68" s="53" t="s">
         <v>350</v>
-      </c>
-      <c r="B68" s="53" t="s">
-        <v>351</v>
       </c>
       <c r="C68" s="54" t="s">
         <v>60</v>
@@ -6022,12 +6245,14 @@
         <v>22</v>
       </c>
       <c r="E68" s="29" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>442</v>
-      </c>
-      <c r="G68" s="8"/>
+        <v>441</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>351</v>
+      </c>
       <c r="H68" s="162"/>
       <c r="I68" s="53"/>
       <c r="J68" s="53"/>
@@ -6043,13 +6268,13 @@
         <v>0</v>
       </c>
       <c r="S68" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T68" s="9" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="U68" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.2">
@@ -6077,10 +6302,10 @@
     </row>
     <row r="70" spans="1:21" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A70" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="B70" s="56" t="s">
         <v>353</v>
-      </c>
-      <c r="B70" s="56" t="s">
-        <v>354</v>
       </c>
       <c r="C70" s="57" t="s">
         <v>60</v>
@@ -6090,7 +6315,9 @@
       </c>
       <c r="E70" s="31"/>
       <c r="F70" s="3"/>
-      <c r="G70" s="3"/>
+      <c r="G70" s="3" t="s">
+        <v>507</v>
+      </c>
       <c r="H70" s="115"/>
       <c r="I70" s="116"/>
       <c r="J70" s="116"/>
@@ -6103,13 +6330,13 @@
       <c r="Q70" s="166"/>
       <c r="R70" s="114"/>
       <c r="S70" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="T70" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="U70" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.2">
@@ -27645,8 +27872,11 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="G10" r:id="rId1" xr:uid="{A6F7C17C-B1FC-4448-B881-0AACCD8815CB}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/docs/TAPP_EPMA_filled.xlsx
+++ b/docs/TAPP_EPMA_filled.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/944a82e2ddcde9eb/Documents/GithubC/USGIN/geochemBuildingBlocks/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="432" documentId="11_3C209AD99577444EEF615C96566D1EBF266D99FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E51B3F03-4ACE-4A76-B070-DA59C3677AFD}"/>
+  <xr:revisionPtr revIDLastSave="437" documentId="11_3C209AD99577444EEF615C96566D1EBF266D99FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22933C28-B03E-405A-BB1E-F05A0FB5867D}"/>
   <bookViews>
     <workbookView xWindow="165" yWindow="1335" windowWidth="27615" windowHeight="14610" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1608,19 +1608,6 @@
   readOnly: False</t>
   </si>
   <si>
-    <t>P0: synthetic Example, 2026
-(Richard and Deng, 2026 )</t>
-  </si>
-  <si>
-    <t>EPMA-WDS major/minor element silicate and oxide, all properties</t>
-  </si>
-  <si>
-    <t>Richard, S.M. ORCID:0000-0001-6041-5302; Deng, Ruolin ORCID:0000-0001-5383-3039</t>
-  </si>
-  <si>
-    <t>IEDA, Columbia University</t>
-  </si>
-  <si>
     <t>https://ror.org/02fjjnc15</t>
   </si>
   <si>
@@ -1630,122 +1617,135 @@
     <t>https://example.org/EMPA/WDS</t>
   </si>
   <si>
-    <t xml:space="preserve">Feldspar, Pyroxene, Olivine </t>
-  </si>
-  <si>
-    <t>25 mm epoxy mount, polished to 0.25 µm diamond, 20 nm C coat</t>
-  </si>
-  <si>
     <t>Probe for EPMA v12.9.5</t>
   </si>
   <si>
-    <t>Cameca PeakSight, CalcZAF</t>
-  </si>
-  <si>
     <t xml:space="preserve"> SXFiveFE </t>
   </si>
   <si>
+    <t>10 by 10</t>
+  </si>
+  <si>
+    <t>None required (anhydrous minerals)</t>
+  </si>
+  <si>
+    <t>Primary major element reference materials are run at beginning and end of every analytical session and the calibration is interpolated</t>
+  </si>
+  <si>
+    <t>WDS</t>
+  </si>
+  <si>
+    <t>Integral</t>
+  </si>
+  <si>
+    <t>+5 mm (High)</t>
+  </si>
+  <si>
+    <t>Kalpha</t>
+  </si>
+  <si>
+    <t>Armstrong/Love-Scott</t>
+  </si>
+  <si>
+    <t>MCMASTER</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Super-precision</t>
+  </si>
+  <si>
+    <t>single-sample mean; quartz</t>
+  </si>
+  <si>
+    <t>Single-sample normalization to JdF-D2 basalt glass</t>
+  </si>
+  <si>
+    <t>10-12 %</t>
+  </si>
+  <si>
+    <t>1-point low with slope factor</t>
+  </si>
+  <si>
+    <t>Direct (measured)</t>
+  </si>
+  <si>
+    <t>USNM 111240/52 VG-2</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>0.01 wt%</t>
+  </si>
+  <si>
+    <t>Additional context about this method.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A.B.(1997)</t>
+  </si>
+  <si>
+    <t>P0: synthetic Example| 2026
+(Richard and Deng| 2026 )</t>
+  </si>
+  <si>
+    <t>EPMA-WDS major/minor element silicate and oxide| all properties</t>
+  </si>
+  <si>
+    <t>Richard| S.M. ORCID:0000-0001-6041-5302; Deng| Ruolin ORCID:0000-0001-5383-3039</t>
+  </si>
+  <si>
+    <t>IEDA| Columbia University</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feldspar| Pyroxene| Olivine </t>
+  </si>
+  <si>
+    <t>25 mm epoxy mount| polished to 0.25 µm diamond| 20 nm C coat</t>
+  </si>
+  <si>
+    <t>Cameca PeakSight| CalcZAF</t>
+  </si>
+  <si>
     <t>Spectrometer number|Orientation|Crystals|Notes
-SP1|Inclined|LiF, PET, TAP, PC2|Less sensitive to specimen height; good for rough surfaces; low pressure
-SP2|Vertical|LLiF, LPET|High pressure for greater sensitivity; large crystals for trace/light elements
-SP3|Vertical|TAP, PC0|Low pressure; light element coverage
-SP4|Vertical|LPET, TAP|Low pressure</t>
-  </si>
-  <si>
-    <t>10 by 10</t>
-  </si>
-  <si>
-    <t>None required (anhydrous minerals)</t>
-  </si>
-  <si>
-    <t>Primary major element reference materials are run at beginning and end of every analytical session and the calibration is interpolated</t>
-  </si>
-  <si>
-    <t>Si,Al,K,Ca,Na,Fe,Mg,Ti,Cr,Mn</t>
-  </si>
-  <si>
-    <t>WDS</t>
-  </si>
-  <si>
-    <t>2,2,2,2,2,4,3,1,1,1</t>
-  </si>
-  <si>
-    <t>LPET,LPET,LLIF,LLIF,LPET,LPET,TAP,LiF,LiF,LiF</t>
-  </si>
-  <si>
-    <t>1,4,3,2</t>
-  </si>
-  <si>
-    <t>High Pressure P10 Flow,High Pressure P10 Flow,High Pressure P10 Flow,High Pressure P10 Flow,High Pressure P10 Flow, Low Pressure P10 Flow,Low Pressure P10 Flow,Low Pressure P10 Flow,Low Pressure P10 Flow,Low Pressure P10 Flow</t>
-  </si>
-  <si>
-    <t>Integral</t>
-  </si>
-  <si>
-    <t>+5 mm (High)</t>
-  </si>
-  <si>
-    <t>Kalpha</t>
-  </si>
-  <si>
-    <t>20,20,20,20,30,20,20,60,60,60</t>
-  </si>
-  <si>
-    <t>Armstrong/Love-Scott</t>
-  </si>
-  <si>
-    <t>MCMASTER</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Super-precision</t>
-  </si>
-  <si>
-    <t>single-sample mean; quartz</t>
-  </si>
-  <si>
-    <t>Single-sample normalization to JdF-D2 basalt glass</t>
-  </si>
-  <si>
-    <t>10-12 %</t>
-  </si>
-  <si>
-    <t>1-point low with slope factor</t>
-  </si>
-  <si>
-    <t>Linear, Linear, Linear, Linear, Linear,Exponential, Double exponential,Double exponential,Double exponential,Exponential</t>
-  </si>
-  <si>
-    <t>Direct (measured)</t>
-  </si>
-  <si>
-    <t>Anorthite,Anorthite,K-feldspar,Anorthite,Jadeite,Fayalite,Forsterite,Synthetic rutile,Cr2O3,Mn2SiO4</t>
-  </si>
-  <si>
-    <t>USNM 111240/52 VG-2</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>0.01 wt%</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> A.B., 1997</t>
-  </si>
-  <si>
-    <t>0.5% (1σ, n=20 for SiO2),,,,,,,,,</t>
-  </si>
-  <si>
-    <t>1.2% relative to GeoReM preferred value for VG-2 SiO2,,,,,,,,,</t>
-  </si>
-  <si>
-    <t>Additional context about this method.</t>
+SP1|Inclined|LiF| PET| TAP| PC2|Less sensitive to specimen height; good for rough surfaces; low pressure
+SP2|Vertical|LLiF| LPET|High pressure for greater sensitivity; large crystals for trace/light elements
+SP3|Vertical|TAP| PC0|Low pressure; light element coverage
+SP4|Vertical|LPET| TAP|Low pressure</t>
+  </si>
+  <si>
+    <t>Si|Al|K|Ca|Na|Fe|Mg|Ti|Cr|Mn</t>
+  </si>
+  <si>
+    <t>2|2|2|2|2|4|3|1|1|1</t>
+  </si>
+  <si>
+    <t>1|3|2|4|5|1|1|2|3|1</t>
+  </si>
+  <si>
+    <t>LPET|LPET|LLIF|LLIF|LPET|LPET|TAP|LiF|LiF|LiF</t>
+  </si>
+  <si>
+    <t>High Pressure P10 Flow|High Pressure P10 Flow|High Pressure P10 Flow|High Pressure P10 Flow|High Pressure P10 Flow| Low Pressure P10 Flow|Low Pressure P10 Flow|Low Pressure P10 Flow|Low Pressure P10 Flow|Low Pressure P10 Flow</t>
+  </si>
+  <si>
+    <t>20|20|20|20|30|20|20|60|60|60</t>
+  </si>
+  <si>
+    <t>Linear| Linear| Linear| Linear| Linear|Exponential| Double exponential|Double exponential|Double exponential|Exponential</t>
+  </si>
+  <si>
+    <t>Anorthite|Anorthite|K-feldspar|Anorthite|Jadeite|Fayalite|Forsterite|Synthetic rutile|Cr2O3|Mn2SiO4</t>
+  </si>
+  <si>
+    <t>1.2% relative to GeoReM preferred value for VG-2 SiO2|||||||||</t>
+  </si>
+  <si>
+    <t>0.5% (1σ, n=20 for SiO2)|||||||||</t>
   </si>
 </sst>
 </file>
@@ -1755,7 +1755,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1860,13 +1860,6 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="10"/>
-      <name val="Arial"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -2278,12 +2271,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="181">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2793,15 +2785,8 @@
     <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -3089,7 +3074,7 @@
     <col min="22" max="16384" width="12.7109375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="45" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3109,7 +3094,7 @@
         <v>408</v>
       </c>
       <c r="G1" s="112" t="s">
-        <v>463</v>
+        <v>490</v>
       </c>
       <c r="H1" s="112" t="s">
         <v>5</v>
@@ -3197,7 +3182,7 @@
       </c>
       <c r="F3" s="63"/>
       <c r="G3" s="117" t="s">
-        <v>464</v>
+        <v>491</v>
       </c>
       <c r="H3" s="117" t="s">
         <v>24</v>
@@ -3322,8 +3307,8 @@
         <v>36</v>
       </c>
       <c r="F5" s="69"/>
-      <c r="G5" s="69" t="s">
-        <v>465</v>
+      <c r="G5" s="119" t="s">
+        <v>492</v>
       </c>
       <c r="H5" s="119" t="s">
         <v>37</v>
@@ -3384,8 +3369,8 @@
         <v>48</v>
       </c>
       <c r="F6" s="69"/>
-      <c r="G6" s="68" t="s">
-        <v>466</v>
+      <c r="G6" s="119" t="s">
+        <v>493</v>
       </c>
       <c r="H6" s="119" t="s">
         <v>49</v>
@@ -3446,8 +3431,8 @@
         <v>62</v>
       </c>
       <c r="F7" s="69"/>
-      <c r="G7" s="69" t="s">
-        <v>467</v>
+      <c r="G7" s="121" t="s">
+        <v>463</v>
       </c>
       <c r="H7" s="121"/>
       <c r="I7" s="72"/>
@@ -3488,7 +3473,7 @@
         <v>46082</v>
       </c>
       <c r="F8" s="69"/>
-      <c r="G8" s="181">
+      <c r="G8" s="123">
         <v>46140</v>
       </c>
       <c r="H8" s="123"/>
@@ -3530,8 +3515,8 @@
         <v>68</v>
       </c>
       <c r="F9" s="69"/>
-      <c r="G9" s="69" t="s">
-        <v>468</v>
+      <c r="G9" s="121" t="s">
+        <v>464</v>
       </c>
       <c r="H9" s="121"/>
       <c r="I9" s="72"/>
@@ -3574,8 +3559,8 @@
         <v>72</v>
       </c>
       <c r="F10" s="69"/>
-      <c r="G10" s="182" t="s">
-        <v>469</v>
+      <c r="G10" s="121" t="s">
+        <v>465</v>
       </c>
       <c r="H10" s="121"/>
       <c r="I10" s="72"/>
@@ -3606,7 +3591,7 @@
       <c r="D11" s="78"/>
       <c r="E11" s="79"/>
       <c r="F11" s="69"/>
-      <c r="G11" s="69"/>
+      <c r="G11" s="126"/>
       <c r="H11" s="126"/>
       <c r="I11" s="127"/>
       <c r="J11" s="127"/>
@@ -3631,7 +3616,7 @@
       <c r="D12" s="176"/>
       <c r="E12" s="176"/>
       <c r="F12" s="69"/>
-      <c r="G12" s="69"/>
+      <c r="G12" s="126"/>
       <c r="H12" s="126"/>
       <c r="I12" s="127"/>
       <c r="J12" s="127"/>
@@ -3664,8 +3649,8 @@
         <v>77</v>
       </c>
       <c r="F13" s="69"/>
-      <c r="G13" s="69" t="s">
-        <v>470</v>
+      <c r="G13" s="129" t="s">
+        <v>494</v>
       </c>
       <c r="H13" s="129" t="s">
         <v>78</v>
@@ -3726,8 +3711,8 @@
         <v>89</v>
       </c>
       <c r="F14" s="69"/>
-      <c r="G14" s="69" t="s">
-        <v>471</v>
+      <c r="G14" s="131" t="s">
+        <v>495</v>
       </c>
       <c r="H14" s="131" t="s">
         <v>90</v>
@@ -3780,7 +3765,7 @@
       <c r="D15" s="78"/>
       <c r="E15" s="79"/>
       <c r="F15" s="69"/>
-      <c r="G15" s="69"/>
+      <c r="G15" s="126"/>
       <c r="H15" s="126"/>
       <c r="I15" s="127"/>
       <c r="J15" s="127"/>
@@ -3805,7 +3790,7 @@
       <c r="D16" s="176"/>
       <c r="E16" s="176"/>
       <c r="F16" s="69"/>
-      <c r="G16" s="69"/>
+      <c r="G16" s="126"/>
       <c r="H16" s="126"/>
       <c r="I16" s="127"/>
       <c r="J16" s="127"/>
@@ -3838,7 +3823,7 @@
         <v>103</v>
       </c>
       <c r="F17" s="69"/>
-      <c r="G17" s="69" t="s">
+      <c r="G17" s="133" t="s">
         <v>106</v>
       </c>
       <c r="H17" s="133" t="s">
@@ -3900,8 +3885,8 @@
         <v>110</v>
       </c>
       <c r="F18" s="69"/>
-      <c r="G18" s="69" t="s">
-        <v>474</v>
+      <c r="G18" s="133" t="s">
+        <v>467</v>
       </c>
       <c r="H18" s="133" t="s">
         <v>111</v>
@@ -3962,7 +3947,7 @@
         <v>121</v>
       </c>
       <c r="F19" s="69"/>
-      <c r="G19" s="69" t="s">
+      <c r="G19" s="133" t="s">
         <v>122</v>
       </c>
       <c r="H19" s="133"/>
@@ -4008,8 +3993,8 @@
         <v>125</v>
       </c>
       <c r="F20" s="69"/>
-      <c r="G20" s="69" t="s">
-        <v>472</v>
+      <c r="G20" s="133" t="s">
+        <v>466</v>
       </c>
       <c r="H20" s="133" t="s">
         <v>126</v>
@@ -4060,8 +4045,8 @@
         <v>131</v>
       </c>
       <c r="F21" s="69"/>
-      <c r="G21" s="69" t="s">
-        <v>473</v>
+      <c r="G21" s="133" t="s">
+        <v>496</v>
       </c>
       <c r="H21" s="133" t="s">
         <v>132</v>
@@ -4099,7 +4084,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="22" spans="1:21" s="70" customFormat="1" ht="114.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:21" s="70" customFormat="1" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A22" s="92" t="s">
         <v>136</v>
       </c>
@@ -4116,8 +4101,8 @@
         <v>138</v>
       </c>
       <c r="F22" s="69"/>
-      <c r="G22" s="69" t="s">
-        <v>475</v>
+      <c r="G22" s="135" t="s">
+        <v>497</v>
       </c>
       <c r="H22" s="135"/>
       <c r="I22" s="93"/>
@@ -4162,7 +4147,7 @@
         <v>143</v>
       </c>
       <c r="F23" s="69"/>
-      <c r="G23" s="69"/>
+      <c r="G23" s="135"/>
       <c r="H23" s="135"/>
       <c r="I23" s="93"/>
       <c r="J23" s="93"/>
@@ -4196,7 +4181,7 @@
       <c r="D24" s="78"/>
       <c r="E24" s="79"/>
       <c r="F24" s="69"/>
-      <c r="G24" s="69"/>
+      <c r="G24" s="126"/>
       <c r="H24" s="126"/>
       <c r="I24" s="127"/>
       <c r="J24" s="127"/>
@@ -4221,7 +4206,7 @@
       <c r="D25" s="176"/>
       <c r="E25" s="176"/>
       <c r="F25" s="69"/>
-      <c r="G25" s="69"/>
+      <c r="G25" s="126"/>
       <c r="H25" s="126"/>
       <c r="I25" s="127"/>
       <c r="J25" s="127"/>
@@ -4254,7 +4239,7 @@
         <v>149</v>
       </c>
       <c r="F26" s="69"/>
-      <c r="G26" s="69" t="s">
+      <c r="G26" s="137" t="s">
         <v>150</v>
       </c>
       <c r="H26" s="137" t="s">
@@ -4318,7 +4303,7 @@
         <v>160</v>
       </c>
       <c r="F27" s="69"/>
-      <c r="G27" s="69">
+      <c r="G27" s="137">
         <v>20</v>
       </c>
       <c r="H27" s="137" t="s">
@@ -4382,7 +4367,7 @@
         <v>167</v>
       </c>
       <c r="F28" s="69"/>
-      <c r="G28" s="69">
+      <c r="G28" s="137">
         <v>5</v>
       </c>
       <c r="H28" s="137" t="s">
@@ -4444,8 +4429,8 @@
         <v>178</v>
       </c>
       <c r="F29" s="69"/>
-      <c r="G29" s="69" t="s">
-        <v>476</v>
+      <c r="G29" s="139" t="s">
+        <v>468</v>
       </c>
       <c r="H29" s="139"/>
       <c r="I29" s="103"/>
@@ -4488,8 +4473,8 @@
         <v>182</v>
       </c>
       <c r="F30" s="69"/>
-      <c r="G30" s="69" t="s">
-        <v>477</v>
+      <c r="G30" s="139" t="s">
+        <v>469</v>
       </c>
       <c r="H30" s="139"/>
       <c r="I30" s="103"/>
@@ -4536,8 +4521,8 @@
         <v>189</v>
       </c>
       <c r="F31" s="110"/>
-      <c r="G31" s="110" t="s">
-        <v>478</v>
+      <c r="G31" s="141" t="s">
+        <v>470</v>
       </c>
       <c r="H31" s="141"/>
       <c r="I31" s="107"/>
@@ -4580,8 +4565,8 @@
         <v>193</v>
       </c>
       <c r="F32" s="3"/>
-      <c r="G32" s="3" t="s">
-        <v>479</v>
+      <c r="G32" s="143" t="s">
+        <v>498</v>
       </c>
       <c r="H32" s="143"/>
       <c r="I32" s="36"/>
@@ -4626,7 +4611,7 @@
       <c r="F33" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="G33" s="3">
+      <c r="G33" s="143">
         <v>10</v>
       </c>
       <c r="H33" s="143" t="s">
@@ -4692,8 +4677,8 @@
       <c r="F34" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>480</v>
+      <c r="G34" s="143" t="s">
+        <v>471</v>
       </c>
       <c r="H34" s="143" t="s">
         <v>206</v>
@@ -4758,8 +4743,8 @@
       <c r="F35" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>481</v>
+      <c r="G35" s="145" t="s">
+        <v>499</v>
       </c>
       <c r="H35" s="145"/>
       <c r="I35" s="39"/>
@@ -4804,8 +4789,8 @@
       <c r="F36" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="G36" s="3" t="s">
-        <v>483</v>
+      <c r="G36" s="145" t="s">
+        <v>500</v>
       </c>
       <c r="H36" s="145"/>
       <c r="I36" s="39"/>
@@ -4850,8 +4835,8 @@
       <c r="F37" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>482</v>
+      <c r="G37" s="143" t="s">
+        <v>501</v>
       </c>
       <c r="H37" s="143"/>
       <c r="I37" s="36"/>
@@ -4879,7 +4864,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="38" spans="1:21" ht="77.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" ht="86.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
         <v>222</v>
       </c>
@@ -4898,8 +4883,8 @@
       <c r="F38" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>484</v>
+      <c r="G38" s="145" t="s">
+        <v>502</v>
       </c>
       <c r="H38" s="145"/>
       <c r="I38" s="39"/>
@@ -4944,8 +4929,8 @@
       <c r="F39" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>485</v>
+      <c r="G39" s="145" t="s">
+        <v>472</v>
       </c>
       <c r="H39" s="145"/>
       <c r="I39" s="39"/>
@@ -4990,8 +4975,8 @@
       <c r="F40" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>487</v>
+      <c r="G40" s="143" t="s">
+        <v>474</v>
       </c>
       <c r="H40" s="143"/>
       <c r="I40" s="36"/>
@@ -5038,8 +5023,8 @@
       <c r="F41" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>488</v>
+      <c r="G41" s="143" t="s">
+        <v>503</v>
       </c>
       <c r="H41" s="143" t="s">
         <v>162</v>
@@ -5094,7 +5079,7 @@
       <c r="F42" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="G42" s="3">
+      <c r="G42" s="143">
         <v>10</v>
       </c>
       <c r="H42" s="143" t="s">
@@ -5148,8 +5133,8 @@
       <c r="F43" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>486</v>
+      <c r="G43" s="145" t="s">
+        <v>473</v>
       </c>
       <c r="H43" s="145"/>
       <c r="I43" s="39"/>
@@ -5182,7 +5167,7 @@
       <c r="D44" s="34"/>
       <c r="E44" s="20"/>
       <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
+      <c r="G44" s="115"/>
       <c r="H44" s="115"/>
       <c r="I44" s="116"/>
       <c r="J44" s="116"/>
@@ -5207,7 +5192,7 @@
       <c r="D45" s="173"/>
       <c r="E45" s="174"/>
       <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
+      <c r="G45" s="115"/>
       <c r="H45" s="115"/>
       <c r="I45" s="116"/>
       <c r="J45" s="116"/>
@@ -5240,8 +5225,8 @@
         <v>259</v>
       </c>
       <c r="F46" s="3"/>
-      <c r="G46" s="3" t="s">
-        <v>489</v>
+      <c r="G46" s="147" t="s">
+        <v>475</v>
       </c>
       <c r="H46" s="147" t="s">
         <v>260</v>
@@ -5298,8 +5283,8 @@
         <v>266</v>
       </c>
       <c r="F47" s="3"/>
-      <c r="G47" s="3" t="s">
-        <v>490</v>
+      <c r="G47" s="147" t="s">
+        <v>476</v>
       </c>
       <c r="H47" s="147"/>
       <c r="I47" s="41"/>
@@ -5342,8 +5327,8 @@
         <v>271</v>
       </c>
       <c r="F48" s="3"/>
-      <c r="G48" s="3" t="s">
-        <v>491</v>
+      <c r="G48" s="149" t="s">
+        <v>477</v>
       </c>
       <c r="H48" s="149"/>
       <c r="I48" s="43"/>
@@ -5390,8 +5375,8 @@
         <v>277</v>
       </c>
       <c r="F49" s="3"/>
-      <c r="G49" s="3" t="s">
-        <v>492</v>
+      <c r="G49" s="147" t="s">
+        <v>478</v>
       </c>
       <c r="H49" s="147"/>
       <c r="I49" s="41"/>
@@ -5434,7 +5419,7 @@
         <v>281</v>
       </c>
       <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
+      <c r="G50" s="149"/>
       <c r="H50" s="149"/>
       <c r="I50" s="43"/>
       <c r="J50" s="43"/>
@@ -5478,8 +5463,8 @@
       <c r="F51" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="G51" s="3" t="s">
-        <v>493</v>
+      <c r="G51" s="151" t="s">
+        <v>479</v>
       </c>
       <c r="H51" s="151"/>
       <c r="I51" s="45"/>
@@ -5524,8 +5509,8 @@
       <c r="F52" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>494</v>
+      <c r="G52" s="151" t="s">
+        <v>480</v>
       </c>
       <c r="H52" s="151"/>
       <c r="I52" s="45"/>
@@ -5570,8 +5555,8 @@
       <c r="F53" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="G53" s="3" t="s">
-        <v>495</v>
+      <c r="G53" s="153" t="s">
+        <v>481</v>
       </c>
       <c r="H53" s="153"/>
       <c r="I53" s="47"/>
@@ -5616,8 +5601,8 @@
       <c r="F54" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>496</v>
+      <c r="G54" s="155" t="s">
+        <v>482</v>
       </c>
       <c r="H54" s="155"/>
       <c r="I54" s="49"/>
@@ -5645,7 +5630,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="55" spans="1:21" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:21" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A55" s="14" t="s">
         <v>297</v>
       </c>
@@ -5664,8 +5649,8 @@
       <c r="F55" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="G55" s="3" t="s">
-        <v>497</v>
+      <c r="G55" s="151" t="s">
+        <v>504</v>
       </c>
       <c r="H55" s="151"/>
       <c r="I55" s="45"/>
@@ -5710,8 +5695,8 @@
       <c r="F56" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="G56" s="3" t="s">
-        <v>498</v>
+      <c r="G56" s="151" t="s">
+        <v>483</v>
       </c>
       <c r="H56" s="151"/>
       <c r="I56" s="45"/>
@@ -5744,7 +5729,7 @@
       <c r="D57" s="34"/>
       <c r="E57" s="20"/>
       <c r="F57" s="3"/>
-      <c r="G57" s="3"/>
+      <c r="G57" s="157"/>
       <c r="H57" s="157"/>
       <c r="I57" s="158"/>
       <c r="J57" s="158"/>
@@ -5769,7 +5754,7 @@
       <c r="D58" s="173"/>
       <c r="E58" s="174"/>
       <c r="F58" s="3"/>
-      <c r="G58" s="3"/>
+      <c r="G58" s="157"/>
       <c r="H58" s="157"/>
       <c r="I58" s="158"/>
       <c r="J58" s="158"/>
@@ -5804,8 +5789,8 @@
       <c r="F59" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>499</v>
+      <c r="G59" s="160" t="s">
+        <v>505</v>
       </c>
       <c r="H59" s="160" t="s">
         <v>233</v>
@@ -5868,8 +5853,8 @@
       <c r="F60" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>500</v>
+      <c r="G60" s="160" t="s">
+        <v>484</v>
       </c>
       <c r="H60" s="160"/>
       <c r="I60" s="51"/>
@@ -5920,8 +5905,8 @@
       <c r="F61" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="G61" s="3" t="s">
-        <v>501</v>
+      <c r="G61" s="160" t="s">
+        <v>485</v>
       </c>
       <c r="H61" s="160"/>
       <c r="I61" s="51"/>
@@ -5966,8 +5951,8 @@
       <c r="F62" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>502</v>
+      <c r="G62" s="162" t="s">
+        <v>486</v>
       </c>
       <c r="H62" s="162"/>
       <c r="I62" s="53"/>
@@ -6012,8 +5997,8 @@
       <c r="F63" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="G63" s="3" t="s">
-        <v>491</v>
+      <c r="G63" s="162" t="s">
+        <v>477</v>
       </c>
       <c r="H63" s="162"/>
       <c r="I63" s="53"/>
@@ -6058,8 +6043,8 @@
       <c r="F64" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="G64" s="3" t="s">
-        <v>503</v>
+      <c r="G64" s="162" t="s">
+        <v>487</v>
       </c>
       <c r="H64" s="162"/>
       <c r="I64" s="53" t="s">
@@ -6114,8 +6099,8 @@
       <c r="F65" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="G65" s="3" t="s">
-        <v>504</v>
+      <c r="G65" s="162" t="s">
+        <v>489</v>
       </c>
       <c r="H65" s="162"/>
       <c r="I65" s="53"/>
@@ -6158,8 +6143,8 @@
       <c r="F66" s="8" t="s">
         <v>441</v>
       </c>
-      <c r="G66" s="8" t="s">
-        <v>505</v>
+      <c r="G66" s="162" t="s">
+        <v>507</v>
       </c>
       <c r="H66" s="162"/>
       <c r="I66" s="53"/>
@@ -6204,7 +6189,7 @@
       <c r="F67" s="8" t="s">
         <v>441</v>
       </c>
-      <c r="G67" s="8" t="s">
+      <c r="G67" s="162" t="s">
         <v>506</v>
       </c>
       <c r="H67" s="162"/>
@@ -6250,7 +6235,7 @@
       <c r="F68" s="8" t="s">
         <v>441</v>
       </c>
-      <c r="G68" s="8" t="s">
+      <c r="G68" s="162" t="s">
         <v>351</v>
       </c>
       <c r="H68" s="162"/>
@@ -6284,7 +6269,7 @@
       <c r="D69" s="55"/>
       <c r="E69" s="30"/>
       <c r="F69" s="9"/>
-      <c r="G69" s="9"/>
+      <c r="G69" s="164"/>
       <c r="H69" s="164"/>
       <c r="I69" s="55"/>
       <c r="J69" s="55"/>
@@ -6315,8 +6300,8 @@
       </c>
       <c r="E70" s="31"/>
       <c r="F70" s="3"/>
-      <c r="G70" s="3" t="s">
-        <v>507</v>
+      <c r="G70" s="115" t="s">
+        <v>488</v>
       </c>
       <c r="H70" s="115"/>
       <c r="I70" s="116"/>
@@ -27763,6 +27748,46 @@
     <mergeCell ref="A45:E45"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B66 A70:E70 C1:D68 E1:E7 E9:E66">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF57BB8A"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:R7 G9:R9">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF57BB8A"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G10:R10">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF57BB8A"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13:R14">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF57BB8A"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H17:R23">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -27772,7 +27797,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:R7 H9:R9">
+  <conditionalFormatting sqref="H26:R43">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF57BB8A"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H46:R58">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -27782,7 +27817,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H10:R10">
+  <conditionalFormatting sqref="H59:R66">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -27792,37 +27827,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H13:R14">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF57BB8A"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H17:R23">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF57BB8A"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H26:R43">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF57BB8A"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H46:R58">
+  <conditionalFormatting sqref="G13:G14">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -27832,7 +27837,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H59:R66">
+  <conditionalFormatting sqref="G17:G23">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -27842,7 +27847,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
+  <conditionalFormatting sqref="G26:G43">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -27852,7 +27857,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4">
+  <conditionalFormatting sqref="G46:G58">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -27862,7 +27867,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G6">
+  <conditionalFormatting sqref="G59:G66">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/docs/TAPP_EPMA_filled.xlsx
+++ b/docs/TAPP_EPMA_filled.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/944a82e2ddcde9eb/Documents/GithubC/USGIN/geochemBuildingBlocks/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="437" documentId="11_3C209AD99577444EEF615C96566D1EBF266D99FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22933C28-B03E-405A-BB1E-F05A0FB5867D}"/>
+  <xr:revisionPtr revIDLastSave="438" documentId="11_3C209AD99577444EEF615C96566D1EBF266D99FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1EDDAC9-3E70-4393-AFD1-6E9BD6CB2B3C}"/>
   <bookViews>
-    <workbookView xWindow="165" yWindow="1335" windowWidth="27615" windowHeight="14610" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-2880" yWindow="2265" windowWidth="27615" windowHeight="14610" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TAPP" sheetId="1" r:id="rId1"/>
@@ -1711,13 +1711,6 @@
     <t>Cameca PeakSight| CalcZAF</t>
   </si>
   <si>
-    <t>Spectrometer number|Orientation|Crystals|Notes
-SP1|Inclined|LiF| PET| TAP| PC2|Less sensitive to specimen height; good for rough surfaces; low pressure
-SP2|Vertical|LLiF| LPET|High pressure for greater sensitivity; large crystals for trace/light elements
-SP3|Vertical|TAP| PC0|Low pressure; light element coverage
-SP4|Vertical|LPET| TAP|Low pressure</t>
-  </si>
-  <si>
     <t>Si|Al|K|Ca|Na|Fe|Mg|Ti|Cr|Mn</t>
   </si>
   <si>
@@ -1746,6 +1739,13 @@
   </si>
   <si>
     <t>0.5% (1σ, n=20 for SiO2)|||||||||</t>
+  </si>
+  <si>
+    <t>name|additionalProperty/name=Orientation|additionalProperty/name=Crystals|description
+SP1|Inclined|LiF, PET, TAP, PC2|Less sensitive to specimen height; good for rough surfaces; low pressure
+SP2|Vertical|LLiF,LPET|High pressure for greater sensitivity; large crystals for trace/light elements
+SP3|Vertical|TAP, PC0|Low pressure; light element coverage
+SP4|Vertical|LPET, TAP|Low pressure</t>
   </si>
 </sst>
 </file>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="F22" s="69"/>
       <c r="G22" s="135" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="H22" s="135"/>
       <c r="I22" s="93"/>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="143" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H32" s="143"/>
       <c r="I32" s="36"/>
@@ -4744,7 +4744,7 @@
         <v>441</v>
       </c>
       <c r="G35" s="145" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H35" s="145"/>
       <c r="I35" s="39"/>
@@ -4790,7 +4790,7 @@
         <v>441</v>
       </c>
       <c r="G36" s="145" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H36" s="145"/>
       <c r="I36" s="39"/>
@@ -4836,7 +4836,7 @@
         <v>441</v>
       </c>
       <c r="G37" s="143" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H37" s="143"/>
       <c r="I37" s="36"/>
@@ -4884,7 +4884,7 @@
         <v>441</v>
       </c>
       <c r="G38" s="145" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H38" s="145"/>
       <c r="I38" s="39"/>
@@ -5024,7 +5024,7 @@
         <v>441</v>
       </c>
       <c r="G41" s="143" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H41" s="143" t="s">
         <v>162</v>
@@ -5650,7 +5650,7 @@
         <v>441</v>
       </c>
       <c r="G55" s="151" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H55" s="151"/>
       <c r="I55" s="45"/>
@@ -5790,7 +5790,7 @@
         <v>441</v>
       </c>
       <c r="G59" s="160" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H59" s="160" t="s">
         <v>233</v>
@@ -6144,7 +6144,7 @@
         <v>441</v>
       </c>
       <c r="G66" s="162" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H66" s="162"/>
       <c r="I66" s="53"/>
@@ -6190,7 +6190,7 @@
         <v>441</v>
       </c>
       <c r="G67" s="162" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H67" s="162"/>
       <c r="I67" s="53"/>
